--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'模块汇总'!$A$1:$D$123</definedName>
@@ -730,6 +730,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="E3" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -803,6 +816,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="E6" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="F6" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -876,6 +902,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="E9" s="29" t="n">
+        <v>101</v>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>100% (25/25)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -949,6 +988,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="E12" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="inlineStr">
+        <is>
+          <t>75% (3/4)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1100,6 +1152,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="E18" s="29" t="n">
+        <v>57</v>
+      </c>
+      <c r="F18" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="inlineStr">
+        <is>
+          <t>94% (15/16)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1246,6 +1311,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="E24" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G24" s="29" t="inlineStr">
+        <is>
+          <t>44% (4/9)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1366,6 +1444,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="E30" s="29" t="n">
+        <v>68</v>
+      </c>
+      <c r="F30" s="29" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G30" s="29" t="inlineStr">
+        <is>
+          <t>84% (26/31)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1424,6 +1515,19 @@
       <c r="D33" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="F33" s="29" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="inlineStr">
+        <is>
+          <t>100% (6/6)</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3578,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
           <t>AdGroupTag</t>
@@ -3495,8 +3599,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 新版调用 TagId筛选 US — 39.6%
+场景2: 旧版调用 含对比日期 TagId筛选 DE — 33.3%
+场景3: 旧版调用 不含对比日期 TagId筛选 DE — 27.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
           <t>AdGroupTag</t>
@@ -3517,8 +3628,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 默认日期范围 无额外筛选 US — 56.4%
+场景2: UserId筛选 US — 9.5%
+场景3: TagId筛选 US — 7.7%
+场景4: 旧版调用 日期趋势视图 TagId筛选 DE — 22.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>AdGroupTag</t>
@@ -3539,8 +3658,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="8">
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 默认列表浏览 含对比日期 US — 58.0%
+场景2: UserId筛选 US — 10.4%
+场景3: TagId筛选 US — 8.0%
+场景4: 旧版调用 TagId筛选 DE — 19.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
           <t>AdGroupTag</t>
@@ -3559,6 +3686,14 @@
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 默认汇总 无额外筛选 US — 43.9%
+场景2: UserId筛选 US — 7.9%
+场景3: TagId筛选 US — 6.1%
+场景4: 旧版调用 TagId筛选 DE — 39.2%</t>
         </is>
       </c>
     </row>
@@ -3884,7 +4019,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="96" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Campaign</t>
@@ -3905,8 +4040,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="23">
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>单个Campaign详情页趋势图（按日Dim） — ?%
+按Campaign状态筛选的汇总趋势图（Dim=ytd） — ?%
+按状态+标签筛选的趋势图 — ?%
+按名称搜索+状态筛选的趋势图 — ?%
+无筛选查看全部Campaign整体趋势图 — ?%
+按广告组合(Portfolio)+状态筛选的趋势图 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Campaign</t>
@@ -3927,8 +4072,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="24">
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>按campaignId+campaignState+日期范围查询campaign列表 — ?%
+按campaignId+日期范围查询campaign列表（不筛选状态） — ?%
+按campaignId+campaignName模糊搜索+campaignState+日期范围查询 — ?%
+按campaignId+campaignState+广告类型(CampaignTypeItems)+日期范围查询 — ?%
+按campaignId+campaignName模糊搜索+日期范围查询（不筛选状态） — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="96" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Campaign</t>
@@ -3949,8 +4103,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="25">
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>按指定CampaignId精确查询单个广告活动效果数据 — ?%
+按状态筛选并附带同期对比查询广告活动列表 — ?%
+按名称搜索并按状态筛选广告活动列表 — ?%
+按状态和标签组合筛选广告活动列表 — ?%
+无附加筛选条件的默认列表查询 — ?%
+按广告类型(CampaignTypeItems)筛选广告活动列表 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="96" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Campaign</t>
@@ -3971,8 +4135,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="26">
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>按效果指标筛选条件查询广告活动列表 — ?%
+无筛选条件的默认活动列表查询 — ?%
+按campaign标签(Tag)筛选查询 — ?%
+按指定campaignIds批量精确查询 — ?%
+按广告类型明细(CampaignTypeItems)筛选查询 — ?%
+按广告组合(Portfolio)筛选查询 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="128" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Campaign</t>
@@ -3991,6 +4165,18 @@
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 勾选指定Campaign汇总 — ?%
+场景2: 按CampaignTag标签筛选汇总 — ?%
+场景3: 按Campaign名称搜索汇总 — ?%
+场景4: 默认总览 State筛选 同期对比 — ?%
+场景5: 按投放状态ServingStatus筛选汇总 — ?%
+场景6: 按Portfolio筛选汇总 — ?%
+场景7: 按广告类型CampaignTypeItems筛选汇总 — ?%
+场景8: 按目标Asin筛选汇总 — ?%</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4762,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="64" customHeight="1">
       <c r="A44" s="21" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4597,8 +4783,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="45">
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>默认日粒度趋势查询(含环比对比期) — ?%
+按CampaignTag过滤的日粒度趋势查询 — ?%
+周粒度(Dim=week)趋势查询 — ?%
+月粒度(Dim=month)趋势查询 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4619,8 +4813,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="46">
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>Brand+品类过滤日粒度Benchmark(无分享链接) — ?%
+不带Brand/品类过滤的整体Benchmark — ?%
+Brand+品类过滤且通过分享链接访问 — ?%
+Brand+品类过滤且按周粒度(Dim=week)展示 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
       <c r="A46" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4641,8 +4843,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="47">
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>单Profile按日期范围查询超预算广告活动列表 — ?%
+多Profile跨店铺合并按日期范围查询超预算广告活动列表 — ?%
+按Campaign Tag筛选查询超预算广告活动列表 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4663,8 +4872,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="48">
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>基础日期范围查询Out of Budget图表（US市场，无标签/活动过滤） — ?%
+非US市场查询Out of Budget图表（汇率换算场景，以CA为代表） — ?%
+按CampaignTagId标签过滤的Out of Budget图表查询 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="80" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4685,8 +4901,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="49">
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>US站点仅日期范围周对比周(单/多Profile聚合) — ?%
+非US市场(DE)基础周对比 — ?%
+CampaignTagId标签过滤 — ?%
+PortfolioId组合过滤 — ?%
+ToMarket未指定(null) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4707,8 +4932,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="50">
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>多账号Portfolio下钻子标签ROAS指标(滚动周期对比) — 45.5%
+单账号下钻子标签ROAS指标(月度环比) — 42.4%
+ACOS指标视角下钻子标签(年度累计vs去年同期对比) — 12.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4729,8 +4961,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="51">
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>仅日期范围过滤查询Campaign Tag绩效widget(无Tag/Portfolio子筛选) — ?%
+按CampaignTagId筛选查询Campaign Tag绩效widget — ?%
+按PortfolioId筛选查询Campaign Tag绩效widget — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4751,8 +4990,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="52">
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>查看标签ROAS目标达成率排名(默认汇率换算) — ?%
+查看标签ACOS目标达成率排名(默认汇率换算) — ?%
+查看标签ACOS目标达成率排名(不做汇率换算) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="80" customHeight="1">
       <c r="A52" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4773,8 +5019,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="53">
+      <c r="E52" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 默认ROAS视图 无标签筛选 — 57.5%
+场景2: ACOS视图 新版CampaignTag命名 无筛选 — 14.2%
+场景3: ACOS视图 旧版Portfolio命名 无筛选 — 14.2%
+场景4: ACOS视图 按CampaignTagId筛选指定标签 — 8.4%
+场景5: ACOS视图 按旧版PortfolioId筛选 — 3.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="80" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4795,8 +5050,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="54">
+      <c r="E53" s="31" t="inlineStr">
+        <is>
+          <t>默认场景：仅日期范围过滤的 Top Performers（按 Spend 排序，开启汇率转换） — ?%
+未开启汇率转换（IsExchange=0）的 Top Performers 场景 — ?%
+按 Campaign Tag 过滤的 Top Performers 场景 — ?%
+按 Sales 排序对比且带自定义对比期的 Top Performers 场景 — ?%
+Bottom Performers（performanceType=1）场景 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
       <c r="A54" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4817,8 +5081,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="55">
+      <c r="E54" s="31" t="inlineStr">
+        <is>
+          <t>仅按报表日期范围查询长尾词报表（无附加过滤） — ?%
+按广告系列标签(CampaignTagId)过滤查询长尾词报表 — ?%
+按Amazon Portfolio(PortfolioId)过滤查询长尾词报表 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="80" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4839,8 +5110,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="56">
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>单词(NumberOfWord=1)长尾关键词按MatchType报表(ROAS指标) — ?%
+双词(NumberOfWord=2)长尾关键词按MatchType报表 — ?%
+三词(NumberOfWord=3)长尾关键词按MatchType报表 — ?%
+四词(NumberOfWord=4)长尾关键词按MatchType报表 — ?%
+分享报表(ShareId)+CampaignTagId标签过滤下的单词长尾关键词报表 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1">
       <c r="A56" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4861,8 +5141,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="57">
+      <c r="E56" s="31" t="inlineStr">
+        <is>
+          <t>基础场景:按天(Dim=date)+CampaignType(headlineSearch)筛选,无Tag/Portfolio筛选 — ?%
+Campaign Tag筛选场景:附加CampaignTagId筛选,按天展示 — ?%
+月粒度场景:Dim=month按月汇总展示 — ?%
+Portfolio筛选场景:附加PortfolioId筛选,按天展示 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="64" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4883,8 +5171,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="58">
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>单日期范围查询campaign类型层级绩效(无对比期无筛选) — ?%
+按日期范围并指定对比期查询campaign类型层级绩效 — ?%
+按CampaignTagId筛选查询campaign类型层级绩效 — ?%
+按PortfolioId筛选并指定对比期查询campaign类型层级绩效 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="96" customHeight="1">
       <c r="A58" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4905,8 +5201,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="59">
+      <c r="E58" s="31" t="inlineStr">
+        <is>
+          <t>Sponsored Products(SP)明细,单一日期范围(无对比期),ROAS指标 — ?%
+Sponsored Brands(SB)明细,单一日期范围(无对比期),ROAS指标 — ?%
+Sponsored Products(SP)明细,含对比期(环比/同比) — ?%
+Sponsored Brands(SB)明细,含对比期(环比/同比) — ?%
+按CampaignTagId(广告系列标签)筛选的明细查询 — ?%
+按PortfolioId(广告组合)筛选的明细查询(含对比期) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="64" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4927,8 +5233,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="60">
+      <c r="E59" s="31" t="inlineStr">
+        <is>
+          <t>查询不合规商品(INELIGIBLE)明细列表 — ?%
+查询缺货商品(NOT BUYABLE)明细列表 — ?%
+查询未获得购物车商品(NOT IN BUYBOX)明细列表 — ?%
+按CampaignTag筛选查询不合规商品(INELIGIBLE)明细列表 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="80" customHeight="1">
       <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4949,8 +5263,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="61">
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>Top Search Terms 按 ROAS 排序（无额外筛选） — ?%
+Top Search Terms 按 ACOS 排序（无额外筛选） — ?%
+按 Campaign Tag 筛选查询 Top Search Terms — ?%
+按 Portfolio 筛选查询 Top Search Terms — ?%
+Poor Search Terms 查询 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="96" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4971,8 +5294,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="62">
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>默认查询(无对比期,ROAS指标) — ?%
+带环比对比期查询(ROAS指标) — ?%
+默认查询(无对比期,ACOS指标) — ?%
+带对比期查询(ACOS指标,非US市场) — ?%
+按Campaign标签筛选查询 — ?%
+按广告组合(Portfolio)筛选查询 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="64" customHeight="1">
       <c r="A62" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -4993,8 +5326,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="63">
+      <c r="E62" s="31" t="inlineStr">
+        <is>
+          <t>多Profile(2-4个)组合非分享链路查询 — ?%
+单Profile非分享链路查询 — ?%
+多Profile组合通过分享链接(ShareId)访问 — ?%
+大批量Profile(5个以上/近全选)组合查询 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -5015,8 +5356,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="64">
+      <c r="E63" s="31" t="inlineStr">
+        <is>
+          <t>仅日期范围过滤查询周维度Campaign表现 — ?%
+按CampaignTagId过滤查询周维度Campaign表现 — ?%
+按PortfolioId过滤查询周维度Campaign表现 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="64" customHeight="1">
       <c r="A64" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -5037,8 +5385,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="65">
+      <c r="E64" s="31" t="inlineStr">
+        <is>
+          <t>默认视图(ROAS指标,仅日期筛选,全部广告类型) — 73.6%
+ACOS指标视图(仅日期筛选,全部广告类型) — 17.2%
+按CampaignTag筛选(标签分组查看Placement绩效) — 5.4%
+按指定广告类型筛选(campaignType=1,非全部类型) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -5059,8 +5415,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="66">
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>按日期范围查询商品异常状态计数（无附加过滤） — ?%
+按广告系列标签(CampaignTagId)过滤后统计商品异常状态计数 — ?%
+按广告组合(PortfolioId)过滤后统计商品异常状态计数 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="80" customHeight="1">
       <c r="A66" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -5081,8 +5444,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="67">
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>默认日期范围查询(多Profile,US市场) — ?%
+非美国市场(DE)日期范围查询 — ?%
+按广告活动标签(CampaignTagId)过滤 — ?%
+分享链接场景+广告活动标签过滤 — ?%
+按广告组合(PortfolioId)过滤 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="64" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -5103,8 +5475,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="68">
+      <c r="E67" s="31" t="inlineStr">
+        <is>
+          <t>仅日期范围过滤查询（美国市场，主流程） — ?%
+非美国市场日期范围查询（跨市场场景） — ?%
+按广告活动标签（CampaignTagId）过滤查询 — ?%
+按 Portfolio ID 过滤查询 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="22" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -5123,6 +5503,13 @@
       <c r="D68" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>默认日期范围查询(无标签/组合筛选) — ?%
+按CampaignTag标签筛选查询 — ?%
+按Portfolio筛选查询 — ?%</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5601,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="48" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
           <t>Keyword</t>
@@ -5235,8 +5622,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="74">
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 按CampaignId批量应用建议出价 — 48%
+场景2: 按关键词标签TaggingIds批量应用建议出价 — 20%
+场景3: 按关键词文本筛选批量应用建议出价 — 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
       <c r="A74" s="22" t="inlineStr">
         <is>
           <t>Keyword</t>
@@ -5257,8 +5651,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="75">
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 按关键词文本精确匹配删除标签 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="48" customHeight="1">
       <c r="A75" s="23" t="inlineStr">
         <is>
           <t>Keyword</t>
@@ -5277,6 +5676,13 @@
       <c r="D75" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 按关键词文本筛选打标签 — 52%
+场景2: 按指标筛选打标签 — 30%
+场景3: 按广告组名称模糊匹配打标签 — 9%</t>
         </is>
       </c>
     </row>
@@ -5759,7 +6165,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="64" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5778,6 +6184,14 @@
       <c r="D95" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E95" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标 — 56.2%
+场景2: SP广告 — 19.8%
+场景3: 不限广告类型 — 4.6%
+场景4: SB+SP广告+含NTB指标 — 3.4%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +6217,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="64" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5824,8 +6238,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="98">
+      <c r="E97" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标 — 59.2%
+场景2: SP广告 — 19.0%
+场景3: 不限广告类型 — 4.6%
+场景4: SB+SP广告+含NTB指标 — 3.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="64" customHeight="1">
       <c r="A98" s="22" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5846,8 +6268,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="99">
+      <c r="E98" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+按分组+Prompt状态汇总 — 20.8%
+场景2: SP广告+含NTB指标 — 20.2%
+场景3: 不限广告类型+按分组维度汇总 — 9.4%
+场景4: SP广告+按分组维度汇总 — 9.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="64" customHeight="1">
       <c r="A99" s="23" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5868,8 +6298,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="100">
+      <c r="E99" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告 — 40.7%
+场景2: SP广告+含NTB指标 — 37.0%
+场景3: SB广告+含NTB指标 — 7.4%
+场景4: SB+SP广告+含NTB指标 — 3.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="64" customHeight="1">
       <c r="A100" s="22" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5890,8 +6328,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="101">
+      <c r="E100" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标 — 47.4%
+场景2: SP广告 — 23.2%
+场景3: 不限广告类型 — 18.9%
+场景4: SB广告+含NTB指标 — 3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
       <c r="A101" s="23" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5912,8 +6358,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="102">
+      <c r="E101" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 不限广告类型 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="64" customHeight="1">
       <c r="A102" s="22" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5934,8 +6385,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="103">
+      <c r="E102" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+按分组+Prompt状态汇总 — 24.4%
+场景2: 不限广告类型+按分组维度汇总 — 12.2%
+场景3: SP广告+按分组维度汇总 — 10.4%
+场景4: SP广告+按分组+Prompt状态汇总 — 6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="64" customHeight="1">
       <c r="A103" s="23" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5956,8 +6415,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="104">
+      <c r="E103" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标 — 53.6%
+场景2: SP广告 — 19.4%
+场景3: 不限广告类型 — 5.0%
+场景4: SB+SP广告+含NTB指标 — 4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="64" customHeight="1">
       <c r="A104" s="22" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -5978,8 +6445,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="105">
+      <c r="E104" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标+含PromptText过滤 — 51.9%
+场景2: SP广告+含PromptText过滤 — 22.4%
+场景3: 不限广告类型+含PromptText过滤 — 7.1%
+场景4: SP广告+含NTB指标+含PromptText过滤 — 1.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="64" customHeight="1">
       <c r="A105" s="23" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -6000,8 +6475,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="106">
+      <c r="E105" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告 — 73.0%
+场景2: 不限广告类型 — 4.4%
+场景3: SB+SP广告 — 4.0%
+场景4: SP广告+指定ASIN过滤 — 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="64" customHeight="1">
       <c r="A106" s="22" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -6022,8 +6505,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="107">
+      <c r="E106" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标 — 42.5%
+场景2: SP广告 — 30.0%
+场景3: SB广告+含NTB指标 — 7.5%
+场景4: SP广告+含NTB指标+指定Campaign过滤 — 7.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="64" customHeight="1">
       <c r="A107" s="23" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -6044,8 +6535,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="108">
+      <c r="E107" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告 — 73.0%
+场景2: SB+SP广告 — 6.0%
+场景3: 不限广告类型 — 6.0%
+场景4: SP广告+指定ASIN过滤 — 3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="64" customHeight="1">
       <c r="A108" s="22" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -6066,8 +6565,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="109">
+      <c r="E108" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告 — 74.2%
+场景2: 不限广告类型 — 5.4%
+场景3: SB+SP广告 — 5.2%
+场景4: SP广告+指定ASIN过滤 — 2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="64" customHeight="1">
       <c r="A109" s="23" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -6088,8 +6595,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="110">
+      <c r="E109" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标 — 56.2%
+场景2: SP广告 — 17.6%
+场景3: 不限广告类型 — 7.6%
+场景4: SB+SP广告+含NTB指标 — 3.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="64" customHeight="1">
       <c r="A110" s="22" t="inlineStr">
         <is>
           <t>PromptAdExtension</t>
@@ -6108,6 +6623,14 @@
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E110" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP广告+含NTB指标 — 16.8%
+场景2: SP广告+含NTB指标 — 13.2%
+场景3: SP广告+按分组+Prompt状态汇总 — 11.6%
+场景4: 不限广告类型+按分组维度汇总 — 8.4%</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7868,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="27" t="inlineStr">
         <is>
           <t>AIManage</t>
@@ -7366,8 +7889,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="29">
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,非真实客户场景) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
           <t>AIManage</t>
@@ -7386,6 +7914,11 @@
       <c r="D29" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,非真实客户场景) — ?%</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7944,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
           <t>AIManage</t>
@@ -7430,6 +7963,11 @@
       <c r="D31" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,默认分页,非真实客户场景) — ?%</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7993,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
           <t>AIManage</t>
@@ -7474,6 +8012,11 @@
       <c r="D33" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,非真实客户场景) — ?%</t>
         </is>
       </c>
     </row>
@@ -8841,7 +9384,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="64" customHeight="1">
       <c r="A96" s="26" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -8862,8 +9405,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="97">
+      <c r="E96" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 单AdGroup ASIN定向新增 — 29.8%
+场景2: 单AdGroup 自定义SKU编号定向新增 — 20.0%
+场景3: 多AdGroup批量 ASIN定向新增 — 35.4%
+场景4: 多AdGroup批量 自定义SKU编号定向新增 — 14.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -8884,8 +9435,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="98">
+      <c r="E97" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 单个SP广告组少量ASIN添加(1-4个) — ?%
+场景2: SP广告组中等批量多规格SKU添加(5-49个) — ?%
+场景3: SP广告组大批量SKU导入(≥50个,整店同步) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
       <c r="A98" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -8904,6 +9462,13 @@
       <c r="D98" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E98" s="31" t="inlineStr">
+        <is>
+          <t>单广告组添加单个ASIN商品定向(含后置归档,可重复) — 27%
+单广告组批量粘贴多个ASIN商品定向(含后置归档,可重复) — 33%
+跨多个广告组批量应用同一ASIN商品定向(含后置归档,可重复) — 40%</t>
         </is>
       </c>
     </row>
@@ -8951,7 +9516,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="48" customHeight="1">
       <c r="A101" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -8972,8 +9537,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="102">
+      <c r="E101" s="31" t="inlineStr">
+        <is>
+          <t>Campaign级批量创建否定精确匹配关键词(SP) — ?%
+Campaign级批量创建否定词组匹配关键词(SB) — ?%
+AdGroup级批量创建否定关键词(SP手动/PAT) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="32" customHeight="1">
       <c r="A102" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -8994,8 +9566,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="103">
+      <c r="E102" s="31" t="inlineStr">
+        <is>
+          <t>SP广告组仅设置ROAS竞价优化目标(ACOS未设置/高频场景) — ?%
+SP手动/PAT广告组同时设置ACOS与ROAS双竞价优化目标(中频场景) — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="48" customHeight="1">
       <c r="A103" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9014,6 +9592,13 @@
       <c r="D103" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E103" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 单ASIN替换 旧目标转Paused 新目标默认 — 90.9%
+场景2: 全字段显式替换 旧目标Archived 新目标Enabled keep=false — 7.07%
+场景3: 保留旧目标keep=true 新增替换目标Paused — 2.02%</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9712,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="48" customHeight="1">
       <c r="A109" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9148,8 +9733,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="110">
+      <c r="E109" s="31" t="inlineStr">
+        <is>
+          <t>CopyAdGroup SP Manual ToDifferentCampaign — 63.8%
+CopyAdGroup SP Manual SameCampaign Duplicate — 17.7%
+CopyAdGroup SP Auto ToDifferentCampaign — 15.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="48" customHeight="1">
       <c r="A110" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9168,6 +9760,13 @@
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E110" s="31" t="inlineStr">
+        <is>
+          <t>场景1: SP手动投放AdGroup单ASIN复制 — 82.4%
+场景2: SP自动投放AdGroup单ASIN复制 — 6.8%
+场景3: SP手动投放AdGroup多ASIN复制 — 8.1%</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9792,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="16" customHeight="1">
       <c r="A112" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9214,8 +9813,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="113">
+      <c r="E112" s="31" t="inlineStr">
+        <is>
+          <t>复制SponsoredDisplay广告组（manual targeting，同campaign内复制） — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
       <c r="A113" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9234,6 +9838,11 @@
       <c r="D113" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E113" s="31" t="inlineStr">
+        <is>
+          <t>复制SD广告组(含创意+ASIN定向,含后置清理,可重复) — ?%</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9868,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="304" customHeight="1">
       <c r="A115" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9280,8 +9889,31 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="116">
+      <c r="E115" s="31" t="inlineStr">
+        <is>
+          <t>SP单个AdGroup批量改价（高频场景） — ?%
+SP多个AdGroup跨Campaign批量改价（中频场景） — ?%
+跨广告类型批量改价含SD设置bidOptimization（中频场景） — ?%
+场景1: SponsoredProducts通用场景 启用AdGroup — ?%
+场景2: SponsoredProducts手动PAT场景 暂停AdGroup — ?%
+场景3: SponsoredDisplay场景 切换AdGroup状态 — ?%
+场景4: SponsoredProducts通用场景 归档AdGroup — ?%
+批量设置SD广告组优化方式为clicks(前置读原值+后置还原,可重复) — ?%
+通过全局唯一id查询广告组编辑数据 — 60%
+通过profileId+campaignId+adGroupId组合查询广告组编辑数据 — 10%
+低价位默认出价调整(&lt;1,含读原值+还原) — 50.8%
+中价位默认出价调整(1~3,含读原值+还原) — 40.9%
+高价位默认出价调整(&gt;3,含读原值+还原) — 8.3%
+SD AdGroup Update Basic Attributes NoCostControl — ?%
+SD AdGroup Update EnableCostControl — ?%
+SD AdGroup Update DisableCostControl — ?%
+批量修改AdGroup名称(含读原值+还原,可重复) — ?%
+普通改名场景-读取原名后改名并还原 — ?%
+带sourceName(Creative Hub来源)的改名场景-读取原名后改名并还原 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="48" customHeight="1">
       <c r="A116" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9300,6 +9932,13 @@
       <c r="D116" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E116" s="31" t="inlineStr">
+        <is>
+          <t>不指定CampaignIds查询全部候选AdGroup — 61.4%
+单个CampaignId查询PAT研究AdGroup — 36.8%
+多个CampaignIds批量查询PAT研究AdGroup — 1.8%</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9964,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="80" customHeight="1">
       <c r="A118" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9346,8 +9985,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="119">
+      <c r="E118" s="31" t="inlineStr">
+        <is>
+          <t>SB广告活动详情页-单Campaign级Adgroup趋势图（按周Dim） — ?%
+Adgroup列表页-账户级总览趋势图（不筛选任何Campaign/AdGroup） — ?%
+AdGroup Tag聚合分析-跨Profile的Tag维度Adgroup趋势图 — ?%
+Adgroup列表页-按Portfolio筛选后的趋势图 — ?%
+Adgroup列表页-钻取到指定AdGroup的趋势图 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="64" customHeight="1">
       <c r="A119" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9368,8 +10016,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="120">
+      <c r="E119" s="31" t="inlineStr">
+        <is>
+          <t>按Campaign查看AdGroup列表(不限定具体AdGroup) — 43.6%
+AdGroup模块主列表(默认活跃状态,不限Campaign) — 25.8%
+AdGroup模块主列表(按AdGroup标签筛选) — 25.6%
+Campaign详情钻取查看单个AdGroup — 4.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="48" customHeight="1">
       <c r="A120" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9390,8 +10046,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="121">
+      <c r="E120" s="31" t="inlineStr">
+        <is>
+          <t>campaignId查询AdgroupTotal 单campaign汇总 — ?%
+campaignId加adgroupId查询AdgroupTotal 指定adgroup汇总 — ?%
+广告类型加状态过滤查询AdgroupTotal 账户级汇总 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="48" customHeight="1">
       <c r="A121" s="23" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9412,8 +10075,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="122">
+      <c r="E121" s="31" t="inlineStr">
+        <is>
+          <t>查询SP手动定位(PAT)广告系列的广告组类型 — ?%
+查询SP通用广告系列的广告组类型 — ?%
+查询SD广告系列的广告组类型 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="80" customHeight="1">
       <c r="A122" s="27" t="inlineStr">
         <is>
           <t>Adgroup</t>
@@ -9432,6 +10102,15 @@
       <c r="D122" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E122" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 同Campaign内复制并保持enabled — ?%
+场景2: 同Campaign内复制并保持paused — ?%
+单个SP广告系列查询广告组列表 — 92.7%
+单个SD广告系列查询广告组列表 — 92.7%
+批量多campaignId查询广告组列表 — 7.3%</t>
         </is>
       </c>
     </row>
@@ -9985,7 +10664,7 @@
         </is>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" s="26" t="inlineStr">
         <is>
           <t>AmazonAiImage</t>
@@ -10006,8 +10685,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="149">
+      <c r="E148" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 单图片区域裁剪编辑 — ?%</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="80" customHeight="1">
       <c r="A149" s="23" t="inlineStr">
         <is>
           <t>AmazonAiImage</t>
@@ -10028,8 +10712,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="150">
+      <c r="E149" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 主题+描述词组合生成 — 46.2%
+场景2: 仅指定主题 — 18.9%
+场景3: 仅描述词无主题 — 13.0%
+场景4: 无主题无描述词默认生成 — 10.1%
+场景5: 主题+描述词+推荐主题开启 — 8.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="32" customHeight="1">
       <c r="A150" s="27" t="inlineStr">
         <is>
           <t>AmazonAiImage</t>
@@ -10050,8 +10743,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="151">
+      <c r="E150" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 不限制返回数量查询 — 80%
+场景2: 限制返回数量查询 — 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
       <c r="A151" s="23" t="inlineStr">
         <is>
           <t>AmazonAiImage</t>
@@ -10070,6 +10769,11 @@
       <c r="D151" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E151" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 查询资产注册状态 — ?%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10799,7 @@
         </is>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="16" customHeight="1">
       <c r="A153" s="23" t="inlineStr">
         <is>
           <t>AmazonAiImage</t>
@@ -10114,6 +10818,11 @@
       <c r="D153" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="E153" s="31" t="inlineStr">
+        <is>
+          <t>场景1: 注册单张AI生成图片素材 — ?%</t>
         </is>
       </c>
     </row>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'模块汇总'!$A$1:$D$123</definedName>
@@ -910,6 +910,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F6" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="34" t="n"/>
@@ -986,6 +999,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F9" s="29" t="n">
+        <v>101</v>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>100% (25/25)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="34" t="n"/>
@@ -1369,6 +1395,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F24" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="inlineStr">
+        <is>
+          <t>44% (4/9)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="34" t="n"/>
@@ -1519,6 +1558,19 @@
       <c r="E30" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>68</v>
+      </c>
+      <c r="G30" s="29" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="H30" s="29" t="inlineStr">
+        <is>
+          <t>90% (28/31)</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4366,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="96" customHeight="1">
       <c r="A22" s="34" t="n"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -4336,8 +4388,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="23">
+      <c r="F22" s="37" t="inlineStr">
+        <is>
+          <t>单个Campaign详情页趋势图（按日Dim）
+按Campaign状态筛选的汇总趋势图（Dim=ytd）
+按状态+标签筛选的趋势图
+按名称搜索+状态筛选的趋势图
+无筛选查看全部Campaign整体趋势图
+按广告组合(Portfolio)+状态筛选的趋势图</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
       <c r="A23" s="34" t="n"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
@@ -4359,8 +4421,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="24">
+      <c r="F23" s="37" t="inlineStr">
+        <is>
+          <t>按campaignId+campaignState+日期范围查询campaign列表
+按campaignId+日期范围查询campaign列表（不筛选状态）
+按campaignId+campaignName模糊搜索+campaignState+日期范围查询
+按campaignId+campaignState+广告类型(CampaignTypeItems)+日期范围查询
+按campaignId+campaignName模糊搜索+日期范围查询（不筛选状态）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="96" customHeight="1">
       <c r="A24" s="34" t="n"/>
       <c r="B24" s="22" t="inlineStr">
         <is>
@@ -4382,8 +4453,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="25">
+      <c r="F24" s="37" t="inlineStr">
+        <is>
+          <t>按指定CampaignId精确查询单个广告活动效果数据
+按状态筛选并附带同期对比查询广告活动列表
+按名称搜索并按状态筛选广告活动列表
+按状态和标签组合筛选广告活动列表
+无附加筛选条件的默认列表查询
+按广告类型(CampaignTypeItems)筛选广告活动列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="96" customHeight="1">
       <c r="A25" s="34" t="n"/>
       <c r="B25" s="23" t="inlineStr">
         <is>
@@ -4405,8 +4486,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="26">
+      <c r="F25" s="37" t="inlineStr">
+        <is>
+          <t>按效果指标筛选条件查询广告活动列表
+无筛选条件的默认活动列表查询
+按campaign标签(Tag)筛选查询
+按指定campaignIds批量精确查询
+按广告类型明细(CampaignTypeItems)筛选查询
+按广告组合(Portfolio)筛选查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="128" customHeight="1">
       <c r="A26" s="34" t="n"/>
       <c r="B26" s="22" t="inlineStr">
         <is>
@@ -4426,6 +4517,18 @@
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F26" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 勾选指定Campaign汇总
+场景2: 按CampaignTag标签筛选汇总
+场景3: 按Campaign名称搜索汇总
+场景4: 默认总览 State筛选 同期对比
+场景5: 按投放状态ServingStatus筛选汇总
+场景6: 按Portfolio筛选汇总
+场景7: 按广告类型CampaignTypeItems筛选汇总
+场景8: 按目标Asin筛选汇总</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5131,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="64" customHeight="1">
       <c r="A44" s="34" t="n"/>
       <c r="B44" s="21" t="inlineStr">
         <is>
@@ -5050,8 +5153,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="45">
+      <c r="F44" s="37" t="inlineStr">
+        <is>
+          <t>默认日粒度趋势查询(含环比对比期)
+按CampaignTag过滤的日粒度趋势查询
+周粒度(Dim=week)趋势查询
+月粒度(Dim=month)趋势查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
       <c r="A45" s="34" t="n"/>
       <c r="B45" s="23" t="inlineStr">
         <is>
@@ -5073,8 +5184,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="46">
+      <c r="F45" s="37" t="inlineStr">
+        <is>
+          <t>Brand+品类过滤日粒度Benchmark(无分享链接)
+不带Brand/品类过滤的整体Benchmark
+Brand+品类过滤且通过分享链接访问
+Brand+品类过滤且按周粒度(Dim=week)展示</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
       <c r="A46" s="34" t="n"/>
       <c r="B46" s="22" t="inlineStr">
         <is>
@@ -5096,8 +5215,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="47">
+      <c r="F46" s="37" t="inlineStr">
+        <is>
+          <t>单Profile按日期范围查询超预算广告活动列表
+多Profile跨店铺合并按日期范围查询超预算广告活动列表
+按Campaign Tag筛选查询超预算广告活动列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="34" t="n"/>
       <c r="B47" s="23" t="inlineStr">
         <is>
@@ -5119,8 +5245,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="48">
+      <c r="F47" s="37" t="inlineStr">
+        <is>
+          <t>基础日期范围查询Out of Budget图表（US市场，无标签/活动过滤）
+非US市场查询Out of Budget图表（汇率换算场景，以CA为代表）
+按CampaignTagId标签过滤的Out of Budget图表查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="80" customHeight="1">
       <c r="A48" s="34" t="n"/>
       <c r="B48" s="22" t="inlineStr">
         <is>
@@ -5142,8 +5275,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="49">
+      <c r="F48" s="37" t="inlineStr">
+        <is>
+          <t>US站点仅日期范围周对比周(单/多Profile聚合)
+非US市场(DE)基础周对比
+CampaignTagId标签过滤
+PortfolioId组合过滤
+ToMarket未指定(null)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
       <c r="A49" s="34" t="n"/>
       <c r="B49" s="23" t="inlineStr">
         <is>
@@ -5165,8 +5307,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="50">
+      <c r="F49" s="37" t="inlineStr">
+        <is>
+          <t>多账号Portfolio下钻子标签ROAS指标(滚动周期对比) — 45.5%
+单账号下钻子标签ROAS指标(月度环比) — 42.4%
+ACOS指标视角下钻子标签(年度累计vs去年同期对比) — 12.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="34" t="n"/>
       <c r="B50" s="22" t="inlineStr">
         <is>
@@ -5188,8 +5337,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="51">
+      <c r="F50" s="37" t="inlineStr">
+        <is>
+          <t>仅日期范围过滤查询Campaign Tag绩效widget(无Tag/Portfolio子筛选)
+按CampaignTagId筛选查询Campaign Tag绩效widget
+按PortfolioId筛选查询Campaign Tag绩效widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="34" t="n"/>
       <c r="B51" s="23" t="inlineStr">
         <is>
@@ -5211,8 +5367,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="52">
+      <c r="F51" s="37" t="inlineStr">
+        <is>
+          <t>查看标签ROAS目标达成率排名(默认汇率换算)
+查看标签ACOS目标达成率排名(默认汇率换算)
+查看标签ACOS目标达成率排名(不做汇率换算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="80" customHeight="1">
       <c r="A52" s="34" t="n"/>
       <c r="B52" s="22" t="inlineStr">
         <is>
@@ -5234,8 +5397,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="53">
+      <c r="F52" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 默认ROAS视图 无标签筛选 — 57.5%
+场景2: ACOS视图 新版CampaignTag命名 无筛选 — 14.2%
+场景3: ACOS视图 旧版Portfolio命名 无筛选 — 14.2%
+场景4: ACOS视图 按CampaignTagId筛选指定标签 — 8.4%
+场景5: ACOS视图 按旧版PortfolioId筛选 — 3.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="80" customHeight="1">
       <c r="A53" s="34" t="n"/>
       <c r="B53" s="23" t="inlineStr">
         <is>
@@ -5257,8 +5429,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="54">
+      <c r="F53" s="37" t="inlineStr">
+        <is>
+          <t>默认场景：仅日期范围过滤的 Top Performers（按 Spend 排序，开启汇率转换）
+未开启汇率转换（IsExchange=0）的 Top Performers 场景
+按 Campaign Tag 过滤的 Top Performers 场景
+按 Sales 排序对比且带自定义对比期的 Top Performers 场景
+Bottom Performers（performanceType=1）场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
       <c r="A54" s="34" t="n"/>
       <c r="B54" s="22" t="inlineStr">
         <is>
@@ -5280,8 +5461,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="55">
+      <c r="F54" s="37" t="inlineStr">
+        <is>
+          <t>仅按报表日期范围查询长尾词报表（无附加过滤）
+按广告系列标签(CampaignTagId)过滤查询长尾词报表
+按Amazon Portfolio(PortfolioId)过滤查询长尾词报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="80" customHeight="1">
       <c r="A55" s="34" t="n"/>
       <c r="B55" s="23" t="inlineStr">
         <is>
@@ -5303,8 +5491,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="56">
+      <c r="F55" s="37" t="inlineStr">
+        <is>
+          <t>单词(NumberOfWord=1)长尾关键词按MatchType报表(ROAS指标)
+双词(NumberOfWord=2)长尾关键词按MatchType报表
+三词(NumberOfWord=3)长尾关键词按MatchType报表
+四词(NumberOfWord=4)长尾关键词按MatchType报表
+分享报表(ShareId)+CampaignTagId标签过滤下的单词长尾关键词报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1">
       <c r="A56" s="34" t="n"/>
       <c r="B56" s="22" t="inlineStr">
         <is>
@@ -5326,8 +5523,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="57">
+      <c r="F56" s="37" t="inlineStr">
+        <is>
+          <t>基础场景:按天(Dim=date)+CampaignType(headlineSearch)筛选,无Tag/Portfolio筛选
+Campaign Tag筛选场景:附加CampaignTagId筛选,按天展示
+月粒度场景:Dim=month按月汇总展示
+Portfolio筛选场景:附加PortfolioId筛选,按天展示</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="64" customHeight="1">
       <c r="A57" s="34" t="n"/>
       <c r="B57" s="23" t="inlineStr">
         <is>
@@ -5349,8 +5554,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="58">
+      <c r="F57" s="37" t="inlineStr">
+        <is>
+          <t>单日期范围查询campaign类型层级绩效(无对比期无筛选)
+按日期范围并指定对比期查询campaign类型层级绩效
+按CampaignTagId筛选查询campaign类型层级绩效
+按PortfolioId筛选并指定对比期查询campaign类型层级绩效</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="96" customHeight="1">
       <c r="A58" s="34" t="n"/>
       <c r="B58" s="22" t="inlineStr">
         <is>
@@ -5372,8 +5585,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="59">
+      <c r="F58" s="37" t="inlineStr">
+        <is>
+          <t>Sponsored Products(SP)明细,单一日期范围(无对比期),ROAS指标
+Sponsored Brands(SB)明细,单一日期范围(无对比期),ROAS指标
+Sponsored Products(SP)明细,含对比期(环比/同比)
+Sponsored Brands(SB)明细,含对比期(环比/同比)
+按CampaignTagId(广告系列标签)筛选的明细查询
+按PortfolioId(广告组合)筛选的明细查询(含对比期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="64" customHeight="1">
       <c r="A59" s="34" t="n"/>
       <c r="B59" s="23" t="inlineStr">
         <is>
@@ -5395,8 +5618,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="60">
+      <c r="F59" s="37" t="inlineStr">
+        <is>
+          <t>查询不合规商品(INELIGIBLE)明细列表
+查询缺货商品(NOT BUYABLE)明细列表
+查询未获得购物车商品(NOT IN BUYBOX)明细列表
+按CampaignTag筛选查询不合规商品(INELIGIBLE)明细列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="80" customHeight="1">
       <c r="A60" s="34" t="n"/>
       <c r="B60" s="22" t="inlineStr">
         <is>
@@ -5418,8 +5649,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="61">
+      <c r="F60" s="37" t="inlineStr">
+        <is>
+          <t>Top Search Terms 按 ROAS 排序（无额外筛选）
+Top Search Terms 按 ACOS 排序（无额外筛选）
+按 Campaign Tag 筛选查询 Top Search Terms
+按 Portfolio 筛选查询 Top Search Terms
+Poor Search Terms 查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="96" customHeight="1">
       <c r="A61" s="34" t="n"/>
       <c r="B61" s="23" t="inlineStr">
         <is>
@@ -5441,8 +5681,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="62">
+      <c r="F61" s="37" t="inlineStr">
+        <is>
+          <t>默认查询(无对比期,ROAS指标)
+带环比对比期查询(ROAS指标)
+默认查询(无对比期,ACOS指标)
+带对比期查询(ACOS指标,非US市场)
+按Campaign标签筛选查询
+按广告组合(Portfolio)筛选查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="64" customHeight="1">
       <c r="A62" s="34" t="n"/>
       <c r="B62" s="22" t="inlineStr">
         <is>
@@ -5464,8 +5714,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="63">
+      <c r="F62" s="37" t="inlineStr">
+        <is>
+          <t>多Profile(2-4个)组合非分享链路查询
+单Profile非分享链路查询
+多Profile组合通过分享链接(ShareId)访问
+大批量Profile(5个以上/近全选)组合查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
       <c r="A63" s="34" t="n"/>
       <c r="B63" s="23" t="inlineStr">
         <is>
@@ -5487,8 +5745,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="64">
+      <c r="F63" s="37" t="inlineStr">
+        <is>
+          <t>仅日期范围过滤查询周维度Campaign表现
+按CampaignTagId过滤查询周维度Campaign表现
+按PortfolioId过滤查询周维度Campaign表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="64" customHeight="1">
       <c r="A64" s="34" t="n"/>
       <c r="B64" s="22" t="inlineStr">
         <is>
@@ -5510,8 +5775,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="65">
+      <c r="F64" s="37" t="inlineStr">
+        <is>
+          <t>默认视图(ROAS指标,仅日期筛选,全部广告类型) — 73.6%
+ACOS指标视图(仅日期筛选,全部广告类型) — 17.2%
+按CampaignTag筛选(标签分组查看Placement绩效) — 5.4%
+按指定广告类型筛选(campaignType=1,非全部类型)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
       <c r="A65" s="34" t="n"/>
       <c r="B65" s="23" t="inlineStr">
         <is>
@@ -5533,8 +5806,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="66">
+      <c r="F65" s="37" t="inlineStr">
+        <is>
+          <t>按日期范围查询商品异常状态计数（无附加过滤）
+按广告系列标签(CampaignTagId)过滤后统计商品异常状态计数
+按广告组合(PortfolioId)过滤后统计商品异常状态计数</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="80" customHeight="1">
       <c r="A66" s="34" t="n"/>
       <c r="B66" s="22" t="inlineStr">
         <is>
@@ -5556,8 +5836,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="67">
+      <c r="F66" s="37" t="inlineStr">
+        <is>
+          <t>默认日期范围查询(多Profile,US市场)
+非美国市场(DE)日期范围查询
+按广告活动标签(CampaignTagId)过滤
+分享链接场景+广告活动标签过滤
+按广告组合(PortfolioId)过滤</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="64" customHeight="1">
       <c r="A67" s="34" t="n"/>
       <c r="B67" s="23" t="inlineStr">
         <is>
@@ -5579,8 +5868,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="68">
+      <c r="F67" s="37" t="inlineStr">
+        <is>
+          <t>仅日期范围过滤查询（美国市场，主流程）
+非美国市场日期范围查询（跨市场场景）
+按广告活动标签（CampaignTagId）过滤查询
+按 Portfolio ID 过滤查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
       <c r="A68" s="34" t="n"/>
       <c r="B68" s="22" t="inlineStr">
         <is>
@@ -5600,6 +5897,13 @@
       <c r="E68" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F68" s="37" t="inlineStr">
+        <is>
+          <t>默认日期范围查询(无标签/组合筛选)
+按CampaignTag标签筛选查询
+按Portfolio筛选查询</t>
         </is>
       </c>
     </row>
@@ -7929,7 +8233,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="34" t="n"/>
       <c r="B28" s="27" t="inlineStr">
         <is>
@@ -7951,8 +8255,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="29">
+      <c r="F28" s="37" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,非真实客户场景)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="34" t="n"/>
       <c r="B29" s="23" t="inlineStr">
         <is>
@@ -7972,6 +8281,11 @@
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F29" s="37" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,非真实客户场景)</t>
         </is>
       </c>
     </row>
@@ -7998,7 +8312,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" s="34" t="n"/>
       <c r="B31" s="23" t="inlineStr">
         <is>
@@ -8018,6 +8332,11 @@
       <c r="E31" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F31" s="37" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,默认分页,非真实客户场景)</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8363,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" s="34" t="n"/>
       <c r="B33" s="23" t="inlineStr">
         <is>
@@ -8064,6 +8383,11 @@
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F33" s="37" t="inlineStr">
+        <is>
+          <t>冒烟测试(dev环境样本,非真实客户场景)</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9877,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="64" customHeight="1">
       <c r="A96" s="34" t="n"/>
       <c r="B96" s="26" t="inlineStr">
         <is>
@@ -9575,8 +9899,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="97">
+      <c r="F96" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 单AdGroup ASIN定向新增 — 29.8%
+场景2: 单AdGroup 自定义SKU编号定向新增 — 20.0%
+场景3: 多AdGroup批量 ASIN定向新增 — 35.4%
+场景4: 多AdGroup批量 自定义SKU编号定向新增 — 14.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
       <c r="A97" s="34" t="n"/>
       <c r="B97" s="23" t="inlineStr">
         <is>
@@ -9598,8 +9930,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="98">
+      <c r="F97" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 单个SP广告组少量ASIN添加(1-4个)
+场景2: SP广告组中等批量多规格SKU添加(5-49个)
+场景3: SP广告组大批量SKU导入(≥50个,整店同步)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
       <c r="A98" s="34" t="n"/>
       <c r="B98" s="27" t="inlineStr">
         <is>
@@ -9619,6 +9958,13 @@
       <c r="E98" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F98" s="37" t="inlineStr">
+        <is>
+          <t>单广告组添加单个ASIN商品定向(含后置归档,可重复) — 27%
+单广告组批量粘贴多个ASIN商品定向(含后置归档,可重复) — 33%
+跨多个广告组批量应用同一ASIN商品定向(含后置归档,可重复) — 40%</t>
         </is>
       </c>
     </row>
@@ -9668,7 +10014,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="48" customHeight="1">
       <c r="A101" s="34" t="n"/>
       <c r="B101" s="23" t="inlineStr">
         <is>
@@ -9690,8 +10036,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="102">
+      <c r="F101" s="37" t="inlineStr">
+        <is>
+          <t>Campaign级批量创建否定精确匹配关键词(SP)
+Campaign级批量创建否定词组匹配关键词(SB)
+AdGroup级批量创建否定关键词(SP手动/PAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="32" customHeight="1">
       <c r="A102" s="34" t="n"/>
       <c r="B102" s="27" t="inlineStr">
         <is>
@@ -9713,8 +10066,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="103">
+      <c r="F102" s="37" t="inlineStr">
+        <is>
+          <t>SP广告组仅设置ROAS竞价优化目标(ACOS未设置/高频场景)
+SP手动/PAT广告组同时设置ACOS与ROAS双竞价优化目标(中频场景)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="48" customHeight="1">
       <c r="A103" s="34" t="n"/>
       <c r="B103" s="23" t="inlineStr">
         <is>
@@ -9734,6 +10093,13 @@
       <c r="E103" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F103" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 单ASIN替换 旧目标转Paused 新目标默认 — 90.9%
+场景2: 全字段显式替换 旧目标Archived 新目标Enabled keep=false — 7.07%
+场景3: 保留旧目标keep=true 新增替换目标Paused — 2.02%</t>
         </is>
       </c>
     </row>
@@ -9852,7 +10218,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="48" customHeight="1">
       <c r="A109" s="34" t="n"/>
       <c r="B109" s="23" t="inlineStr">
         <is>
@@ -9874,8 +10240,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="110">
+      <c r="F109" s="37" t="inlineStr">
+        <is>
+          <t>CopyAdGroup SP Manual ToDifferentCampaign — 63.8%
+CopyAdGroup SP Manual SameCampaign Duplicate — 17.7%
+CopyAdGroup SP Auto ToDifferentCampaign — 15.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="48" customHeight="1">
       <c r="A110" s="34" t="n"/>
       <c r="B110" s="27" t="inlineStr">
         <is>
@@ -9895,6 +10268,13 @@
       <c r="E110" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F110" s="37" t="inlineStr">
+        <is>
+          <t>场景1: SP手动投放AdGroup单ASIN复制 — 82.4%
+场景2: SP自动投放AdGroup单ASIN复制 — 6.8%
+场景3: SP手动投放AdGroup多ASIN复制 — 8.1%</t>
         </is>
       </c>
     </row>
@@ -9921,7 +10301,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="16" customHeight="1">
       <c r="A112" s="34" t="n"/>
       <c r="B112" s="27" t="inlineStr">
         <is>
@@ -9943,8 +10323,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="113">
+      <c r="F112" s="37" t="inlineStr">
+        <is>
+          <t>复制SponsoredDisplay广告组（manual targeting，同campaign内复制）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
       <c r="A113" s="34" t="n"/>
       <c r="B113" s="23" t="inlineStr">
         <is>
@@ -9964,6 +10349,11 @@
       <c r="E113" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F113" s="37" t="inlineStr">
+        <is>
+          <t>复制SD广告组(含创意+ASIN定向,含后置清理,可重复)</t>
         </is>
       </c>
     </row>
@@ -9990,7 +10380,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="304" customHeight="1">
       <c r="A115" s="34" t="n"/>
       <c r="B115" s="23" t="inlineStr">
         <is>
@@ -10012,8 +10402,31 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="116">
+      <c r="F115" s="37" t="inlineStr">
+        <is>
+          <t>SP单个AdGroup批量改价（高频场景）
+SP多个AdGroup跨Campaign批量改价（中频场景）
+跨广告类型批量改价含SD设置bidOptimization（中频场景）
+场景1: SponsoredProducts通用场景 启用AdGroup
+场景2: SponsoredProducts手动PAT场景 暂停AdGroup
+场景3: SponsoredDisplay场景 切换AdGroup状态
+场景4: SponsoredProducts通用场景 归档AdGroup
+批量设置SD广告组优化方式为clicks(前置读原值+后置还原,可重复)
+通过全局唯一id查询广告组编辑数据 — 60%
+通过profileId+campaignId+adGroupId组合查询广告组编辑数据 — 10%
+低价位默认出价调整(&lt;1,含读原值+还原) — 50.8%
+中价位默认出价调整(1~3,含读原值+还原) — 40.9%
+高价位默认出价调整(&gt;3,含读原值+还原) — 8.3%
+SD AdGroup Update Basic Attributes NoCostControl
+SD AdGroup Update EnableCostControl
+SD AdGroup Update DisableCostControl
+批量修改AdGroup名称(含读原值+还原,可重复)
+普通改名场景-读取原名后改名并还原
+带sourceName(Creative Hub来源)的改名场景-读取原名后改名并还原</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="48" customHeight="1">
       <c r="A116" s="34" t="n"/>
       <c r="B116" s="27" t="inlineStr">
         <is>
@@ -10033,6 +10446,13 @@
       <c r="E116" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F116" s="37" t="inlineStr">
+        <is>
+          <t>不指定CampaignIds查询全部候选AdGroup — 61.4%
+单个CampaignId查询PAT研究AdGroup — 36.8%
+多个CampaignIds批量查询PAT研究AdGroup — 1.8%</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10479,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="80" customHeight="1">
       <c r="A118" s="34" t="n"/>
       <c r="B118" s="27" t="inlineStr">
         <is>
@@ -10081,8 +10501,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="119">
+      <c r="F118" s="37" t="inlineStr">
+        <is>
+          <t>SB广告活动详情页-单Campaign级Adgroup趋势图（按周Dim）
+Adgroup列表页-账户级总览趋势图（不筛选任何Campaign/AdGroup）
+AdGroup Tag聚合分析-跨Profile的Tag维度Adgroup趋势图
+Adgroup列表页-按Portfolio筛选后的趋势图
+Adgroup列表页-钻取到指定AdGroup的趋势图</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="64" customHeight="1">
       <c r="A119" s="34" t="n"/>
       <c r="B119" s="23" t="inlineStr">
         <is>
@@ -10104,8 +10533,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="120">
+      <c r="F119" s="37" t="inlineStr">
+        <is>
+          <t>按Campaign查看AdGroup列表(不限定具体AdGroup) — 43.6%
+AdGroup模块主列表(默认活跃状态,不限Campaign) — 25.8%
+AdGroup模块主列表(按AdGroup标签筛选) — 25.6%
+Campaign详情钻取查看单个AdGroup — 4.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="48" customHeight="1">
       <c r="A120" s="34" t="n"/>
       <c r="B120" s="27" t="inlineStr">
         <is>
@@ -10127,8 +10564,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="121">
+      <c r="F120" s="37" t="inlineStr">
+        <is>
+          <t>campaignId查询AdgroupTotal 单campaign汇总
+campaignId加adgroupId查询AdgroupTotal 指定adgroup汇总
+广告类型加状态过滤查询AdgroupTotal 账户级汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="48" customHeight="1">
       <c r="A121" s="34" t="n"/>
       <c r="B121" s="23" t="inlineStr">
         <is>
@@ -10150,8 +10594,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="122">
+      <c r="F121" s="37" t="inlineStr">
+        <is>
+          <t>查询SP手动定位(PAT)广告系列的广告组类型
+查询SP通用广告系列的广告组类型
+查询SD广告系列的广告组类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="80" customHeight="1">
       <c r="A122" s="34" t="n"/>
       <c r="B122" s="27" t="inlineStr">
         <is>
@@ -10171,6 +10622,15 @@
       <c r="E122" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F122" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 同Campaign内复制并保持enabled
+场景2: 同Campaign内复制并保持paused
+单个SP广告系列查询广告组列表 — 92.7%
+单个SD广告系列查询广告组列表 — 92.7%
+批量多campaignId查询广告组列表 — 7.3%</t>
         </is>
       </c>
     </row>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'模块汇总'!$A$1:$D$123</definedName>
@@ -1898,6 +1898,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F43" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="inlineStr">
+        <is>
+          <t>100% (3/3)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="34" t="n"/>
@@ -13446,7 +13459,7 @@
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="16" customHeight="1">
       <c r="A235" s="34" t="n"/>
       <c r="B235" s="24" t="inlineStr">
         <is>
@@ -13468,8 +13481,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="236">
+      <c r="F235" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 按ProfileId获取品牌列表 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="16" customHeight="1">
       <c r="A236" s="34" t="n"/>
       <c r="B236" s="27" t="inlineStr">
         <is>
@@ -13491,8 +13509,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="237">
+      <c r="F236" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 按国家码US获取品类列表 — 97.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="16" customHeight="1">
       <c r="A237" s="34" t="n"/>
       <c r="B237" s="23" t="inlineStr">
         <is>
@@ -13512,6 +13535,11 @@
       <c r="E237" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F237" s="37" t="inlineStr">
+        <is>
+          <t>场景1: 获取DSP广告品类首页列表 — 100.0%</t>
         </is>
       </c>
     </row>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4740" yWindow="1480" windowWidth="41400" windowHeight="22860" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'模块汇总'!$A$1:$H$126</definedName>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -89,8 +89,12 @@
       <color rgb="FF808080"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -152,8 +156,13 @@
         <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0504D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -269,11 +278,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -384,6 +407,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2545,6 +2577,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F62" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" s="29" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="H62" s="29" t="inlineStr">
+        <is>
+          <t>50% (3/6)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="38" t="n"/>
@@ -8081,7 +8126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1446"/>
+  <dimension ref="A1:G1446"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8090,6 +8135,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="72" customWidth="1" min="5" max="5"/>
     <col width="14.1640625" customWidth="1" min="6" max="9"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8121,6 +8167,11 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>场景覆盖</t>
+        </is>
+      </c>
+      <c r="G1" s="42" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -28474,7 +28525,7 @@
         </is>
       </c>
     </row>
-    <row r="831">
+    <row r="831" ht="90" customHeight="1">
       <c r="A831" s="38" t="n"/>
       <c r="B831" s="24" t="inlineStr">
         <is>
@@ -28496,8 +28547,18 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="832">
+      <c r="F831" s="41" t="inlineStr">
+        <is>
+          <t>导出Campaign报表(单日Dim=date)</t>
+        </is>
+      </c>
+      <c r="G831" s="43" t="inlineStr">
+        <is>
+          <t>疑似废弃·零流量：本路由90天0次调用；同DTO的 /api/Campaign/v3/DownloadCampaignPageData 90天37357次(日均~400)。Swagger未标deprecated，但功能已并入Campaign路由，此为遗留/别名路由。测试513为超管profile数据量过大触发后端SQL expression limit/执行超时，非接口缺陷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="832" ht="16" customHeight="1">
       <c r="A832" s="38" t="n"/>
       <c r="B832" s="27" t="inlineStr">
         <is>
@@ -28517,6 +28578,11 @@
       <c r="E832" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F832" s="41" t="inlineStr">
+        <is>
+          <t>下载已完成任务文件(链式取id)</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28609,7 @@
         </is>
       </c>
     </row>
-    <row r="834">
+    <row r="834" ht="16" customHeight="1">
       <c r="A834" s="38" t="n"/>
       <c r="B834" s="27" t="inlineStr">
         <is>
@@ -28563,6 +28629,11 @@
       <c r="E834" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F834" s="41" t="inlineStr">
+        <is>
+          <t>下载中心任务列表分页</t>
         </is>
       </c>
     </row>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -153,7 +153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -269,11 +269,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -384,6 +398,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2857,6 +2874,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F75" s="29" t="n">
+        <v>68</v>
+      </c>
+      <c r="G75" s="29" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H75" s="29" t="inlineStr">
+        <is>
+          <t>100% (63/63)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="38" t="n"/>
@@ -3452,6 +3482,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F99" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G99" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H99" s="29" t="inlineStr">
+        <is>
+          <t>100% (13/13)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="38" t="n"/>
@@ -3515,6 +3558,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F102" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="G102" s="29" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="H102" s="29" t="inlineStr">
+        <is>
+          <t>100% (10/10)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="38" t="n"/>
@@ -3654,6 +3710,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F108" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="G108" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H108" s="29" t="inlineStr">
+        <is>
+          <t>100% (11/11)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="38" t="n"/>
@@ -3717,6 +3786,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F111" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G111" s="29" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="H111" s="29" t="inlineStr">
+        <is>
+          <t>100% (7/7)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="38" t="n"/>
@@ -3780,6 +3862,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F114" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G114" s="29" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="H114" s="29" t="inlineStr">
+        <is>
+          <t>100% (10/10)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="38" t="n"/>
@@ -3919,6 +4014,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F120" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="G120" s="29" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="H120" s="29" t="inlineStr">
+        <is>
+          <t>100% (19/19)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="38" t="n"/>
@@ -3980,6 +4088,19 @@
       <c r="E123" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F123" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G123" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H123" s="29" t="inlineStr">
+        <is>
+          <t>100% (15/15)</t>
         </is>
       </c>
     </row>
@@ -30759,7 +30880,7 @@
         </is>
       </c>
     </row>
-    <row r="926">
+    <row r="926" ht="16" customHeight="1">
       <c r="A926" s="38" t="n"/>
       <c r="B926" s="26" t="inlineStr">
         <is>
@@ -30781,8 +30902,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="927">
+      <c r="F926" s="41" t="inlineStr">
+        <is>
+          <t>创建关键词(旧版,含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="927" ht="16" customHeight="1">
       <c r="A927" s="38" t="n"/>
       <c r="B927" s="23" t="inlineStr">
         <is>
@@ -30804,8 +30930,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="928">
+      <c r="F927" s="41" t="inlineStr">
+        <is>
+          <t>跨Profile批量创建关键词(含后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="928" ht="80" customHeight="1">
       <c r="A928" s="38" t="n"/>
       <c r="B928" s="27" t="inlineStr">
         <is>
@@ -30827,8 +30958,17 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="929">
+      <c r="F928" s="41" t="inlineStr">
+        <is>
+          <t>创建关键词(含后置归档,可重复)
+更新单个关键词出价(含前置创建/后置归档,可重复)
+关键词状态流转(含前置创建/后置归档,可重复)
+应用建议出价(含前置创建/后置归档,可重复)
+批量精确调价(含前置创建/后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="929" ht="16" customHeight="1">
       <c r="A929" s="38" t="n"/>
       <c r="B929" s="23" t="inlineStr">
         <is>
@@ -30850,8 +30990,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="930">
+      <c r="F929" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 23.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="930" ht="16" customHeight="1">
       <c r="A930" s="38" t="n"/>
       <c r="B930" s="27" t="inlineStr">
         <is>
@@ -30873,8 +31018,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="931">
+      <c r="F930" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 28.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="931" ht="16" customHeight="1">
       <c r="A931" s="38" t="n"/>
       <c r="B931" s="23" t="inlineStr">
         <is>
@@ -30896,8 +31046,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="932">
+      <c r="F931" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 6.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="932" ht="16" customHeight="1">
       <c r="A932" s="38" t="n"/>
       <c r="B932" s="27" t="inlineStr">
         <is>
@@ -30919,8 +31074,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="933">
+      <c r="F932" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 16.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="933" ht="16" customHeight="1">
       <c r="A933" s="38" t="n"/>
       <c r="B933" s="23" t="inlineStr">
         <is>
@@ -30942,8 +31102,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="934">
+      <c r="F933" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 28.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="934" ht="16" customHeight="1">
       <c r="A934" s="38" t="n"/>
       <c r="B934" s="27" t="inlineStr">
         <is>
@@ -30965,8 +31130,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="935">
+      <c r="F934" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 36.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="935" ht="16" customHeight="1">
       <c r="A935" s="38" t="n"/>
       <c r="B935" s="23" t="inlineStr">
         <is>
@@ -30986,6 +31156,11 @@
       <c r="E935" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F935" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 40.4%</t>
         </is>
       </c>
     </row>
@@ -31012,7 +31187,7 @@
         </is>
       </c>
     </row>
-    <row r="937">
+    <row r="937" ht="16" customHeight="1">
       <c r="A937" s="38" t="n"/>
       <c r="B937" s="23" t="inlineStr">
         <is>
@@ -31034,8 +31209,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="938">
+      <c r="F937" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标 — 44.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="938" ht="16" customHeight="1">
       <c r="A938" s="38" t="n"/>
       <c r="B938" s="27" t="inlineStr">
         <is>
@@ -31057,8 +31237,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="939">
+      <c r="F938" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="939" ht="16" customHeight="1">
       <c r="A939" s="38" t="n"/>
       <c r="B939" s="23" t="inlineStr">
         <is>
@@ -31080,8 +31265,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="940">
+      <c r="F939" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="940" ht="16" customHeight="1">
       <c r="A940" s="38" t="n"/>
       <c r="B940" s="27" t="inlineStr">
         <is>
@@ -31103,8 +31293,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="941">
+      <c r="F940" s="41" t="inlineStr">
+        <is>
+          <t>按筛选条件批量操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="941" ht="16" customHeight="1">
       <c r="A941" s="38" t="n"/>
       <c r="B941" s="23" t="inlineStr">
         <is>
@@ -31126,8 +31321,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="942">
+      <c r="F941" s="41" t="inlineStr">
+        <is>
+          <t>按筛选条件批量操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="942" ht="16" customHeight="1">
       <c r="A942" s="38" t="n"/>
       <c r="B942" s="27" t="inlineStr">
         <is>
@@ -31149,8 +31349,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="943">
+      <c r="F942" s="41" t="inlineStr">
+        <is>
+          <t>按筛选条件批量操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="943" ht="16" customHeight="1">
       <c r="A943" s="38" t="n"/>
       <c r="B943" s="23" t="inlineStr">
         <is>
@@ -31172,8 +31377,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="944">
+      <c r="F943" s="41" t="inlineStr">
+        <is>
+          <t>按筛选条件批量操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="944" ht="16" customHeight="1">
       <c r="A944" s="38" t="n"/>
       <c r="B944" s="27" t="inlineStr">
         <is>
@@ -31195,8 +31405,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="945">
+      <c r="F944" s="41" t="inlineStr">
+        <is>
+          <t>按筛选条件批量操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="945" ht="16" customHeight="1">
       <c r="A945" s="38" t="n"/>
       <c r="B945" s="23" t="inlineStr">
         <is>
@@ -31216,6 +31431,11 @@
       <c r="E945" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F945" s="41" t="inlineStr">
+        <is>
+          <t>按筛选条件批量操作</t>
         </is>
       </c>
     </row>
@@ -31242,7 +31462,7 @@
         </is>
       </c>
     </row>
-    <row r="947">
+    <row r="947" ht="16" customHeight="1">
       <c r="A947" s="38" t="n"/>
       <c r="B947" s="23" t="inlineStr">
         <is>
@@ -31264,8 +31484,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="948">
+      <c r="F947" s="41" t="inlineStr">
+        <is>
+          <t>下载节日关键词数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="948" ht="16" customHeight="1">
       <c r="A948" s="38" t="n"/>
       <c r="B948" s="27" t="inlineStr">
         <is>
@@ -31287,8 +31512,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="949">
+      <c r="F948" s="41" t="inlineStr">
+        <is>
+          <t>检查已存在/新增关键词 — 5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="949" ht="16" customHeight="1">
       <c r="A949" s="38" t="n"/>
       <c r="B949" s="23" t="inlineStr">
         <is>
@@ -31310,8 +31540,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="950">
+      <c r="F949" s="41" t="inlineStr">
+        <is>
+          <t>按campaignId查AdGroup列表 — 22.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="950" ht="16" customHeight="1">
       <c r="A950" s="38" t="n"/>
       <c r="B950" s="27" t="inlineStr">
         <is>
@@ -31333,8 +31568,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="951">
+      <c r="F950" s="41" t="inlineStr">
+        <is>
+          <t>按单campaign查关键词AdGroup映射 — 91.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="951" ht="16" customHeight="1">
       <c r="A951" s="38" t="n"/>
       <c r="B951" s="23" t="inlineStr">
         <is>
@@ -31356,8 +31596,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="952">
+      <c r="F951" s="41" t="inlineStr">
+        <is>
+          <t>查关键词出价景观数据 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="952" ht="16" customHeight="1">
       <c r="A952" s="38" t="n"/>
       <c r="B952" s="27" t="inlineStr">
         <is>
@@ -31379,8 +31624,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="953">
+      <c r="F952" s="41" t="inlineStr">
+        <is>
+          <t>按tagIds查campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="953" ht="32" customHeight="1">
       <c r="A953" s="38" t="n"/>
       <c r="B953" s="23" t="inlineStr">
         <is>
@@ -31402,8 +31652,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="954">
+      <c r="F953" s="41" t="inlineStr">
+        <is>
+          <t>按TargetTypes=Keyword过滤campaign — 41.6%
+不带类型过滤查全部campaign — 34.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="954" ht="16" customHeight="1">
       <c r="A954" s="38" t="n"/>
       <c r="B954" s="27" t="inlineStr">
         <is>
@@ -31425,8 +31681,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="955">
+      <c r="F954" s="41" t="inlineStr">
+        <is>
+          <t>按profileId查campaign战术(旧版)</t>
+        </is>
+      </c>
+    </row>
+    <row r="955" ht="32" customHeight="1">
       <c r="A955" s="38" t="n"/>
       <c r="B955" s="23" t="inlineStr">
         <is>
@@ -31448,8 +31709,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="956">
+      <c r="F955" s="41" t="inlineStr">
+        <is>
+          <t>不带state过滤查campaign战术列表 — 61.4%
+按states=enabled过滤 — 36.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="956" ht="16" customHeight="1">
       <c r="A956" s="38" t="n"/>
       <c r="B956" s="27" t="inlineStr">
         <is>
@@ -31471,8 +31738,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="957">
+      <c r="F956" s="41" t="inlineStr">
+        <is>
+          <t>按Tactics查campaign(旧版)</t>
+        </is>
+      </c>
+    </row>
+    <row r="957" ht="16" customHeight="1">
       <c r="A957" s="38" t="n"/>
       <c r="B957" s="23" t="inlineStr">
         <is>
@@ -31494,8 +31766,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="958">
+      <c r="F957" s="41" t="inlineStr">
+        <is>
+          <t>按Tactics=T00020查campaign — 5.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="958" ht="16" customHeight="1">
       <c r="A958" s="38" t="n"/>
       <c r="B958" s="27" t="inlineStr">
         <is>
@@ -31517,8 +31794,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="959">
+      <c r="F958" s="41" t="inlineStr">
+        <is>
+          <t>Fead版关键词报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="959" ht="16" customHeight="1">
       <c r="A959" s="38" t="n"/>
       <c r="B959" s="23" t="inlineStr">
         <is>
@@ -31540,8 +31822,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="960">
+      <c r="F959" s="41" t="inlineStr">
+        <is>
+          <t>Fead版关键词汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="960" ht="16" customHeight="1">
       <c r="A960" s="38" t="n"/>
       <c r="B960" s="27" t="inlineStr">
         <is>
@@ -31563,8 +31850,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="961">
+      <c r="F960" s="41" t="inlineStr">
+        <is>
+          <t>按keywords数组批量查详情 — 91.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="961" ht="16" customHeight="1">
       <c r="A961" s="38" t="n"/>
       <c r="B961" s="23" t="inlineStr">
         <is>
@@ -31586,8 +31878,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="962">
+      <c r="F961" s="41" t="inlineStr">
+        <is>
+          <t>按关键词文本查所属campaign数 — 38.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="962" ht="16" customHeight="1">
       <c r="A962" s="38" t="n"/>
       <c r="B962" s="27" t="inlineStr">
         <is>
@@ -31609,8 +31906,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="963">
+      <c r="F962" s="41" t="inlineStr">
+        <is>
+          <t>关键词看板</t>
+        </is>
+      </c>
+    </row>
+    <row r="963" ht="16" customHeight="1">
       <c r="A963" s="38" t="n"/>
       <c r="B963" s="23" t="inlineStr">
         <is>
@@ -31632,8 +31934,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="964">
+      <c r="F963" s="41" t="inlineStr">
+        <is>
+          <t>按campaign查关键词列表 — 97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="964" ht="16" customHeight="1">
       <c r="A964" s="38" t="n"/>
       <c r="B964" s="27" t="inlineStr">
         <is>
@@ -31655,8 +31962,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="965">
+      <c r="F964" s="41" t="inlineStr">
+        <is>
+          <t>按ASIN查关键词分组 — 57.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="965" ht="16" customHeight="1">
       <c r="A965" s="38" t="n"/>
       <c r="B965" s="23" t="inlineStr">
         <is>
@@ -31678,8 +31990,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="966">
+      <c r="F965" s="41" t="inlineStr">
+        <is>
+          <t>关键词表现看板</t>
+        </is>
+      </c>
+    </row>
+    <row r="966" ht="16" customHeight="1">
       <c r="A966" s="38" t="n"/>
       <c r="B966" s="27" t="inlineStr">
         <is>
@@ -31701,8 +32018,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="967">
+      <c r="F966" s="41" t="inlineStr">
+        <is>
+          <t>关键词占比看板</t>
+        </is>
+      </c>
+    </row>
+    <row r="967" ht="16" customHeight="1">
       <c r="A967" s="38" t="n"/>
       <c r="B967" s="23" t="inlineStr">
         <is>
@@ -31724,8 +32046,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="968">
+      <c r="F967" s="41" t="inlineStr">
+        <is>
+          <t>查关键词标签(带isCheckEdit) — 88.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="968" ht="16" customHeight="1">
       <c r="A968" s="38" t="n"/>
       <c r="B968" s="27" t="inlineStr">
         <is>
@@ -31747,8 +32074,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="969">
+      <c r="F968" s="41" t="inlineStr">
+        <is>
+          <t>关键词标签表现 — 4.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="969" ht="16" customHeight="1">
       <c r="A969" s="38" t="n"/>
       <c r="B969" s="23" t="inlineStr">
         <is>
@@ -31770,8 +32102,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="970">
+      <c r="F969" s="41" t="inlineStr">
+        <is>
+          <t>按关键词文本批量查标签 — 65.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="970" ht="16" customHeight="1">
       <c r="A970" s="38" t="n"/>
       <c r="B970" s="27" t="inlineStr">
         <is>
@@ -31793,8 +32130,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="971">
+      <c r="F970" s="41" t="inlineStr">
+        <is>
+          <t>按关键词文本查标签层级 — 65.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="971" ht="16" customHeight="1">
       <c r="A971" s="38" t="n"/>
       <c r="B971" s="23" t="inlineStr">
         <is>
@@ -31816,8 +32158,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="972">
+      <c r="F971" s="41" t="inlineStr">
+        <is>
+          <t>关键词文本占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="972" ht="16" customHeight="1">
       <c r="A972" s="38" t="n"/>
       <c r="B972" s="27" t="inlineStr">
         <is>
@@ -31839,8 +32186,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="973">
+      <c r="F972" s="41" t="inlineStr">
+        <is>
+          <t>长尾词报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="973" ht="16" customHeight="1">
       <c r="A973" s="38" t="n"/>
       <c r="B973" s="23" t="inlineStr">
         <is>
@@ -31862,8 +32214,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="974">
+      <c r="F973" s="41" t="inlineStr">
+        <is>
+          <t>长尾词按匹配类型分组报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="974" ht="32" customHeight="1">
       <c r="A974" s="38" t="n"/>
       <c r="B974" s="27" t="inlineStr">
         <is>
@@ -31885,8 +32242,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="975">
+      <c r="F974" s="41" t="inlineStr">
+        <is>
+          <t>默认聚合趋势图(无过滤) — 9.2%
+按keywordIds过滤趋势图 — 2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="975" ht="16" customHeight="1">
       <c r="A975" s="38" t="n"/>
       <c r="B975" s="23" t="inlineStr">
         <is>
@@ -31908,8 +32271,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="976">
+      <c r="F975" s="41" t="inlineStr">
+        <is>
+          <t>单关键词详情趋势图 — 7.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="976" ht="16" customHeight="1">
       <c r="A976" s="38" t="n"/>
       <c r="B976" s="27" t="inlineStr">
         <is>
@@ -31931,8 +32299,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="977">
+      <c r="F976" s="41" t="inlineStr">
+        <is>
+          <t>全选关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="977" ht="32" customHeight="1">
       <c r="A977" s="38" t="n"/>
       <c r="B977" s="23" t="inlineStr">
         <is>
@@ -31954,8 +32327,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="978">
+      <c r="F977" s="41" t="inlineStr">
+        <is>
+          <t>默认聚合报表(无关键词过滤) — 20.8%
+按keywordText过滤报表 — 20.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="978" ht="16" customHeight="1">
       <c r="A978" s="38" t="n"/>
       <c r="B978" s="27" t="inlineStr">
         <is>
@@ -31977,8 +32356,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="979">
+      <c r="F978" s="41" t="inlineStr">
+        <is>
+          <t>按keywordText过滤汇总 — 8.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="979" ht="16" customHeight="1">
       <c r="A979" s="38" t="n"/>
       <c r="B979" s="23" t="inlineStr">
         <is>
@@ -32000,8 +32384,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="980">
+      <c r="F979" s="41" t="inlineStr">
+        <is>
+          <t>按关键词文本查最高CPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="980" ht="16" customHeight="1">
       <c r="A980" s="38" t="n"/>
       <c r="B980" s="27" t="inlineStr">
         <is>
@@ -32023,8 +32412,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="981">
+      <c r="F980" s="41" t="inlineStr">
+        <is>
+          <t>创建/复制关键词或投放目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="981" ht="16" customHeight="1">
       <c r="A981" s="38" t="n"/>
       <c r="B981" s="23" t="inlineStr">
         <is>
@@ -32046,8 +32440,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="982">
+      <c r="F981" s="41" t="inlineStr">
+        <is>
+          <t>按小时查平均值 — 50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="982" ht="16" customHeight="1">
       <c r="A982" s="38" t="n"/>
       <c r="B982" s="27" t="inlineStr">
         <is>
@@ -32069,8 +32468,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="983">
+      <c r="F982" s="41" t="inlineStr">
+        <is>
+          <t>按关键词文本批量打标签(含后置清理,可重复) — 88.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="983" ht="16" customHeight="1">
       <c r="A983" s="38" t="n"/>
       <c r="B983" s="23" t="inlineStr">
         <is>
@@ -32090,6 +32494,11 @@
       <c r="E983" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F983" s="41" t="inlineStr">
+        <is>
+          <t>按关键词数组批量搜索</t>
         </is>
       </c>
     </row>
@@ -32116,7 +32525,7 @@
         </is>
       </c>
     </row>
-    <row r="985">
+    <row r="985" ht="16" customHeight="1">
       <c r="A985" s="38" t="n"/>
       <c r="B985" s="23" t="inlineStr">
         <is>
@@ -32138,8 +32547,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="986">
+      <c r="F985" s="41" t="inlineStr">
+        <is>
+          <t>应用建议出价</t>
+        </is>
+      </c>
+    </row>
+    <row r="986" ht="16" customHeight="1">
       <c r="A986" s="38" t="n"/>
       <c r="B986" s="27" t="inlineStr">
         <is>
@@ -32161,8 +32575,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="987">
+      <c r="F986" s="41" t="inlineStr">
+        <is>
+          <t>应用建议出价</t>
+        </is>
+      </c>
+    </row>
+    <row r="987" ht="112" customHeight="1">
       <c r="A987" s="38" t="n"/>
       <c r="B987" s="23" t="inlineStr">
         <is>
@@ -32184,8 +32603,19 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="988">
+      <c r="F987" s="41" t="inlineStr">
+        <is>
+          <t>创建关键词(含后置归档,可重复)
+创建关键词(旧版,含后置归档,可重复)
+跨Profile批量创建关键词(含后置归档,可重复)
+更新单个关键词出价(含前置创建/后置归档,可重复)
+关键词状态流转(含前置创建/后置归档,可重复)
+应用建议出价(含前置创建/后置归档,可重复)
+批量精确调价(含前置创建/后置归档,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="988" ht="16" customHeight="1">
       <c r="A988" s="38" t="n"/>
       <c r="B988" s="27" t="inlineStr">
         <is>
@@ -32205,6 +32635,11 @@
       <c r="E988" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F988" s="41" t="inlineStr">
+        <is>
+          <t>应用建议出价</t>
         </is>
       </c>
     </row>
@@ -36613,7 +37048,7 @@
         </is>
       </c>
     </row>
-    <row r="1175">
+    <row r="1175" ht="16" customHeight="1">
       <c r="A1175" s="38" t="n"/>
       <c r="B1175" s="24" t="inlineStr">
         <is>
@@ -36635,8 +37070,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1176">
+      <c r="F1175" s="41" t="inlineStr">
+        <is>
+          <t>获取服务器时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176" ht="16" customHeight="1">
       <c r="A1176" s="38" t="n"/>
       <c r="B1176" s="27" t="inlineStr">
         <is>
@@ -36658,8 +37098,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1177">
+      <c r="F1176" s="41" t="inlineStr">
+        <is>
+          <t>仅按Asin查询SQP数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177" ht="16" customHeight="1">
       <c r="A1177" s="38" t="n"/>
       <c r="B1177" s="23" t="inlineStr">
         <is>
@@ -36681,8 +37126,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1178">
+      <c r="F1177" s="41" t="inlineStr">
+        <is>
+          <t>仅按Query查询SQP数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178" ht="16" customHeight="1">
       <c r="A1178" s="38" t="n"/>
       <c r="B1178" s="27" t="inlineStr">
         <is>
@@ -36704,8 +37154,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1179">
+      <c r="F1178" s="41" t="inlineStr">
+        <is>
+          <t>按Query查询详情图表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179" ht="16" customHeight="1">
       <c r="A1179" s="38" t="n"/>
       <c r="B1179" s="23" t="inlineStr">
         <is>
@@ -36727,8 +37182,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1180">
+      <c r="F1179" s="41" t="inlineStr">
+        <is>
+          <t>按字段查询趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180" ht="16" customHeight="1">
       <c r="A1180" s="38" t="n"/>
       <c r="B1180" s="27" t="inlineStr">
         <is>
@@ -36750,8 +37210,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1181">
+      <c r="F1180" s="41" t="inlineStr">
+        <is>
+          <t>查询详情分页列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181" ht="16" customHeight="1">
       <c r="A1181" s="38" t="n"/>
       <c r="B1181" s="23" t="inlineStr">
         <is>
@@ -36773,8 +37238,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1182">
+      <c r="F1181" s="41" t="inlineStr">
+        <is>
+          <t>查询详情饼图</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182" ht="16" customHeight="1">
       <c r="A1182" s="38" t="n"/>
       <c r="B1182" s="27" t="inlineStr">
         <is>
@@ -36796,8 +37266,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1183">
+      <c r="F1182" s="41" t="inlineStr">
+        <is>
+          <t>查询详情汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183" ht="16" customHeight="1">
       <c r="A1183" s="38" t="n"/>
       <c r="B1183" s="23" t="inlineStr">
         <is>
@@ -36819,8 +37294,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1184">
+      <c r="F1183" s="41" t="inlineStr">
+        <is>
+          <t>查询详情趋势列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184" ht="16" customHeight="1">
       <c r="A1184" s="38" t="n"/>
       <c r="B1184" s="27" t="inlineStr">
         <is>
@@ -36842,8 +37322,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1185">
+      <c r="F1184" s="41" t="inlineStr">
+        <is>
+          <t>查询详情趋势标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185" ht="32" customHeight="1">
       <c r="A1185" s="38" t="n"/>
       <c r="B1185" s="23" t="inlineStr">
         <is>
@@ -36865,8 +37350,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1186">
+      <c r="F1185" s="41" t="inlineStr">
+        <is>
+          <t>按SearchQuery文本搜索 — 1.4%
+按KeywordTagIds标签过滤 — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186" ht="16" customHeight="1">
       <c r="A1186" s="38" t="n"/>
       <c r="B1186" s="27" t="inlineStr">
         <is>
@@ -36888,8 +37379,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1187">
+      <c r="F1186" s="41" t="inlineStr">
+        <is>
+          <t>按SearchQuery文本搜索汇总 — 1.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187" ht="16" customHeight="1">
       <c r="A1187" s="38" t="n"/>
       <c r="B1187" s="23" t="inlineStr">
         <is>
@@ -36909,6 +37405,11 @@
       <c r="E1187" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1187" s="41" t="inlineStr">
+        <is>
+          <t>标记/取消标记关注ASIN(含后置还原,可重复)</t>
         </is>
       </c>
     </row>
@@ -36981,7 +37482,7 @@
         </is>
       </c>
     </row>
-    <row r="1191">
+    <row r="1191" ht="16" customHeight="1">
       <c r="A1191" s="38" t="n"/>
       <c r="B1191" s="24" t="inlineStr">
         <is>
@@ -37003,8 +37504,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1192">
+      <c r="F1191" s="41" t="inlineStr">
+        <is>
+          <t>按条件批量调整关键词出价</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192" ht="16" customHeight="1">
       <c r="A1192" s="38" t="n"/>
       <c r="B1192" s="27" t="inlineStr">
         <is>
@@ -37026,8 +37532,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1193">
+      <c r="F1192" s="41" t="inlineStr">
+        <is>
+          <t>批量添加关键词标签(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193" ht="32" customHeight="1">
       <c r="A1193" s="38" t="n"/>
       <c r="B1193" s="23" t="inlineStr">
         <is>
@@ -37049,8 +37560,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1194">
+      <c r="F1193" s="41" t="inlineStr">
+        <is>
+          <t>默认聚合图表(无文本过滤) — 7.0%
+按query文本过滤图表 — 9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194" ht="32" customHeight="1">
       <c r="A1194" s="38" t="n"/>
       <c r="B1194" s="27" t="inlineStr">
         <is>
@@ -37072,8 +37589,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1195">
+      <c r="F1194" s="41" t="inlineStr">
+        <is>
+          <t>默认聚合报表(无文本过滤) — 2.4%
+按query文本过滤报表 — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195" ht="16" customHeight="1">
       <c r="A1195" s="38" t="n"/>
       <c r="B1195" s="23" t="inlineStr">
         <is>
@@ -37095,8 +37618,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1196">
+      <c r="F1195" s="41" t="inlineStr">
+        <is>
+          <t>全选查询词</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196" ht="32" customHeight="1">
       <c r="A1196" s="38" t="n"/>
       <c r="B1196" s="27" t="inlineStr">
         <is>
@@ -37118,8 +37646,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1197">
+      <c r="F1196" s="41" t="inlineStr">
+        <is>
+          <t>默认聚合汇总(无文本过滤) — 3.4%
+按query文本过滤汇总 — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197" ht="16" customHeight="1">
       <c r="A1197" s="38" t="n"/>
       <c r="B1197" s="23" t="inlineStr">
         <is>
@@ -37141,8 +37675,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1198">
+      <c r="F1197" s="41" t="inlineStr">
+        <is>
+          <t>PAT查询词趋势图</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198" ht="16" customHeight="1">
       <c r="A1198" s="38" t="n"/>
       <c r="B1198" s="27" t="inlineStr">
         <is>
@@ -37164,8 +37703,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1199">
+      <c r="F1198" s="41" t="inlineStr">
+        <is>
+          <t>按Metric条件过滤PAT报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199" ht="16" customHeight="1">
       <c r="A1199" s="38" t="n"/>
       <c r="B1199" s="23" t="inlineStr">
         <is>
@@ -37187,8 +37731,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1200">
+      <c r="F1199" s="41" t="inlineStr">
+        <is>
+          <t>PAT全选查询词</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200" ht="16" customHeight="1">
       <c r="A1200" s="38" t="n"/>
       <c r="B1200" s="27" t="inlineStr">
         <is>
@@ -37208,6 +37757,11 @@
       <c r="E1200" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1200" s="41" t="inlineStr">
+        <is>
+          <t>PAT查询词汇总</t>
         </is>
       </c>
     </row>
@@ -38026,7 +38580,7 @@
         </is>
       </c>
     </row>
-    <row r="1236">
+    <row r="1236" ht="16" customHeight="1">
       <c r="A1236" s="38" t="n"/>
       <c r="B1236" s="26" t="inlineStr">
         <is>
@@ -38048,8 +38602,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1237">
+      <c r="F1236" s="41" t="inlineStr">
+        <is>
+          <t>创建品牌广告迁移任务 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237" ht="16" customHeight="1">
       <c r="A1237" s="38" t="n"/>
       <c r="B1237" s="23" t="inlineStr">
         <is>
@@ -38071,8 +38630,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1238">
+      <c r="F1237" s="41" t="inlineStr">
+        <is>
+          <t>查可迁移Campaign概览 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238" ht="16" customHeight="1">
       <c r="A1238" s="38" t="n"/>
       <c r="B1238" s="27" t="inlineStr">
         <is>
@@ -38094,8 +38658,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1239">
+      <c r="F1238" s="41" t="inlineStr">
+        <is>
+          <t>按campaignId数组查迁移标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239" ht="16" customHeight="1">
       <c r="A1239" s="38" t="n"/>
       <c r="B1239" s="23" t="inlineStr">
         <is>
@@ -38117,8 +38686,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1240">
+      <c r="F1239" s="41" t="inlineStr">
+        <is>
+          <t>按profile+campaign查迁移物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240" ht="16" customHeight="1">
       <c r="A1240" s="38" t="n"/>
       <c r="B1240" s="27" t="inlineStr">
         <is>
@@ -38140,8 +38714,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1241">
+      <c r="F1240" s="41" t="inlineStr">
+        <is>
+          <t>查迁移相关Campaign计数 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241" ht="32" customHeight="1">
       <c r="A1241" s="38" t="n"/>
       <c r="B1241" s="23" t="inlineStr">
         <is>
@@ -38163,8 +38742,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1242">
+      <c r="F1241" s="41" t="inlineStr">
+        <is>
+          <t>查可迁移Campaign列表(Migrable)
+查已迁移Campaign列表(Migrated) — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242" ht="32" customHeight="1">
       <c r="A1242" s="38" t="n"/>
       <c r="B1242" s="27" t="inlineStr">
         <is>
@@ -38186,8 +38771,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1243">
+      <c r="F1242" s="41" t="inlineStr">
+        <is>
+          <t>按PrfileIds查用户迁移状态 — 98.6%
+全小写字段名+空列表查询 — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243" ht="16" customHeight="1">
       <c r="A1243" s="38" t="n"/>
       <c r="B1243" s="23" t="inlineStr">
         <is>
@@ -38209,8 +38800,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1244">
+      <c r="F1243" s="41" t="inlineStr">
+        <is>
+          <t>执行迁移Job同步</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244" ht="16" customHeight="1">
       <c r="A1244" s="38" t="n"/>
       <c r="B1244" s="27" t="inlineStr">
         <is>
@@ -38232,8 +38828,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1245">
+      <c r="F1244" s="41" t="inlineStr">
+        <is>
+          <t>撤销迁移Campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245" ht="16" customHeight="1">
       <c r="A1245" s="38" t="n"/>
       <c r="B1245" s="23" t="inlineStr">
         <is>
@@ -38255,8 +38856,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1246">
+      <c r="F1245" s="41" t="inlineStr">
+        <is>
+          <t>手动设置迁移Campaign映射</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246" ht="16" customHeight="1">
       <c r="A1246" s="38" t="n"/>
       <c r="B1246" s="27" t="inlineStr">
         <is>
@@ -38276,6 +38882,11 @@
       <c r="E1246" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1246" s="41" t="inlineStr">
+        <is>
+          <t>更新自动化迁移状态</t>
         </is>
       </c>
     </row>
@@ -38716,7 +39327,7 @@
         </is>
       </c>
     </row>
-    <row r="1266">
+    <row r="1266" ht="16" customHeight="1">
       <c r="A1266" s="38" t="n"/>
       <c r="B1266" s="26" t="inlineStr">
         <is>
@@ -38738,8 +39349,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1267">
+      <c r="F1266" s="41" t="inlineStr">
+        <is>
+          <t>复制SP Campaign到同profile(含后置归档,可重复) — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267" ht="16" customHeight="1">
       <c r="A1267" s="38" t="n"/>
       <c r="B1267" s="23" t="inlineStr">
         <is>
@@ -38761,8 +39377,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1268">
+      <c r="F1267" s="41" t="inlineStr">
+        <is>
+          <t>复制SP Campaign并指定AdGroup ASIN(含后置归档,可重复) — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268" ht="16" customHeight="1">
       <c r="A1268" s="38" t="n"/>
       <c r="B1268" s="27" t="inlineStr">
         <is>
@@ -38784,8 +39405,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1269">
+      <c r="F1268" s="41" t="inlineStr">
+        <is>
+          <t>在已有AdGroup下创建Ad(含后置归档,可重复) — 81.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269" ht="16" customHeight="1">
       <c r="A1269" s="38" t="n"/>
       <c r="B1269" s="23" t="inlineStr">
         <is>
@@ -38807,8 +39433,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1270">
+      <c r="F1269" s="41" t="inlineStr">
+        <is>
+          <t>在已有Campaign下创建AdGroup(含后置归档,可重复) — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270" ht="16" customHeight="1">
       <c r="A1270" s="38" t="n"/>
       <c r="B1270" s="27" t="inlineStr">
         <is>
@@ -38830,8 +39461,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1271">
+      <c r="F1270" s="41" t="inlineStr">
+        <is>
+          <t>创建SP手动投放Campaign(含后置归档,可重复) — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271" ht="16" customHeight="1">
       <c r="A1271" s="38" t="n"/>
       <c r="B1271" s="23" t="inlineStr">
         <is>
@@ -38853,8 +39489,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1272">
+      <c r="F1271" s="41" t="inlineStr">
+        <is>
+          <t>更新广告视频素材 — 53.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272" ht="16" customHeight="1">
       <c r="A1272" s="38" t="n"/>
       <c r="B1272" s="27" t="inlineStr">
         <is>
@@ -38874,6 +39515,11 @@
       <c r="E1272" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1272" s="41" t="inlineStr">
+        <is>
+          <t>批量调整Campaign出价策略 — 76.8%</t>
         </is>
       </c>
     </row>
@@ -39061,7 +39707,7 @@
         </is>
       </c>
     </row>
-    <row r="1281">
+    <row r="1281" ht="16" customHeight="1">
       <c r="A1281" s="38" t="n"/>
       <c r="B1281" s="24" t="inlineStr">
         <is>
@@ -39083,8 +39729,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1282">
+      <c r="F1281" s="41" t="inlineStr">
+        <is>
+          <t>按日期范围同步Campaign数据 — 1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282" ht="16" customHeight="1">
       <c r="A1282" s="38" t="n"/>
       <c r="B1282" s="27" t="inlineStr">
         <is>
@@ -39106,8 +39757,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1283">
+      <c r="F1282" s="41" t="inlineStr">
+        <is>
+          <t>同步DSP数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283" ht="16" customHeight="1">
       <c r="A1283" s="38" t="n"/>
       <c r="B1283" s="23" t="inlineStr">
         <is>
@@ -39129,8 +39785,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1284">
+      <c r="F1283" s="41" t="inlineStr">
+        <is>
+          <t>查DSP表现同步数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284" ht="16" customHeight="1">
       <c r="A1284" s="38" t="n"/>
       <c r="B1284" s="27" t="inlineStr">
         <is>
@@ -39152,8 +39813,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1285">
+      <c r="F1284" s="41" t="inlineStr">
+        <is>
+          <t>查DSP设置同步数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285" ht="16" customHeight="1">
       <c r="A1285" s="38" t="n"/>
       <c r="B1285" s="23" t="inlineStr">
         <is>
@@ -39175,8 +39841,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1286">
+      <c r="F1285" s="41" t="inlineStr">
+        <is>
+          <t>查最近AMS同步时间 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286" ht="16" customHeight="1">
       <c r="A1286" s="38" t="n"/>
       <c r="B1286" s="27" t="inlineStr">
         <is>
@@ -39198,8 +39869,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1287">
+      <c r="F1286" s="41" t="inlineStr">
+        <is>
+          <t>查最近DSP同步时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287" ht="16" customHeight="1">
       <c r="A1287" s="38" t="n"/>
       <c r="B1287" s="23" t="inlineStr">
         <is>
@@ -39221,8 +39897,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1288">
+      <c r="F1287" s="41" t="inlineStr">
+        <is>
+          <t>查最近Eligibility同步时间 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288" ht="16" customHeight="1">
       <c r="A1288" s="38" t="n"/>
       <c r="B1288" s="27" t="inlineStr">
         <is>
@@ -39244,8 +39925,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1289">
+      <c r="F1288" s="41" t="inlineStr">
+        <is>
+          <t>分页查询同步数据 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289" ht="16" customHeight="1">
       <c r="A1289" s="38" t="n"/>
       <c r="B1289" s="23" t="inlineStr">
         <is>
@@ -39267,8 +39953,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1290">
+      <c r="F1289" s="41" t="inlineStr">
+        <is>
+          <t>分页查询同步信息数据 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290" ht="16" customHeight="1">
       <c r="A1290" s="38" t="n"/>
       <c r="B1290" s="27" t="inlineStr">
         <is>
@@ -39288,6 +39979,11 @@
       <c r="E1290" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1290" s="41" t="inlineStr">
+        <is>
+          <t>触发Eligibility同步 — 100.0%</t>
         </is>
       </c>
     </row>
@@ -41308,7 +42004,7 @@
         </is>
       </c>
     </row>
-    <row r="1378">
+    <row r="1378" ht="16" customHeight="1">
       <c r="A1378" s="38" t="n"/>
       <c r="B1378" s="26" t="inlineStr">
         <is>
@@ -41330,8 +42026,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1379">
+      <c r="F1378" s="41" t="inlineStr">
+        <is>
+          <t>按clientId批量重新纳管</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379" ht="16" customHeight="1">
       <c r="A1379" s="38" t="n"/>
       <c r="B1379" s="23" t="inlineStr">
         <is>
@@ -41353,8 +42054,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1380">
+      <c r="F1379" s="41" t="inlineStr">
+        <is>
+          <t>按profileId查已选中账号 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380" ht="16" customHeight="1">
       <c r="A1380" s="38" t="n"/>
       <c r="B1380" s="27" t="inlineStr">
         <is>
@@ -41376,8 +42082,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1381">
+      <c r="F1380" s="41" t="inlineStr">
+        <is>
+          <t>批量检查profile纳管状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381" ht="16" customHeight="1">
       <c r="A1381" s="38" t="n"/>
       <c r="B1381" s="23" t="inlineStr">
         <is>
@@ -41399,8 +42110,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1382">
+      <c r="F1381" s="41" t="inlineStr">
+        <is>
+          <t>查询当前用户是否被纳管 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382" ht="32" customHeight="1">
       <c r="A1382" s="38" t="n"/>
       <c r="B1382" s="27" t="inlineStr">
         <is>
@@ -41420,6 +42136,11 @@
       <c r="E1382" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1382" s="41" t="inlineStr">
+        <is>
+          <t>创建品牌(含后置清理,可重复) — 100.0%</t>
         </is>
       </c>
     </row>
@@ -41446,7 +42167,7 @@
         </is>
       </c>
     </row>
-    <row r="1384">
+    <row r="1384" ht="32" customHeight="1">
       <c r="A1384" s="38" t="n"/>
       <c r="B1384" s="27" t="inlineStr">
         <is>
@@ -41468,8 +42189,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1385">
+      <c r="F1384" s="41" t="inlineStr">
+        <is>
+          <t>按isManage=1过滤已纳管账号 — 52.8%
+不带过滤条件查询全部账号 — 47.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385" ht="16" customHeight="1">
       <c r="A1385" s="38" t="n"/>
       <c r="B1385" s="23" t="inlineStr">
         <is>
@@ -41491,8 +42218,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1386">
+      <c r="F1385" s="41" t="inlineStr">
+        <is>
+          <t>查询亚马逊授权列表 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386" ht="64" customHeight="1">
       <c r="A1386" s="38" t="n"/>
       <c r="B1386" s="27" t="inlineStr">
         <is>
@@ -41514,8 +42246,16 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1387">
+      <c r="F1386" s="41" t="inlineStr">
+        <is>
+          <t>查未纳管账号,不带过滤 — 84.2%
+查已纳管账号,不带过滤 — 4.2%
+已纳管账号按DSP平台类型过滤 — 4.6%
+未纳管账号按profileId搜索 — 4.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387" ht="16" customHeight="1">
       <c r="A1387" s="38" t="n"/>
       <c r="B1387" s="23" t="inlineStr">
         <is>
@@ -41537,8 +42277,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1388">
+      <c r="F1387" s="41" t="inlineStr">
+        <is>
+          <t>分页查询账号列表 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388" ht="32" customHeight="1">
       <c r="A1388" s="38" t="n"/>
       <c r="B1388" s="27" t="inlineStr">
         <is>
@@ -41560,8 +42305,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1389">
+      <c r="F1388" s="41" t="inlineStr">
+        <is>
+          <t>查单个profile的品牌 — 62.6%
+批量查多个profile的品牌 — 37.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389" ht="32" customHeight="1">
       <c r="A1389" s="38" t="n"/>
       <c r="B1389" s="23" t="inlineStr">
         <is>
@@ -41583,8 +42334,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1390">
+      <c r="F1389" s="41" t="inlineStr">
+        <is>
+          <t>查单个profile的品牌列表 — 41.0%
+批量查多个profile的品牌列表 — 59.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390" ht="16" customHeight="1">
       <c r="A1390" s="38" t="n"/>
       <c r="B1390" s="27" t="inlineStr">
         <is>
@@ -41606,8 +42363,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1391">
+      <c r="F1390" s="41" t="inlineStr">
+        <is>
+          <t>按userId查用户详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391" ht="16" customHeight="1">
       <c r="A1391" s="38" t="n"/>
       <c r="B1391" s="23" t="inlineStr">
         <is>
@@ -41629,8 +42391,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1392">
+      <c r="F1391" s="41" t="inlineStr">
+        <is>
+          <t>设置单个账号纳管状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392" ht="32" customHeight="1">
       <c r="A1392" s="38" t="n"/>
       <c r="B1392" s="27" t="inlineStr">
         <is>
@@ -41652,8 +42419,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1393">
+      <c r="F1392" s="41" t="inlineStr">
+        <is>
+          <t>批量开启纳管 — 37.4%
+批量关闭纳管 — 62.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393" ht="16" customHeight="1">
       <c r="A1393" s="38" t="n"/>
       <c r="B1393" s="23" t="inlineStr">
         <is>
@@ -41675,8 +42448,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1394">
+      <c r="F1393" s="41" t="inlineStr">
+        <is>
+          <t>移除标签匹配规则(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394" ht="16" customHeight="1">
       <c r="A1394" s="38" t="n"/>
       <c r="B1394" s="27" t="inlineStr">
         <is>
@@ -41698,8 +42476,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1395">
+      <c r="F1394" s="41" t="inlineStr">
+        <is>
+          <t>更新品牌名(含前置创建/后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395" ht="16" customHeight="1">
       <c r="A1395" s="38" t="n"/>
       <c r="B1395" s="23" t="inlineStr">
         <is>
@@ -41721,8 +42504,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1396">
+      <c r="F1395" s="41" t="inlineStr">
+        <is>
+          <t>修改用户邮箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396" ht="16" customHeight="1">
       <c r="A1396" s="38" t="n"/>
       <c r="B1396" s="27" t="inlineStr">
         <is>
@@ -41742,6 +42530,11 @@
       <c r="E1396" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1396" s="41" t="inlineStr">
+        <is>
+          <t>修改用户密码</t>
         </is>
       </c>
     </row>
@@ -42550,7 +43343,7 @@
         </is>
       </c>
     </row>
-    <row r="1432">
+    <row r="1432" ht="16" customHeight="1">
       <c r="A1432" s="38" t="n"/>
       <c r="B1432" s="26" t="inlineStr">
         <is>
@@ -42572,8 +43365,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1433">
+      <c r="F1432" s="41" t="inlineStr">
+        <is>
+          <t>默认天气桩接口 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433" ht="16" customHeight="1">
       <c r="A1433" s="38" t="n"/>
       <c r="B1433" s="23" t="inlineStr">
         <is>
@@ -42595,8 +43393,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1434">
+      <c r="F1433" s="41" t="inlineStr">
+        <is>
+          <t>获取当前时间字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434" ht="16" customHeight="1">
       <c r="A1434" s="38" t="n"/>
       <c r="B1434" s="27" t="inlineStr">
         <is>
@@ -42618,8 +43421,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1435">
+      <c r="F1434" s="41" t="inlineStr">
+        <is>
+          <t>获取虚拟profile标识</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435" ht="16" customHeight="1">
       <c r="A1435" s="38" t="n"/>
       <c r="B1435" s="23" t="inlineStr">
         <is>
@@ -42641,8 +43449,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1436">
+      <c r="F1435" s="41" t="inlineStr">
+        <is>
+          <t>重置虚拟profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436" ht="16" customHeight="1">
       <c r="A1436" s="38" t="n"/>
       <c r="B1436" s="27" t="inlineStr">
         <is>
@@ -42664,8 +43477,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1437">
+      <c r="F1436" s="41" t="inlineStr">
+        <is>
+          <t>测试同步数据(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437" ht="16" customHeight="1">
       <c r="A1437" s="38" t="n"/>
       <c r="B1437" s="23" t="inlineStr">
         <is>
@@ -42687,8 +43505,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1438">
+      <c r="F1437" s="41" t="inlineStr">
+        <is>
+          <t>按clientId获取campaign字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438" ht="16" customHeight="1">
       <c r="A1438" s="38" t="n"/>
       <c r="B1438" s="27" t="inlineStr">
         <is>
@@ -42710,8 +43533,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1439">
+      <c r="F1438" s="41" t="inlineStr">
+        <is>
+          <t>按clientId获取毛利设置比率</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439" ht="16" customHeight="1">
       <c r="A1439" s="38" t="n"/>
       <c r="B1439" s="23" t="inlineStr">
         <is>
@@ -42733,8 +43561,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1440">
+      <c r="F1439" s="41" t="inlineStr">
+        <is>
+          <t>按clientId获取profileId/campaignId字符串</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440" ht="16" customHeight="1">
       <c r="A1440" s="38" t="n"/>
       <c r="B1440" s="27" t="inlineStr">
         <is>
@@ -42756,8 +43589,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1441">
+      <c r="F1440" s="41" t="inlineStr">
+        <is>
+          <t>测试品牌视频广告V4(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441" ht="16" customHeight="1">
       <c r="A1441" s="38" t="n"/>
       <c r="B1441" s="23" t="inlineStr">
         <is>
@@ -42779,8 +43617,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1442">
+      <c r="F1441" s="41" t="inlineStr">
+        <is>
+          <t>测试广告组V4(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442" ht="16" customHeight="1">
       <c r="A1442" s="38" t="n"/>
       <c r="B1442" s="27" t="inlineStr">
         <is>
@@ -42802,8 +43645,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1443">
+      <c r="F1442" s="41" t="inlineStr">
+        <is>
+          <t>测试商品集合广告V4(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443" ht="16" customHeight="1">
       <c r="A1443" s="38" t="n"/>
       <c r="B1443" s="23" t="inlineStr">
         <is>
@@ -42825,8 +43673,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1444">
+      <c r="F1443" s="41" t="inlineStr">
+        <is>
+          <t>测试店铺聚焦广告V4(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444" ht="16" customHeight="1">
       <c r="A1444" s="38" t="n"/>
       <c r="B1444" s="27" t="inlineStr">
         <is>
@@ -42848,8 +43701,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1445">
+      <c r="F1444" s="41" t="inlineStr">
+        <is>
+          <t>测试视频广告V4(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445" ht="16" customHeight="1">
       <c r="A1445" s="38" t="n"/>
       <c r="B1445" s="23" t="inlineStr">
         <is>
@@ -42871,8 +43729,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1446">
+      <c r="F1445" s="41" t="inlineStr">
+        <is>
+          <t>测试Campaign V4(调试接口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446" ht="16" customHeight="1">
       <c r="A1446" s="39" t="n"/>
       <c r="B1446" s="27" t="inlineStr">
         <is>
@@ -42892,6 +43755,11 @@
       <c r="E1446" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1446" s="41" t="inlineStr">
+        <is>
+          <t>测试否定投放(调试接口)</t>
         </is>
       </c>
     </row>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -2171,6 +2171,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F46" t="n">
+        <v>32</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>89% (34/38)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="41" t="n"/>
@@ -2337,7 +2350,7 @@
         </is>
       </c>
       <c r="F52" s="29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G52" s="29" t="inlineStr">
         <is>
@@ -2514,6 +2527,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="41" t="n"/>
@@ -2603,6 +2629,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F61" t="n">
+        <v>385</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>100% (66/66)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="41" t="n"/>
@@ -2690,6 +2729,19 @@
       <c r="E64" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
         </is>
       </c>
     </row>
@@ -16680,6 +16732,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>确认并执行广告组改名(含后置还原,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="41" t="n"/>
@@ -16703,6 +16760,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>确认并执行预算变更(含后置还原,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="41" t="n"/>
@@ -16726,6 +16788,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>确认并执行Campaign改名(含后置还原,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="41" t="n"/>
@@ -16749,6 +16816,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>确认并执行状态变更(含后置还原,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="41" t="n"/>
@@ -16772,6 +16844,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>确认并执行定向状态变更(含后置还原,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="41" t="n"/>
@@ -16795,6 +16872,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>确认并执行新建正向关键词定向(含后置归档,可重复)
+确认并执行新建否定关键词定向(含后置归档,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="41" t="n"/>
@@ -16818,6 +16901,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>按广告组导出改名文件 — 93.3%
+仅按Campaign导出改名文件(不指定Adgroup) — 6.7%</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="41" t="n"/>
@@ -16864,6 +16953,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>按BatchId+KindType导出失败日志 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="41" t="n"/>
@@ -16887,6 +16981,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>按BatchId导出预算变更失败日志 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="41" t="n"/>
@@ -16910,6 +17009,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>按Campaign导出预算变更文件 — 99.4%</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="41" t="n"/>
@@ -16933,6 +17037,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>按Campaign导出改名文件 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="41" t="n"/>
@@ -16956,6 +17065,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>按Campaign导出状态变更文件 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="41" t="n"/>
@@ -16979,6 +17093,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>按BatchId导出Campaign操作失败日志 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="41" t="n"/>
@@ -17002,6 +17121,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>按Campaign+KindType导出创建定向文件 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="41" t="n"/>
@@ -17025,6 +17149,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>按Campaign+KindType+定向状态导出变更文件 — 97.9%
+按时间范围+定向状态导出变更文件 — 2.1%</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="41" t="n"/>
@@ -17048,6 +17178,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>按BatchId查询批量操作明细日志 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="41" t="n"/>
@@ -17071,6 +17206,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>查询批量操作日志列表 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="41" t="n"/>
@@ -17094,6 +17234,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>按BatchId查询预算变更明细日志 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="41" t="n"/>
@@ -17140,6 +17285,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>按BatchId查询命名变更明细日志 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="41" t="n"/>
@@ -17163,6 +17313,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>查询命名变更日志列表</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="41" t="n"/>
@@ -17186,6 +17341,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>预览广告组改名文件 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="41" t="n"/>
@@ -17209,6 +17369,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>预览预算变更文件 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="41" t="n"/>
@@ -17232,6 +17397,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>预览Campaign改名文件 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="41" t="n"/>
@@ -17255,6 +17425,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>预览状态变更文件 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="41" t="n"/>
@@ -17278,6 +17453,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>预览定向出价变更文件 — 98%
+预览定向状态变更文件 — 2%</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="41" t="n"/>
@@ -17301,6 +17482,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>预览新建否定定向文件 — 65.4%
+预览新建正向定向文件 — 34.6%</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="41" t="n"/>
@@ -17483,6 +17670,11 @@
       <c r="E376" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>校验批量上传Excel文件类型 — 100%</t>
         </is>
       </c>
     </row>
@@ -23526,10 +23718,8 @@
       </c>
       <c r="F615" s="34" t="inlineStr">
         <is>
-          <t>首页加载SP+SD campaign列表(dimNames形态) — 38%
-翻页浏览campaign列表(keyword形态) — 38%
-首页加载campaign列表(keyword形态) — 20%
-指定维度过滤(dimNames) — 2%</t>
+          <t>keyword搜索模式 — 58.0%
+dimNames维度模式 — 42.0%</t>
         </is>
       </c>
     </row>
@@ -26947,6 +27137,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>场景1: 单批次复制SB创意文案与素材到已有广告组</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="41" t="n"/>
@@ -26970,6 +27165,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>场景1: 单批次复制SD创意文案与素材到已有广告组</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="41" t="n"/>
@@ -26993,6 +27193,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>场景1: 按ASSET TYPE+扩展名筛选素材库并按创建时间倒序分页</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="41" t="n"/>
@@ -27014,6 +27219,11 @@
       <c r="E746" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>场景1: Copy后重命名广告活动</t>
         </is>
       </c>
     </row>
@@ -27559,6 +27769,20 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>全部Profile+无过滤 — 36.2%
+单Profile+无过滤 — 22.6%
+单Profile+按CampaignIds过滤 — 13.2%
+单Profile+按CampaignTag过滤 — 11.2%
+全部Profile+按CampaignTag过滤 — 7.6%
+多Profile+无过滤 — 2.4%
+单Profile+按CampaignTag过滤+含环比对比(CompareType=2) — 2.4%
+全部Profile+无过滤+含环比对比(CompareType=2) — 1.2%
+全部Profile+按CampaignIds过滤 — 1.0%
+单Profile+无过滤+含环比对比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="41" t="n"/>
@@ -27582,6 +27806,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含Placement维度(IsPlacement=1) — 37.1%
+单Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 22.9%
+单Profile+按CampaignTag过滤+含Placement维度(IsPlacement=1) — 11.4%
+单Profile+按CampaignIds过滤+含Placement维度(IsPlacement=2) — 11.4%
+全部Profile+无过滤+含Placement维度(IsPlacement=1) — 8.6%
+全部Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 2.9%
+多Profile+按CampaignTag过滤+含环比对比(CompareType=2)+含Placement维度(IsPlacement=1) — 2.9%
+多Profile+无过滤+含Placement维度(IsPlacement=1) — 2.9%</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="41" t="n"/>
@@ -27605,6 +27841,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含Placement维度(IsPlacement=2) — 50.0%
+单Profile+无过滤+含Placement维度(IsPlacement=1) — 50.0%</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="41" t="n"/>
@@ -27628,6 +27870,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>全部Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" s="41" t="n"/>
@@ -27651,6 +27898,13 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>dim=ytd+单Profile+AudienceName+CampaignType — 63.6%
+dim=ytd+多Profile+AudienceName+CampaignType — 25.2%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 10.6%</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="41" t="n"/>
@@ -27674,6 +27928,17 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 43.2%
+dim=ytd+单Profile+CampaignType — 33.0%
+dim=ytd+单Profile+AudienceName+CampaignType — 10.2%
+dim=ytd+多Profile+AudienceName+CampaignType — 5.0%
+dim=ytd+单Profile+CampaignType+CampaignTag — 4.8%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 1.4%
+dim=ytd+单Profile+AudienceName+CampaignType+Portfolio — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="41" t="n"/>
@@ -27697,6 +27962,20 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 30.0%
+dim=ytd+单Profile+CampaignType — 23.4%
+dim=month+单Profile+AudienceName — 10.8%
+dim=week+单Profile+AudienceName — 7.2%
+dim=date+单Profile+AudienceName — 6.6%
+dim=ytd+单Profile+AudienceName+CampaignType — 5.8%
+dim=month+单Profile+AudienceName — 5.0%
+dim=ytd+多Profile+AudienceName+CampaignType — 4.6%
+dim=ytd+单Profile+CampaignType+CampaignTag — 4.0%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="41" t="n"/>
@@ -27720,6 +27999,16 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 44.6%
+dim=ytd+单Profile+CampaignType — 31.0%
+dim=ytd+单Profile+AudienceName+CampaignType — 10.0%
+dim=ytd+多Profile+AudienceName+CampaignType — 7.2%
+dim=ytd+单Profile+CampaignType+CampaignTag — 3.2%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 2.2%</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="41" t="n"/>
@@ -27743,6 +28032,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>dim=ytd+单Profile+AudienceName — 39.6%
+dim=ytd+多Profile+CampaignType — 19.8%
+dim=ytd+单Profile+CampaignType — 15.4%
+dim=ytd+多Profile+AudienceName — 9.2%
+dim=ytd+单Profile+AudienceName+CampaignType — 5.8%
+dim=ytd+单Profile+CampaignType+CampaignTag — 3.2%
+dim=ytd+多Profile+AudienceName+CampaignType — 2.2%
+dim=ytd+单Profile+AudienceName+CampaignTag — 2.0%</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="41" t="n"/>
@@ -27766,6 +28067,16 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>dim=ytd+多Profile+CampaignType — 42.2%
+dim=ytd+单Profile+CampaignType — 35.8%
+dim=ytd+单Profile+AudienceName+CampaignType — 9.6%
+dim=ytd+多Profile+AudienceName+CampaignType — 6.4%
+dim=ytd+单Profile+CampaignType+CampaignTag — 3.0%
+dim=ytd+单Profile+AudienceName+CampaignType+CampaignTag — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" s="41" t="n"/>
@@ -27789,6 +28100,13 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>CampaignType=sponsoredProducts+无过滤 — 77.3%
+CampaignType=sponsoredProducts+ASIN过滤 — 17.3%
+CampaignType=SponsoredDisplay+无过滤 — 3.5%</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="41" t="n"/>
@@ -27812,6 +28130,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>有Profile过滤+有Advertiser过滤 — 92.6%
+无Profile过滤+有Advertiser过滤 — 7.4%</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" s="41" t="n"/>
@@ -27835,6 +28159,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 99.6%</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" s="41" t="n"/>
@@ -27858,6 +28187,15 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>单Profile+Brand=All+含Category+TimeType=1 — 62.8%
+单Profile+指定Brand+含Category+TimeType=1 — 12.6%
+单Profile+指定Brand+无Category+TimeType=1 — 12.4%
+单Profile+Brand=All+含Category+TimeType=0 — 9.4%
+单Profile+指定Brand+含Category+TimeType=3 — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" s="41" t="n"/>
@@ -27881,6 +28219,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 81.4%
+多Profile+无过滤 — 18.6%</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="41" t="n"/>
@@ -27904,6 +28248,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 100.0%</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="41" t="n"/>
@@ -27927,6 +28276,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 100.0%</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" s="41" t="n"/>
@@ -27950,6 +28304,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 100.0%</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" s="41" t="n"/>
@@ -27973,6 +28332,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 31.2%
+单Profile+无过滤 — 30.6%
+单Profile+按CampaignTag过滤 — 21.0%
+单Profile+无过滤+含环比(CompareType=2) — 5.6%
+全部Profile+无过滤 — 3.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+多Profile+按CampaignTag过滤 — 2.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" s="41" t="n"/>
@@ -27996,6 +28367,20 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 35.0%
+单Profile+无过滤 — 20.6%
+多Profile+无过滤 — 16.8%
+多Profile+按CampaignTag过滤 — 12.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 5.2%
+单Profile+无过滤+含环比(CompareType=2) — 2.8%
+全部Profile+无过滤 — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.4%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" s="41" t="n"/>
@@ -28019,6 +28404,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 33.8%
+多Profile+无过滤 — 20.8%
+单Profile+无过滤 — 19.2%
+多Profile+按CampaignTag过滤 — 11.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 7.2%
+单Profile+无过滤+含环比(CompareType=2) — 3.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%
+全部Profile+无过滤 — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="41" t="n"/>
@@ -28042,6 +28439,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 34.0%
+单Profile+无过滤 — 28.6%
+单Profile+按CampaignTag过滤 — 20.4%
+单Profile+无过滤+含环比(CompareType=2) — 5.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+全部Profile+无过滤 — 2.8%
+多Profile+按CampaignTag过滤 — 1.8%
+单Profile+无过滤+含环比(CompareType=1) — 1.6%</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" s="41" t="n"/>
@@ -28065,6 +28474,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 33.2%
+多Profile+无过滤 — 22.6%
+单Profile+无过滤 — 21.4%
+多Profile+按CampaignTag过滤 — 11.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.4%
+单Profile+无过滤+含环比(CompareType=2) — 3.0%
+全部Profile+无过滤 — 1.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="41" t="n"/>
@@ -28088,6 +28509,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 41.2%
+单Profile+无过滤 — 25.2%
+单Profile+按CampaignTag过滤 — 23.8%
+多Profile+按CampaignTag过滤 — 2.4%
+全部Profile+无过滤 — 2.4%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.0%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="41" t="n"/>
@@ -28111,6 +28544,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 30.8%
+多Profile+无过滤 — 30.8%
+单Profile+按CampaignTag过滤 — 21.6%
+单Profile+无过滤+含环比(CompareType=2) — 5.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+多Profile+按CampaignTag过滤 — 2.8%
+全部Profile+无过滤 — 2.0%
+单Profile+无过滤+含环比(CompareType=1) — 1.4%</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" s="41" t="n"/>
@@ -28134,6 +28579,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 34.4%
+单Profile+无过滤 — 26.0%
+单Profile+按CampaignTag过滤 — 23.6%
+单Profile+无过滤+含环比(CompareType=2) — 4.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.2%
+全部Profile+无过滤 — 2.0%
+多Profile+按CampaignTag过滤 — 2.0%
+单Profile+无过滤+含环比(CompareType=1) — 1.4%</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" s="41" t="n"/>
@@ -28157,6 +28614,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 34.4%
+单Profile+无过滤 — 33.6%
+单Profile+按CampaignTag过滤 — 19.0%
+单Profile+无过滤+含环比(CompareType=2) — 3.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+多Profile+按CampaignTag过滤 — 2.0%
+全部Profile+无过滤 — 2.0%
+多Profile+无过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" s="41" t="n"/>
@@ -28180,6 +28649,16 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 59.8%
+多Profile+按CampaignTag过滤 — 29.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 6.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.4%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" s="41" t="n"/>
@@ -28203,6 +28682,17 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 55.6%
+多Profile+按CampaignTag过滤 — 28.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 6.4%
+单Profile+无过滤 — 3.8%
+多Profile+无过滤 — 2.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" s="41" t="n"/>
@@ -28226,6 +28716,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 56.0%
+多Profile+按CampaignTag过滤 — 26.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 7.2%
+单Profile+无过滤 — 2.8%
+多Profile+无过滤 — 2.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.2%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="41" t="n"/>
@@ -28249,6 +28751,15 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 61.0%
+多Profile+无过滤 — 27.6%
+单Profile+无过滤+含环比(CompareType=2) — 7.2%
+单Profile+无过滤+含环比(CompareType=1) — 2.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.6%</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="41" t="n"/>
@@ -28272,6 +28783,17 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 60.2%
+多Profile+按CampaignTag过滤 — 28.2%
+单Profile+无过滤 — 3.8%
+多Profile+无过滤 — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" s="41" t="n"/>
@@ -28295,6 +28817,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 31.4%
+单Profile+无过滤 — 30.8%
+单Profile+按CampaignTag过滤 — 24.0%
+单Profile+无过滤+含环比(CompareType=2) — 4.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+多Profile+按CampaignTag过滤 — 2.6%
+全部Profile+无过滤 — 2.0%
+多Profile+无过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" s="41" t="n"/>
@@ -28318,6 +28852,17 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 32.8%
+单Profile+无过滤 — 32.8%
+单Profile+按CampaignTag过滤 — 20.8%
+单Profile+无过滤+含环比(CompareType=2) — 4.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.8%
+多Profile+按CampaignTag过滤 — 2.2%
+全部Profile+无过滤 — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" s="41" t="n"/>
@@ -28341,6 +28886,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 32.4%
+单Profile+无过滤 — 29.4%
+单Profile+按CampaignTag过滤 — 21.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.4%
+单Profile+无过滤+含环比(CompareType=2) — 4.2%
+全部Profile+无过滤 — 2.4%
+多Profile+按CampaignTag过滤 — 2.2%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" s="41" t="n"/>
@@ -28364,6 +28921,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 31.8%
+单Profile+无过滤 — 27.6%
+单Profile+按CampaignTag过滤 — 23.0%
+单Profile+无过滤+含环比(CompareType=2) — 5.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.4%
+多Profile+按CampaignTag过滤 — 2.6%
+全部Profile+无过滤 — 1.8%
+单Profile+无过滤+含环比(CompareType=1) — 1.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" s="41" t="n"/>
@@ -28387,6 +28957,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 33.8%
+单Profile+按CampaignTag过滤 — 22.4%
+单Profile+无过滤 — 13.6%
+多Profile+无过滤 — 12.6%
+多Profile+按CampaignTag过滤 — 9.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="41" t="n"/>
@@ -28410,6 +28992,16 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>单Profile+按CampaignTag过滤 — 55.6%
+多Profile+按CampaignTag过滤 — 25.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 8.2%
+单Profile+无过滤 — 4.2%
+多Profile+无过滤 — 2.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.2%</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="41" t="n"/>
@@ -28433,6 +29025,14 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 86.4%
+多Profile+无过滤 — 7.4%
+单Profile+无过滤+含环比(CompareType=1) — 3.0%
+单Profile+无过滤+含环比(CompareType=2) — 2.2%</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="41" t="n"/>
@@ -28456,6 +29056,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" s="41" t="n"/>
@@ -28479,6 +29084,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含环比对比(CompareType=2) — 100.0%</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" s="41" t="n"/>
@@ -28502,6 +29112,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>全部Profile+无过滤 — 38.6%
+单Profile+无过滤 — 24.6%
+单Profile+按CampaignTag过滤 — 13.4%
+单Profile+按CampaignIds过滤 — 11.4%
+全部Profile+按CampaignTag过滤 — 4.2%
+全部Profile+按CampaignIds过滤 — 2.2%
+多Profile+按CampaignIds过滤 — 1.0%
+多Profile+无过滤 — 1.0%
+单Profile+无过滤+含环比对比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="41" t="n"/>
@@ -28525,6 +29148,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤+含环比对比(CompareType=2) — 50.0%
+单Profile+无过滤+含环比对比(CompareType=2)+含Placement维度(IsPlacement=1) — 50.0%</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" s="41" t="n"/>
@@ -28548,6 +29177,23 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>全部Profile+无过滤 — 19.4%
+全部Profile+无过滤+含Placement维度(IsPlacement=1) — 18.6%
+单Profile+无过滤+含Placement维度(IsPlacement=1) — 12.6%
+单Profile+无过滤 — 11.4%
+单Profile+按CampaignTag过滤 — 7.4%
+单Profile+按CampaignIds过滤 — 6.4%
+单Profile+按CampaignTag过滤+含Placement维度(IsPlacement=1) — 4.8%
+单Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 4.0%
+全部Profile+按CampaignTag过滤 — 2.0%
+全部Profile+按CampaignTag过滤+含Placement维度(IsPlacement=1) — 1.6%
+全部Profile+按CampaignIds过滤+含Placement维度(IsPlacement=1) — 1.4%
+全部Profile+按CampaignIds过滤 — 1.4%
+单Profile+无过滤+含Placement维度(IsPlacement=2) — 1.4%</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" s="41" t="n"/>
@@ -28571,6 +29217,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" s="41" t="n"/>
@@ -28594,6 +29245,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 29.6%
+单Profile+无过滤 — 26.0%
+单Profile+按CampaignTag过滤 — 19.8%
+多Profile+按CampaignTag过滤 — 15.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.8%
+多Profile+无过滤+含环比(CompareType=2) — 1.2%
+单Profile+无过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" s="41" t="n"/>
@@ -28617,6 +29280,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 30.8%
+多Profile+无过滤 — 27.4%
+单Profile+按CampaignTag过滤 — 16.8%
+多Profile+按CampaignTag过滤 — 14.4%
+单Profile+无过滤+含环比(CompareType=2) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.6%
+多Profile+无过滤+含环比(CompareType=2) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" s="41" t="n"/>
@@ -28640,6 +29316,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 30.0%
+单Profile+无过滤 — 28.4%
+单Profile+按CampaignTag过滤 — 15.4%
+多Profile+按CampaignTag过滤 — 13.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.6%
+单Profile+无过滤+含环比(CompareType=2) — 1.8%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.6%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" s="41" t="n"/>
@@ -28663,6 +29352,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 28.8%
+单Profile+无过滤 — 26.4%
+单Profile+按CampaignTag过滤 — 19.2%
+多Profile+按CampaignTag过滤 — 13.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 4.6%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.4%</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" s="41" t="n"/>
@@ -28686,6 +29387,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 29.6%
+单Profile+无过滤 — 26.4%
+单Profile+按CampaignTag过滤 — 19.4%
+多Profile+按CampaignTag过滤 — 14.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.8%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 2.2%
+单Profile+无过滤+含环比(CompareType=2) — 1.8%
+多Profile+无过滤+含环比(CompareType=2) — 1.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" s="41" t="n"/>
@@ -28709,6 +29423,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 29.2%
+多Profile+无过滤 — 28.4%
+单Profile+按CampaignTag过滤 — 20.4%
+多Profile+按CampaignTag过滤 — 12.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.2%
+单Profile+按CampaignTag过滤+含环比(CompareType=1) — 1.6%
+单Profile+无过滤+含环比(CompareType=2) — 1.6%
+多Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" s="41" t="n"/>
@@ -28732,6 +29458,15 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 53.2%
+单Profile+按CampaignTag过滤 — 35.4%
+单Profile+无过滤+含环比(CompareType=1) — 5.1%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 3.8%
+单Profile+无过滤+含环比(CompareType=2) — 2.5%</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" s="41" t="n"/>
@@ -28755,6 +29490,14 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 84.4%
+多Profile+无过滤 — 7.6%
+单Profile+无过滤+含环比(CompareType=2) — 4.2%
+单Profile+无过滤+含环比(CompareType=1) — 3.2%</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" s="41" t="n"/>
@@ -28778,6 +29521,14 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 85.6%
+多Profile+无过滤 — 7.8%
+单Profile+无过滤+含环比(CompareType=2) — 2.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.8%</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="41" t="n"/>
@@ -28801,6 +29552,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 46.0%
+单Profile+无过滤 — 34.0%
+单Profile+按CampaignTag过滤 — 9.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.4%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 2.2%
+多Profile+按CampaignTag过滤 — 2.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.4%
+全部Profile+无过滤 — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="41" t="n"/>
@@ -28824,6 +29587,18 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 46.2%
+单Profile+无过滤 — 35.6%
+单Profile+按CampaignTag过滤 — 9.4%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.8%
+单Profile+无过滤+含环比(CompareType=1) — 1.4%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%
+多Profile+按CampaignTag过滤 — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" s="41" t="n"/>
@@ -28847,6 +29622,13 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>type=sp — 85.0%
+type=sb — 13.9%
+type=sd — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" s="41" t="n"/>
@@ -28870,6 +29652,16 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>全部Profile+无状态过滤 — 48.8%
+单Profile+无状态过滤 — 33.6%
+多Profile+无状态过滤 — 10.6%
+单Profile+eligibilityStatus=ELIGIBLE WITH WARNING — 2.8%
+单Profile+eligibilityStatus=INELIGIBLE — 1.8%
+多Profile+eligibilityStatus=INELIGIBLE — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" s="41" t="n"/>
@@ -28893,6 +29685,17 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 44.2%
+单Profile+无过滤 — 36.4%
+单Profile+按CampaignTag过滤 — 10.0%
+多Profile+按CampaignTag过滤 — 2.2%
+单Profile+无过滤+含环比(CompareType=1) — 1.8%
+多Profile+无过滤+含环比(CompareType=1) — 1.4%
+单Profile+无过滤+含环比(CompareType=2) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" s="41" t="n"/>
@@ -28916,6 +29719,16 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 53.8%
+单Profile+无过滤 — 30.4%
+单Profile+按CampaignTag过滤 — 7.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.4%
+单Profile+无过滤+含环比(CompareType=2) — 1.6%
+多Profile+按CampaignTag过滤 — 1.4%</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" s="41" t="n"/>
@@ -28939,6 +29752,17 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>多Profile+无过滤 — 43.8%
+单Profile+无过滤 — 36.8%
+单Profile+按CampaignTag过滤 — 10.2%
+单Profile+无过滤+含环比(CompareType=1) — 2.6%
+单Profile+按CampaignTag过滤+含环比(CompareType=2) — 1.6%
+单Profile+无过滤+含环比(CompareType=2) — 1.0%
+多Profile+无过滤+含环比(CompareType=1) — 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" s="41" t="n"/>
@@ -28962,6 +29786,17 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 43.6%
+多Profile+无过滤 — 37.8%
+单Profile+按CampaignTag过滤 — 8.6%
+单Profile+无过滤+含环比(CompareType=1) — 3.0%
+单Profile+无过滤+含环比(CompareType=2) — 2.0%
+多Profile+按CampaignTag过滤 — 1.6%
+多Profile+无过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" s="41" t="n"/>
@@ -28985,6 +29820,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤(无真实流量,复用同结构接口入参验证可达性)</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" s="41" t="n"/>
@@ -29008,6 +29848,15 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>单Profile+无过滤 — 86.0%
+多Profile+无过滤 — 6.6%
+单Profile+无过滤+含环比(CompareType=2) — 2.8%
+单Profile+无过滤+含环比(CompareType=1) — 2.6%
+多Profile+无过滤+含环比(CompareType=1) — 1.2%</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" s="41" t="n"/>
@@ -29031,6 +29880,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>版本号查询(无业务参数) — 100.0%</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" s="41" t="n"/>
@@ -29054,6 +29908,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>健康检查/语言测试(无业务参数) — 100.0%</t>
+        </is>
+      </c>
     </row>
     <row r="831" ht="90" customHeight="1">
       <c r="A831" s="41" t="n"/>
@@ -29286,6 +30145,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>场景1: 按Profile+Campaign+AdGroup查询广告组Explorer详情 — 99.6%</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" s="41" t="n"/>
@@ -29309,6 +30173,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>场景1: 按Profile+Campaign查询广告活动Explorer详情 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" s="41" t="n"/>
@@ -29332,6 +30201,12 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>场景1: 全量Portfolio交互数据按Spend排序 不过滤名称 — 77.9%
+场景2: 按dimName关键词过滤Portfolio交互数据 — 20.1%</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" s="41" t="n"/>
@@ -29355,6 +30230,11 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>场景1: 按Profile+Portfolio查询组合Explorer详情 — 100%</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" s="41" t="n"/>
@@ -29376,6 +30256,11 @@
       <c r="E843" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>场景1: 按ProfileId查询Profile级Explorer详情 — 99.6%</t>
         </is>
       </c>
     </row>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -948,6 +948,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F4" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>83% (5/6)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="n"/>
@@ -1037,6 +1050,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F7" s="29" t="n">
+        <v>59</v>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>100% (13/13)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="41" t="n"/>
@@ -1093,7 +1119,7 @@
         </is>
       </c>
       <c r="F9" s="29" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
@@ -1126,6 +1152,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F10" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>100% (3/3)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="41" t="n"/>
@@ -1157,7 +1196,7 @@
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
-          <t>100% (1/1)</t>
+          <t>0% (0/1)</t>
         </is>
       </c>
     </row>
@@ -1215,6 +1254,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F13" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="41" t="n"/>
@@ -1291,9 +1343,19 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
+      <c r="F16" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="41" t="n"/>
@@ -1383,6 +1445,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F19" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="41" t="n"/>
@@ -1472,6 +1547,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F22" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="inlineStr">
+        <is>
+          <t>0% (0/6)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="41" t="n"/>
@@ -1548,6 +1636,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F25" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="G25" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>52% (14/27)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="41" t="n"/>
@@ -1637,6 +1738,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F28" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="G28" s="29" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="41" t="n"/>
@@ -1702,7 +1816,7 @@
       </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>90% (28/31)</t>
+          <t>84% (26/31)</t>
         </is>
       </c>
     </row>
@@ -1726,6 +1840,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F31" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="29" t="inlineStr">
+        <is>
+          <t>42% (5/12)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="41" t="n"/>
@@ -1815,6 +1942,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F34" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="G34" s="29" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="H34" s="29" t="inlineStr">
+        <is>
+          <t>100% (3/3)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="41" t="n"/>
@@ -1837,16 +1977,16 @@
         </is>
       </c>
       <c r="F35" s="29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>67% (4/6)</t>
+          <t>86% (6/7)</t>
         </is>
       </c>
     </row>
@@ -1871,16 +2011,16 @@
         </is>
       </c>
       <c r="F36" s="29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H36" s="29" t="inlineStr">
         <is>
-          <t>25% (1/4)</t>
+          <t>100% (4/4)</t>
         </is>
       </c>
     </row>
@@ -1904,6 +2044,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F37" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="41" t="n"/>
@@ -1926,7 +2079,7 @@
         </is>
       </c>
       <c r="F38" s="29" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
@@ -1993,6 +2146,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F40" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G40" s="29" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="inlineStr">
+        <is>
+          <t>94% (17/18)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="41" t="n"/>
@@ -2082,15 +2248,15 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="29" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="29" t="inlineStr">
         <is>
           <t>100% (3/3)</t>
         </is>
@@ -2269,7 +2435,7 @@
         </is>
       </c>
       <c r="F50" s="29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
@@ -2380,7 +2546,7 @@
       </c>
       <c r="H53" s="29" t="inlineStr">
         <is>
-          <t>66% (50/76)</t>
+          <t>62% (47/76)</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2622,7 @@
       </c>
       <c r="H56" s="29" t="inlineStr">
         <is>
-          <t>110% (11/10)</t>
+          <t>100% (10/10)</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2702,7 @@
         </is>
       </c>
       <c r="F59" s="29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
@@ -2545,7 +2711,7 @@
       </c>
       <c r="H59" s="29" t="inlineStr">
         <is>
-          <t>62% (5/8)</t>
+          <t>75% (6/8)</t>
         </is>
       </c>
     </row>
@@ -2713,6 +2879,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F65" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G65" s="29" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="H65" s="29" t="inlineStr">
+        <is>
+          <t>40% (10/25)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="41" t="n"/>
@@ -2734,6 +2913,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F66" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H66" s="29" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="41" t="n"/>
@@ -2852,6 +3044,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F71" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="G71" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H71" s="29" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="41" t="n"/>
@@ -2928,6 +3133,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F74" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G74" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H74" s="29" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="41" t="n"/>
@@ -2991,6 +3209,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F77" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>57% (4/7)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="41" t="n"/>
@@ -3067,6 +3298,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F80" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G80" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H80" s="29" t="inlineStr">
+        <is>
+          <t>61% (14/23)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="41" t="n"/>
@@ -3098,7 +3342,7 @@
       </c>
       <c r="H81" s="29" t="inlineStr">
         <is>
-          <t>108% (28/26)</t>
+          <t>100% (26/26)</t>
         </is>
       </c>
     </row>
@@ -3143,6 +3387,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F83" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G83" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H83" s="29" t="inlineStr">
+        <is>
+          <t>100% (7/7)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="41" t="n"/>
@@ -3295,6 +3552,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F89" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="G89" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H89" s="29" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="41" t="n"/>
@@ -3326,7 +3596,7 @@
       </c>
       <c r="H90" s="29" t="inlineStr">
         <is>
-          <t>200% (4/2)</t>
+          <t>100% (2/2)</t>
         </is>
       </c>
     </row>
@@ -3447,6 +3717,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F95" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G95" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H95" s="29" t="inlineStr">
+        <is>
+          <t>91% (10/11)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="41" t="n"/>
@@ -3523,6 +3806,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F98" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="G98" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H98" s="29" t="inlineStr">
+        <is>
+          <t>100% (13/13)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="41" t="n"/>
@@ -3586,6 +3882,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F101" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G101" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H101" s="29" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="41" t="n"/>
@@ -3649,6 +3958,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F104" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H104" s="29" t="inlineStr">
+        <is>
+          <t>15% (2/13)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="41" t="n"/>
@@ -3723,6 +4045,19 @@
       <c r="E107" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F107" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G107" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H107" s="29" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4575,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="159.95" customHeight="1">
+    <row r="2" ht="160" customHeight="1">
       <c r="A2" s="43" t="inlineStr">
         <is>
           <t>us</t>
@@ -4266,7 +4601,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F2" s="30" t="inlineStr">
+      <c r="F2" s="44" t="inlineStr">
         <is>
           <t>场景1: 默认列表浏览 ytd State筛选 Spend降序 — 18.6%
 场景2: Campaign下钻 ytd CampaignId筛选 — 40.2%
@@ -4281,7 +4616,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="207.95" customHeight="1">
+    <row r="3" ht="208" customHeight="1">
       <c r="A3" s="41" t="n"/>
       <c r="B3" s="23" t="inlineStr">
         <is>
@@ -4303,7 +4638,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="44" t="inlineStr">
         <is>
           <t>场景1: 默认列表浏览 ytd State筛选 Spend降序 — 39.2%
 场景2: Campaign下钻 ytd CampaignId筛选 — 24.8%
@@ -4343,7 +4678,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>场景1: 默认列表浏览 ytd State筛选 Spend降序 — 2.6%
 场景2: Campaign下钻 ytd CampaignId筛选 — 23.0%
@@ -4379,7 +4714,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F5" s="34" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>场景1: 新版调用 TagId筛选 US — 39.6%
 场景2: 旧版调用 含对比日期 TagId筛选 DE — 33.3%
@@ -4387,7 +4722,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="63.95" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="41" t="n"/>
       <c r="B6" s="22" t="inlineStr">
         <is>
@@ -4409,7 +4744,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="44" t="inlineStr">
         <is>
           <t>场景1: 默认日期范围 无额外筛选 US — 56.4%
 场景2: UserId筛选 US — 9.5%
@@ -4418,7 +4753,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="63.95" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="41" t="n"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4440,7 +4775,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F7" s="44" t="inlineStr">
         <is>
           <t>场景1: 默认列表浏览 含对比日期 US — 58.0%
 场景2: UserId筛选 US — 10.4%
@@ -4449,7 +4784,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="63.95" customHeight="1">
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="41" t="n"/>
       <c r="B8" s="22" t="inlineStr">
         <is>
@@ -4471,7 +4806,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F8" s="34" t="inlineStr">
+      <c r="F8" s="44" t="inlineStr">
         <is>
           <t>场景1: 默认汇总 无额外筛选 US — 43.9%
 场景2: UserId筛选 US — 7.9%
@@ -4480,7 +4815,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="41" t="n"/>
       <c r="B9" s="24" t="inlineStr">
         <is>
@@ -4502,8 +4837,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="10">
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>暂停指定广告并还原(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="41" t="n"/>
       <c r="B10" s="22" t="inlineStr">
         <is>
@@ -4525,8 +4865,17 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="11">
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>US ytd 默认 AdState 趋势
+US ytd Campaign下钻趋势
+US ytd 广告组下钻趋势
+US ytd SP/SD 广告类型筛选趋势
+JP ytd 默认市场趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="41" t="n"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -4548,8 +4897,17 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="12">
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>US ytd 默认列表 pageSize=25
+US ytd Campaign下钻 pageSize=100
+US ytd 广告名称搜索
+US ytd 广告组下钻列表
+JP ytd 默认列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="41" t="n"/>
       <c r="B12" s="22" t="inlineStr">
         <is>
@@ -4571,8 +4929,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="13">
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>Campaign+AdGroup 拉取广告
+仅 AdGroup 拉取广告
+Campaign+AdGroup 按 ASIN 名称搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
       <c r="A13" s="41" t="n"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -4592,6 +4957,14 @@
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>US ytd 默认合计 pageSize=25
+US ytd Campaign下钻合计 pageSize=100
+US ytd 广告名称搜索合计
+JP ytd 默认市场合计</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4991,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="41" t="n"/>
       <c r="B15" s="24" t="inlineStr">
         <is>
@@ -4638,6 +5011,12 @@
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>获取全部AsinTag树(不过滤编辑权限) — 74.4%
+仅返回有编辑权限的AsinTag树 — 25.6%</t>
         </is>
       </c>
     </row>
@@ -4663,9 +5042,9 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
-        <is>
-          <t>按TagId列表查子标签数据(ytd汇总) — 78.0%
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>按TagId列表查子标签数据(ytd汇总) — 77.4%
 按TagId查子标签+带对比期 — 0.0%</t>
         </is>
       </c>
@@ -4692,10 +5071,10 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
-        <is>
-          <t>无TagId过滤，ytd趋势图(单Profile) — 70.6%
-多Profile+IsGroupByProfile+TagId过滤 — 7.8%</t>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>无TagId过滤，ytd趋势图(单Profile) — 67.2%
+多Profile+IsGroupByProfile+TagId过滤 — 4.0%</t>
         </is>
       </c>
     </row>
@@ -4721,10 +5100,10 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
-        <is>
-          <t>US市场+多TagId+带对比期 — 79.0%
-非US(JP)市场+TagId+对比期 — 20.4%</t>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>US市场+多TagId+带对比期 — 76.8%
+非US(JP)市场+TagId+对比期 — 23.0%</t>
         </is>
       </c>
     </row>
@@ -4750,7 +5129,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="44" t="inlineStr">
         <is>
           <t>大量Profile+AsinTagId+NTB指标 — 51.4%
 带ACOS指标过滤+对比期+AsinTagId — 35.0%</t>
@@ -4779,10 +5158,10 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
-        <is>
-          <t>单ASIN查已绑定Tag(US市场) — 60.0%
-单ASIN查已绑定Tag(DE市场) — 40.0%</t>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>单ASIN查已绑定Tag(US市场) — 63.6%
+单ASIN查已绑定Tag(DE市场) — 36.4%</t>
         </is>
       </c>
     </row>
@@ -4808,10 +5187,10 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
-        <is>
-          <t>非US市场(AU)+单Profile+无对比 — 20.6%
-US市场+IsGroupByProfile+带对比期 — 78.6%</t>
+      <c r="F21" s="44" t="inlineStr">
+        <is>
+          <t>非US市场(AU)+单Profile+无对比 — 22.4%
+US市场+IsGroupByProfile+带对比期 — 77.2%</t>
         </is>
       </c>
     </row>
@@ -4837,7 +5216,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F22" s="34" t="inlineStr">
+      <c r="F22" s="44" t="inlineStr">
         <is>
           <t>单个Campaign详情页趋势图（按日Dim）
 按Campaign状态筛选的汇总趋势图（Dim=ytd）
@@ -4870,7 +5249,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F23" s="34" t="inlineStr">
+      <c r="F23" s="44" t="inlineStr">
         <is>
           <t>按campaignId+campaignState+日期范围查询campaign列表
 按campaignId+日期范围查询campaign列表（不筛选状态）
@@ -4902,7 +5281,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F24" s="34" t="inlineStr">
+      <c r="F24" s="44" t="inlineStr">
         <is>
           <t>按指定CampaignId精确查询单个广告活动效果数据
 按状态筛选并附带同期对比查询广告活动列表
@@ -4935,7 +5314,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F25" s="34" t="inlineStr">
+      <c r="F25" s="44" t="inlineStr">
         <is>
           <t>按效果指标筛选条件查询广告活动列表
 无筛选条件的默认活动列表查询
@@ -4968,7 +5347,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F26" s="34" t="inlineStr">
+      <c r="F26" s="44" t="inlineStr">
         <is>
           <t>场景1: 勾选指定Campaign汇总
 场景2: 按CampaignTag标签筛选汇总
@@ -5003,18 +5382,12 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId) — 54.0%
-场景2 [US] (CampaignId+CostType) — 9.0%
-场景3 [US] (SegmentName) — 5.2%
-场景4 [US] (ACOS) — 3.2%
-场景5 [JP] (CampaignTagId+SegmentName) — 1.4%
-场景6 [US] (CampaignTagId) — 6.8%
-场景7 [IN] (CampaignName) — 0.0%
-场景8 [UK] (Conversion+ShopperCohortBiddingPercentage) — 0.2%
-场景9 [US] (ACOS+Conversion) — 0.8%
-场景10 [JP] (ROAS+SegmentName) — 0.0%</t>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign下钻
+US ytd 默认浏览
+US ytd Campaign+CostType
+US ytd SegmentName搜索</t>
         </is>
       </c>
     </row>
@@ -5040,18 +5413,12 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId) — 12.6%
-场景2 [US] (CampaignId+CostType) — 3.4%
-场景3 [JP] (SegmentName) — 0.0%
-场景4 [US] (CampaignTagId) — 0.8%
-场景5 [US] (ACOS) — 1.8%
-场景6 [JP] (CampaignTagId+SegmentName) — 1.0%
-场景7 [JP] (CampaignName+SegmentName) — 0.0%
-场景8 [JP] (CampaignTagId+ROAS+SegmentName) — 0.4%
-场景9 [MX] (CampaignName) — 0.0%
-场景10 [US] (CampaignTypeItems+SegmentName) — 0.0%</t>
+      <c r="F28" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign下钻 pageSize=100
+US ytd Campaign+CostType pageSize=100
+US ytd 默认浏览 pageSize=100
+US ytd 默认浏览 pageSize=25</t>
         </is>
       </c>
     </row>
@@ -5077,18 +5444,12 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId) — 13.0%
-场景2 [US] (CampaignId+CostType) — 3.0%
-场景3 [JP] (SegmentName) — 0.2%
-场景4 [US] (CampaignTagId) — 0.6%
-场景5 [JP] (CampaignTagId+SegmentName) — 2.2%
-场景6 [US] (ACOS) — 2.8%
-场景7 [US] (Conversion+ShopperCohortBiddingPercentage) — 0.2%
-场景8 [US] (CampaignName) — 0.6%
-场景9 [US] (CampaignTypeItems+SegmentName) — 0.4%
-场景10 [UK] (Conversion+PortfolioId+ShopperCohortBiddingPercentage) — 0.2%</t>
+      <c r="F29" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign下钻 pageSize=100
+US ytd 默认浏览 pageSize=100
+US ytd Campaign+CostType pageSize=100
+US ytd 默认浏览 pageSize=25</t>
         </is>
       </c>
     </row>
@@ -5114,18 +5475,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId) — 44.6%
-场景2 [US] (CampaignName) — 1.8%
-场景3 [US] (ACOS) — 2.2%
-场景4 [US] (CampaignTagId) — 1.8%
-场景5 [US] (ACOS+Conversion) — 0.4%
-场景6 [US] (AmazonSites) — 0.0%
-场景7 [US] (ROAS+Spend) — 0.0%
-场景8 [US] (PortfolioId) — 0.0%
-场景9 [US] (CampaignId) — 0.0%
-场景10 [US] (CPC) — 0.4%</t>
+      <c r="F30" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign下钻
+US ytd 默认浏览
+UK ytd 默认浏览
+CA ytd Campaign下钻
+US ytd CampaignName搜索</t>
         </is>
       </c>
     </row>
@@ -5151,18 +5507,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId) — 24.4%
-场景2 [US] (CampaignName) — 2.2%
-场景3 [US] (ACOS) — 1.2%
-场景4 [US] (CampaignTagId) — 2.4%
-场景5 [US] (ACOS+Conversion) — 1.0%
-场景6 [US] (ROAS+Spend) — 0.4%
-场景7 [US] (AmazonSites) — 0.4%
-场景8 [US] (CPC) — 0.0%
-场景9 [US] (PortfolioId) — 0.0%
-场景10 [US] (CampaignId) — 0.0%</t>
+      <c r="F31" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign下钻 pageSize=100
+US ytd 默认浏览 pageSize=100
+US ytd 默认浏览 pageSize=25
+US ytd Campaign下钻 pageSize=25
+UK ytd 默认浏览 pageSize=100</t>
         </is>
       </c>
     </row>
@@ -5188,18 +5539,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId) — 21.8%
-场景2 [US] (CampaignName) — 1.4%
-场景3 [US] (ACOS) — 2.0%
-场景4 [US] (CampaignTagId) — 2.2%
-场景5 [US] (ACOS+Conversion) — 0.8%
-场景6 [US] (CampaignId) — 0.0%
-场景7 [US] (AmazonSites) — 0.2%
-场景8 [US] (ROAS+Spend) — 0.4%
-场景9 [US] (CPC) — 0.0%
-场景10 [US] (PortfolioId) — 0.0%</t>
+      <c r="F32" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign下钻 pageSize=100
+US ytd 默认浏览 pageSize=100
+US ytd 默认浏览 pageSize=25
+US ytd Campaign下钻 pageSize=25
+UK ytd 默认浏览 pageSize=100</t>
         </is>
       </c>
     </row>
@@ -5225,18 +5571,11 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId+PlacementTypes) — 78.6%
-场景2 [US] (CampaignId+CostType+PlacementTypes) — 11.6%
-场景3 [JP] (CampaignId+PlacementTypes) — 3.4%
-场景4 [US] (CampaignState) — 2.0%
-场景5 [US] (CampaignState) — 0.8%
-场景6 [US] (CampaignTypeItems) — 1.0%
-场景7 [US] (CampaignName) — 0.8%
-场景8 [US] (CPC) — 0.0%
-场景9 [US] (CampaignId+PlacementTypes) — 1.0%
-场景10 [US] (CampaignState+CampaignTagId) — 0.2%</t>
+      <c r="F33" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign+PlacementTypes
+US ytd Campaign+CostType+PlacementTypes
+US ytd Feed模式 Campaign+PlacementTypes</t>
         </is>
       </c>
     </row>
@@ -5262,18 +5601,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId+CampaignName+CampaignState) — 17.9%
-场景2 [US] (CampaignId+CampaignName+CampaignState+ServingStatus) — 0.0%
-场景3 [US] (CampaignId+CampaignState) — 7.9%
-场景4 [US] (CampaignId) — 0.0%
-场景5 [US] (CampaignId+CampaignState) — 2.6%
-场景6 [US] (CampaignId+CampaignName+CampaignState) — 3.3%
-场景7 [US] (CampaignId+CampaignName) — 0.0%
-场景8 [US] (CampaignId+CampaignState+PortfolioId) — 1.2%
-场景9 [US] (CampaignId+CampaignState+ServingStatus) — 0.0%
-场景10 [US] (CampaignId+CampaignTypeItems) — 0.5%</t>
+      <c r="F34" s="44" t="inlineStr">
+        <is>
+          <t>US ytd CampaignName+State pageSize=10000
+US ytd CampaignType+Name+State pageSize=10000
+US ytd Campaign+State pageSize=10000
+US ytd Name+State+ServingStatus pageSize=10000
+US ytd Campaign下钻 pageSize=10000</t>
         </is>
       </c>
     </row>
@@ -5299,18 +5633,12 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignState) — 67.8%
-场景2 [US] (CampaignName) — 1.0%
-场景3 [US] (CampaignName+CampaignState) — 12.2%
-场景4 [US] (CampaignState) — 0.0%
-场景5 [US] (CampaignState+CampaignTagId) — 6.8%
-场景6 [US] (CampaignTypeItems) — 8.0%
-场景7 [US] (CampaignTypeItems) — 0.0%
-场景8 [US] (CampaignId) — 0.2%
-场景9 [US] (CampaignState+CampaignTagId) — 0.0%
-场景10 [US] (CampaignId+CampaignState) — 0.0%</t>
+      <c r="F35" s="44" t="inlineStr">
+        <is>
+          <t>US ytd CampaignState默认 pageSize=25
+US ytd CampaignState默认 pageSize=500
+US ytd 默认浏览 pageSize=100
+US ytd CampaignType筛选 pageSize=100</t>
         </is>
       </c>
     </row>
@@ -5336,18 +5664,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId+PlacementTypes) — 41.2%
-场景2 [US] (CampaignId+CostType+PlacementTypes) — 5.4%
-场景3 [US] (CampaignId+PlacementTypes) — 0.0%
-场景4 [US] (CampaignId+CostType+PlacementTypes) — 0.0%
-场景5 [US] (CampaignName) — 1.4%
-场景6 [US] (CampaignId+PlacementTypes) — 1.0%
-场景7 [US] (CampaignState) — 45.4%
-场景8 [US] (CampaignTagId) — 0.2%
-场景9 [US] (CampaignState+CampaignTagId) — 0.0%
-场景10 [US] (CampaignId+CampaignState) — 0.0%</t>
+      <c r="F36" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign+PlacementTypes pageSize=100
+US ytd Campaign+PlacementTypes pageSize=25
+US ytd Campaign+CostType+PlacementTypes pageSize=100
+US ytd Feed模式 Campaign+PlacementTypes pageSize=100
+US ytd Campaign+PlacementTypes pageSize=50</t>
         </is>
       </c>
     </row>
@@ -5373,18 +5696,12 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (PlacementTypes) — 31.8%
-场景2 [US] (CampaignId+PlacementTypes) — 14.0%
-场景3 [US] (CampaignTagId+PlacementTypes) — 14.4%
-场景4 [US] (CampaignName+PlacementTypes) — 9.0%
-场景5 [JP] (CampaignName+PlacementTypes) — 3.4%
-场景6 [US] (CampaignTypeItems+PlacementTypes) — 4.8%
-场景7 [JP] (CampaignName+CampaignTagId+PlacementTypes) — 0.0%
-场景8 [US] (ACOS+PlacementTypes) — 4.0%
-场景9 [CA] (PlacementTypes+PortfolioId) — 1.0%
-场景10 [US] (CampaignTagId+CVR+PlacementTypes) — 1.4%</t>
+      <c r="F37" s="44" t="inlineStr">
+        <is>
+          <t>US ytd PlacementTypes默认
+US ytd Campaign+PlacementTypes
+US ytd CampaignName+PlacementTypes
+US ytd GroupBy=Placement</t>
         </is>
       </c>
     </row>
@@ -5410,18 +5727,14 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (CampaignId+PlacementTypes) — 37.0%
-场景2 [US] (CampaignId+CostType+PlacementTypes) — 4.6%
-场景3 [US] (PlacementTypes) — 5.0%
-场景4 [JP] (CampaignId+PlacementTypes) — 1.2%
-场景5 [US] (CampaignTagId+PlacementTypes) — 3.2%
-场景6 [US] (CampaignName+PlacementTypes) — 1.6%
-场景7 [US] (CampaignName+PlacementTypes) — 0.0%
-场景8 [JP] (PlacementTypes+ROAS+Spend) — 0.0%
-场景9 [JP] (CampaignName+CampaignTagId+PlacementTypes) — 0.0%
-场景10 [US] (CampaignId+CostType+PlacementTypes) — 0.0%</t>
+      <c r="F38" s="44" t="inlineStr">
+        <is>
+          <t>US ytd Campaign+PlacementTypes pageSize=100
+US ytd Campaign+PlacementTypes pageSize=25
+US ytd Campaign+CostType+PlacementTypes pageSize=100
+US ytd PlacementTypes默认 pageSize=100
+US ytd PlacementTypes默认 pageSize=25
+US ytd GroupBy=Placement GroupByPlacement pageSize=100</t>
         </is>
       </c>
     </row>
@@ -5447,18 +5760,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
-        <is>
-          <t>场景1 [US] (PlacementTypes) — 20.4%
-场景2 [US] (CampaignId+PlacementTypes) — 9.2%
-场景3 [US] (CampaignTagId+PlacementTypes) — 10.0%
-场景4 [JP] (CampaignName+PlacementTypes) — 1.6%
-场景5 [JP] (CampaignName+PlacementTypes) — 0.0%
-场景6 [US] (CampaignName+PlacementTypes) — 4.4%
-场景7 [JP] (CampaignName+CampaignTagId+PlacementTypes) — 0.0%
-场景8 [JP] (CampaignName+CampaignTypeItems+PlacementTypes) — 0.8%
-场景9 [US] (ACOS+PlacementTypes) — 1.6%
-场景10 [UK] (CampaignTypeItems+PlacementTypes) — 1.8%</t>
+      <c r="F39" s="44" t="inlineStr">
+        <is>
+          <t>US ytd PlacementTypes默认 pageSize=100
+US ytd PlacementTypes默认 pageSize=25
+US ytd Campaign+PlacementTypes pageSize=100
+US ytd CampaignName+PlacementTypes pageSize=100
+US ytd GroupBy=Placement GroupByPlacement pageSize=100</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5792,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="44" t="inlineStr">
         <is>
           <t>单Profile+CampaignTagId+ytd图表 — 37.4%
 多Profile+CampaignTagId+ytd图表 — 0.0%
@@ -5514,7 +5822,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="44" t="inlineStr">
         <is>
           <t>多CampaignTagId+无对比期(US) — 28.0%
 单CampaignTagId+带对比期(US) — 39.6%</t>
@@ -5543,7 +5851,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="F42" s="44" t="inlineStr">
         <is>
           <t>单Profile+CampaignTagId+对比期 — 16.0%
 多Profile+CampaignTagId+自定义MetricIds — 1.2%
@@ -5573,14 +5881,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F43" s="30" t="inlineStr">
+      <c r="F43" s="44" t="inlineStr">
         <is>
           <t>US市场+无TagId过滤(全标签汇总栏) — 75.0%
 非US市场(IN)+多Profile — 23.6%</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="63.95" customHeight="1">
+    <row r="44" ht="64" customHeight="1">
       <c r="A44" s="41" t="n"/>
       <c r="B44" s="21" t="inlineStr">
         <is>
@@ -5602,7 +5910,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F44" s="34" t="inlineStr">
+      <c r="F44" s="44" t="inlineStr">
         <is>
           <t>默认日粒度趋势查询(含环比对比期)
 按CampaignTag过滤的日粒度趋势查询
@@ -5611,7 +5919,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="63.95" customHeight="1">
+    <row r="45" ht="64" customHeight="1">
       <c r="A45" s="41" t="n"/>
       <c r="B45" s="23" t="inlineStr">
         <is>
@@ -5633,7 +5941,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F45" s="34" t="inlineStr">
+      <c r="F45" s="44" t="inlineStr">
         <is>
           <t>Brand+品类过滤日粒度Benchmark(无分享链接)
 不带Brand/品类过滤的整体Benchmark
@@ -5664,10 +5972,9 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F46" s="34" t="inlineStr">
+      <c r="F46" s="44" t="inlineStr">
         <is>
           <t>单Profile按日期范围查询超预算广告活动列表
-多Profile跨店铺合并按日期范围查询超预算广告活动列表
 按Campaign Tag筛选查询超预算广告活动列表</t>
         </is>
       </c>
@@ -5694,7 +6001,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F47" s="34" t="inlineStr">
+      <c r="F47" s="44" t="inlineStr">
         <is>
           <t>基础日期范围查询Out of Budget图表（US市场，无标签/活动过滤）
 非US市场查询Out of Budget图表（汇率换算场景，以CA为代表）
@@ -5724,7 +6031,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F48" s="34" t="inlineStr">
+      <c r="F48" s="44" t="inlineStr">
         <is>
           <t>US站点仅日期范围周对比周(单/多Profile聚合)
 非US市场(DE)基础周对比
@@ -5756,7 +6063,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F49" s="34" t="inlineStr">
+      <c r="F49" s="44" t="inlineStr">
         <is>
           <t>多账号Portfolio下钻子标签ROAS指标(滚动周期对比) — 45.5%
 单账号下钻子标签ROAS指标(月度环比) — 42.4%
@@ -5786,7 +6093,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F50" s="34" t="inlineStr">
+      <c r="F50" s="44" t="inlineStr">
         <is>
           <t>仅日期范围过滤查询Campaign Tag绩效widget(无Tag/Portfolio子筛选)
 按CampaignTagId筛选查询Campaign Tag绩效widget
@@ -5816,7 +6123,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F51" s="34" t="inlineStr">
+      <c r="F51" s="44" t="inlineStr">
         <is>
           <t>查看标签ROAS目标达成率排名(默认汇率换算)
 查看标签ACOS目标达成率排名(默认汇率换算)
@@ -5846,7 +6153,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F52" s="34" t="inlineStr">
+      <c r="F52" s="44" t="inlineStr">
         <is>
           <t>场景1: 默认ROAS视图 无标签筛选 — 57.5%
 场景2: ACOS视图 新版CampaignTag命名 无筛选 — 14.2%
@@ -5878,7 +6185,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F53" s="34" t="inlineStr">
+      <c r="F53" s="44" t="inlineStr">
         <is>
           <t>默认场景：仅日期范围过滤的 Top Performers（按 Spend 排序，开启汇率转换）
 未开启汇率转换（IsExchange=0）的 Top Performers 场景
@@ -5910,7 +6217,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F54" s="34" t="inlineStr">
+      <c r="F54" s="44" t="inlineStr">
         <is>
           <t>仅按报表日期范围查询长尾词报表（无附加过滤）
 按广告系列标签(CampaignTagId)过滤查询长尾词报表
@@ -5940,7 +6247,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F55" s="34" t="inlineStr">
+      <c r="F55" s="44" t="inlineStr">
         <is>
           <t>单词(NumberOfWord=1)长尾关键词按MatchType报表(ROAS指标)
 双词(NumberOfWord=2)长尾关键词按MatchType报表
@@ -5950,7 +6257,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="63.95" customHeight="1">
+    <row r="56" ht="64" customHeight="1">
       <c r="A56" s="41" t="n"/>
       <c r="B56" s="22" t="inlineStr">
         <is>
@@ -5972,7 +6279,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F56" s="34" t="inlineStr">
+      <c r="F56" s="44" t="inlineStr">
         <is>
           <t>基础场景:按天(Dim=date)+CampaignType(headlineSearch)筛选,无Tag/Portfolio筛选
 Campaign Tag筛选场景:附加CampaignTagId筛选,按天展示
@@ -5981,7 +6288,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="63.95" customHeight="1">
+    <row r="57" ht="64" customHeight="1">
       <c r="A57" s="41" t="n"/>
       <c r="B57" s="23" t="inlineStr">
         <is>
@@ -6003,7 +6310,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F57" s="34" t="inlineStr">
+      <c r="F57" s="44" t="inlineStr">
         <is>
           <t>单日期范围查询campaign类型层级绩效(无对比期无筛选)
 按日期范围并指定对比期查询campaign类型层级绩效
@@ -6034,7 +6341,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F58" s="34" t="inlineStr">
+      <c r="F58" s="44" t="inlineStr">
         <is>
           <t>Sponsored Products(SP)明细,单一日期范围(无对比期),ROAS指标
 Sponsored Brands(SB)明细,单一日期范围(无对比期),ROAS指标
@@ -6045,7 +6352,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="63.95" customHeight="1">
+    <row r="59" ht="64" customHeight="1">
       <c r="A59" s="41" t="n"/>
       <c r="B59" s="23" t="inlineStr">
         <is>
@@ -6067,7 +6374,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F59" s="34" t="inlineStr">
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>查询不合规商品(INELIGIBLE)明细列表
 查询缺货商品(NOT BUYABLE)明细列表
@@ -6098,7 +6405,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F60" s="34" t="inlineStr">
+      <c r="F60" s="44" t="inlineStr">
         <is>
           <t>Top Search Terms 按 ROAS 排序（无额外筛选）
 Top Search Terms 按 ACOS 排序（无额外筛选）
@@ -6130,7 +6437,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F61" s="34" t="inlineStr">
+      <c r="F61" s="44" t="inlineStr">
         <is>
           <t>默认查询(无对比期,ROAS指标)
 带环比对比期查询(ROAS指标)
@@ -6163,12 +6470,10 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F62" s="34" t="inlineStr">
-        <is>
-          <t>多Profile(2-4个)组合非分享链路查询
-单Profile非分享链路查询
-多Profile组合通过分享链接(ShareId)访问
-大批量Profile(5个以上/近全选)组合查询</t>
+      <c r="F62" s="44" t="inlineStr">
+        <is>
+          <t>单Profile非分享链路查询
+多Profile组合通过分享链接(ShareId)访问</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6499,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F63" s="34" t="inlineStr">
+      <c r="F63" s="44" t="inlineStr">
         <is>
           <t>仅日期范围过滤查询周维度Campaign表现
 按CampaignTagId过滤查询周维度Campaign表现
@@ -6202,7 +6507,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="63.95" customHeight="1">
+    <row r="64" ht="64" customHeight="1">
       <c r="A64" s="41" t="n"/>
       <c r="B64" s="22" t="inlineStr">
         <is>
@@ -6224,7 +6529,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F64" s="34" t="inlineStr">
+      <c r="F64" s="44" t="inlineStr">
         <is>
           <t>默认视图(ROAS指标,仅日期筛选,全部广告类型) — 73.6%
 ACOS指标视图(仅日期筛选,全部广告类型) — 17.2%
@@ -6255,7 +6560,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F65" s="34" t="inlineStr">
+      <c r="F65" s="44" t="inlineStr">
         <is>
           <t>按日期范围查询商品异常状态计数（无附加过滤）
 按广告系列标签(CampaignTagId)过滤后统计商品异常状态计数
@@ -6285,7 +6590,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F66" s="34" t="inlineStr">
+      <c r="F66" s="44" t="inlineStr">
         <is>
           <t>默认日期范围查询(多Profile,US市场)
 非美国市场(DE)日期范围查询
@@ -6295,7 +6600,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="63.95" customHeight="1">
+    <row r="67" ht="64" customHeight="1">
       <c r="A67" s="41" t="n"/>
       <c r="B67" s="23" t="inlineStr">
         <is>
@@ -6317,7 +6622,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F67" s="34" t="inlineStr">
+      <c r="F67" s="44" t="inlineStr">
         <is>
           <t>仅日期范围过滤查询（美国市场，主流程）
 非美国市场日期范围查询（跨市场场景）
@@ -6348,7 +6653,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F68" s="34" t="inlineStr">
+      <c r="F68" s="44" t="inlineStr">
         <is>
           <t>默认日期范围查询(无标签/组合筛选)
 按CampaignTag标签筛选查询
@@ -6356,7 +6661,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="96" customHeight="1">
       <c r="A69" s="41" t="n"/>
       <c r="B69" s="24" t="inlineStr">
         <is>
@@ -6378,8 +6683,18 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="70">
+      <c r="F69" s="44" t="inlineStr">
+        <is>
+          <t>US 默认启用/暂停状态 100条分页
+US 按日维度广告活动下钻
+US 仅日期过滤无状态条件
+US 广告活动名称搜索
+US 25条分页默认状态
+US Feed模式列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="80" customHeight="1">
       <c r="A70" s="41" t="n"/>
       <c r="B70" s="22" t="inlineStr">
         <is>
@@ -6401,8 +6716,17 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="71">
+      <c r="F70" s="44" t="inlineStr">
+        <is>
+          <t>US 按日广告活动下钻图表
+US ytd 启用/暂停状态图表
+US 仅日期过滤图表
+US 广告活动名称搜索图表
+US Feed模式图表</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="80" customHeight="1">
       <c r="A71" s="41" t="n"/>
       <c r="B71" s="23" t="inlineStr">
         <is>
@@ -6422,6 +6746,15 @@
       <c r="E71" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F71" s="44" t="inlineStr">
+        <is>
+          <t>US 默认启用/暂停状态汇总
+US 按日广告活动下钻汇总
+US 25条分页状态汇总
+US 仅日期过滤汇总
+US 广告活动名称搜索汇总</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6803,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F73" s="34" t="inlineStr">
+      <c r="F73" s="44" t="inlineStr">
         <is>
           <t>场景1: 按CampaignId批量应用建议出价 — 48%
 场景2: 按关键词标签TaggingIds批量应用建议出价 — 20%
@@ -6478,7 +6811,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="15.95" customHeight="1">
+    <row r="74" ht="16" customHeight="1">
       <c r="A74" s="41" t="n"/>
       <c r="B74" s="22" t="inlineStr">
         <is>
@@ -6500,7 +6833,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F74" s="34" t="inlineStr">
+      <c r="F74" s="44" t="inlineStr">
         <is>
           <t>场景1: 按关键词文本精确匹配删除标签 — 100%</t>
         </is>
@@ -6528,7 +6861,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F75" s="34" t="inlineStr">
+      <c r="F75" s="44" t="inlineStr">
         <is>
           <t>场景1: 按关键词文本筛选打标签 — 52%
 场景2: 按指标筛选打标签 — 30%
@@ -6559,7 +6892,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="48" customHeight="1">
       <c r="A77" s="41" t="n"/>
       <c r="B77" s="24" t="inlineStr">
         <is>
@@ -6581,8 +6914,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="78">
+      <c r="F77" s="44" t="inlineStr">
+        <is>
+          <t>US 子标签绩效列表
+US Feed账号子标签列表
+US 精简字段子标签查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="64" customHeight="1">
       <c r="A78" s="41" t="n"/>
       <c r="B78" s="22" t="inlineStr">
         <is>
@@ -6604,8 +6944,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="79">
+      <c r="F78" s="44" t="inlineStr">
+        <is>
+          <t>US 默认汇总趋势
+US 指定关键词标签汇总
+JP 市场汇总趋势
+US 月度趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="64" customHeight="1">
       <c r="A79" s="41" t="n"/>
       <c r="B79" s="23" t="inlineStr">
         <is>
@@ -6627,8 +6975,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="80">
+      <c r="F79" s="44" t="inlineStr">
+        <is>
+          <t>US 默认标签列表
+JP 标签列表
+未指定市场标签列表
+指定关键词标签筛选</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="64" customHeight="1">
       <c r="A80" s="41" t="n"/>
       <c r="B80" s="22" t="inlineStr">
         <is>
@@ -6650,8 +7006,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="81">
+      <c r="F80" s="44" t="inlineStr">
+        <is>
+          <t>US 默认25条分页
+US 100条大页浏览
+US 指定标签100条分页
+US Feed账号100条分页</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="64" customHeight="1">
       <c r="A81" s="41" t="n"/>
       <c r="B81" s="23" t="inlineStr">
         <is>
@@ -6671,6 +7035,14 @@
       <c r="E81" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F81" s="44" t="inlineStr">
+        <is>
+          <t>US 默认25条汇总
+US 100条汇总
+US 指定标签100条汇总
+US Feed账号100条汇总</t>
         </is>
       </c>
     </row>
@@ -6696,7 +7068,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F82" s="30" t="inlineStr">
+      <c r="F82" s="44" t="inlineStr">
         <is>
           <t>场景1: 单关键词精确匹配单标签 — 10%
 场景2: 中等关键词集匹配少量标签 — 30%
@@ -6726,14 +7098,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F83" s="30" t="inlineStr">
+      <c r="F83" s="44" t="inlineStr">
         <is>
           <t>场景1: 标准搜索词报告浏览 ytd US Spend降序 — 80%
 场景2: pageSize100 ACOS指标 大量TagIds — 20%</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="15.95" customHeight="1">
+    <row r="84" ht="16" customHeight="1">
       <c r="A84" s="41" t="n"/>
       <c r="B84" s="22" t="inlineStr">
         <is>
@@ -6755,7 +7127,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F84" s="30" t="inlineStr">
+      <c r="F84" s="44" t="inlineStr">
         <is>
           <t>场景1: 标准搜索词报告浏览 ytd US</t>
         </is>
@@ -6783,14 +7155,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F85" s="30" t="inlineStr">
+      <c r="F85" s="44" t="inlineStr">
         <is>
           <t>场景1: SP手动 按关键词文本分组 指定匹配类型 词数过滤 — 40%
 场景2: SP手动 Phrase匹配类型 IncludeZero pageSize100 — 20%</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15.95" customHeight="1">
+    <row r="86" ht="16" customHeight="1">
       <c r="A86" s="41" t="n"/>
       <c r="B86" s="22" t="inlineStr">
         <is>
@@ -6812,7 +7184,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F86" s="30" t="inlineStr">
+      <c r="F86" s="44" t="inlineStr">
         <is>
           <t>场景1: 指定CampaignId过滤 全量States ytd US</t>
         </is>
@@ -6840,7 +7212,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F87" s="30" t="inlineStr">
+      <c r="F87" s="44" t="inlineStr">
         <is>
           <t>场景1: 单关键词多标签匹配 — 100.0%
 场景2: 多关键词少量标签匹配 — 0.0%</t>
@@ -6870,7 +7242,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="16" customHeight="1">
       <c r="A89" s="41" t="n"/>
       <c r="B89" s="24" t="inlineStr">
         <is>
@@ -6892,8 +7264,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="90">
+      <c r="F89" s="44" t="inlineStr">
+        <is>
+          <t>启用并恢复单个SP否定关键词(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="112" customHeight="1">
       <c r="A90" s="41" t="n"/>
       <c r="B90" s="22" t="inlineStr">
         <is>
@@ -6913,6 +7290,17 @@
       <c r="E90" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F90" s="44" t="inlineStr">
+        <is>
+          <t>US Campaign 100条分页
+US Profile 100条分页
+US Campaign 25条分页
+CA Profile 100条分页
+US 名称关键词搜索
+US Enabled状态筛选
+US Campaign与AdGroup钻取</t>
         </is>
       </c>
     </row>
@@ -6938,7 +7326,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F91" s="30" t="inlineStr">
+      <c r="F91" s="44" t="inlineStr">
         <is>
           <t>场景1: ytd US 单ASIN过滤 日期范围图表 — 40%
 场景2: ytd US Campaign过滤 状态过滤 — 40%
@@ -6946,7 +7334,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="48" customHeight="1">
+    <row r="92" ht="64" customHeight="1">
       <c r="A92" s="41" t="n"/>
       <c r="B92" s="22" t="inlineStr">
         <is>
@@ -6968,11 +7356,12 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F92" s="30" t="inlineStr">
+      <c r="F92" s="44" t="inlineStr">
         <is>
           <t>场景1: 标准分页列表 ytd JP市场 Spend排序 — 35%
 场景2: ytd US ASIN过滤 AsinGroupBy isSameSku — 30%
-场景3: JP市场 状态过滤 完整字段列表 — 35%</t>
+场景3: JP市场 状态过滤 完整字段列表 — 35%
+场景2: ytd US ASIN过滤 AsinGroupBy isSameSku — 30%</t>
         </is>
       </c>
     </row>
@@ -6998,10 +7387,9 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F93" s="30" t="inlineStr">
-        <is>
-          <t>场景1: 全量导出 enabled状态 ES市场 isFead过滤 — 40%
-场景2: ytd US ASIN过滤 AsinGroupBy isSameSku — 30%</t>
+      <c r="F93" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 全量导出 enabled状态 ES市场 isFead过滤 — 40%</t>
         </is>
       </c>
     </row>
@@ -7027,14 +7415,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F94" s="30" t="inlineStr">
+      <c r="F94" s="44" t="inlineStr">
         <is>
           <t>场景1: 多Profile汇总 US ASIN过滤 状态过滤 — 60%
 场景2: 单Profile汇总 US 标准状态过滤 无ASIN过滤 — 40%</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="63.95" customHeight="1">
+    <row r="95" ht="64" customHeight="1">
       <c r="A95" s="41" t="n"/>
       <c r="B95" s="24" t="inlineStr">
         <is>
@@ -7056,7 +7444,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F95" s="34" t="inlineStr">
+      <c r="F95" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标 — 56.2%
 场景2: SP广告 — 19.8%
@@ -7088,7 +7476,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="63.95" customHeight="1">
+    <row r="97" ht="64" customHeight="1">
       <c r="A97" s="41" t="n"/>
       <c r="B97" s="23" t="inlineStr">
         <is>
@@ -7110,7 +7498,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F97" s="34" t="inlineStr">
+      <c r="F97" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标 — 59.2%
 场景2: SP广告 — 19.0%
@@ -7119,7 +7507,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="63.95" customHeight="1">
+    <row r="98" ht="64" customHeight="1">
       <c r="A98" s="41" t="n"/>
       <c r="B98" s="22" t="inlineStr">
         <is>
@@ -7141,7 +7529,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F98" s="34" t="inlineStr">
+      <c r="F98" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+按分组+Prompt状态汇总 — 20.8%
 场景2: SP广告+含NTB指标 — 20.2%
@@ -7150,7 +7538,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="63.95" customHeight="1">
+    <row r="99" ht="64" customHeight="1">
       <c r="A99" s="41" t="n"/>
       <c r="B99" s="23" t="inlineStr">
         <is>
@@ -7172,7 +7560,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F99" s="34" t="inlineStr">
+      <c r="F99" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告 — 40.7%
 场景2: SP广告+含NTB指标 — 37.0%
@@ -7181,7 +7569,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="63.95" customHeight="1">
+    <row r="100" ht="64" customHeight="1">
       <c r="A100" s="41" t="n"/>
       <c r="B100" s="22" t="inlineStr">
         <is>
@@ -7203,7 +7591,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F100" s="34" t="inlineStr">
+      <c r="F100" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标 — 47.4%
 场景2: SP广告 — 23.2%
@@ -7212,7 +7600,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15.95" customHeight="1">
+    <row r="101" ht="16" customHeight="1">
       <c r="A101" s="41" t="n"/>
       <c r="B101" s="23" t="inlineStr">
         <is>
@@ -7234,13 +7622,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F101" s="34" t="inlineStr">
+      <c r="F101" s="44" t="inlineStr">
         <is>
           <t>场景1: 不限广告类型 — 100.0%</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="63.95" customHeight="1">
+    <row r="102" ht="64" customHeight="1">
       <c r="A102" s="41" t="n"/>
       <c r="B102" s="22" t="inlineStr">
         <is>
@@ -7262,7 +7650,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F102" s="34" t="inlineStr">
+      <c r="F102" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+按分组+Prompt状态汇总 — 24.4%
 场景2: 不限广告类型+按分组维度汇总 — 12.2%
@@ -7271,7 +7659,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="63.95" customHeight="1">
+    <row r="103" ht="64" customHeight="1">
       <c r="A103" s="41" t="n"/>
       <c r="B103" s="23" t="inlineStr">
         <is>
@@ -7293,7 +7681,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F103" s="34" t="inlineStr">
+      <c r="F103" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标 — 53.6%
 场景2: SP广告 — 19.4%
@@ -7302,7 +7690,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="63.95" customHeight="1">
+    <row r="104" ht="64" customHeight="1">
       <c r="A104" s="41" t="n"/>
       <c r="B104" s="22" t="inlineStr">
         <is>
@@ -7324,7 +7712,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F104" s="34" t="inlineStr">
+      <c r="F104" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标+含PromptText过滤 — 51.9%
 场景2: SP广告+含PromptText过滤 — 22.4%
@@ -7333,7 +7721,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="63.95" customHeight="1">
+    <row r="105" ht="64" customHeight="1">
       <c r="A105" s="41" t="n"/>
       <c r="B105" s="23" t="inlineStr">
         <is>
@@ -7355,7 +7743,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F105" s="34" t="inlineStr">
+      <c r="F105" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告 — 73.0%
 场景2: 不限广告类型 — 4.4%
@@ -7364,7 +7752,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="63.95" customHeight="1">
+    <row r="106" ht="64" customHeight="1">
       <c r="A106" s="41" t="n"/>
       <c r="B106" s="22" t="inlineStr">
         <is>
@@ -7386,7 +7774,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F106" s="34" t="inlineStr">
+      <c r="F106" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标 — 42.5%
 场景2: SP广告 — 30.0%
@@ -7395,7 +7783,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="63.95" customHeight="1">
+    <row r="107" ht="64" customHeight="1">
       <c r="A107" s="41" t="n"/>
       <c r="B107" s="23" t="inlineStr">
         <is>
@@ -7417,7 +7805,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F107" s="34" t="inlineStr">
+      <c r="F107" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告 — 73.0%
 场景2: SB+SP广告 — 6.0%
@@ -7426,7 +7814,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="63.95" customHeight="1">
+    <row r="108" ht="64" customHeight="1">
       <c r="A108" s="41" t="n"/>
       <c r="B108" s="22" t="inlineStr">
         <is>
@@ -7448,7 +7836,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F108" s="34" t="inlineStr">
+      <c r="F108" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告 — 74.2%
 场景2: 不限广告类型 — 5.4%
@@ -7457,7 +7845,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="63.95" customHeight="1">
+    <row r="109" ht="64" customHeight="1">
       <c r="A109" s="41" t="n"/>
       <c r="B109" s="23" t="inlineStr">
         <is>
@@ -7479,7 +7867,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F109" s="34" t="inlineStr">
+      <c r="F109" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标 — 56.2%
 场景2: SP广告 — 17.6%
@@ -7488,7 +7876,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="63.95" customHeight="1">
+    <row r="110" ht="64" customHeight="1">
       <c r="A110" s="41" t="n"/>
       <c r="B110" s="22" t="inlineStr">
         <is>
@@ -7510,7 +7898,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F110" s="34" t="inlineStr">
+      <c r="F110" s="44" t="inlineStr">
         <is>
           <t>场景1: SP广告+含NTB指标 — 16.8%
 场景2: SP广告+含NTB指标 — 13.2%
@@ -7519,7 +7907,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="16" customHeight="1">
       <c r="A111" s="41" t="n"/>
       <c r="B111" s="24" t="inlineStr">
         <is>
@@ -7541,8 +7929,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="112">
+      <c r="F111" s="44" t="inlineStr">
+        <is>
+          <t>按搜索词添加标签并清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1">
       <c r="A112" s="41" t="n"/>
       <c r="B112" s="22" t="inlineStr">
         <is>
@@ -7564,8 +7957,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="113">
+      <c r="F112" s="44" t="inlineStr">
+        <is>
+          <t>精确目标调价并还原</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
       <c r="A113" s="41" t="n"/>
       <c r="B113" s="23" t="inlineStr">
         <is>
@@ -7587,8 +7985,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="114">
+      <c r="F113" s="44" t="inlineStr">
+        <is>
+          <t>暂停受控SP否定词并还原</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="48" customHeight="1">
       <c r="A114" s="41" t="n"/>
       <c r="B114" s="22" t="inlineStr">
         <is>
@@ -7610,8 +8013,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="115">
+      <c r="F114" s="44" t="inlineStr">
+        <is>
+          <t>US默认汇总趋势
+US活动钻取趋势
+US逐日趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="16" customHeight="1">
       <c r="A115" s="41" t="n"/>
       <c r="B115" s="23" t="inlineStr">
         <is>
@@ -7633,8 +8043,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="116">
+      <c r="F115" s="44" t="inlineStr">
+        <is>
+          <t>查询搜索词否定状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1">
       <c r="A116" s="41" t="n"/>
       <c r="B116" s="22" t="inlineStr">
         <is>
@@ -7656,8 +8071,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="117">
+      <c r="F116" s="44" t="inlineStr">
+        <is>
+          <t>Click与ROAS筛选后全选
+零转化高点击筛选后全选</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="64" customHeight="1">
       <c r="A117" s="41" t="n"/>
       <c r="B117" s="23" t="inlineStr">
         <is>
@@ -7679,8 +8100,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="118">
+      <c r="F117" s="44" t="inlineStr">
+        <is>
+          <t>US活动钻取分页报表
+US默认分页报表
+大页导出浏览
+US逐日报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="48" customHeight="1">
       <c r="A118" s="41" t="n"/>
       <c r="B118" s="22" t="inlineStr">
         <is>
@@ -7700,6 +8129,13 @@
       <c r="E118" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F118" s="44" t="inlineStr">
+        <is>
+          <t>US默认汇总
+US活动钻取汇总
+US逐日口径汇总</t>
         </is>
       </c>
     </row>
@@ -7725,7 +8161,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F119" s="30" t="inlineStr">
+      <c r="F119" s="44" t="inlineStr">
         <is>
           <t>场景1: Campaign+日期过滤 Campaign汇总含广告组数 — 52.6%
 场景2: Campaign+日期过滤 CostControl输出不含AdGroupCount — 18.8%
@@ -7758,7 +8194,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F120" s="34" t="inlineStr">
+      <c r="F120" s="44" t="inlineStr">
         <is>
           <t>场景1: 按百分比批量调整竞价 Type0 — 48%
 场景2: 固定竞价批量更新 Type1 — 31%
@@ -7788,7 +8224,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F121" s="34" t="inlineStr">
+      <c r="F121" s="44" t="inlineStr">
         <is>
           <t>场景1: 批量暂停Target — 67%
 场景2: 批量启用Target — 29%</t>
@@ -7841,7 +8277,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="15.95" customHeight="1">
+    <row r="124" ht="16" customHeight="1">
       <c r="A124" s="41" t="n"/>
       <c r="B124" s="22" t="inlineStr">
         <is>
@@ -7863,7 +8299,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F124" s="34" t="inlineStr">
+      <c r="F124" s="44" t="inlineStr">
         <is>
           <t>场景1: 单日小时级Target报表 JP市场 — 14%</t>
         </is>
@@ -7960,7 +8396,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F128" s="34" t="inlineStr">
+      <c r="F128" s="44" t="inlineStr">
         <is>
           <t>场景1: 单Campaign默认视图 ytd US Spend降序 — 35%
 场景2: 跨账号ROAS+Spend过滤 多Profile — 5%
@@ -7990,7 +8426,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F129" s="34" t="inlineStr">
+      <c r="F129" s="44" t="inlineStr">
         <is>
           <t>场景1: 单Campaign汇总行 ytd US — 55%
 场景2: 带ROAS过滤的跨账号汇总 — 20%</t>
@@ -8825,7 +9261,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.95" customHeight="1">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="41" t="n"/>
       <c r="B28" s="27" t="inlineStr">
         <is>
@@ -8847,13 +9283,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F28" s="34" t="inlineStr">
+      <c r="F28" s="44" t="inlineStr">
         <is>
           <t>冒烟测试(dev环境样本,非真实客户场景)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15.95" customHeight="1">
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="41" t="n"/>
       <c r="B29" s="23" t="inlineStr">
         <is>
@@ -8875,7 +9311,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F29" s="34" t="inlineStr">
+      <c r="F29" s="44" t="inlineStr">
         <is>
           <t>冒烟测试(dev环境样本,非真实客户场景)</t>
         </is>
@@ -8904,7 +9340,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.95" customHeight="1">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" s="41" t="n"/>
       <c r="B31" s="23" t="inlineStr">
         <is>
@@ -8926,7 +9362,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F31" s="34" t="inlineStr">
+      <c r="F31" s="44" t="inlineStr">
         <is>
           <t>冒烟测试(dev环境样本,默认分页,非真实客户场景)</t>
         </is>
@@ -8955,7 +9391,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.95" customHeight="1">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" s="41" t="n"/>
       <c r="B33" s="23" t="inlineStr">
         <is>
@@ -8977,7 +9413,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F33" s="34" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>冒烟测试(dev环境样本,非真实客户场景)</t>
         </is>
@@ -9144,7 +9580,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="41" t="n"/>
       <c r="B41" s="23" t="inlineStr">
         <is>
@@ -9164,6 +9600,12 @@
       <c r="E41" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F41" s="44" t="inlineStr">
+        <is>
+          <t>isManaged=0 导出全部账号
+isManaged=1 导出已托管账号</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9632,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="16" customHeight="1">
       <c r="A43" s="41" t="n"/>
       <c r="B43" s="23" t="inlineStr">
         <is>
@@ -9212,8 +9654,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="44">
+      <c r="F43" s="44" t="inlineStr">
+        <is>
+          <t>无参拉取管理者全部 Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="41" t="n"/>
       <c r="B44" s="27" t="inlineStr">
         <is>
@@ -9235,8 +9682,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="45">
+      <c r="F44" s="44" t="inlineStr">
+        <is>
+          <t>单个 advertiserId 查 3P Profile
+两个 advertiserId 查 3P Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
       <c r="A45" s="41" t="n"/>
       <c r="B45" s="23" t="inlineStr">
         <is>
@@ -9258,8 +9711,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="46">
+      <c r="F45" s="44" t="inlineStr">
+        <is>
+          <t>amazon 查自己的 Profile 列表
+dsp 查自己的 Profile 列表
+dsp 仅 targetUserId 无 addedByUserId
+amazon 仅 targetUserId 无 addedByUserId</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
       <c r="A46" s="41" t="n"/>
       <c r="B46" s="27" t="inlineStr">
         <is>
@@ -9281,8 +9742,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="47">
+      <c r="F46" s="44" t="inlineStr">
+        <is>
+          <t>按 DSP profileId 查托管广告主</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
       <c r="A47" s="41" t="n"/>
       <c r="B47" s="23" t="inlineStr">
         <is>
@@ -9302,6 +9768,11 @@
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F47" s="44" t="inlineStr">
+        <is>
+          <t>按 advertiserId 查托管日志</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9799,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="64" customHeight="1">
       <c r="A49" s="41" t="n"/>
       <c r="B49" s="23" t="inlineStr">
         <is>
@@ -9350,8 +9821,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="50">
+      <c r="F49" s="44" t="inlineStr">
+        <is>
+          <t>US 市场托管日志
+CA 市场托管日志
+JP 市场托管日志
+UK 市场托管日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="41" t="n"/>
       <c r="B50" s="27" t="inlineStr">
         <is>
@@ -9371,6 +9850,12 @@
       <c r="E50" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F50" s="44" t="inlineStr">
+        <is>
+          <t>amazon 查其他 client Profile
+dsp 查其他 client Profile</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9882,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="32" customHeight="1">
       <c r="A52" s="41" t="n"/>
       <c r="B52" s="27" t="inlineStr">
         <is>
@@ -9419,8 +9904,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="53">
+      <c r="F52" s="44" t="inlineStr">
+        <is>
+          <t>仅 userId 查活动标签权限
+userId+时区 查活动标签权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
       <c r="A53" s="41" t="n"/>
       <c r="B53" s="23" t="inlineStr">
         <is>
@@ -9442,8 +9933,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="54">
+      <c r="F53" s="44" t="inlineStr">
+        <is>
+          <t>无参拉取 Vendor 账号组</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
       <c r="A54" s="41" t="n"/>
       <c r="B54" s="27" t="inlineStr">
         <is>
@@ -9463,6 +9959,11 @@
       <c r="E54" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F54" s="44" t="inlineStr">
+        <is>
+          <t>无参查询当前用户标签权限开关</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9990,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="16" customHeight="1">
       <c r="A56" s="41" t="n"/>
       <c r="B56" s="27" t="inlineStr">
         <is>
@@ -9511,8 +10012,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="57">
+      <c r="F56" s="44" t="inlineStr">
+        <is>
+          <t>取消托管后还原</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
       <c r="A57" s="41" t="n"/>
       <c r="B57" s="23" t="inlineStr">
         <is>
@@ -9532,6 +10038,11 @@
       <c r="E57" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F57" s="44" t="inlineStr">
+        <is>
+          <t>修改 Profile 昵称后还原</t>
         </is>
       </c>
     </row>
@@ -9627,7 +10138,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="16" customHeight="1">
       <c r="A62" s="41" t="n"/>
       <c r="B62" s="27" t="inlineStr">
         <is>
@@ -9647,6 +10158,11 @@
       <c r="E62" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F62" s="44" t="inlineStr">
+        <is>
+          <t>修改 Vendor 账号名后还原</t>
         </is>
       </c>
     </row>
@@ -9673,7 +10189,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15.95" customHeight="1">
+    <row r="64" ht="16" customHeight="1">
       <c r="A64" s="41" t="n"/>
       <c r="B64" s="27" t="inlineStr">
         <is>
@@ -9695,7 +10211,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F64" s="34" t="inlineStr">
+      <c r="F64" s="44" t="inlineStr">
         <is>
           <t>场景1: 批量改广告名(可逆,占比100%) — 100%</t>
         </is>
@@ -9815,7 +10331,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F69" s="34" t="inlineStr">
+      <c r="F69" s="44" t="inlineStr">
         <is>
           <t>场景1: 按Profile+Campaign查广告(占比90%) — 90%
 场景2: 指定Adgroup查广告(占比10%) — 10%</t>
@@ -9844,7 +10360,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F70" s="34" t="inlineStr">
+      <c r="F70" s="44" t="inlineStr">
         <is>
           <t>场景1: 广告级逐日趋势(dim=date,占比99%) — 99%
 场景2: Profile汇总(dim=ytd,占比1%) — 1%</t>
@@ -9896,7 +10412,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F72" s="34" t="inlineStr">
+      <c r="F72" s="44" t="inlineStr">
         <is>
           <t>场景1: SB广告单活动详情(SbAds,占比96%) — 96%
 场景2: Profile聚合列表(aggregate,占比4%) — 4%</t>
@@ -9925,7 +10441,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F73" s="34" t="inlineStr">
+      <c r="F73" s="44" t="inlineStr">
         <is>
           <t>场景1: SB广告单活动汇总(SbAds,占比75%) — 75%
 场景2: Profile聚合汇总(aggregate,占比25%) — 25%</t>
@@ -10115,7 +10631,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F81" s="34" t="inlineStr">
+      <c r="F81" s="44" t="inlineStr">
         <is>
           <t>批量创建ENABLED状态PROMPTS广告扩展(含后置清理) — 94.1%
 批量创建PAUSED状态PROMPTS广告扩展 — 5.9%</t>
@@ -10191,7 +10707,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="64" customHeight="1">
       <c r="A85" s="41" t="n"/>
       <c r="B85" s="24" t="inlineStr">
         <is>
@@ -10213,8 +10729,16 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="86">
+      <c r="F85" s="44" t="inlineStr">
+        <is>
+          <t>US ytd 子标签 pageSize=10000
+US ytd 子标签 pageSize=300
+DE ytd 子标签 pageSize=300
+CA ytd 子标签 pageSize=300</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
       <c r="A86" s="41" t="n"/>
       <c r="B86" s="27" t="inlineStr">
         <is>
@@ -10236,8 +10760,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="87">
+      <c r="F86" s="44" t="inlineStr">
+        <is>
+          <t>默认拉取广告组标签树</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="80" customHeight="1">
       <c r="A87" s="41" t="n"/>
       <c r="B87" s="23" t="inlineStr">
         <is>
@@ -10259,8 +10788,17 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="88">
+      <c r="F87" s="44" t="inlineStr">
+        <is>
+          <t>US ytd 默认汇总趋势
+US ytd UserId筛选趋势
+US ytd TagId筛选趋势
+DE date TagId日粒度趋势
+US date TagId日粒度趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="96" customHeight="1">
       <c r="A88" s="41" t="n"/>
       <c r="B88" s="27" t="inlineStr">
         <is>
@@ -10282,8 +10820,18 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="89">
+      <c r="F88" s="44" t="inlineStr">
+        <is>
+          <t>US ytd 默认列表 pageSize=25
+US ytd UserId筛选 pageSize=25
+DE ytd TagId筛选 pageSize=300
+US ytd 列表 pageSize=100
+CA ytd TagId筛选 pageSize=300
+US ytd TagId筛选 pageSize=25</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="96" customHeight="1">
       <c r="A89" s="41" t="n"/>
       <c r="B89" s="23" t="inlineStr">
         <is>
@@ -10303,6 +10851,16 @@
       <c r="E89" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F89" s="44" t="inlineStr">
+        <is>
+          <t>US ytd 默认合计
+DE ytd TagId合计
+US ytd TagId合计
+CA ytd TagId合计
+US ytd UserId合计
+US ytd 合计 pageSize=100</t>
         </is>
       </c>
     </row>
@@ -10468,14 +11026,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F95" s="34" t="inlineStr">
+      <c r="F95" s="44" t="inlineStr">
         <is>
           <t>更新SD广告组状态为paused（含后置恢复） — 75%
 更新SD广告组状态为enabled（含后置恢复） — 15%</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="63.95" customHeight="1">
+    <row r="96" ht="64" customHeight="1">
       <c r="A96" s="41" t="n"/>
       <c r="B96" s="26" t="inlineStr">
         <is>
@@ -10497,7 +11055,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F96" s="34" t="inlineStr">
+      <c r="F96" s="44" t="inlineStr">
         <is>
           <t>场景1: 单AdGroup ASIN定向新增 — 29.8%
 场景2: 单AdGroup 自定义SKU编号定向新增 — 20.0%
@@ -10528,7 +11086,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F97" s="34" t="inlineStr">
+      <c r="F97" s="44" t="inlineStr">
         <is>
           <t>场景1: 单个SP广告组少量ASIN添加(1-4个)
 场景2: SP广告组中等批量多规格SKU添加(5-49个)
@@ -10558,7 +11116,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F98" s="34" t="inlineStr">
+      <c r="F98" s="44" t="inlineStr">
         <is>
           <t>单广告组添加单个ASIN商品定向(含后置归档,可重复) — 27%
 单广告组批量粘贴多个ASIN商品定向(含后置归档,可重复) — 33%
@@ -10634,7 +11192,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F101" s="34" t="inlineStr">
+      <c r="F101" s="44" t="inlineStr">
         <is>
           <t>Campaign级批量创建否定精确匹配关键词(SP)
 Campaign级批量创建否定词组匹配关键词(SB)
@@ -10664,7 +11222,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F102" s="34" t="inlineStr">
+      <c r="F102" s="44" t="inlineStr">
         <is>
           <t>SP广告组仅设置ROAS竞价优化目标(ACOS未设置/高频场景)
 SP手动/PAT广告组同时设置ACOS与ROAS双竞价优化目标(中频场景)</t>
@@ -10693,7 +11251,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F103" s="34" t="inlineStr">
+      <c r="F103" s="44" t="inlineStr">
         <is>
           <t>场景1: 单ASIN替换 旧目标转Paused 新目标默认 — 90.9%
 场景2: 全字段显式替换 旧目标Archived 新目标Enabled keep=false — 7.07%
@@ -10724,7 +11282,7 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="48" customHeight="1">
       <c r="A105" s="41" t="n"/>
       <c r="B105" s="23" t="inlineStr">
         <is>
@@ -10746,8 +11304,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="106">
+      <c r="F105" s="44" t="inlineStr">
+        <is>
+          <t>SP单个AdGroup批量改价（高频场景）
+SP多个AdGroup跨Campaign批量改价（中频场景）
+跨广告类型批量改价含SD设置bidOptimization（中频场景）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="128" customHeight="1">
       <c r="A106" s="41" t="n"/>
       <c r="B106" s="27" t="inlineStr">
         <is>
@@ -10767,6 +11332,18 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F106" s="44" t="inlineStr">
+        <is>
+          <t>场景1: SponsoredProducts通用场景 启用AdGroup
+场景2: SponsoredProducts手动PAT场景 暂停AdGroup
+场景3: SponsoredDisplay场景 切换AdGroup状态
+场景4: SponsoredProducts通用场景 归档AdGroup
+CopyAdGroup SP Manual ToDifferentCampaign — 63.8%
+CopyAdGroup SP Manual SameCampaign Duplicate — 17.7%
+CopyAdGroup SP Auto ToDifferentCampaign — 15.6%
+复制SponsoredDisplay广告组（manual targeting，同campaign内复制）</t>
         </is>
       </c>
     </row>
@@ -10793,7 +11370,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="16" customHeight="1">
       <c r="A108" s="41" t="n"/>
       <c r="B108" s="27" t="inlineStr">
         <is>
@@ -10813,6 +11390,11 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F108" s="44" t="inlineStr">
+        <is>
+          <t>批量设置SD广告组优化方式为clicks(前置读原值+后置还原,可重复)</t>
         </is>
       </c>
     </row>
@@ -10868,7 +11450,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F110" s="34" t="inlineStr">
+      <c r="F110" s="44" t="inlineStr">
         <is>
           <t>场景1: SP手动投放AdGroup单ASIN复制 — 82.4%
 场景2: SP自动投放AdGroup单ASIN复制 — 6.8%
@@ -10876,7 +11458,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="32" customHeight="1">
       <c r="A111" s="41" t="n"/>
       <c r="B111" s="23" t="inlineStr">
         <is>
@@ -10896,6 +11478,12 @@
       <c r="E111" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F111" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 同Campaign内复制并保持enabled
+场景2: 同Campaign内复制并保持paused</t>
         </is>
       </c>
     </row>
@@ -10927,7 +11515,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="15.95" customHeight="1">
+    <row r="113" ht="16" customHeight="1">
       <c r="A113" s="41" t="n"/>
       <c r="B113" s="23" t="inlineStr">
         <is>
@@ -10949,7 +11537,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F113" s="34" t="inlineStr">
+      <c r="F113" s="44" t="inlineStr">
         <is>
           <t>复制SD广告组(含创意+ASIN定向,含后置清理,可重复)</t>
         </is>
@@ -11000,27 +11588,10 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F115" s="34" t="inlineStr">
-        <is>
-          <t>SP单个AdGroup批量改价（高频场景）
-SP多个AdGroup跨Campaign批量改价（中频场景）
-跨广告类型批量改价含SD设置bidOptimization（中频场景）
-场景1: SponsoredProducts通用场景 启用AdGroup
-场景2: SponsoredProducts手动PAT场景 暂停AdGroup
-场景3: SponsoredDisplay场景 切换AdGroup状态
-场景4: SponsoredProducts通用场景 归档AdGroup
-批量设置SD广告组优化方式为clicks(前置读原值+后置还原,可重复)
-通过全局唯一id查询广告组编辑数据 — 60%
-通过profileId+campaignId+adGroupId组合查询广告组编辑数据 — 10%
-低价位默认出价调整(&lt;1,含读原值+还原) — 50.8%
-中价位默认出价调整(1~3,含读原值+还原) — 40.9%
-高价位默认出价调整(&gt;3,含读原值+还原) — 8.3%
-SD AdGroup Update Basic Attributes NoCostControl
-SD AdGroup Update EnableCostControl
-SD AdGroup Update DisableCostControl
-批量修改AdGroup名称(含读原值+还原,可重复)
-普通改名场景-读取原名后改名并还原
-带sourceName(Creative Hub来源)的改名场景-读取原名后改名并还原</t>
+      <c r="F115" s="44" t="inlineStr">
+        <is>
+          <t>通过全局唯一id查询广告组编辑数据 — 60%
+通过profileId+campaignId+adGroupId组合查询广告组编辑数据 — 10%</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11617,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F116" s="34" t="inlineStr">
+      <c r="F116" s="44" t="inlineStr">
         <is>
           <t>不指定CampaignIds查询全部候选AdGroup — 61.4%
 单个CampaignId查询PAT研究AdGroup — 36.8%
@@ -11099,7 +11670,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F118" s="34" t="inlineStr">
+      <c r="F118" s="44" t="inlineStr">
         <is>
           <t>SB广告活动详情页-单Campaign级Adgroup趋势图（按周Dim）
 Adgroup列表页-账户级总览趋势图（不筛选任何Campaign/AdGroup）
@@ -11109,7 +11680,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="63.95" customHeight="1">
+    <row r="119" ht="64" customHeight="1">
       <c r="A119" s="41" t="n"/>
       <c r="B119" s="23" t="inlineStr">
         <is>
@@ -11131,7 +11702,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F119" s="34" t="inlineStr">
+      <c r="F119" s="44" t="inlineStr">
         <is>
           <t>按Campaign查看AdGroup列表(不限定具体AdGroup) — 43.6%
 AdGroup模块主列表(默认活跃状态,不限Campaign) — 25.8%
@@ -11162,7 +11733,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F120" s="34" t="inlineStr">
+      <c r="F120" s="44" t="inlineStr">
         <is>
           <t>campaignId查询AdgroupTotal 单campaign汇总
 campaignId加adgroupId查询AdgroupTotal 指定adgroup汇总
@@ -11192,7 +11763,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F121" s="34" t="inlineStr">
+      <c r="F121" s="44" t="inlineStr">
         <is>
           <t>查询SP手动定位(PAT)广告系列的广告组类型
 查询SP通用广告系列的广告组类型
@@ -11222,17 +11793,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F122" s="34" t="inlineStr">
-        <is>
-          <t>场景1: 同Campaign内复制并保持enabled
-场景2: 同Campaign内复制并保持paused
-单个SP广告系列查询广告组列表 — 92.7%
+      <c r="F122" s="44" t="inlineStr">
+        <is>
+          <t>单个SP广告系列查询广告组列表 — 92.7%
 单个SD广告系列查询广告组列表 — 92.7%
 批量多campaignId查询广告组列表 — 7.3%</t>
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="48" customHeight="1">
       <c r="A123" s="41" t="n"/>
       <c r="B123" s="23" t="inlineStr">
         <is>
@@ -11254,8 +11823,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="124">
+      <c r="F123" s="44" t="inlineStr">
+        <is>
+          <t>低价位默认出价调整(&lt;1,含读原值+还原) — 50.8%
+中价位默认出价调整(1~3,含读原值+还原) — 40.9%
+高价位默认出价调整(&gt;3,含读原值+还原) — 8.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="48" customHeight="1">
       <c r="A124" s="41" t="n"/>
       <c r="B124" s="27" t="inlineStr">
         <is>
@@ -11277,8 +11853,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="125">
+      <c r="F124" s="44" t="inlineStr">
+        <is>
+          <t>SD AdGroup Update Basic Attributes NoCostControl
+SD AdGroup Update EnableCostControl
+SD AdGroup Update DisableCostControl</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="32" customHeight="1">
       <c r="A125" s="41" t="n"/>
       <c r="B125" s="23" t="inlineStr">
         <is>
@@ -11300,8 +11883,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="126">
+      <c r="F125" s="44" t="inlineStr">
+        <is>
+          <t>普通改名场景-读取原名后改名并还原
+带sourceName(Creative Hub来源)的改名场景-读取原名后改名并还原</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1">
       <c r="A126" s="41" t="n"/>
       <c r="B126" s="27" t="inlineStr">
         <is>
@@ -11321,6 +11910,11 @@
       <c r="E126" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F126" s="44" t="inlineStr">
+        <is>
+          <t>批量修改AdGroup名称(含读原值+还原,可重复)</t>
         </is>
       </c>
     </row>
@@ -11462,7 +12056,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="32" customHeight="1">
       <c r="A133" s="41" t="n"/>
       <c r="B133" s="23" t="inlineStr">
         <is>
@@ -11484,8 +12078,14 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="134">
+      <c r="F133" s="44" t="inlineStr">
+        <is>
+          <t>5个品牌词约90天询价
+大批量54个关键词约30天询价</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="48" customHeight="1">
       <c r="A134" s="41" t="n"/>
       <c r="B134" s="27" t="inlineStr">
         <is>
@@ -11507,8 +12107,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="135">
+      <c r="F134" s="44" t="inlineStr">
+        <is>
+          <t>单关键词预定校验
+3到4个品牌词批量校验
+大批量54个关键词校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="16" customHeight="1">
       <c r="A135" s="41" t="n"/>
       <c r="B135" s="23" t="inlineStr">
         <is>
@@ -11530,8 +12137,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="136">
+      <c r="F135" s="44" t="inlineStr">
+        <is>
+          <t>拉取品牌词推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
       <c r="A136" s="41" t="n"/>
       <c r="B136" s="27" t="inlineStr">
         <is>
@@ -11553,8 +12165,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="137">
+      <c r="F136" s="44" t="inlineStr">
+        <is>
+          <t>按单个dealId查询广告交易</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
       <c r="A137" s="41" t="n"/>
       <c r="B137" s="23" t="inlineStr">
         <is>
@@ -11574,6 +12191,11 @@
       <c r="E137" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F137" s="44" t="inlineStr">
+        <is>
+          <t>按单个dealId查询交易目标</t>
         </is>
       </c>
     </row>
@@ -11684,7 +12306,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="15.95" customHeight="1">
+    <row r="142" ht="16" customHeight="1">
       <c r="A142" s="41" t="n"/>
       <c r="B142" s="27" t="inlineStr">
         <is>
@@ -11706,7 +12328,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F142" s="34" t="inlineStr">
+      <c r="F142" s="44" t="inlineStr">
         <is>
           <t>查询广告组下的亚马逊广告列表 — 100%</t>
         </is>
@@ -11796,7 +12418,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="15.95" customHeight="1">
+    <row r="146" ht="16" customHeight="1">
       <c r="A146" s="41" t="n"/>
       <c r="B146" s="27" t="inlineStr">
         <is>
@@ -11818,7 +12440,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F146" s="34" t="inlineStr">
+      <c r="F146" s="44" t="inlineStr">
         <is>
           <t>更新STV广告视频素材（含后置恢复） — 100%</t>
         </is>
@@ -11846,7 +12468,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F147" s="34" t="inlineStr">
+      <c r="F147" s="44" t="inlineStr">
         <is>
           <t>批量暂停广告（含后置恢复） — 35%
 批量启用广告（含后置恢复） — 30%
@@ -11854,7 +12476,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="15.95" customHeight="1">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" s="41" t="n"/>
       <c r="B148" s="26" t="inlineStr">
         <is>
@@ -11876,7 +12498,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F148" s="34" t="inlineStr">
+      <c r="F148" s="44" t="inlineStr">
         <is>
           <t>场景1: 单图片区域裁剪编辑</t>
         </is>
@@ -11904,7 +12526,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F149" s="34" t="inlineStr">
+      <c r="F149" s="44" t="inlineStr">
         <is>
           <t>场景1: 主题+描述词组合生成 — 46.2%
 场景2: 仅指定主题 — 18.9%
@@ -11936,14 +12558,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F150" s="34" t="inlineStr">
+      <c r="F150" s="44" t="inlineStr">
         <is>
           <t>场景1: 不限制返回数量查询 — 80%
 场景2: 限制返回数量查询 — 20%</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="15.95" customHeight="1">
+    <row r="151" ht="16" customHeight="1">
       <c r="A151" s="41" t="n"/>
       <c r="B151" s="23" t="inlineStr">
         <is>
@@ -11965,13 +12587,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F151" s="34" t="inlineStr">
+      <c r="F151" s="44" t="inlineStr">
         <is>
           <t>场景1: 查询资产注册状态</t>
         </is>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="16" customHeight="1">
       <c r="A152" s="41" t="n"/>
       <c r="B152" s="27" t="inlineStr">
         <is>
@@ -11993,8 +12615,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="153" ht="15.95" customHeight="1">
+      <c r="F152" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 按profileId查询可用主题列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
       <c r="A153" s="41" t="n"/>
       <c r="B153" s="23" t="inlineStr">
         <is>
@@ -12016,13 +12643,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F153" s="34" t="inlineStr">
+      <c r="F153" s="44" t="inlineStr">
         <is>
           <t>场景1: 注册单张AI生成图片素材</t>
         </is>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="96" customHeight="1">
       <c r="A154" s="41" t="n"/>
       <c r="B154" s="26" t="inlineStr">
         <is>
@@ -12044,8 +12671,18 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="155">
+      <c r="F154" s="44" t="inlineStr">
+        <is>
+          <t>单ASIN+MANUAL默认排序推荐关键词
+Campaign+AdGroup去重推荐关键词
+2-5个ASIN批量MANUAL推荐
+单ASIN+AUTO FOR SALES推荐
+单ASIN+LEGACY FOR SALES推荐
+仅AdGroup(空campaignIds)推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="48" customHeight="1">
       <c r="A155" s="41" t="n"/>
       <c r="B155" s="23" t="inlineStr">
         <is>
@@ -12067,8 +12704,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="156">
+      <c r="F155" s="44" t="inlineStr">
+        <is>
+          <t>单ASIN默认count=50推荐商品
+单ASIN大页count=1000推荐商品
+多ASIN count=50推荐商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="48" customHeight="1">
       <c r="A156" s="41" t="n"/>
       <c r="B156" s="27" t="inlineStr">
         <is>
@@ -12090,8 +12734,15 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="157">
+      <c r="F156" s="44" t="inlineStr">
+        <is>
+          <t>单ASIN建议类目
+两个ASIN建议类目
+3-5个ASIN批量建议类目</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
       <c r="A157" s="41" t="n"/>
       <c r="B157" s="24" t="inlineStr">
         <is>
@@ -12113,8 +12764,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="158">
+      <c r="F157" s="44" t="inlineStr">
+        <is>
+          <t>获取归因广告主列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
       <c r="A158" s="41" t="n"/>
       <c r="B158" s="27" t="inlineStr">
         <is>
@@ -12134,6 +12790,11 @@
       <c r="E158" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F158" s="44" t="inlineStr">
+        <is>
+          <t>获取归因发布商列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12820,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F159" s="34" t="inlineStr">
+      <c r="F159" s="44" t="inlineStr">
         <is>
           <t>单宏发布商获取归因宏标签 — 67%
 多宏发布商批量获取归因宏标签 — 17%</t>
@@ -12188,14 +12849,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F160" s="34" t="inlineStr">
+      <c r="F160" s="44" t="inlineStr">
         <is>
           <t>单非宏发布商获取归因非宏模板标签 — 90%
 多非宏发布商批量获取归因非宏模板标签 — 5%</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="15.95" customHeight="1">
+    <row r="161" ht="16" customHeight="1">
       <c r="A161" s="41" t="n"/>
       <c r="B161" s="23" t="inlineStr">
         <is>
@@ -12217,7 +12878,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F161" s="34" t="inlineStr">
+      <c r="F161" s="44" t="inlineStr">
         <is>
           <t>查询归因性能报表（publisher+日期范围） — 100%</t>
         </is>
@@ -12245,14 +12906,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F162" s="34" t="inlineStr">
+      <c r="F162" s="44" t="inlineStr">
         <is>
           <t>查询归因商品报表（仅指定开始日期） — 67%
 查询归因商品报表（指定完整日期范围） — 33%</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="15.95" customHeight="1">
+    <row r="163" ht="16" customHeight="1">
       <c r="A163" s="41" t="n"/>
       <c r="B163" s="24" t="inlineStr">
         <is>
@@ -12274,13 +12935,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F163" s="34" t="inlineStr">
+      <c r="F163" s="44" t="inlineStr">
         <is>
           <t>按Profile+Campaign查询受众投放Campaign</t>
         </is>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="16" customHeight="1">
       <c r="A164" s="41" t="n"/>
       <c r="B164" s="27" t="inlineStr">
         <is>
@@ -12302,8 +12963,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="165">
+      <c r="F164" s="44" t="inlineStr">
+        <is>
+          <t>写入受众Campaign到Clickhouse(仅构造未执行) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
       <c r="A165" s="41" t="n"/>
       <c r="B165" s="23" t="inlineStr">
         <is>
@@ -12325,8 +12991,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="166">
+      <c r="F165" s="44" t="inlineStr">
+        <is>
+          <t>全量刷新受众Campaign库存(仅构造未执行) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="16" customHeight="1">
       <c r="A166" s="41" t="n"/>
       <c r="B166" s="27" t="inlineStr">
         <is>
@@ -12348,8 +13019,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="167">
+      <c r="F166" s="44" t="inlineStr">
+        <is>
+          <t>按Profile刷新受众Campaign库存(仅构造未执行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="16" customHeight="1">
       <c r="A167" s="41" t="n"/>
       <c r="B167" s="24" t="inlineStr">
         <is>
@@ -12371,8 +13047,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="168">
+      <c r="F167" s="44" t="inlineStr">
+        <is>
+          <t>按profile+campaign查活动表现(样本不足)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="32" customHeight="1">
       <c r="A168" s="41" t="n"/>
       <c r="B168" s="27" t="inlineStr">
         <is>
@@ -12392,6 +13073,12 @@
       <c r="E168" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F168" s="44" t="inlineStr">
+        <is>
+          <t>ytd否定词审计(广告活动层级level=1)
+ytd否定词审计(不限层级level=null)</t>
         </is>
       </c>
     </row>
@@ -12417,7 +13104,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F169" s="34" t="inlineStr">
+      <c r="F169" s="44" t="inlineStr">
         <is>
           <t>按品类+品牌查看ASIN排名表(分页) — 27.2%
 按品类查看ASIN排名表(无指定品牌) — 27.2%
@@ -12447,7 +13134,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F170" s="34" t="inlineStr">
+      <c r="F170" s="44" t="inlineStr">
         <is>
           <t>US市场按品牌查看ASIN SOV日趋势 — 81.3%
 非US市场按品牌查看ASIN SOV日趋势(UK) — 9.3%
@@ -12477,7 +13164,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F171" s="34" t="inlineStr">
+      <c r="F171" s="44" t="inlineStr">
         <is>
           <t>US市场获取ASIN标签列表 — 83.9%
 IN市场获取ASIN标签列表 — 8.1%
@@ -12507,7 +13194,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F172" s="34" t="inlineStr">
+      <c r="F172" s="44" t="inlineStr">
         <is>
           <t>按Profile获取全量ASIN列表 — 33.4%
 按标签过滤获取ASIN列表 — 33.4%
@@ -12537,7 +13224,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F173" s="34" t="inlineStr">
+      <c r="F173" s="44" t="inlineStr">
         <is>
           <t>US市场获取亚马逊广告主列表 — 82.6%
 IN市场获取亚马逊广告主列表 — 8.7%
@@ -12567,7 +13254,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F174" s="34" t="inlineStr">
+      <c r="F174" s="44" t="inlineStr">
         <is>
           <t>US市场获取Analytics profile列表 — 82.7%
 非US市场获取Analytics profile列表 — 8.7%
@@ -12597,7 +13284,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F175" s="34" t="inlineStr">
+      <c r="F175" s="44" t="inlineStr">
         <is>
           <t>获取Campaign标签列表 — 33.2%
 按市场获取Campaign标签 — 33.0%
@@ -12627,7 +13314,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F176" s="34" t="inlineStr">
+      <c r="F176" s="44" t="inlineStr">
         <is>
           <t>纯SP广告花费按Campaign类型分布 — 33.3%
 SP+DSP广告花费按Campaign类型分布 — 33.3%
@@ -12657,7 +13344,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F177" s="34" t="inlineStr">
+      <c r="F177" s="44" t="inlineStr">
         <is>
           <t>纯SP点击分布趋势 — 33.3%
 SP+DSP点击分布趋势 — 33.3%
@@ -12687,7 +13374,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F178" s="34" t="inlineStr">
+      <c r="F178" s="44" t="inlineStr">
         <is>
           <t>US市场获取DSP profile及广告主 — 83.0%
 IN市场获取DSP profile及广告主 — 8.5%
@@ -12717,7 +13404,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F179" s="34" t="inlineStr">
+      <c r="F179" s="44" t="inlineStr">
         <is>
           <t>纯SP净利润率趋势图 — 33.3%
 SP+DSP净利润率趋势图 — 33.3%
@@ -12747,7 +13434,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F180" s="34" t="inlineStr">
+      <c r="F180" s="44" t="inlineStr">
         <is>
           <t>按品类获取其他品牌列表 — 33.3%
 清洁品类获取其他品牌 — 33.3%
@@ -12777,7 +13464,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F181" s="34" t="inlineStr">
+      <c r="F181" s="44" t="inlineStr">
         <is>
           <t>纯SP销售来源分布图 — 33.4%
 SP+DSP销售来源分布图 — 33.4%
@@ -12807,7 +13494,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F182" s="34" t="inlineStr">
+      <c r="F182" s="44" t="inlineStr">
         <is>
           <t>纯SP销售来源明细表+日期范围 — 33.4%
 SP+DSP销售来源明细表+日期范围 — 33.4%
@@ -12837,7 +13524,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F183" s="34" t="inlineStr">
+      <c r="F183" s="44" t="inlineStr">
         <is>
           <t>US市场SOV日趋势图 — 83.0%
 非US市场SOV日趋势图(UK) — 8.4%
@@ -12867,7 +13554,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F184" s="34" t="inlineStr">
+      <c r="F184" s="44" t="inlineStr">
         <is>
           <t>US市场获取SOV分组 — 100.0%
 UK市场获取SOV分组 — 0.0%
@@ -12897,7 +13584,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F185" s="34" t="inlineStr">
+      <c r="F185" s="44" t="inlineStr">
         <is>
           <t>按品类filter获取SOV关键词 — 33.5%
 按品类filter+关键词获取SOV关键词 — 33.5%
@@ -12927,10 +13614,9 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F186" s="34" t="inlineStr">
+      <c r="F186" s="44" t="inlineStr">
         <is>
           <t>按品牌+品类查看Top总收入 — 33.5%
-跨品类查看Top总收入(All品类) — 33.5%
 不同品牌品类查看Top总收入(清洁品类) — 33.1%</t>
         </is>
       </c>
@@ -13143,7 +13829,7 @@
         </is>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="16" customHeight="1">
       <c r="A195" s="41" t="n"/>
       <c r="B195" s="24" t="inlineStr">
         <is>
@@ -13165,8 +13851,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="196">
+      <c r="F195" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN条件添加到Tag(含后置清理:从Tag移除,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="16" customHeight="1">
       <c r="A196" s="41" t="n"/>
       <c r="B196" s="27" t="inlineStr">
         <is>
@@ -13188,8 +13879,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="197">
+      <c r="F196" s="44" t="inlineStr">
+        <is>
+          <t>批量添加ASIN为商品广告到指定Campaign/AdGroup[高风险-建议人工验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="16" customHeight="1">
       <c r="A197" s="41" t="n"/>
       <c r="B197" s="23" t="inlineStr">
         <is>
@@ -13211,8 +13907,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="198">
+      <c r="F197" s="44" t="inlineStr">
+        <is>
+          <t>按profile+campaign+adgroup批量查ASIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="16" customHeight="1">
       <c r="A198" s="41" t="n"/>
       <c r="B198" s="27" t="inlineStr">
         <is>
@@ -13234,8 +13935,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="199">
+      <c r="F198" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN条件批量改状态(含后置清理:改回enabled,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="16" customHeight="1">
       <c r="A199" s="41" t="n"/>
       <c r="B199" s="23" t="inlineStr">
         <is>
@@ -13257,8 +13963,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="200">
+      <c r="F199" s="44" t="inlineStr">
+        <is>
+          <t>按profile+campaign+adgroup单值查ASIN[NEEDS REAL VALUE:真实用户样本]</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="16" customHeight="1">
       <c r="A200" s="41" t="n"/>
       <c r="B200" s="27" t="inlineStr">
         <is>
@@ -13280,8 +13991,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="201">
+      <c r="F200" s="44" t="inlineStr">
+        <is>
+          <t>查ASIN主图URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="16" customHeight="1">
       <c r="A201" s="41" t="n"/>
       <c r="B201" s="23" t="inlineStr">
         <is>
@@ -13303,8 +14019,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="202">
+      <c r="F201" s="44" t="inlineStr">
+        <is>
+          <t>按profile+asins+国家查ASIN信息[NEEDS REAL VALUE:真实用户样本]</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="16" customHeight="1">
       <c r="A202" s="41" t="n"/>
       <c r="B202" s="27" t="inlineStr">
         <is>
@@ -13326,8 +14047,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="203">
+      <c r="F202" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN条件从Tag移除(含前置铺垫:先加入,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="16" customHeight="1">
       <c r="A203" s="41" t="n"/>
       <c r="B203" s="23" t="inlineStr">
         <is>
@@ -13349,8 +14075,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="204">
+      <c r="F203" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN/SKU+profile搜索广告商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="16" customHeight="1">
       <c r="A204" s="41" t="n"/>
       <c r="B204" s="27" t="inlineStr">
         <is>
@@ -13372,8 +14103,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="205">
+      <c r="F204" s="44" t="inlineStr">
+        <is>
+          <t>按SKU+profile搜索广告商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="16" customHeight="1">
       <c r="A205" s="41" t="n"/>
       <c r="B205" s="23" t="inlineStr">
         <is>
@@ -13395,8 +14131,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="206">
+      <c r="F205" s="44" t="inlineStr">
+        <is>
+          <t>查用户ASIN追踪配额</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="16" customHeight="1">
       <c r="A206" s="41" t="n"/>
       <c r="B206" s="27" t="inlineStr">
         <is>
@@ -13418,8 +14159,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="207">
+      <c r="F206" s="44" t="inlineStr">
+        <is>
+          <t>ASIN趋势图表(默认全部广告类型+可用状态)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="16" customHeight="1">
       <c r="A207" s="41" t="n"/>
       <c r="B207" s="23" t="inlineStr">
         <is>
@@ -13441,8 +14187,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="208">
+      <c r="F207" s="44" t="inlineStr">
+        <is>
+          <t>ASIN关联广告位竞价情况(分页)[NEEDS REAL VALUE:真实用户样本]</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="16" customHeight="1">
       <c r="A208" s="41" t="n"/>
       <c r="B208" s="27" t="inlineStr">
         <is>
@@ -13464,8 +14215,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="209">
+      <c r="F208" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN查关联广告位竞价情况[NEEDS REAL VALUE:真实用户样本]</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="16" customHeight="1">
       <c r="A209" s="41" t="n"/>
       <c r="B209" s="23" t="inlineStr">
         <is>
@@ -13487,8 +14243,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="210">
+      <c r="F209" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN维度分组查广告竞价情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="16" customHeight="1">
       <c r="A210" s="41" t="n"/>
       <c r="B210" s="27" t="inlineStr">
         <is>
@@ -13510,8 +14271,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="211">
+      <c r="F210" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign维度查ASIN竞价情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="16" customHeight="1">
       <c r="A211" s="41" t="n"/>
       <c r="B211" s="23" t="inlineStr">
         <is>
@@ -13533,8 +14299,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="212">
+      <c r="F211" s="44" t="inlineStr">
+        <is>
+          <t>ASIN列表分页数据(按campaign层级查看)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="16" customHeight="1">
       <c r="A212" s="41" t="n"/>
       <c r="B212" s="27" t="inlineStr">
         <is>
@@ -13556,8 +14327,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="213" ht="15.95" customHeight="1">
+      <c r="F212" s="44" t="inlineStr">
+        <is>
+          <t>ASIN列表汇总统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="16" customHeight="1">
       <c r="A213" s="41" t="n"/>
       <c r="B213" s="24" t="inlineStr">
         <is>
@@ -13579,13 +14355,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F213" s="34" t="inlineStr">
+      <c r="F213" s="44" t="inlineStr">
         <is>
           <t>按tagId查子标签分页数据</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="15.95" customHeight="1">
+    <row r="214" ht="16" customHeight="1">
       <c r="A214" s="41" t="n"/>
       <c r="B214" s="27" t="inlineStr">
         <is>
@@ -13607,13 +14383,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F214" s="34" t="inlineStr">
+      <c r="F214" s="44" t="inlineStr">
         <is>
           <t>子标签分组聚合数据</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="63.95" customHeight="1">
+    <row r="215" ht="64" customHeight="1">
       <c r="A215" s="41" t="n"/>
       <c r="B215" s="23" t="inlineStr">
         <is>
@@ -13635,7 +14411,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F215" s="34" t="inlineStr">
+      <c r="F215" s="44" t="inlineStr">
         <is>
           <t>US市场tagId过滤日期维度 — 48%
 US市场subTagId过滤日期维度 — 30%
@@ -13644,7 +14420,7 @@
         </is>
       </c>
     </row>
-    <row r="216" ht="63.95" customHeight="1">
+    <row r="216" ht="64" customHeight="1">
       <c r="A216" s="41" t="n"/>
       <c r="B216" s="27" t="inlineStr">
         <is>
@@ -13666,7 +14442,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F216" s="34" t="inlineStr">
+      <c r="F216" s="44" t="inlineStr">
         <is>
           <t>US市场tagId过滤日期维度 — 43%
 US市场subTagId过滤日期维度 — 33%
@@ -13697,7 +14473,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F217" s="34" t="inlineStr">
+      <c r="F217" s="44" t="inlineStr">
         <is>
           <t>US市场tagId过滤日期维度 — 40%
 US市场subTagId过滤日期维度 — 28%
@@ -13707,7 +14483,7 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="15.95" customHeight="1">
+    <row r="218" ht="16" customHeight="1">
       <c r="A218" s="41" t="n"/>
       <c r="B218" s="27" t="inlineStr">
         <is>
@@ -13729,13 +14505,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F218" s="34" t="inlineStr">
+      <c r="F218" s="44" t="inlineStr">
         <is>
           <t>按tagId获取ASIN列表</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="15.95" customHeight="1">
+    <row r="219" ht="16" customHeight="1">
       <c r="A219" s="41" t="n"/>
       <c r="B219" s="24" t="inlineStr">
         <is>
@@ -13757,13 +14533,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F219" s="34" t="inlineStr">
+      <c r="F219" s="44" t="inlineStr">
         <is>
           <t>按品牌+分类+广告类型查询AdFormat与目标分布 — 39.0%</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="15.95" customHeight="1">
+    <row r="220" ht="16" customHeight="1">
       <c r="A220" s="41" t="n"/>
       <c r="B220" s="27" t="inlineStr">
         <is>
@@ -13785,13 +14561,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F220" s="34" t="inlineStr">
+      <c r="F220" s="44" t="inlineStr">
         <is>
           <t>按分类+广告类型查询品牌分布 — 39.2%</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="15.95" customHeight="1">
+    <row r="221" ht="16" customHeight="1">
       <c r="A221" s="41" t="n"/>
       <c r="B221" s="23" t="inlineStr">
         <is>
@@ -13813,13 +14589,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F221" s="34" t="inlineStr">
+      <c r="F221" s="44" t="inlineStr">
         <is>
           <t>按Profile+日期粒度查询可选品牌列表 — 86.0%</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="15.95" customHeight="1">
+    <row r="222" ht="16" customHeight="1">
       <c r="A222" s="41" t="n"/>
       <c r="B222" s="27" t="inlineStr">
         <is>
@@ -13841,13 +14617,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F222" s="34" t="inlineStr">
+      <c r="F222" s="44" t="inlineStr">
         <is>
           <t>按品牌筛选查询浏览分类 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="15.95" customHeight="1">
+    <row r="223" ht="16" customHeight="1">
       <c r="A223" s="41" t="n"/>
       <c r="B223" s="23" t="inlineStr">
         <is>
@@ -13869,13 +14645,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F223" s="34" t="inlineStr">
+      <c r="F223" s="44" t="inlineStr">
         <is>
           <t>按品牌+报表类型查询浏览分类树 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="15.95" customHeight="1">
+    <row r="224" ht="16" customHeight="1">
       <c r="A224" s="41" t="n"/>
       <c r="B224" s="27" t="inlineStr">
         <is>
@@ -13897,13 +14673,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F224" s="34" t="inlineStr">
+      <c r="F224" s="44" t="inlineStr">
         <is>
           <t>按品牌+分类查询广告类型对比 — 37.6%</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="15.95" customHeight="1">
+    <row r="225" ht="16" customHeight="1">
       <c r="A225" s="41" t="n"/>
       <c r="B225" s="23" t="inlineStr">
         <is>
@@ -13925,13 +14701,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F225" s="34" t="inlineStr">
+      <c r="F225" s="44" t="inlineStr">
         <is>
           <t>按品牌+广告类型查询分类对比 — 39.4%</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="15.95" customHeight="1">
+    <row r="226" ht="16" customHeight="1">
       <c r="A226" s="41" t="n"/>
       <c r="B226" s="27" t="inlineStr">
         <is>
@@ -13953,13 +14729,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F226" s="34" t="inlineStr">
+      <c r="F226" s="44" t="inlineStr">
         <is>
           <t>按多Profile查询已收藏Benchmark — 76.2%</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="15.95" customHeight="1">
+    <row r="227" ht="16" customHeight="1">
       <c r="A227" s="41" t="n"/>
       <c r="B227" s="23" t="inlineStr">
         <is>
@@ -13981,13 +14757,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F227" s="34" t="inlineStr">
+      <c r="F227" s="44" t="inlineStr">
         <is>
           <t>按多Profile+广告主查询收藏星标状态 — 99.4%</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="15.95" customHeight="1">
+    <row r="228" ht="16" customHeight="1">
       <c r="A228" s="41" t="n"/>
       <c r="B228" s="27" t="inlineStr">
         <is>
@@ -14009,13 +14785,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F228" s="34" t="inlineStr">
+      <c r="F228" s="44" t="inlineStr">
         <is>
           <t>按多Profile+广告主+广告类型查询全部品牌Benchmark概览 — 80.0%</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="15.95" customHeight="1">
+    <row r="229" ht="16" customHeight="1">
       <c r="A229" s="41" t="n"/>
       <c r="B229" s="23" t="inlineStr">
         <is>
@@ -14037,13 +14813,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F229" s="34" t="inlineStr">
+      <c r="F229" s="44" t="inlineStr">
         <is>
           <t>按单Profile+品牌查询单品牌Benchmark概览 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="15.95" customHeight="1">
+    <row r="230" ht="16" customHeight="1">
       <c r="A230" s="41" t="n"/>
       <c r="B230" s="27" t="inlineStr">
         <is>
@@ -14065,13 +14841,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F230" s="34" t="inlineStr">
+      <c r="F230" s="44" t="inlineStr">
         <is>
           <t>按DSP品牌+分类查询趋势 — 16.6%</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="15.95" customHeight="1">
+    <row r="231" ht="16" customHeight="1">
       <c r="A231" s="41" t="n"/>
       <c r="B231" s="23" t="inlineStr">
         <is>
@@ -14093,13 +14869,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F231" s="34" t="inlineStr">
+      <c r="F231" s="44" t="inlineStr">
         <is>
           <t>按品牌+分类+分页查询表现不佳Campaign — 42.2%</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="15.95" customHeight="1">
+    <row r="232" ht="16" customHeight="1">
       <c r="A232" s="41" t="n"/>
       <c r="B232" s="27" t="inlineStr">
         <is>
@@ -14121,13 +14897,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F232" s="34" t="inlineStr">
+      <c r="F232" s="44" t="inlineStr">
         <is>
           <t>按品牌+分类+CampaignId查询表现不佳Target数 — 53.5%</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="15.95" customHeight="1">
+    <row r="233" ht="16" customHeight="1">
       <c r="A233" s="41" t="n"/>
       <c r="B233" s="23" t="inlineStr">
         <is>
@@ -14149,13 +14925,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F233" s="34" t="inlineStr">
+      <c r="F233" s="44" t="inlineStr">
         <is>
           <t>按Profile查询PAT可用ASIN</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="15.95" customHeight="1">
+    <row r="234" ht="16" customHeight="1">
       <c r="A234" s="41" t="n"/>
       <c r="B234" s="27" t="inlineStr">
         <is>
@@ -14177,13 +14953,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F234" s="34" t="inlineStr">
+      <c r="F234" s="44" t="inlineStr">
         <is>
           <t>收藏Benchmark品牌+分类组合(含后置取消收藏)</t>
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="16" customHeight="1">
       <c r="A235" s="41" t="n"/>
       <c r="B235" s="24" t="inlineStr">
         <is>
@@ -14205,13 +14981,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F235" s="44" t="inlineStr">
         <is>
           <t>场景1: 按ProfileId获取品牌列表 — 100.0%</t>
         </is>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="16" customHeight="1">
       <c r="A236" s="41" t="n"/>
       <c r="B236" s="27" t="inlineStr">
         <is>
@@ -14233,13 +15009,13 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F236" s="44" t="inlineStr">
         <is>
           <t>场景1: 按国家码US获取品类列表 — 97.3%</t>
         </is>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="16" customHeight="1">
       <c r="A237" s="41" t="n"/>
       <c r="B237" s="23" t="inlineStr">
         <is>
@@ -14261,7 +15037,7 @@
           <t>limin</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
+      <c r="F237" s="44" t="inlineStr">
         <is>
           <t>场景1: 获取DSP广告品类首页列表 — 100.0%</t>
         </is>
@@ -14289,7 +15065,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F238" s="34" t="inlineStr">
+      <c r="F238" s="44" t="inlineStr">
         <is>
           <t>US市场新建品牌追踪 — 55%
 非US市场品牌追踪(UK) — 25%
@@ -14297,7 +15073,7 @@
         </is>
       </c>
     </row>
-    <row r="239" ht="15.95" customHeight="1">
+    <row r="239" ht="16" customHeight="1">
       <c r="A239" s="41" t="n"/>
       <c r="B239" s="23" t="inlineStr">
         <is>
@@ -14319,13 +15095,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F239" s="34" t="inlineStr">
+      <c r="F239" s="44" t="inlineStr">
         <is>
           <t>触发单品牌审计 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="15.95" customHeight="1">
+    <row r="240" ht="16" customHeight="1">
       <c r="A240" s="41" t="n"/>
       <c r="B240" s="27" t="inlineStr">
         <is>
@@ -14347,13 +15123,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F240" s="34" t="inlineStr">
-        <is>
-          <t>批量触发品牌审计 — ?%</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="15.95" customHeight="1">
+      <c r="F240" s="44" t="inlineStr">
+        <is>
+          <t>批量触发品牌审计</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="16" customHeight="1">
       <c r="A241" s="41" t="n"/>
       <c r="B241" s="23" t="inlineStr">
         <is>
@@ -14375,7 +15151,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F241" s="34" t="inlineStr">
+      <c r="F241" s="44" t="inlineStr">
         <is>
           <t>删除品牌追踪记录(单品牌) — 100%</t>
         </is>
@@ -17532,7 +18308,7 @@
         </is>
       </c>
     </row>
-    <row r="379" ht="15.95" customHeight="1">
+    <row r="379" ht="16" customHeight="1">
       <c r="A379" s="41" t="n"/>
       <c r="B379" s="24" t="inlineStr">
         <is>
@@ -17554,7 +18330,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F379" s="37" t="inlineStr">
+      <c r="F379" s="44" t="inlineStr">
         <is>
           <t>批量保存广告组标签(空pfms)</t>
         </is>
@@ -17588,7 +18364,7 @@
         </is>
       </c>
     </row>
-    <row r="381" ht="15.95" customHeight="1">
+    <row r="381" ht="16" customHeight="1">
       <c r="A381" s="41" t="n"/>
       <c r="B381" s="23" t="inlineStr">
         <is>
@@ -17610,13 +18386,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F381" s="37" t="inlineStr">
+      <c r="F381" s="44" t="inlineStr">
         <is>
           <t>提交标准SP批量模板</t>
         </is>
       </c>
     </row>
-    <row r="382" ht="15.95" customHeight="1">
+    <row r="382" ht="16" customHeight="1">
       <c r="A382" s="41" t="n"/>
       <c r="B382" s="27" t="inlineStr">
         <is>
@@ -17638,13 +18414,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F382" s="37" t="inlineStr">
+      <c r="F382" s="44" t="inlineStr">
         <is>
           <t>提交Amazon SP批量模板</t>
         </is>
       </c>
     </row>
-    <row r="383" ht="15.95" customHeight="1">
+    <row r="383" ht="16" customHeight="1">
       <c r="A383" s="41" t="n"/>
       <c r="B383" s="23" t="inlineStr">
         <is>
@@ -17666,7 +18442,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F383" s="37" t="inlineStr">
+      <c r="F383" s="44" t="inlineStr">
         <is>
           <t>提交NewTempV1批量模板</t>
         </is>
@@ -17700,7 +18476,7 @@
         </is>
       </c>
     </row>
-    <row r="385" ht="15.95" customHeight="1">
+    <row r="385" ht="16" customHeight="1">
       <c r="A385" s="41" t="n"/>
       <c r="B385" s="23" t="inlineStr">
         <is>
@@ -17722,13 +18498,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F385" s="37" t="inlineStr">
+      <c r="F385" s="44" t="inlineStr">
         <is>
           <t>提交Amazon SB批量模板</t>
         </is>
       </c>
     </row>
-    <row r="386" ht="15.95" customHeight="1">
+    <row r="386" ht="16" customHeight="1">
       <c r="A386" s="41" t="n"/>
       <c r="B386" s="27" t="inlineStr">
         <is>
@@ -17750,7 +18526,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F386" s="37" t="inlineStr">
+      <c r="F386" s="44" t="inlineStr">
         <is>
           <t>提交Amazon SD批量模板</t>
         </is>
@@ -17840,7 +18616,7 @@
         </is>
       </c>
     </row>
-    <row r="390" ht="15.95" customHeight="1">
+    <row r="390" ht="16" customHeight="1">
       <c r="A390" s="41" t="n"/>
       <c r="B390" s="27" t="inlineStr">
         <is>
@@ -17862,13 +18638,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F390" s="37" t="inlineStr">
+      <c r="F390" s="44" t="inlineStr">
         <is>
           <t>确认CampaignTag Target指标变更</t>
         </is>
       </c>
     </row>
-    <row r="391" ht="15.95" customHeight="1">
+    <row r="391" ht="16" customHeight="1">
       <c r="A391" s="41" t="n"/>
       <c r="B391" s="23" t="inlineStr">
         <is>
@@ -17890,13 +18666,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F391" s="37" t="inlineStr">
+      <c r="F391" s="44" t="inlineStr">
         <is>
           <t>确认Campaign Target设定变更(autotest活动)</t>
         </is>
       </c>
     </row>
-    <row r="392" ht="15.95" customHeight="1">
+    <row r="392" ht="16" customHeight="1">
       <c r="A392" s="41" t="n"/>
       <c r="B392" s="27" t="inlineStr">
         <is>
@@ -17918,7 +18694,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F392" s="37" t="inlineStr">
+      <c r="F392" s="44" t="inlineStr">
         <is>
           <t>确认关键词映射变更(空data)</t>
         </is>
@@ -17946,7 +18722,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F393" s="37" t="inlineStr">
+      <c r="F393" s="44" t="inlineStr">
         <is>
           <t>SP 模板类型检测 — 98%
 SB 模板类型检测 — 1.6%
@@ -17954,7 +18730,7 @@
         </is>
       </c>
     </row>
-    <row r="394" ht="15.95" customHeight="1">
+    <row r="394" ht="16" customHeight="1">
       <c r="A394" s="41" t="n"/>
       <c r="B394" s="27" t="inlineStr">
         <is>
@@ -17976,7 +18752,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F394" s="37" t="inlineStr">
+      <c r="F394" s="44" t="inlineStr">
         <is>
           <t>按filePath下载批量操作文件 — 100%</t>
         </is>
@@ -18038,7 +18814,7 @@
         </is>
       </c>
     </row>
-    <row r="397" ht="15.95" customHeight="1">
+    <row r="397" ht="16" customHeight="1">
       <c r="A397" s="41" t="n"/>
       <c r="B397" s="23" t="inlineStr">
         <is>
@@ -18060,13 +18836,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F397" s="37" t="inlineStr">
+      <c r="F397" s="44" t="inlineStr">
         <is>
           <t>导出全量Asset信息 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="398" ht="15.95" customHeight="1">
+    <row r="398" ht="16" customHeight="1">
       <c r="A398" s="41" t="n"/>
       <c r="B398" s="27" t="inlineStr">
         <is>
@@ -18088,13 +18864,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F398" s="37" t="inlineStr">
+      <c r="F398" s="44" t="inlineStr">
         <is>
           <t>按campaignIds导出SP广告关键词 — 97%</t>
         </is>
       </c>
     </row>
-    <row r="399" ht="15.95" customHeight="1">
+    <row r="399" ht="16" customHeight="1">
       <c r="A399" s="41" t="n"/>
       <c r="B399" s="23" t="inlineStr">
         <is>
@@ -18116,7 +18892,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F399" s="37" t="inlineStr">
+      <c r="F399" s="44" t="inlineStr">
         <is>
           <t>按profileIds+campaignIds导出定向 — 100%</t>
         </is>
@@ -18150,7 +18926,7 @@
         </is>
       </c>
     </row>
-    <row r="401" ht="15.95" customHeight="1">
+    <row r="401" ht="16" customHeight="1">
       <c r="A401" s="41" t="n"/>
       <c r="B401" s="23" t="inlineStr">
         <is>
@@ -18172,7 +18948,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F401" s="37" t="inlineStr">
+      <c r="F401" s="44" t="inlineStr">
         <is>
           <t>按logId导出ASIN标签批注历史 — 100%</t>
         </is>
@@ -18234,7 +19010,7 @@
         </is>
       </c>
     </row>
-    <row r="404" ht="15.95" customHeight="1">
+    <row r="404" ht="16" customHeight="1">
       <c r="A404" s="41" t="n"/>
       <c r="B404" s="27" t="inlineStr">
         <is>
@@ -18256,7 +19032,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F404" s="37" t="inlineStr">
+      <c r="F404" s="44" t="inlineStr">
         <is>
           <t>按logId导出关键词标签批注历史 — 100%</t>
         </is>
@@ -18290,7 +19066,7 @@
         </is>
       </c>
     </row>
-    <row r="406" ht="15.95" customHeight="1">
+    <row r="406" ht="16" customHeight="1">
       <c r="A406" s="41" t="n"/>
       <c r="B406" s="27" t="inlineStr">
         <is>
@@ -18312,13 +19088,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F406" s="37" t="inlineStr">
+      <c r="F406" s="44" t="inlineStr">
         <is>
           <t>按logId导出Portfolio批注历史 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="407" ht="15.95" customHeight="1">
+    <row r="407" ht="16" customHeight="1">
       <c r="A407" s="41" t="n"/>
       <c r="B407" s="23" t="inlineStr">
         <is>
@@ -18340,13 +19116,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F407" s="37" t="inlineStr">
+      <c r="F407" s="44" t="inlineStr">
         <is>
           <t>导出SB活动全量数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="408" ht="15.95" customHeight="1">
+    <row r="408" ht="16" customHeight="1">
       <c r="A408" s="41" t="n"/>
       <c r="B408" s="27" t="inlineStr">
         <is>
@@ -18368,13 +19144,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F408" s="37" t="inlineStr">
+      <c r="F408" s="44" t="inlineStr">
         <is>
           <t>导出SD活动全量数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="409" ht="15.95" customHeight="1">
+    <row r="409" ht="16" customHeight="1">
       <c r="A409" s="41" t="n"/>
       <c r="B409" s="23" t="inlineStr">
         <is>
@@ -18396,13 +19172,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F409" s="37" t="inlineStr">
+      <c r="F409" s="44" t="inlineStr">
         <is>
           <t>导出SP活动全量数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="410" ht="15.95" customHeight="1">
+    <row r="410" ht="16" customHeight="1">
       <c r="A410" s="41" t="n"/>
       <c r="B410" s="27" t="inlineStr">
         <is>
@@ -18424,7 +19200,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F410" s="37" t="inlineStr">
+      <c r="F410" s="44" t="inlineStr">
         <is>
           <t>SP广告批量导入预览首页 — 100%</t>
         </is>
@@ -18452,7 +19228,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F411" s="37" t="inlineStr">
+      <c r="F411" s="44" t="inlineStr">
         <is>
           <t>SP 类型广告模板预览 — 93.8%
 SD 类型广告模板预览 — 6.2%</t>
@@ -18487,7 +19263,7 @@
         </is>
       </c>
     </row>
-    <row r="413" ht="15.95" customHeight="1">
+    <row r="413" ht="16" customHeight="1">
       <c r="A413" s="41" t="n"/>
       <c r="B413" s="23" t="inlineStr">
         <is>
@@ -18509,7 +19285,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F413" s="37" t="inlineStr">
+      <c r="F413" s="44" t="inlineStr">
         <is>
           <t>预览SP批量Excel的AdGroup首页 — 100%</t>
         </is>
@@ -18537,7 +19313,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F414" s="37" t="inlineStr">
+      <c r="F414" s="44" t="inlineStr">
         <is>
           <t>SP 类型模板读取广告组 — 83%
 SD 类型模板读取广告组 — 5%</t>
@@ -18600,7 +19376,7 @@
         </is>
       </c>
     </row>
-    <row r="417" ht="15.95" customHeight="1">
+    <row r="417" ht="16" customHeight="1">
       <c r="A417" s="41" t="n"/>
       <c r="B417" s="23" t="inlineStr">
         <is>
@@ -18622,13 +19398,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F417" s="37" t="inlineStr">
+      <c r="F417" s="44" t="inlineStr">
         <is>
           <t>空body获取ASIN标签模板 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="418" ht="15.95" customHeight="1">
+    <row r="418" ht="16" customHeight="1">
       <c r="A418" s="41" t="n"/>
       <c r="B418" s="27" t="inlineStr">
         <is>
@@ -18650,13 +19426,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F418" s="37" t="inlineStr">
+      <c r="F418" s="44" t="inlineStr">
         <is>
           <t>SP 批量操作预览首页查询 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="419" ht="15.95" customHeight="1">
+    <row r="419" ht="16" customHeight="1">
       <c r="A419" s="41" t="n"/>
       <c r="B419" s="23" t="inlineStr">
         <is>
@@ -18678,13 +19454,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F419" s="37" t="inlineStr">
+      <c r="F419" s="44" t="inlineStr">
         <is>
           <t>空入参拉取批次列表 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="420" ht="15.95" customHeight="1">
+    <row r="420" ht="16" customHeight="1">
       <c r="A420" s="41" t="n"/>
       <c r="B420" s="27" t="inlineStr">
         <is>
@@ -18706,7 +19482,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F420" s="37" t="inlineStr">
+      <c r="F420" s="44" t="inlineStr">
         <is>
           <t>无参获取Target活动批次列表 — 100%</t>
         </is>
@@ -18734,7 +19510,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F421" s="37" t="inlineStr">
+      <c r="F421" s="44" t="inlineStr">
         <is>
           <t>高频批次5955 — 27%
 次高频批次5938 — 20%
@@ -18764,7 +19540,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F422" s="37" t="inlineStr">
+      <c r="F422" s="44" t="inlineStr">
         <is>
           <t>SP 模板预览 — 82.6%
 SD 模板预览 — 4.6%</t>
@@ -18827,7 +19603,7 @@
         </is>
       </c>
     </row>
-    <row r="425" ht="15.95" customHeight="1">
+    <row r="425" ht="16" customHeight="1">
       <c r="A425" s="41" t="n"/>
       <c r="B425" s="23" t="inlineStr">
         <is>
@@ -18849,13 +19625,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F425" s="37" t="inlineStr">
+      <c r="F425" s="44" t="inlineStr">
         <is>
           <t>SP模板预览否定关键词(Campaign级)</t>
         </is>
       </c>
     </row>
-    <row r="426" ht="15.95" customHeight="1">
+    <row r="426" ht="16" customHeight="1">
       <c r="A426" s="41" t="n"/>
       <c r="B426" s="27" t="inlineStr">
         <is>
@@ -18877,13 +19653,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F426" s="37" t="inlineStr">
+      <c r="F426" s="44" t="inlineStr">
         <is>
           <t>SP模板预览否定定向(Campaign级)</t>
         </is>
       </c>
     </row>
-    <row r="427" ht="15.95" customHeight="1">
+    <row r="427" ht="16" customHeight="1">
       <c r="A427" s="41" t="n"/>
       <c r="B427" s="23" t="inlineStr">
         <is>
@@ -18905,13 +19681,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F427" s="37" t="inlineStr">
+      <c r="F427" s="44" t="inlineStr">
         <is>
           <t>空body查询批量打标日志 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="428" ht="15.95" customHeight="1">
+    <row r="428" ht="16" customHeight="1">
       <c r="A428" s="41" t="n"/>
       <c r="B428" s="27" t="inlineStr">
         <is>
@@ -18933,13 +19709,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F428" s="37" t="inlineStr">
+      <c r="F428" s="44" t="inlineStr">
         <is>
           <t>查询CampaignTag Target批量更新记录</t>
         </is>
       </c>
     </row>
-    <row r="429" ht="15.95" customHeight="1">
+    <row r="429" ht="16" customHeight="1">
       <c r="A429" s="41" t="n"/>
       <c r="B429" s="23" t="inlineStr">
         <is>
@@ -18961,13 +19737,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F429" s="37" t="inlineStr">
+      <c r="F429" s="44" t="inlineStr">
         <is>
           <t>SD创意广告模板预览 — 30%</t>
         </is>
       </c>
     </row>
-    <row r="430" ht="15.95" customHeight="1">
+    <row r="430" ht="16" customHeight="1">
       <c r="A430" s="41" t="n"/>
       <c r="B430" s="27" t="inlineStr">
         <is>
@@ -18989,7 +19765,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F430" s="37" t="inlineStr">
+      <c r="F430" s="44" t="inlineStr">
         <is>
           <t>SP Excel 创建/编辑数据预览 — 100%</t>
         </is>
@@ -19017,7 +19793,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F431" s="37" t="inlineStr">
+      <c r="F431" s="44" t="inlineStr">
         <is>
           <t>SB 类型模板取数 — 10.4%
 SD 类型模板取数 — 4.0%</t>
@@ -19052,7 +19828,7 @@
         </is>
       </c>
     </row>
-    <row r="433" ht="15.95" customHeight="1">
+    <row r="433" ht="16" customHeight="1">
       <c r="A433" s="41" t="n"/>
       <c r="B433" s="23" t="inlineStr">
         <is>
@@ -19074,13 +19850,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F433" s="37" t="inlineStr">
+      <c r="F433" s="44" t="inlineStr">
         <is>
           <t>SP关键词批量结果首页查看 — 99.6%</t>
         </is>
       </c>
     </row>
-    <row r="434" ht="15.95" customHeight="1">
+    <row r="434" ht="16" customHeight="1">
       <c r="A434" s="41" t="n"/>
       <c r="B434" s="27" t="inlineStr">
         <is>
@@ -19102,7 +19878,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F434" s="37" t="inlineStr">
+      <c r="F434" s="44" t="inlineStr">
         <is>
           <t>SB 模板预览关键词 — 12.6%</t>
         </is>
@@ -19136,7 +19912,7 @@
         </is>
       </c>
     </row>
-    <row r="436" ht="15.95" customHeight="1">
+    <row r="436" ht="16" customHeight="1">
       <c r="A436" s="41" t="n"/>
       <c r="B436" s="27" t="inlineStr">
         <is>
@@ -19158,13 +19934,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F436" s="37" t="inlineStr">
+      <c r="F436" s="44" t="inlineStr">
         <is>
           <t>空body获取关键词标签模板 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="437" ht="15.95" customHeight="1">
+    <row r="437" ht="16" customHeight="1">
       <c r="A437" s="41" t="n"/>
       <c r="B437" s="23" t="inlineStr">
         <is>
@@ -19186,13 +19962,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F437" s="37" t="inlineStr">
+      <c r="F437" s="44" t="inlineStr">
         <is>
           <t>按mappingBatchId查询映射批次明细 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="438" ht="15.95" customHeight="1">
+    <row r="438" ht="16" customHeight="1">
       <c r="A438" s="41" t="n"/>
       <c r="B438" s="27" t="inlineStr">
         <is>
@@ -19214,13 +19990,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F438" s="37" t="inlineStr">
+      <c r="F438" s="44" t="inlineStr">
         <is>
           <t>空请求体获取映射批次列表 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="439" ht="15.95" customHeight="1">
+    <row r="439" ht="16" customHeight="1">
       <c r="A439" s="41" t="n"/>
       <c r="B439" s="23" t="inlineStr">
         <is>
@@ -19242,7 +20018,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F439" s="37" t="inlineStr">
+      <c r="F439" s="44" t="inlineStr">
         <is>
           <t>SP批量操作预览否定关键词(默认分页) — 100%</t>
         </is>
@@ -19270,14 +20046,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F440" s="37" t="inlineStr">
+      <c r="F440" s="44" t="inlineStr">
         <is>
           <t>SP 批量模板预览否定关键词 — 84%
 SB 批量模板预览否定关键词 — 16%</t>
         </is>
       </c>
     </row>
-    <row r="441" ht="15.95" customHeight="1">
+    <row r="441" ht="16" customHeight="1">
       <c r="A441" s="41" t="n"/>
       <c r="B441" s="23" t="inlineStr">
         <is>
@@ -19299,7 +20075,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F441" s="37" t="inlineStr">
+      <c r="F441" s="44" t="inlineStr">
         <is>
           <t>SP上传预览默认首页 — 100%</t>
         </is>
@@ -19327,7 +20103,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F442" s="37" t="inlineStr">
+      <c r="F442" s="44" t="inlineStr">
         <is>
           <t>SP 负向定向预览 — 82.2%
 SD 负向定向预览 — 5.0%</t>
@@ -19356,7 +20132,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F443" s="37" t="inlineStr">
+      <c r="F443" s="44" t="inlineStr">
         <is>
           <t>单profile按campaign过滤 — 64.8%
 多profile按campaign过滤 — 18.8%
@@ -19392,7 +20168,7 @@
         </is>
       </c>
     </row>
-    <row r="445" ht="15.95" customHeight="1">
+    <row r="445" ht="16" customHeight="1">
       <c r="A445" s="41" t="n"/>
       <c r="B445" s="23" t="inlineStr">
         <is>
@@ -19414,13 +20190,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F445" s="37" t="inlineStr">
+      <c r="F445" s="44" t="inlineStr">
         <is>
           <t>空body查询标签批量日志 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="446" ht="15.95" customHeight="1">
+    <row r="446" ht="16" customHeight="1">
       <c r="A446" s="41" t="n"/>
       <c r="B446" s="27" t="inlineStr">
         <is>
@@ -19442,13 +20218,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F446" s="37" t="inlineStr">
+      <c r="F446" s="44" t="inlineStr">
         <is>
           <t>按 logId 查询标签批量日志详情 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="447" ht="15.95" customHeight="1">
+    <row r="447" ht="16" customHeight="1">
       <c r="A447" s="41" t="n"/>
       <c r="B447" s="23" t="inlineStr">
         <is>
@@ -19470,7 +20246,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F447" s="37" t="inlineStr">
+      <c r="F447" s="44" t="inlineStr">
         <is>
           <t>SP 批量模板预览定向词 — 100%</t>
         </is>
@@ -19498,7 +20274,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F448" s="37" t="inlineStr">
+      <c r="F448" s="44" t="inlineStr">
         <is>
           <t>SP赞助商品模板预览 — 83%
 SD展示推广模板预览 — 5%</t>
@@ -19527,7 +20303,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F449" s="37" t="inlineStr">
+      <c r="F449" s="44" t="inlineStr">
         <is>
           <t>引用常规上传的完整 xlsx 批次 — 96.7%
 引用测试账号自有上传批次 — 2.6%
@@ -19535,7 +20311,7 @@
         </is>
       </c>
     </row>
-    <row r="450" ht="15.95" customHeight="1">
+    <row r="450" ht="16" customHeight="1">
       <c r="A450" s="41" t="n"/>
       <c r="B450" s="27" t="inlineStr">
         <is>
@@ -19557,7 +20333,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F450" s="37" t="inlineStr">
+      <c r="F450" s="44" t="inlineStr">
         <is>
           <t>按上传批次初始化AMZ模板错误信息 — 100%</t>
         </is>
@@ -19585,14 +20361,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F451" s="37" t="inlineStr">
+      <c r="F451" s="44" t="inlineStr">
         <is>
           <t>有效上传文件回填SB模板错误信息 — 98%
 空文件路径仅按批次回填 — 2%</t>
         </is>
       </c>
     </row>
-    <row r="452" ht="15.95" customHeight="1">
+    <row r="452" ht="16" customHeight="1">
       <c r="A452" s="41" t="n"/>
       <c r="B452" s="27" t="inlineStr">
         <is>
@@ -19614,7 +20390,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F452" s="37" t="inlineStr">
+      <c r="F452" s="44" t="inlineStr">
         <is>
           <t>初始化已上传SD模板的AMZ错误信息 — 100%</t>
         </is>
@@ -19676,7 +20452,7 @@
         </is>
       </c>
     </row>
-    <row r="455" ht="63.95" customHeight="1">
+    <row r="455" ht="64" customHeight="1">
       <c r="A455" s="41" t="n"/>
       <c r="B455" s="23" t="inlineStr">
         <is>
@@ -19698,7 +20474,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F455" s="37" t="inlineStr">
+      <c r="F455" s="44" t="inlineStr">
         <is>
           <t>批量多账号预览adgroupTag模板 — 46%
 双账号预览adgroupTag模板 — 29%
@@ -19729,7 +20505,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F456" s="37" t="inlineStr">
+      <c r="F456" s="44" t="inlineStr">
         <is>
           <t>xlsx 模板预览 — 95.9%
 xls 模板预览 — 2.7%
@@ -19759,7 +20535,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F457" s="37" t="inlineStr">
+      <c r="F457" s="44" t="inlineStr">
         <is>
           <t>AdGroup记录+SP类型预览 — 48.4%
 Campaign记录+SP类型预览 — 46.4%
@@ -19767,7 +20543,7 @@
         </is>
       </c>
     </row>
-    <row r="458" ht="15.95" customHeight="1">
+    <row r="458" ht="16" customHeight="1">
       <c r="A458" s="41" t="n"/>
       <c r="B458" s="27" t="inlineStr">
         <is>
@@ -19789,7 +20565,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F458" s="37" t="inlineStr">
+      <c r="F458" s="44" t="inlineStr">
         <is>
           <t>预览CampaignTag模板数据</t>
         </is>
@@ -19823,7 +20599,7 @@
         </is>
       </c>
     </row>
-    <row r="460" ht="15.95" customHeight="1">
+    <row r="460" ht="16" customHeight="1">
       <c r="A460" s="41" t="n"/>
       <c r="B460" s="27" t="inlineStr">
         <is>
@@ -19845,7 +20621,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F460" s="37" t="inlineStr">
+      <c r="F460" s="44" t="inlineStr">
         <is>
           <t>预览campaignTag模板 — 100%</t>
         </is>
@@ -19873,7 +20649,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F461" s="37" t="inlineStr">
+      <c r="F461" s="44" t="inlineStr">
         <is>
           <t>单 profile 预览 campaign 模板 — 81%
 多 profile 批量预览 campaign 模板 — 17%
@@ -19881,7 +20657,7 @@
         </is>
       </c>
     </row>
-    <row r="462" ht="15.95" customHeight="1">
+    <row r="462" ht="16" customHeight="1">
       <c r="A462" s="41" t="n"/>
       <c r="B462" s="27" t="inlineStr">
         <is>
@@ -19903,7 +20679,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F462" s="37" t="inlineStr">
+      <c r="F462" s="44" t="inlineStr">
         <is>
           <t>预览 keywordTag 模板上传数据 — 100%</t>
         </is>
@@ -19931,7 +20707,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F463" s="37" t="inlineStr">
+      <c r="F463" s="44" t="inlineStr">
         <is>
           <t>Keyword 关键词日志预览(SP) — 21%
 Ad 广告日志预览(SP) — 21%
@@ -19941,7 +20717,7 @@
         </is>
       </c>
     </row>
-    <row r="464" ht="15.95" customHeight="1">
+    <row r="464" ht="16" customHeight="1">
       <c r="A464" s="41" t="n"/>
       <c r="B464" s="27" t="inlineStr">
         <is>
@@ -19963,13 +20739,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F464" s="37" t="inlineStr">
+      <c r="F464" s="44" t="inlineStr">
         <is>
           <t>预览Portfolio模板数据</t>
         </is>
       </c>
     </row>
-    <row r="465" ht="15.95" customHeight="1">
+    <row r="465" ht="16" customHeight="1">
       <c r="A465" s="41" t="n"/>
       <c r="B465" s="23" t="inlineStr">
         <is>
@@ -19991,7 +20767,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F465" s="37" t="inlineStr">
+      <c r="F465" s="44" t="inlineStr">
         <is>
           <t>campaignMapping 模板关键词映射预览 — 100%</t>
         </is>
@@ -20025,7 +20801,7 @@
         </is>
       </c>
     </row>
-    <row r="467" ht="15.95" customHeight="1">
+    <row r="467" ht="16" customHeight="1">
       <c r="A467" s="41" t="n"/>
       <c r="B467" s="23" t="inlineStr">
         <is>
@@ -20047,7 +20823,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F467" s="37" t="inlineStr">
+      <c r="F467" s="44" t="inlineStr">
         <is>
           <t>校验CampaignTag模板 — 100%</t>
         </is>
@@ -20075,7 +20851,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F468" s="37" t="inlineStr">
+      <c r="F468" s="44" t="inlineStr">
         <is>
           <t>单profile校验Campaign模板 — 81%
 多profile校验Campaign模板 — 19%</t>
@@ -23191,7 +23967,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F603" s="37" t="inlineStr">
+      <c r="F603" s="44" t="inlineStr">
         <is>
           <t>场景1: 基础查询无过滤器 — 67.2%
 场景2: 按SP广告类型过滤 — 12.6%
@@ -23223,7 +23999,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F604" s="37" t="inlineStr">
+      <c r="F604" s="44" t="inlineStr">
         <is>
           <t>场景1: 按Spend排序查Portfolio Tag数据 — 90%
 场景2: 按portfolioName排序查Portfolio Tag数据 — 10%</t>
@@ -23252,10 +24028,9 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F605" s="37" t="inlineStr">
-        <is>
-          <t>场景1: 单Profile查Portfolio Tag详情 — 90%
-场景2: 多Profile查Portfolio Tag详情 — 10%</t>
+      <c r="F605" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile查Portfolio Tag详情 — 90%</t>
         </is>
       </c>
     </row>
@@ -23282,7 +24057,7 @@
         </is>
       </c>
     </row>
-    <row r="607">
+    <row r="607" ht="16" customHeight="1">
       <c r="A607" s="41" t="n"/>
       <c r="B607" s="23" t="inlineStr">
         <is>
@@ -23302,6 +24077,11 @@
       <c r="E607" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F607" s="44" t="inlineStr">
+        <is>
+          <t>为已有映射批量设置标签(含创建测试映射+清理)</t>
         </is>
       </c>
     </row>
@@ -23328,7 +24108,7 @@
         </is>
       </c>
     </row>
-    <row r="609" ht="15.95" customHeight="1">
+    <row r="609" ht="16" customHeight="1">
       <c r="A609" s="41" t="n"/>
       <c r="B609" s="23" t="inlineStr">
         <is>
@@ -23350,7 +24130,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F609" s="34" t="inlineStr">
+      <c r="F609" s="44" t="inlineStr">
         <is>
           <t>无筛选下载全部映射 — 25.0%</t>
         </is>
@@ -23378,7 +24158,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F610" s="34" t="inlineStr">
+      <c r="F610" s="44" t="inlineStr">
         <is>
           <t>场景1: 按ExludeFixedPrice过滤广告组 — 44.4%
 场景2: 按IsFilterKeyword过滤广告组 — 23.4%
@@ -23389,7 +24169,7 @@
         </is>
       </c>
     </row>
-    <row r="611" ht="15.95" customHeight="1">
+    <row r="611" ht="16" customHeight="1">
       <c r="A611" s="41" t="n"/>
       <c r="B611" s="23" t="inlineStr">
         <is>
@@ -23411,7 +24191,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F611" s="34" t="inlineStr">
+      <c r="F611" s="44" t="inlineStr">
         <is>
           <t>按Source Profile+日期范围+市场筛选查询映射列表 — 98.6%</t>
         </is>
@@ -23439,14 +24219,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F612" s="34" t="inlineStr">
-        <is>
-          <t>获取当前用户所有CampaignMapping标签 — 100.0%
-为已有映射批量设置标签(含创建测试映射+清理)</t>
-        </is>
-      </c>
-    </row>
-    <row r="613" ht="15.95" customHeight="1">
+      <c r="F612" s="44" t="inlineStr">
+        <is>
+          <t>获取当前用户所有CampaignMapping标签 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="16" customHeight="1">
       <c r="A613" s="41" t="n"/>
       <c r="B613" s="23" t="inlineStr">
         <is>
@@ -23468,13 +24247,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F613" s="34" t="inlineStr">
+      <c r="F613" s="44" t="inlineStr">
         <is>
           <t>创建SP广告组到SD广告组的映射(含定位+后置清理) — 100.0%</t>
         </is>
       </c>
     </row>
-    <row r="614" ht="15.95" customHeight="1">
+    <row r="614" ht="16" customHeight="1">
       <c r="A614" s="41" t="n"/>
       <c r="B614" s="27" t="inlineStr">
         <is>
@@ -23496,7 +24275,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F614" s="34" t="inlineStr">
+      <c r="F614" s="44" t="inlineStr">
         <is>
           <t>创建新标签(含后置清理) — 100.0%</t>
         </is>
@@ -23673,7 +24452,7 @@
         </is>
       </c>
     </row>
-    <row r="621" ht="15.95" customHeight="1">
+    <row r="621" ht="16" customHeight="1">
       <c r="A621" s="41" t="n"/>
       <c r="B621" s="23" t="inlineStr">
         <is>
@@ -23695,7 +24474,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F621" s="34" t="inlineStr">
+      <c r="F621" s="44" t="inlineStr">
         <is>
           <t>设置campaign结束日期(含后置还原,可重复) — 100%</t>
         </is>
@@ -23785,7 +24564,7 @@
         </is>
       </c>
     </row>
-    <row r="625" ht="15.95" customHeight="1">
+    <row r="625" ht="16" customHeight="1">
       <c r="A625" s="41" t="n"/>
       <c r="B625" s="23" t="inlineStr">
         <is>
@@ -23807,13 +24586,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F625" s="34" t="inlineStr">
+      <c r="F625" s="44" t="inlineStr">
         <is>
           <t>批量复制SP campaign(含后置归档,可重复) — 100%</t>
         </is>
       </c>
     </row>
-    <row r="626" ht="15.95" customHeight="1">
+    <row r="626" ht="16" customHeight="1">
       <c r="A626" s="41" t="n"/>
       <c r="B626" s="27" t="inlineStr">
         <is>
@@ -23835,7 +24614,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F626" s="34" t="inlineStr">
+      <c r="F626" s="44" t="inlineStr">
         <is>
           <t>从portfolio移除campaign(含后置还原,可重复)</t>
         </is>
@@ -23925,7 +24704,7 @@
         </is>
       </c>
     </row>
-    <row r="630" ht="15.95" customHeight="1">
+    <row r="630" ht="16" customHeight="1">
       <c r="A630" s="41" t="n"/>
       <c r="B630" s="27" t="inlineStr">
         <is>
@@ -23947,7 +24726,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F630" s="34" t="inlineStr">
+      <c r="F630" s="44" t="inlineStr">
         <is>
           <t>更新campaign所属portfolio(设为当前,可重复)</t>
         </is>
@@ -24037,7 +24816,7 @@
         </is>
       </c>
     </row>
-    <row r="634" ht="15.95" customHeight="1">
+    <row r="634" ht="16" customHeight="1">
       <c r="A634" s="41" t="n"/>
       <c r="B634" s="27" t="inlineStr">
         <is>
@@ -24059,13 +24838,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F634" s="34" t="inlineStr">
+      <c r="F634" s="44" t="inlineStr">
         <is>
           <t>批量编辑campaign(现值回写,可重复)</t>
         </is>
       </c>
     </row>
-    <row r="635" ht="15.95" customHeight="1">
+    <row r="635" ht="16" customHeight="1">
       <c r="A635" s="41" t="n"/>
       <c r="B635" s="23" t="inlineStr">
         <is>
@@ -24087,7 +24866,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F635" s="34" t="inlineStr">
+      <c r="F635" s="44" t="inlineStr">
         <is>
           <t>复制SP campaign(含后置归档,可重复) — 100%</t>
         </is>
@@ -24149,7 +24928,7 @@
         </is>
       </c>
     </row>
-    <row r="638" ht="15.95" customHeight="1">
+    <row r="638" ht="16" customHeight="1">
       <c r="A638" s="41" t="n"/>
       <c r="B638" s="27" t="inlineStr">
         <is>
@@ -24171,7 +24950,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F638" s="34" t="inlineStr">
+      <c r="F638" s="44" t="inlineStr">
         <is>
           <t>复制SP campaign V2(含后置归档,可重复)</t>
         </is>
@@ -24205,7 +24984,7 @@
         </is>
       </c>
     </row>
-    <row r="640" ht="15.95" customHeight="1">
+    <row r="640" ht="16" customHeight="1">
       <c r="A640" s="41" t="n"/>
       <c r="B640" s="27" t="inlineStr">
         <is>
@@ -24227,13 +25006,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F640" s="34" t="inlineStr">
+      <c r="F640" s="44" t="inlineStr">
         <is>
           <t>删除campaign备注(前置创建,可重复)</t>
         </is>
       </c>
     </row>
-    <row r="641" ht="15.95" customHeight="1">
+    <row r="641" ht="16" customHeight="1">
       <c r="A641" s="41" t="n"/>
       <c r="B641" s="23" t="inlineStr">
         <is>
@@ -24255,13 +25034,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F641" s="34" t="inlineStr">
+      <c r="F641" s="44" t="inlineStr">
         <is>
           <t>查询AMC受众关联campaign数 — 98.3%</t>
         </is>
       </c>
     </row>
-    <row r="642" ht="15.95" customHeight="1">
+    <row r="642" ht="16" customHeight="1">
       <c r="A642" s="41" t="n"/>
       <c r="B642" s="27" t="inlineStr">
         <is>
@@ -24283,13 +25062,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F642" s="34" t="inlineStr">
+      <c r="F642" s="44" t="inlineStr">
         <is>
           <t>查询campaign的广告组和ASIN — 99.3%</t>
         </is>
       </c>
     </row>
-    <row r="643" ht="15.95" customHeight="1">
+    <row r="643" ht="16" customHeight="1">
       <c r="A643" s="41" t="n"/>
       <c r="B643" s="23" t="inlineStr">
         <is>
@@ -24311,7 +25090,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F643" s="34" t="inlineStr">
+      <c r="F643" s="44" t="inlineStr">
         <is>
           <t>查询广告组定向类型 — 100%</t>
         </is>
@@ -24373,7 +25152,7 @@
         </is>
       </c>
     </row>
-    <row r="646" ht="15.95" customHeight="1">
+    <row r="646" ht="16" customHeight="1">
       <c r="A646" s="41" t="n"/>
       <c r="B646" s="27" t="inlineStr">
         <is>
@@ -24395,13 +25174,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F646" s="34" t="inlineStr">
+      <c r="F646" s="44" t="inlineStr">
         <is>
           <t>查询Amazon AMC受众Id(SP) — 26.7%</t>
         </is>
       </c>
     </row>
-    <row r="647" ht="15.95" customHeight="1">
+    <row r="647" ht="16" customHeight="1">
       <c r="A647" s="41" t="n"/>
       <c r="B647" s="23" t="inlineStr">
         <is>
@@ -24423,13 +25202,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F647" s="34" t="inlineStr">
+      <c r="F647" s="44" t="inlineStr">
         <is>
           <t>查询AMC受众列表(SD) — 96%</t>
         </is>
       </c>
     </row>
-    <row r="648" ht="15.95" customHeight="1">
+    <row r="648" ht="16" customHeight="1">
       <c r="A648" s="41" t="n"/>
       <c r="B648" s="27" t="inlineStr">
         <is>
@@ -24451,7 +25230,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F648" s="34" t="inlineStr">
+      <c r="F648" s="44" t="inlineStr">
         <is>
           <t>查询AMC受众(报告用) — 100%</t>
         </is>
@@ -24479,14 +25258,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F649" s="34" t="inlineStr">
+      <c r="F649" s="44" t="inlineStr">
         <is>
           <t>实时查询AMC受众(SP) — 73.3%
 实时查询AMC受众(SB) — 16%</t>
         </is>
       </c>
     </row>
-    <row r="650" ht="15.95" customHeight="1">
+    <row r="650" ht="16" customHeight="1">
       <c r="A650" s="41" t="n"/>
       <c r="B650" s="27" t="inlineStr">
         <is>
@@ -24508,7 +25287,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F650" s="34" t="inlineStr">
+      <c r="F650" s="44" t="inlineStr">
         <is>
           <t>查询批量改价SP/SB campaign名称列表 — 2.3%</t>
         </is>
@@ -24542,7 +25321,7 @@
         </is>
       </c>
     </row>
-    <row r="652" ht="15.95" customHeight="1">
+    <row r="652" ht="16" customHeight="1">
       <c r="A652" s="41" t="n"/>
       <c r="B652" s="27" t="inlineStr">
         <is>
@@ -24564,7 +25343,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F652" s="34" t="inlineStr">
+      <c r="F652" s="44" t="inlineStr">
         <is>
           <t>查询campaign预算状态 — 100%</t>
         </is>
@@ -24598,7 +25377,7 @@
         </is>
       </c>
     </row>
-    <row r="654" ht="15.95" customHeight="1">
+    <row r="654" ht="16" customHeight="1">
       <c r="A654" s="41" t="n"/>
       <c r="B654" s="27" t="inlineStr">
         <is>
@@ -24620,13 +25399,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F654" s="34" t="inlineStr">
+      <c r="F654" s="44" t="inlineStr">
         <is>
           <t>查询campaign下ASIN分时分页数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="655" ht="15.95" customHeight="1">
+    <row r="655" ht="16" customHeight="1">
       <c r="A655" s="41" t="n"/>
       <c r="B655" s="23" t="inlineStr">
         <is>
@@ -24648,7 +25427,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F655" s="34" t="inlineStr">
+      <c r="F655" s="44" t="inlineStr">
         <is>
           <t>查询campaign分时平均数据(基础) — 100%</t>
         </is>
@@ -24676,7 +25455,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F656" s="34" t="inlineStr">
+      <c r="F656" s="44" t="inlineStr">
         <is>
           <t>查询campaign分时位置数据(单campaign) — 76.9%
 查询campaign分时位置数据(含市场) — 18.3%</t>
@@ -24705,14 +25484,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F657" s="34" t="inlineStr">
+      <c r="F657" s="44" t="inlineStr">
         <is>
           <t>查询campaign分时平均数据(单campaign) — 27.3%
 查询campaign分时平均数据(多campaign+市场) — 8.4%</t>
         </is>
       </c>
     </row>
-    <row r="658" ht="15.95" customHeight="1">
+    <row r="658" ht="16" customHeight="1">
       <c r="A658" s="41" t="n"/>
       <c r="B658" s="27" t="inlineStr">
         <is>
@@ -24734,7 +25513,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F658" s="34" t="inlineStr">
+      <c r="F658" s="44" t="inlineStr">
         <is>
           <t>查询campaign备注列表 — 100%</t>
         </is>
@@ -24762,7 +25541,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F659" s="34" t="inlineStr">
+      <c r="F659" s="44" t="inlineStr">
         <is>
           <t>加载SP campaign设置 — 89.7%
 加载SP campaign设置(含ShopperCohort竞价) — 7.7%</t>
@@ -24797,7 +25576,7 @@
         </is>
       </c>
     </row>
-    <row r="661" ht="15.95" customHeight="1">
+    <row r="661" ht="16" customHeight="1">
       <c r="A661" s="41" t="n"/>
       <c r="B661" s="23" t="inlineStr">
         <is>
@@ -24819,13 +25598,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F661" s="34" t="inlineStr">
+      <c r="F661" s="44" t="inlineStr">
         <is>
           <t>查询campaign下ASIN分时平均数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="662" ht="15.95" customHeight="1">
+    <row r="662" ht="16" customHeight="1">
       <c r="A662" s="41" t="n"/>
       <c r="B662" s="27" t="inlineStr">
         <is>
@@ -24847,13 +25626,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F662" s="34" t="inlineStr">
+      <c r="F662" s="44" t="inlineStr">
         <is>
           <t>查询campaign下ASIN分周平均数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="663" ht="15.95" customHeight="1">
+    <row r="663" ht="16" customHeight="1">
       <c r="A663" s="41" t="n"/>
       <c r="B663" s="23" t="inlineStr">
         <is>
@@ -24875,7 +25654,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F663" s="34" t="inlineStr">
+      <c r="F663" s="44" t="inlineStr">
         <is>
           <t>查询可加否定定向的campaign列表 — 89.9%</t>
         </is>
@@ -24909,7 +25688,7 @@
         </is>
       </c>
     </row>
-    <row r="665" ht="15.95" customHeight="1">
+    <row r="665" ht="16" customHeight="1">
       <c r="A665" s="41" t="n"/>
       <c r="B665" s="23" t="inlineStr">
         <is>
@@ -24931,13 +25710,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F665" s="34" t="inlineStr">
+      <c r="F665" s="44" t="inlineStr">
         <is>
           <t>按profile分页查询campaign — 94.9%</t>
         </is>
       </c>
     </row>
-    <row r="666" ht="15.95" customHeight="1">
+    <row r="666" ht="16" customHeight="1">
       <c r="A666" s="41" t="n"/>
       <c r="B666" s="27" t="inlineStr">
         <is>
@@ -24959,13 +25738,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F666" s="34" t="inlineStr">
+      <c r="F666" s="44" t="inlineStr">
         <is>
           <t>查询PAT分时分页数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="667" ht="15.95" customHeight="1">
+    <row r="667" ht="16" customHeight="1">
       <c r="A667" s="41" t="n"/>
       <c r="B667" s="23" t="inlineStr">
         <is>
@@ -24987,13 +25766,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F667" s="34" t="inlineStr">
+      <c r="F667" s="44" t="inlineStr">
         <is>
           <t>查询PAT表达式分时平均数据 — 31.6%</t>
         </is>
       </c>
     </row>
-    <row r="668" ht="15.95" customHeight="1">
+    <row r="668" ht="16" customHeight="1">
       <c r="A668" s="41" t="n"/>
       <c r="B668" s="27" t="inlineStr">
         <is>
@@ -25015,13 +25794,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F668" s="34" t="inlineStr">
+      <c r="F668" s="44" t="inlineStr">
         <is>
           <t>查询PAT表达式分周平均数据 — 31.6%</t>
         </is>
       </c>
     </row>
-    <row r="669" ht="15.95" customHeight="1">
+    <row r="669" ht="16" customHeight="1">
       <c r="A669" s="41" t="n"/>
       <c r="B669" s="23" t="inlineStr">
         <is>
@@ -25043,7 +25822,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F669" s="34" t="inlineStr">
+      <c r="F669" s="44" t="inlineStr">
         <is>
           <t>查询SB campaign分时平均汇总 — 99.2%</t>
         </is>
@@ -25071,14 +25850,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F670" s="34" t="inlineStr">
+      <c r="F670" s="44" t="inlineStr">
         <is>
           <t>加载SB campaign设置 — 65.3%
 加载SB campaign设置(含ShopperCohort竞价) — 32.3%</t>
         </is>
       </c>
     </row>
-    <row r="671" ht="15.95" customHeight="1">
+    <row r="671" ht="16" customHeight="1">
       <c r="A671" s="41" t="n"/>
       <c r="B671" s="23" t="inlineStr">
         <is>
@@ -25100,13 +25879,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F671" s="34" t="inlineStr">
+      <c r="F671" s="44" t="inlineStr">
         <is>
           <t>按版本查询SB campaign列表 — 99.3%</t>
         </is>
       </c>
     </row>
-    <row r="672" ht="15.95" customHeight="1">
+    <row r="672" ht="16" customHeight="1">
       <c r="A672" s="41" t="n"/>
       <c r="B672" s="27" t="inlineStr">
         <is>
@@ -25128,13 +25907,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F672" s="34" t="inlineStr">
+      <c r="F672" s="44" t="inlineStr">
         <is>
           <t>查询SB关键词ASIN分时平均数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="673" ht="15.95" customHeight="1">
+    <row r="673" ht="16" customHeight="1">
       <c r="A673" s="41" t="n"/>
       <c r="B673" s="23" t="inlineStr">
         <is>
@@ -25156,13 +25935,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F673" s="34" t="inlineStr">
+      <c r="F673" s="44" t="inlineStr">
         <is>
           <t>查询SB关键词ASIN分周平均数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="674" ht="15.95" customHeight="1">
+    <row r="674" ht="16" customHeight="1">
       <c r="A674" s="41" t="n"/>
       <c r="B674" s="27" t="inlineStr">
         <is>
@@ -25184,13 +25963,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F674" s="34" t="inlineStr">
+      <c r="F674" s="44" t="inlineStr">
         <is>
           <t>查询SB Top50分时关键词 — 99.2%</t>
         </is>
       </c>
     </row>
-    <row r="675" ht="15.95" customHeight="1">
+    <row r="675" ht="16" customHeight="1">
       <c r="A675" s="41" t="n"/>
       <c r="B675" s="23" t="inlineStr">
         <is>
@@ -25212,7 +25991,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F675" s="34" t="inlineStr">
+      <c r="F675" s="44" t="inlineStr">
         <is>
           <t>查询SD campaign分时平均汇总 — 100%</t>
         </is>
@@ -25240,14 +26019,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F676" s="34" t="inlineStr">
+      <c r="F676" s="44" t="inlineStr">
         <is>
           <t>加载SD campaign设置 — 90%
 加载SD campaign设置(含ShopperCohort竞价) — 8%</t>
         </is>
       </c>
     </row>
-    <row r="677" ht="15.95" customHeight="1">
+    <row r="677" ht="16" customHeight="1">
       <c r="A677" s="41" t="n"/>
       <c r="B677" s="23" t="inlineStr">
         <is>
@@ -25269,13 +26048,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F677" s="34" t="inlineStr">
+      <c r="F677" s="44" t="inlineStr">
         <is>
           <t>查询SD广告组素材 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="678" ht="15.95" customHeight="1">
+    <row r="678" ht="16" customHeight="1">
       <c r="A678" s="41" t="n"/>
       <c r="B678" s="27" t="inlineStr">
         <is>
@@ -25297,7 +26076,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F678" s="34" t="inlineStr">
+      <c r="F678" s="44" t="inlineStr">
         <is>
           <t>加载STV campaign设置 — 45.2%</t>
         </is>
@@ -25331,7 +26110,7 @@
         </is>
       </c>
     </row>
-    <row r="680" ht="15.95" customHeight="1">
+    <row r="680" ht="16" customHeight="1">
       <c r="A680" s="41" t="n"/>
       <c r="B680" s="27" t="inlineStr">
         <is>
@@ -25353,7 +26132,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F680" s="34" t="inlineStr">
+      <c r="F680" s="44" t="inlineStr">
         <is>
           <t>设置SP shopper cohort竞价(含后置清除,可重复)</t>
         </is>
@@ -25471,7 +26250,7 @@
         </is>
       </c>
     </row>
-    <row r="685" ht="15.95" customHeight="1">
+    <row r="685" ht="16" customHeight="1">
       <c r="A685" s="41" t="n"/>
       <c r="B685" s="23" t="inlineStr">
         <is>
@@ -25493,7 +26272,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F685" s="34" t="inlineStr">
+      <c r="F685" s="44" t="inlineStr">
         <is>
           <t>更新受众竞价百分比(含后置清除,可重复)</t>
         </is>
@@ -25527,7 +26306,7 @@
         </is>
       </c>
     </row>
-    <row r="687" ht="15.95" customHeight="1">
+    <row r="687" ht="16" customHeight="1">
       <c r="A687" s="41" t="n"/>
       <c r="B687" s="23" t="inlineStr">
         <is>
@@ -25549,13 +26328,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F687" s="34" t="inlineStr">
+      <c r="F687" s="44" t="inlineStr">
         <is>
           <t>更新SB竞价优化(现值回写,可重复)</t>
         </is>
       </c>
     </row>
-    <row r="688" ht="15.95" customHeight="1">
+    <row r="688" ht="16" customHeight="1">
       <c r="A688" s="41" t="n"/>
       <c r="B688" s="27" t="inlineStr">
         <is>
@@ -25577,13 +26356,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F688" s="34" t="inlineStr">
+      <c r="F688" s="44" t="inlineStr">
         <is>
           <t>更新SP竞价策略(读取原值回写,可重复)</t>
         </is>
       </c>
     </row>
-    <row r="689" ht="15.95" customHeight="1">
+    <row r="689" ht="16" customHeight="1">
       <c r="A689" s="41" t="n"/>
       <c r="B689" s="23" t="inlineStr">
         <is>
@@ -25605,7 +26384,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F689" s="34" t="inlineStr">
+      <c r="F689" s="44" t="inlineStr">
         <is>
           <t>更新SP campaign名称(读取原值回写,可重复)</t>
         </is>
@@ -25639,7 +26418,7 @@
         </is>
       </c>
     </row>
-    <row r="691" ht="15.95" customHeight="1">
+    <row r="691" ht="16" customHeight="1">
       <c r="A691" s="41" t="n"/>
       <c r="B691" s="23" t="inlineStr">
         <is>
@@ -25661,7 +26440,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F691" s="34" t="inlineStr">
+      <c r="F691" s="44" t="inlineStr">
         <is>
           <t>创建campaign备注(含后置删除,可重复) — 100%</t>
         </is>
@@ -26518,7 +27297,7 @@
         </is>
       </c>
     </row>
-    <row r="729" ht="15.95" customHeight="1">
+    <row r="729" ht="16" customHeight="1">
       <c r="A729" s="41" t="n"/>
       <c r="B729" s="24" t="inlineStr">
         <is>
@@ -26540,7 +27319,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F729" s="34" t="inlineStr">
+      <c r="F729" s="44" t="inlineStr">
         <is>
           <t>SP单Campaign竞价策略修改(含后置还原)</t>
         </is>
@@ -26568,7 +27347,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F730" s="34" t="inlineStr">
+      <c r="F730" s="44" t="inlineStr">
         <is>
           <t>SP竞价策略批量切换-autoForSales(含后置还原,可重复) — 88.4%
 SP搜索结果其他广告位调整(eventType=2,含后置还原) — 3.8%
@@ -26576,7 +27355,7 @@
         </is>
       </c>
     </row>
-    <row r="731" ht="15.95" customHeight="1">
+    <row r="731" ht="16" customHeight="1">
       <c r="A731" s="41" t="n"/>
       <c r="B731" s="23" t="inlineStr">
         <is>
@@ -26598,13 +27377,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F731" s="34" t="inlineStr">
+      <c r="F731" s="44" t="inlineStr">
         <is>
           <t>SP和SB竞价策略批量修改(含后置还原)</t>
         </is>
       </c>
     </row>
-    <row r="732" ht="15.95" customHeight="1">
+    <row r="732" ht="16" customHeight="1">
       <c r="A732" s="41" t="n"/>
       <c r="B732" s="27" t="inlineStr">
         <is>
@@ -26626,13 +27405,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F732" s="34" t="inlineStr">
+      <c r="F732" s="44" t="inlineStr">
         <is>
           <t>批量Campaign站外预算策略MAXIMIZE REACH(含后置还原)</t>
         </is>
       </c>
     </row>
-    <row r="733" ht="15.95" customHeight="1">
+    <row r="733" ht="16" customHeight="1">
       <c r="A733" s="41" t="n"/>
       <c r="B733" s="23" t="inlineStr">
         <is>
@@ -26654,13 +27433,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F733" s="34" t="inlineStr">
+      <c r="F733" s="44" t="inlineStr">
         <is>
           <t>设置Campaign结束日期(含后置还原)</t>
         </is>
       </c>
     </row>
-    <row r="734" ht="15.95" customHeight="1">
+    <row r="734" ht="16" customHeight="1">
       <c r="A734" s="41" t="n"/>
       <c r="B734" s="27" t="inlineStr">
         <is>
@@ -26682,13 +27461,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F734" s="34" t="inlineStr">
+      <c r="F734" s="44" t="inlineStr">
         <is>
           <t>Campaign重命名(含后置还原,可重复) — 100%</t>
         </is>
       </c>
     </row>
-    <row r="735" ht="15.95" customHeight="1">
+    <row r="735" ht="16" customHeight="1">
       <c r="A735" s="41" t="n"/>
       <c r="B735" s="23" t="inlineStr">
         <is>
@@ -26710,7 +27489,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F735" s="34" t="inlineStr">
+      <c r="F735" s="44" t="inlineStr">
         <is>
           <t>设置Campaign站外预算控制策略MAXIMIZE REACH(含后置还原)</t>
         </is>
@@ -26738,7 +27517,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F736" s="34" t="inlineStr">
+      <c r="F736" s="44" t="inlineStr">
         <is>
           <t>保存Campaign设置-仅绑定标签无目标指标(含后置清理) — 50%
 保存Campaign基本信息-无标签无目标指标(含后置还原) — 26%
@@ -26749,7 +27528,7 @@
         </is>
       </c>
     </row>
-    <row r="737" ht="15.95" customHeight="1">
+    <row r="737" ht="16" customHeight="1">
       <c r="A737" s="41" t="n"/>
       <c r="B737" s="23" t="inlineStr">
         <is>
@@ -26771,13 +27550,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F737" s="34" t="inlineStr">
+      <c r="F737" s="44" t="inlineStr">
         <is>
           <t>设置Campaign开始日期(含后置还原,可重复) — 100%</t>
         </is>
       </c>
     </row>
-    <row r="738" ht="15.95" customHeight="1">
+    <row r="738" ht="32" customHeight="1">
       <c r="A738" s="41" t="n"/>
       <c r="B738" s="27" t="inlineStr">
         <is>
@@ -26799,9 +27578,10 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F738" s="34" t="inlineStr">
-        <is>
-          <t>暂停SP Campaign并还原为enabled(含后置恢复,可重复)</t>
+      <c r="F738" s="44" t="inlineStr">
+        <is>
+          <t>暂停SP Campaign并还原为enabled(含后置恢复,可重复)
+归档SP Campaign(create新建后归档,自包含可重复) — 50%</t>
         </is>
       </c>
     </row>
@@ -27163,7 +27943,7 @@
       </c>
       <c r="F751" s="44" t="inlineStr">
         <is>
-          <t>月度+关键词标签过滤 — 73%
+          <t>月度+关键词标签过滤 — 73%（已迁移，无需测试）
 月度+无关键词标签过滤 — 23%
 自定义日期区间 — 5%</t>
         </is>
@@ -27223,7 +28003,7 @@
       </c>
       <c r="F753" s="44" t="inlineStr">
         <is>
-          <t>未覆盖：近90天无非测试账号真实调用（0条），为无入参连通性探测接口，无真实业务场景可提取。</t>
+          <t>连通性冒烟</t>
         </is>
       </c>
     </row>
@@ -27255,7 +28035,7 @@
         </is>
       </c>
     </row>
-    <row r="755" ht="15.95" customHeight="1">
+    <row r="755" ht="16" customHeight="1">
       <c r="A755" s="41" t="n"/>
       <c r="B755" s="24" t="inlineStr">
         <is>
@@ -27277,7 +28057,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F755" s="34" t="inlineStr">
+      <c r="F755" s="44" t="inlineStr">
         <is>
           <t>关键词维度Home看板导出 — 31.4%</t>
         </is>
@@ -27305,7 +28085,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F756" s="34" t="inlineStr">
+      <c r="F756" s="44" t="inlineStr">
         <is>
           <t>场景1: 基础维度查询Benchmark趋势 — 81.0%
 场景2: 含adFormat+campaignGoal查询Benchmark趋势 — 18.0%</t>
@@ -27334,14 +28114,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F757" s="34" t="inlineStr">
+      <c r="F757" s="44" t="inlineStr">
         <is>
           <t>场景1: 按Profile+日期查询品牌分类列表 — 98.2%
 场景2: 按Profile+日期+shareId查询品牌分类列表 — 1.6%</t>
         </is>
       </c>
     </row>
-    <row r="758" ht="15.95" customHeight="1">
+    <row r="758" ht="16" customHeight="1">
       <c r="A758" s="41" t="n"/>
       <c r="B758" s="27" t="inlineStr">
         <is>
@@ -27363,13 +28143,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F758" s="34" t="inlineStr">
+      <c r="F758" s="44" t="inlineStr">
         <is>
           <t>查询超预算Campaign汇总</t>
         </is>
       </c>
     </row>
-    <row r="759" ht="15.95" customHeight="1">
+    <row r="759" ht="16" customHeight="1">
       <c r="A759" s="41" t="n"/>
       <c r="B759" s="23" t="inlineStr">
         <is>
@@ -27391,13 +28171,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F759" s="34" t="inlineStr">
+      <c r="F759" s="44" t="inlineStr">
         <is>
           <t>查询转化效率看板数据</t>
         </is>
       </c>
     </row>
-    <row r="760" ht="15.95" customHeight="1">
+    <row r="760" ht="16" customHeight="1">
       <c r="A760" s="41" t="n"/>
       <c r="B760" s="27" t="inlineStr">
         <is>
@@ -27419,13 +28199,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F760" s="34" t="inlineStr">
+      <c r="F760" s="44" t="inlineStr">
         <is>
           <t>查询ROAS看板数据</t>
         </is>
       </c>
     </row>
-    <row r="761" ht="15.95" customHeight="1">
+    <row r="761" ht="16" customHeight="1">
       <c r="A761" s="41" t="n"/>
       <c r="B761" s="23" t="inlineStr">
         <is>
@@ -27447,13 +28227,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F761" s="34" t="inlineStr">
+      <c r="F761" s="44" t="inlineStr">
         <is>
           <t>查询Campaign目标ACOS达成情况</t>
         </is>
       </c>
     </row>
-    <row r="762" ht="15.95" customHeight="1">
+    <row r="762" ht="16" customHeight="1">
       <c r="A762" s="41" t="n"/>
       <c r="B762" s="27" t="inlineStr">
         <is>
@@ -27475,13 +28255,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F762" s="34" t="inlineStr">
+      <c r="F762" s="44" t="inlineStr">
         <is>
           <t>查询Campaign目标CPA达成情况</t>
         </is>
       </c>
     </row>
-    <row r="763" ht="15.95" customHeight="1">
+    <row r="763" ht="16" customHeight="1">
       <c r="A763" s="41" t="n"/>
       <c r="B763" s="23" t="inlineStr">
         <is>
@@ -27503,13 +28283,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F763" s="34" t="inlineStr">
+      <c r="F763" s="44" t="inlineStr">
         <is>
           <t>查询Campaign目标CPC达成情况</t>
         </is>
       </c>
     </row>
-    <row r="764" ht="15.95" customHeight="1">
+    <row r="764" ht="16" customHeight="1">
       <c r="A764" s="41" t="n"/>
       <c r="B764" s="27" t="inlineStr">
         <is>
@@ -27531,7 +28311,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F764" s="34" t="inlineStr">
+      <c r="F764" s="44" t="inlineStr">
         <is>
           <t>查询Campaign目标ROAS达成情况</t>
         </is>
@@ -29077,7 +29857,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F831" s="37" t="inlineStr">
+      <c r="F831" s="44" t="inlineStr">
         <is>
           <t>导出Campaign报表(单日Dim=date)</t>
         </is>
@@ -29088,7 +29868,7 @@
         </is>
       </c>
     </row>
-    <row r="832" ht="15.95" customHeight="1">
+    <row r="832" ht="16" customHeight="1">
       <c r="A832" s="41" t="n"/>
       <c r="B832" s="27" t="inlineStr">
         <is>
@@ -29110,7 +29890,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F832" s="37" t="inlineStr">
+      <c r="F832" s="44" t="inlineStr">
         <is>
           <t>下载已完成任务文件(链式取id)</t>
         </is>
@@ -29139,7 +29919,7 @@
         </is>
       </c>
     </row>
-    <row r="834" ht="15.95" customHeight="1">
+    <row r="834" ht="16" customHeight="1">
       <c r="A834" s="41" t="n"/>
       <c r="B834" s="27" t="inlineStr">
         <is>
@@ -29161,7 +29941,7 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-      <c r="F834" s="37" t="inlineStr">
+      <c r="F834" s="44" t="inlineStr">
         <is>
           <t>下载中心任务列表分页</t>
         </is>
@@ -29213,7 +29993,7 @@
         </is>
       </c>
     </row>
-    <row r="837" ht="15.95" customHeight="1">
+    <row r="837" ht="16" customHeight="1">
       <c r="A837" s="41" t="n"/>
       <c r="B837" s="24" t="inlineStr">
         <is>
@@ -29235,13 +30015,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F837" s="34" t="inlineStr">
+      <c r="F837" s="44" t="inlineStr">
         <is>
           <t>查询全部货币汇率 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="838">
+    <row r="838" ht="16" customHeight="1">
       <c r="A838" s="41" t="n"/>
       <c r="B838" s="27" t="inlineStr">
         <is>
@@ -29261,6 +30041,11 @@
       <c r="E838" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F838" s="44" t="inlineStr">
+        <is>
+          <t>开启多币种汇率转换</t>
         </is>
       </c>
     </row>
@@ -29401,6 +30186,17 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile查全部广告组趋势图 — 88.2%
+场景2: 指定单Campaign下钻广告组趋势图 — 11.8%</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>历史样本(近1年)补测，近90天生产零流量；case已跑通</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" s="41" t="n"/>
@@ -29424,8 +30220,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="846">
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile查全部ASIN趋势图 — 85.8%
+场景2: 指定单Campaign下钻ASIN趋势图 — 14.2%</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>历史样本(近1年)补测，近90天生产零流量；case已跑通</t>
+        </is>
+      </c>
+    </row>
+    <row r="846" ht="32" customHeight="1">
       <c r="A846" s="41" t="n"/>
       <c r="B846" s="27" t="inlineStr">
         <is>
@@ -29445,6 +30252,12 @@
       <c r="E846" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F846" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 指定Campaign查实时趋势图(不带对比) — 86.1%
+场景2: 指定Campaign查实时趋势图(带同环比对比) — 13.9%</t>
         </is>
       </c>
     </row>
@@ -29470,6 +30283,17 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>场景1: 指定单Campaign查Placement趋势图 — 86.8%
+场景2: 单Profile聚合Placement趋势图 — 13.2%</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>历史样本(近1年)补测，近90天生产零流量；case已跑通</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" s="41" t="n"/>
@@ -29493,6 +30317,17 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile查广告组分页 — 90.2%
+场景2: 指定单Campaign下钻广告组分页 — 9.8%</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>历史样本(近1年)补测，近90天生产零流量；case已跑通</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" s="41" t="n"/>
@@ -29516,6 +30351,17 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile查广告组汇总 — 90.1%
+场景2: 指定单Campaign下钻广告组汇总 — 9.9%</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>历史样本补测；接口返回513反序列化错误(SBSDNewToBrandOrdersPercentage null→Decimal)，测试账号无SB/SD数据触发，疑似后端缺陷，case FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" s="41" t="n"/>
@@ -29539,6 +30385,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" s="41" t="n"/>
@@ -29562,6 +30413,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" s="41" t="n"/>
@@ -29585,6 +30441,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="41" t="n"/>
@@ -29608,6 +30469,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" s="41" t="n"/>
@@ -29631,6 +30497,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="41" t="n"/>
@@ -29654,8 +30525,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="856">
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="856" ht="16" customHeight="1">
       <c r="A856" s="41" t="n"/>
       <c r="B856" s="27" t="inlineStr">
         <is>
@@ -29677,8 +30553,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="857">
+      <c r="F856" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile默认窗口查小时级数据 — 37.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="857" ht="16" customHeight="1">
       <c r="A857" s="41" t="n"/>
       <c r="B857" s="23" t="inlineStr">
         <is>
@@ -29698,6 +30579,11 @@
       <c r="E857" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F857" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile无过滤查小时级数据(OLAP) — 62.1%</t>
         </is>
       </c>
     </row>
@@ -29723,6 +30609,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" s="41" t="n"/>
@@ -29746,6 +30637,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" s="41" t="n"/>
@@ -29769,6 +30665,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" s="41" t="n"/>
@@ -29792,6 +30693,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" s="41" t="n"/>
@@ -29815,6 +30721,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" s="41" t="n"/>
@@ -29838,6 +30749,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="41" t="n"/>
@@ -29861,6 +30777,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="41" t="n"/>
@@ -29884,8 +30805,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="866">
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="866" ht="16" customHeight="1">
       <c r="A866" s="41" t="n"/>
       <c r="B866" s="27" t="inlineStr">
         <is>
@@ -29907,8 +30833,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="867">
+      <c r="F866" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile取实时数据最大时间 — 35.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="867" ht="16" customHeight="1">
       <c r="A867" s="41" t="n"/>
       <c r="B867" s="23" t="inlineStr">
         <is>
@@ -29928,6 +30859,11 @@
       <c r="E867" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F867" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 单Profile取实时数据最大时间(OLAP) — 78.6%</t>
         </is>
       </c>
     </row>
@@ -29953,8 +30889,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="869">
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>零流量(90d 0次，近1年0次)，实时看板未调用，疑似废弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="869" ht="16" customHeight="1">
       <c r="A869" s="41" t="n"/>
       <c r="B869" s="24" t="inlineStr">
         <is>
@@ -29974,6 +30915,11 @@
       <c r="E869" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F869" s="44" t="inlineStr">
+        <is>
+          <t>上传文件(仅构造未执行)</t>
         </is>
       </c>
     </row>
@@ -30092,7 +31038,7 @@
         </is>
       </c>
     </row>
-    <row r="875" ht="15.95" customHeight="1">
+    <row r="875" ht="16" customHeight="1">
       <c r="A875" s="41" t="n"/>
       <c r="B875" s="24" t="inlineStr">
         <is>
@@ -30114,7 +31060,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F875" s="34" t="inlineStr">
+      <c r="F875" s="44" t="inlineStr">
         <is>
           <t>按Profile+事件类型查询操作历史 — 100%</t>
         </is>
@@ -30258,7 +31204,7 @@
         </is>
       </c>
     </row>
-    <row r="882">
+    <row r="882" ht="16" customHeight="1">
       <c r="A882" s="41" t="n"/>
       <c r="B882" s="26" t="inlineStr">
         <is>
@@ -30280,8 +31226,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="883">
+      <c r="F882" s="44" t="inlineStr">
+        <is>
+          <t>获取战略中心节假日列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="883" ht="16" customHeight="1">
       <c r="A883" s="41" t="n"/>
       <c r="B883" s="23" t="inlineStr">
         <is>
@@ -30303,8 +31254,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="884">
+      <c r="F883" s="44" t="inlineStr">
+        <is>
+          <t>US市场单profile节假日策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="884" ht="208" customHeight="1">
       <c r="A884" s="41" t="n"/>
       <c r="B884" s="27" t="inlineStr">
         <is>
@@ -30326,8 +31282,25 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="885">
+      <c r="F884" s="44" t="inlineStr">
+        <is>
+          <t>US市场单profile(场景1) — 58.4%
+CA市场单profile(场景2) — 6.5%
+JP市场单profile(场景3) — 6.2%
+US市场多profile(场景4) — 5.8%
+UK市场单profile(场景5) — 3.5%
+MX市场单profile(场景6) — 2.9%
+DE市场单profile(场景7) — 2.9%
+AU市场单profile(场景8) — 2.4%
+FR市场单profile(场景9) — 2.2%
+ES市场单profile(场景10) — 2.0%
+IT市场单profile(场景11) — 1.5%
+BR市场单profile(场景12) — 1.3%
+IN市场单profile(场景13) — 1.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="885" ht="192" customHeight="1">
       <c r="A885" s="41" t="n"/>
       <c r="B885" s="23" t="inlineStr">
         <is>
@@ -30349,8 +31322,24 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="886" ht="15.95" customHeight="1">
+      <c r="F885" s="44" t="inlineStr">
+        <is>
+          <t>US市场近期节假日(场景1) — 63%
+JP市场近期节假日(场景2) — 7.2%
+CA市场近期节假日(场景3) — 6.8%
+UK市场近期节假日(场景4) — 5%
+MX市场近期节假日(场景5) — 3.2%
+AU市场近期节假日(场景6) — 2.4%
+FR市场近期节假日(场景7) — 2.4%
+IN市场近期节假日(场景8) — 2.4%
+DE市场近期节假日(场景9) — 2.2%
+IT市场近期节假日(场景10) — 1.8%
+ES市场近期节假日(场景11) — 1.8%
+BR市场近期节假日(场景12) — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="886" ht="16" customHeight="1">
       <c r="A886" s="41" t="n"/>
       <c r="B886" s="26" t="inlineStr">
         <is>
@@ -30372,13 +31361,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F886" s="36" t="inlineStr">
+      <c r="F886" s="44" t="inlineStr">
         <is>
           <t>按Campaign+AdGroup维度查询小时级图表数据 — 65.2%</t>
         </is>
       </c>
     </row>
-    <row r="887" ht="15.95" customHeight="1">
+    <row r="887" ht="16" customHeight="1">
       <c r="A887" s="41" t="n"/>
       <c r="B887" s="23" t="inlineStr">
         <is>
@@ -30400,13 +31389,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F887" s="36" t="inlineStr">
+      <c r="F887" s="44" t="inlineStr">
         <is>
           <t>按Keyword+Asin维度查询小时级图表数据 — 58.4%</t>
         </is>
       </c>
     </row>
-    <row r="888" ht="15.95" customHeight="1">
+    <row r="888" ht="16" customHeight="1">
       <c r="A888" s="41" t="n"/>
       <c r="B888" s="27" t="inlineStr">
         <is>
@@ -30428,13 +31417,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F888" s="36" t="inlineStr">
+      <c r="F888" s="44" t="inlineStr">
         <is>
           <t>按Keyword+Campaign+AdGroup维度查询小时级图表数据 — 25.0%</t>
         </is>
       </c>
     </row>
-    <row r="889" ht="15.95" customHeight="1">
+    <row r="889" ht="16" customHeight="1">
       <c r="A889" s="41" t="n"/>
       <c r="B889" s="23" t="inlineStr">
         <is>
@@ -30456,13 +31445,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F889" s="36" t="inlineStr">
+      <c r="F889" s="44" t="inlineStr">
         <is>
           <t>按Keyword+Campaign维度查询小时级图表数据 — 14.8%</t>
         </is>
       </c>
     </row>
-    <row r="890" ht="15.95" customHeight="1">
+    <row r="890" ht="16" customHeight="1">
       <c r="A890" s="41" t="n"/>
       <c r="B890" s="27" t="inlineStr">
         <is>
@@ -30484,13 +31473,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F890" s="36" t="inlineStr">
+      <c r="F890" s="44" t="inlineStr">
         <is>
           <t>按Keyword+CampaignType维度查询小时级图表数据 — 60.0%</t>
         </is>
       </c>
     </row>
-    <row r="891" ht="15.95" customHeight="1">
+    <row r="891" ht="16" customHeight="1">
       <c r="A891" s="41" t="n"/>
       <c r="B891" s="23" t="inlineStr">
         <is>
@@ -30512,13 +31501,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F891" s="36" t="inlineStr">
+      <c r="F891" s="44" t="inlineStr">
         <is>
           <t>按Keyword+Placement维度查询小时级图表数据 — 39.6%</t>
         </is>
       </c>
     </row>
-    <row r="892" ht="15.95" customHeight="1">
+    <row r="892" ht="16" customHeight="1">
       <c r="A892" s="41" t="n"/>
       <c r="B892" s="27" t="inlineStr">
         <is>
@@ -30540,13 +31529,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F892" s="36" t="inlineStr">
+      <c r="F892" s="44" t="inlineStr">
         <is>
           <t>查询Keyword维度小时级汇总对比数据 — 39.6%</t>
         </is>
       </c>
     </row>
-    <row r="893" ht="15.95" customHeight="1">
+    <row r="893" ht="16" customHeight="1">
       <c r="A893" s="41" t="n"/>
       <c r="B893" s="23" t="inlineStr">
         <is>
@@ -30568,13 +31557,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F893" s="36" t="inlineStr">
+      <c r="F893" s="44" t="inlineStr">
         <is>
           <t>查询Keyword维度小时级趋势图数据 — 42.1%</t>
         </is>
       </c>
     </row>
-    <row r="894" ht="15.95" customHeight="1">
+    <row r="894" ht="16" customHeight="1">
       <c r="A894" s="41" t="n"/>
       <c r="B894" s="27" t="inlineStr">
         <is>
@@ -30596,13 +31585,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F894" s="36" t="inlineStr">
+      <c r="F894" s="44" t="inlineStr">
         <is>
           <t>按CampaignTag维度查询小时级Profile图表数据 — 100.0%</t>
         </is>
       </c>
     </row>
-    <row r="895" ht="15.95" customHeight="1">
+    <row r="895" ht="16" customHeight="1">
       <c r="A895" s="41" t="n"/>
       <c r="B895" s="23" t="inlineStr">
         <is>
@@ -30624,13 +31613,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F895" s="36" t="inlineStr">
+      <c r="F895" s="44" t="inlineStr">
         <is>
           <t>按Campaign+AdGroup维度分页查询小时级表格数据 — 66.2%</t>
         </is>
       </c>
     </row>
-    <row r="896" ht="15.95" customHeight="1">
+    <row r="896" ht="16" customHeight="1">
       <c r="A896" s="41" t="n"/>
       <c r="B896" s="27" t="inlineStr">
         <is>
@@ -30652,13 +31641,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F896" s="36" t="inlineStr">
+      <c r="F896" s="44" t="inlineStr">
         <is>
           <t>按Keyword+Asin维度分页查询小时级表格数据 — 32.2%</t>
         </is>
       </c>
     </row>
-    <row r="897" ht="15.95" customHeight="1">
+    <row r="897" ht="16" customHeight="1">
       <c r="A897" s="41" t="n"/>
       <c r="B897" s="23" t="inlineStr">
         <is>
@@ -30680,13 +31669,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F897" s="36" t="inlineStr">
+      <c r="F897" s="44" t="inlineStr">
         <is>
           <t>按Keyword+Campaign+AdGroup维度分页查询小时级表格数据 — 50.0%</t>
         </is>
       </c>
     </row>
-    <row r="898" ht="15.95" customHeight="1">
+    <row r="898" ht="16" customHeight="1">
       <c r="A898" s="41" t="n"/>
       <c r="B898" s="27" t="inlineStr">
         <is>
@@ -30708,13 +31697,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F898" s="36" t="inlineStr">
+      <c r="F898" s="44" t="inlineStr">
         <is>
           <t>按Keyword+Campaign维度分页查询小时级表格数据 — 19.4%</t>
         </is>
       </c>
     </row>
-    <row r="899" ht="15.95" customHeight="1">
+    <row r="899" ht="16" customHeight="1">
       <c r="A899" s="41" t="n"/>
       <c r="B899" s="23" t="inlineStr">
         <is>
@@ -30736,13 +31725,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F899" s="36" t="inlineStr">
+      <c r="F899" s="44" t="inlineStr">
         <is>
           <t>按Keyword+CampaignType维度分页查询小时级表格数据 — 70.3%</t>
         </is>
       </c>
     </row>
-    <row r="900" ht="15.95" customHeight="1">
+    <row r="900" ht="16" customHeight="1">
       <c r="A900" s="41" t="n"/>
       <c r="B900" s="27" t="inlineStr">
         <is>
@@ -30764,13 +31753,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F900" s="36" t="inlineStr">
+      <c r="F900" s="44" t="inlineStr">
         <is>
           <t>按Asin+Placement维度分页查询小时级表格数据 — 23.8%</t>
         </is>
       </c>
     </row>
-    <row r="901" ht="15.95" customHeight="1">
+    <row r="901" ht="16" customHeight="1">
       <c r="A901" s="41" t="n"/>
       <c r="B901" s="23" t="inlineStr">
         <is>
@@ -30792,13 +31781,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F901" s="36" t="inlineStr">
+      <c r="F901" s="44" t="inlineStr">
         <is>
           <t>按CampaignTag维度分页查询小时级Profile表格数据 — 48.5%</t>
         </is>
       </c>
     </row>
-    <row r="902" ht="15.95" customHeight="1">
+    <row r="902" ht="16" customHeight="1">
       <c r="A902" s="41" t="n"/>
       <c r="B902" s="27" t="inlineStr">
         <is>
@@ -30820,13 +31809,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F902" s="36" t="inlineStr">
+      <c r="F902" s="44" t="inlineStr">
         <is>
           <t>按Asin+Target维度分页查询小时级表格数据 — 25.4%</t>
         </is>
       </c>
     </row>
-    <row r="903" ht="15.95" customHeight="1">
+    <row r="903" ht="16" customHeight="1">
       <c r="A903" s="41" t="n"/>
       <c r="B903" s="23" t="inlineStr">
         <is>
@@ -30848,7 +31837,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F903" s="36" t="inlineStr">
+      <c r="F903" s="44" t="inlineStr">
         <is>
           <t>按Campaign+AdGroup维度查询小时级Target图表数据 — 41.6%</t>
         </is>
@@ -31268,7 +32257,7 @@
         </is>
       </c>
     </row>
-    <row r="922">
+    <row r="922" ht="32" customHeight="1">
       <c r="A922" s="41" t="n"/>
       <c r="B922" s="26" t="inlineStr">
         <is>
@@ -31288,6 +32277,12 @@
       <c r="E922" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F922" s="44" t="inlineStr">
+        <is>
+          <t>单关键词添加(含后置清理,可重复) — 54%
+多关键词批量添加(含后置清理,可重复) — 46%</t>
         </is>
       </c>
     </row>
@@ -31314,7 +32309,7 @@
         </is>
       </c>
     </row>
-    <row r="924">
+    <row r="924" ht="64" customHeight="1">
       <c r="A924" s="41" t="n"/>
       <c r="B924" s="27" t="inlineStr">
         <is>
@@ -31336,8 +32331,16 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="925">
+      <c r="F924" s="44" t="inlineStr">
+        <is>
+          <t>JP近期月份(2026-01) — 42%
+JP上月(2025-12) — 33%
+JP较早月份(2026-02) — 13%
+JP历史月份(2025-11) — 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="925" ht="16" customHeight="1">
       <c r="A925" s="41" t="n"/>
       <c r="B925" s="23" t="inlineStr">
         <is>
@@ -31357,6 +32360,11 @@
       <c r="E925" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F925" s="44" t="inlineStr">
+        <is>
+          <t>查询关键词总数 — 100%</t>
         </is>
       </c>
     </row>
@@ -32947,7 +33955,7 @@
         </is>
       </c>
     </row>
-    <row r="995">
+    <row r="995" ht="16" customHeight="1">
       <c r="A995" s="41" t="n"/>
       <c r="B995" s="23" t="inlineStr">
         <is>
@@ -32969,8 +33977,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="996">
+      <c r="F995" s="44" t="inlineStr">
+        <is>
+          <t>Okta OAuth回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="996" ht="112" customHeight="1">
       <c r="A996" s="41" t="n"/>
       <c r="B996" s="27" t="inlineStr">
         <is>
@@ -32992,8 +34005,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="997">
+      <c r="F996" s="44" t="inlineStr">
+        <is>
+          <t>Colgate+Commerce OAuth回调 — 51%
+Emerson+Amazon OAuth回调 — 21%
+Emerson+Commerce OAuth回调 — 12%
+Colgate+Amazon OAuth回调 — 10%
+Colgate+Walmart OAuth回调 — 3%
+Tinuiti+Amazon OAuth回调 — 2%
+Colgate+DSP OAuth回调 — 1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="997" ht="96" customHeight="1">
       <c r="A997" s="41" t="n"/>
       <c r="B997" s="23" t="inlineStr">
         <is>
@@ -33015,8 +34039,18 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="998">
+      <c r="F997" s="44" t="inlineStr">
+        <is>
+          <t>获取Colgate Okta授权URL — 54.5%
+获取Emerson Okta授权URL — 27.5%
+client=t/login/null — 9.5%
+client=t/login/sign — 2.5%
+client=/login/null — 2%
+client=null — 1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="998" ht="144" customHeight="1">
       <c r="A998" s="41" t="n"/>
       <c r="B998" s="27" t="inlineStr">
         <is>
@@ -33036,6 +34070,19 @@
       <c r="E998" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F998" s="44" t="inlineStr">
+        <is>
+          <t>Amazon平台OAuth回调 — 35.8%
+Walmart平台OAuth回调 — 29.4%
+Target平台OAuth回调 — 9.4%
+Criteo平台OAuth回调 — 8.2%
+SamsClub平台OAuth回调 — 6%
+Instacart平台OAuth回调 — 3.4%
+DoorDash平台OAuth回调 — 3.2%
+DSP平台OAuth回调 — 2.4%
+Kroger平台OAuth回调 — 1.4%</t>
         </is>
       </c>
     </row>
@@ -33315,7 +34362,7 @@
         </is>
       </c>
     </row>
-    <row r="1011">
+    <row r="1011" ht="16" customHeight="1">
       <c r="A1011" s="41" t="n"/>
       <c r="B1011" s="23" t="inlineStr">
         <is>
@@ -33337,8 +34384,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1012">
+      <c r="F1011" s="44" t="inlineStr">
+        <is>
+          <t>批量更新Card预算与锁定（含前置建/后置删,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012" ht="16" customHeight="1">
       <c r="A1012" s="41" t="n"/>
       <c r="B1012" s="27" t="inlineStr">
         <is>
@@ -33358,6 +34410,11 @@
       <c r="E1012" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1012" s="44" t="inlineStr">
+        <is>
+          <t>跨计划批量拆分更新Card（含前置建/后置删,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -33384,7 +34441,7 @@
         </is>
       </c>
     </row>
-    <row r="1014">
+    <row r="1014" ht="16" customHeight="1">
       <c r="A1014" s="41" t="n"/>
       <c r="B1014" s="27" t="inlineStr">
         <is>
@@ -33406,8 +34463,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1015">
+      <c r="F1014" s="44" t="inlineStr">
+        <is>
+          <t>拉取Reach与Performance预测（含前置建/后置删,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015" ht="16" customHeight="1">
       <c r="A1015" s="41" t="n"/>
       <c r="B1015" s="23" t="inlineStr">
         <is>
@@ -33429,8 +34491,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1016">
+      <c r="F1015" s="44" t="inlineStr">
+        <is>
+          <t>按 Profile 查询媒体计划列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016" ht="16" customHeight="1">
       <c r="A1016" s="41" t="n"/>
       <c r="B1016" s="27" t="inlineStr">
         <is>
@@ -33450,6 +34517,11 @@
       <c r="E1016" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1016" s="44" t="inlineStr">
+        <is>
+          <t>按用户查询媒体计划列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -33476,7 +34548,7 @@
         </is>
       </c>
     </row>
-    <row r="1018">
+    <row r="1018" ht="16" customHeight="1">
       <c r="A1018" s="41" t="n"/>
       <c r="B1018" s="27" t="inlineStr">
         <is>
@@ -33496,6 +34568,11 @@
       <c r="E1018" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1018" s="44" t="inlineStr">
+        <is>
+          <t>批量推荐Deals（含前置建/后置删,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -33522,7 +34599,7 @@
         </is>
       </c>
     </row>
-    <row r="1020">
+    <row r="1020" ht="16" customHeight="1">
       <c r="A1020" s="41" t="n"/>
       <c r="B1020" s="27" t="inlineStr">
         <is>
@@ -33542,6 +34619,11 @@
       <c r="E1020" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1020" s="44" t="inlineStr">
+        <is>
+          <t>新建SP零售媒体计划（含后置清理,可重复） — 85%</t>
         </is>
       </c>
     </row>
@@ -33591,7 +34673,7 @@
         </is>
       </c>
     </row>
-    <row r="1023">
+    <row r="1023" ht="48" customHeight="1">
       <c r="A1023" s="41" t="n"/>
       <c r="B1023" s="23" t="inlineStr">
         <is>
@@ -33613,8 +34695,15 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1024">
+      <c r="F1023" s="44" t="inlineStr">
+        <is>
+          <t>查询计划详情及全部Cards（含前置建/后置删,可重复） — 100%
+更新媒体计划字段（含前置建/后置删,可重复） — 100%
+删除媒体计划及全部Cards（含前置建,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024" ht="48" customHeight="1">
       <c r="A1024" s="41" t="n"/>
       <c r="B1024" s="27" t="inlineStr">
         <is>
@@ -33636,8 +34725,15 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1025">
+      <c r="F1024" s="44" t="inlineStr">
+        <is>
+          <t>查询计划详情及全部Cards（含前置建/后置删,可重复） — 100%
+更新媒体计划字段（含前置建/后置删,可重复） — 100%
+删除媒体计划及全部Cards（含前置建,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025" ht="48" customHeight="1">
       <c r="A1025" s="41" t="n"/>
       <c r="B1025" s="23" t="inlineStr">
         <is>
@@ -33659,8 +34755,15 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1026">
+      <c r="F1025" s="44" t="inlineStr">
+        <is>
+          <t>查询计划详情及全部Cards（含前置建/后置删,可重复） — 100%
+更新媒体计划字段（含前置建/后置删,可重复） — 100%
+删除媒体计划及全部Cards（含前置建,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026" ht="16" customHeight="1">
       <c r="A1026" s="41" t="n"/>
       <c r="B1026" s="27" t="inlineStr">
         <is>
@@ -33680,6 +34783,11 @@
       <c r="E1026" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1026" s="44" t="inlineStr">
+        <is>
+          <t>切换计划预算类型（含前置建/后置删,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -33706,7 +34814,7 @@
         </is>
       </c>
     </row>
-    <row r="1028">
+    <row r="1028" ht="32" customHeight="1">
       <c r="A1028" s="41" t="n"/>
       <c r="B1028" s="27" t="inlineStr">
         <is>
@@ -33728,8 +34836,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1029">
+      <c r="F1028" s="44" t="inlineStr">
+        <is>
+          <t>新增Card到计划（含前置建/后置删,可重复） — 100%
+删除指定Card（含前置建/后置删,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029" ht="32" customHeight="1">
       <c r="A1029" s="41" t="n"/>
       <c r="B1029" s="23" t="inlineStr">
         <is>
@@ -33751,8 +34865,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1030">
+      <c r="F1029" s="44" t="inlineStr">
+        <is>
+          <t>新增Card到计划（含前置建/后置删,可重复） — 100%
+删除指定Card（含前置建/后置删,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030" ht="16" customHeight="1">
       <c r="A1030" s="41" t="n"/>
       <c r="B1030" s="27" t="inlineStr">
         <is>
@@ -33774,8 +34894,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1031" ht="15.95" customHeight="1">
+      <c r="F1030" s="44" t="inlineStr">
+        <is>
+          <t>按定向类型拆分更新Card（含前置建/后置删,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031" ht="16" customHeight="1">
       <c r="A1031" s="41" t="n"/>
       <c r="B1031" s="24" t="inlineStr">
         <is>
@@ -33797,13 +34922,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1031" s="36" t="inlineStr">
+      <c r="F1031" s="44" t="inlineStr">
         <is>
           <t>查询当前用户全部否定关键词列表 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1032" ht="15.95" customHeight="1">
+    <row r="1032" ht="16" customHeight="1">
       <c r="A1032" s="41" t="n"/>
       <c r="B1032" s="27" t="inlineStr">
         <is>
@@ -33825,13 +34950,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1032" s="36" t="inlineStr">
+      <c r="F1032" s="44" t="inlineStr">
         <is>
           <t>查询否定关键词应用状态明细(v1)</t>
         </is>
       </c>
     </row>
-    <row r="1033" ht="15.95" customHeight="1">
+    <row r="1033" ht="16" customHeight="1">
       <c r="A1033" s="41" t="n"/>
       <c r="B1033" s="23" t="inlineStr">
         <is>
@@ -33853,13 +34978,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1033" s="36" t="inlineStr">
+      <c r="F1033" s="44" t="inlineStr">
         <is>
           <t>查询否定关键词应用状态明细(v2) — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1034">
+    <row r="1034" ht="16" customHeight="1">
       <c r="A1034" s="41" t="n"/>
       <c r="B1034" s="27" t="inlineStr">
         <is>
@@ -33881,8 +35006,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1035">
+      <c r="F1034" s="44" t="inlineStr">
+        <is>
+          <t>批量直接创建AdGroup级否定关键词(含创建Campaign+清理) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035" ht="16" customHeight="1">
       <c r="A1035" s="41" t="n"/>
       <c r="B1035" s="23" t="inlineStr">
         <is>
@@ -33904,8 +35034,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1036">
+      <c r="F1035" s="44" t="inlineStr">
+        <is>
+          <t>查询Campaign当前关联的否定关键词列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036" ht="16" customHeight="1">
       <c r="A1036" s="41" t="n"/>
       <c r="B1036" s="27" t="inlineStr">
         <is>
@@ -33925,6 +35060,11 @@
       <c r="E1036" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1036" s="44" t="inlineStr">
+        <is>
+          <t>批量为多个列表添加同一关键词(含创建+清理) — 84.1%</t>
         </is>
       </c>
     </row>
@@ -33950,11 +35090,9 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1037" s="36" t="inlineStr">
-        <is>
-          <t>创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100%
-为单个Campaign直接应用否定关键词列表(含创建+清理) — 90.9%
-批量为多个列表添加同一关键词(含创建+清理) — 84.1%</t>
+      <c r="F1037" s="44" t="inlineStr">
+        <is>
+          <t>创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100%</t>
         </is>
       </c>
     </row>
@@ -34050,7 +35188,7 @@
         </is>
       </c>
     </row>
-    <row r="1042" ht="15.95" customHeight="1">
+    <row r="1042" ht="16" customHeight="1">
       <c r="A1042" s="41" t="n"/>
       <c r="B1042" s="27" t="inlineStr">
         <is>
@@ -34072,13 +35210,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1042" s="36" t="inlineStr">
+      <c r="F1042" s="44" t="inlineStr">
         <is>
           <t>按Profile查询AdGroup列表 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1043" ht="15.95" customHeight="1">
+    <row r="1043" ht="16" customHeight="1">
       <c r="A1043" s="41" t="n"/>
       <c r="B1043" s="23" t="inlineStr">
         <is>
@@ -34100,13 +35238,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1043" s="36" t="inlineStr">
+      <c r="F1043" s="44" t="inlineStr">
         <is>
           <t>按Campaign查询AdGroup已有否定关键词 — 69.8%</t>
         </is>
       </c>
     </row>
-    <row r="1044" ht="15.95" customHeight="1">
+    <row r="1044" ht="16" customHeight="1">
       <c r="A1044" s="41" t="n"/>
       <c r="B1044" s="27" t="inlineStr">
         <is>
@@ -34128,13 +35266,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1044" s="36" t="inlineStr">
+      <c r="F1044" s="44" t="inlineStr">
         <is>
           <t>按Campaign查询AdGroup定位信息 — 64.4%</t>
         </is>
       </c>
     </row>
-    <row r="1045" ht="15.95" customHeight="1">
+    <row r="1045" ht="16" customHeight="1">
       <c r="A1045" s="41" t="n"/>
       <c r="B1045" s="23" t="inlineStr">
         <is>
@@ -34156,13 +35294,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1045" s="36" t="inlineStr">
+      <c r="F1045" s="44" t="inlineStr">
         <is>
           <t>按关键词查询关联品牌列表 — 60.2%</t>
         </is>
       </c>
     </row>
-    <row r="1046" ht="15.95" customHeight="1">
+    <row r="1046" ht="16" customHeight="1">
       <c r="A1046" s="41" t="n"/>
       <c r="B1046" s="27" t="inlineStr">
         <is>
@@ -34184,13 +35322,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1046" s="36" t="inlineStr">
+      <c r="F1046" s="44" t="inlineStr">
         <is>
           <t>查询Campaign否定关键词自动化探索状态 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1047" ht="15.95" customHeight="1">
+    <row r="1047" ht="16" customHeight="1">
       <c r="A1047" s="41" t="n"/>
       <c r="B1047" s="23" t="inlineStr">
         <is>
@@ -34212,7 +35350,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1047" s="36" t="inlineStr">
+      <c r="F1047" s="44" t="inlineStr">
         <is>
           <t>按Profile+Level查询可选Campaign列表 — 85.6%</t>
         </is>
@@ -34241,7 +35379,7 @@
         </is>
       </c>
     </row>
-    <row r="1049" ht="15.95" customHeight="1">
+    <row r="1049" ht="16" customHeight="1">
       <c r="A1049" s="41" t="n"/>
       <c r="B1049" s="23" t="inlineStr">
         <is>
@@ -34263,7 +35401,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1049" s="36" t="inlineStr">
+      <c r="F1049" s="44" t="inlineStr">
         <is>
           <t>按Id查询列表详情(分享链接场景) — 100%</t>
         </is>
@@ -34292,7 +35430,7 @@
         </is>
       </c>
     </row>
-    <row r="1051">
+    <row r="1051" ht="16" customHeight="1">
       <c r="A1051" s="41" t="n"/>
       <c r="B1051" s="23" t="inlineStr">
         <is>
@@ -34314,8 +35452,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1052" ht="15.95" customHeight="1">
+      <c r="F1051" s="44" t="inlineStr">
+        <is>
+          <t>按CampaignTag查询自动化否定统计 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052" ht="16" customHeight="1">
       <c r="A1052" s="41" t="n"/>
       <c r="B1052" s="27" t="inlineStr">
         <is>
@@ -34337,7 +35480,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1052" s="36" t="inlineStr">
+      <c r="F1052" s="44" t="inlineStr">
         <is>
           <t>分页查询关键词级应用状态 — 100%</t>
         </is>
@@ -34389,7 +35532,7 @@
         </is>
       </c>
     </row>
-    <row r="1055">
+    <row r="1055" ht="16" customHeight="1">
       <c r="A1055" s="41" t="n"/>
       <c r="B1055" s="23" t="inlineStr">
         <is>
@@ -34409,6 +35552,11 @@
       <c r="E1055" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1055" s="44" t="inlineStr">
+        <is>
+          <t>为单个Campaign直接应用否定关键词列表(含创建+清理) — 90.9%</t>
         </is>
       </c>
     </row>
@@ -34734,7 +35882,7 @@
         </is>
       </c>
     </row>
-    <row r="1070">
+    <row r="1070" ht="16" customHeight="1">
       <c r="A1070" s="41" t="n"/>
       <c r="B1070" s="26" t="inlineStr">
         <is>
@@ -34754,6 +35902,11 @@
       <c r="E1070" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1070" s="44" t="inlineStr">
+        <is>
+          <t>变更否定词状态归档(含前置创建,可重复)</t>
         </is>
       </c>
     </row>
@@ -34779,6 +35932,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1071" s="44" t="inlineStr">
+        <is>
+          <t>广告组级negativeExact(含后置清理,可重复) — 49.8%
+Campaign级negativeExact(含后置清理,可重复) — 40.4%
+广告组级negativePhrase(含后置清理,可重复) — 7.0%
+Campaign级negativePhrase(含后置清理,可重复) — 2.8%</t>
+        </is>
+      </c>
     </row>
     <row r="1072" ht="48" customHeight="1">
       <c r="A1072" s="41" t="n"/>
@@ -34802,8 +35963,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1073" ht="15.95" customHeight="1">
+      <c r="F1072" s="44" t="inlineStr">
+        <is>
+          <t>否定商品asinSameAs(含后置清理,可重复) — 90.1%
+否定品牌asinBrandSameAs(含后置清理,可重复) — 9.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073" ht="48" customHeight="1">
       <c r="A1073" s="41" t="n"/>
       <c r="B1073" s="23" t="inlineStr">
         <is>
@@ -34825,8 +35992,15 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1074" ht="15.95" customHeight="1">
+      <c r="F1073" s="44" t="inlineStr">
+        <is>
+          <t>查询否定关键词(exact+phrase) — 59.6%
+查询否定投放(product+brand) — 37.2%
+查询全部否定类型 — 3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074" ht="16" customHeight="1">
       <c r="A1074" s="41" t="n"/>
       <c r="B1074" s="27" t="inlineStr">
         <is>
@@ -34848,8 +36022,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1075" ht="15.95" customHeight="1">
+      <c r="F1074" s="44" t="inlineStr">
+        <is>
+          <t>按关键词查否定状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075" ht="16" customHeight="1">
       <c r="A1075" s="41" t="n"/>
       <c r="B1075" s="23" t="inlineStr">
         <is>
@@ -34871,8 +36050,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1076">
+      <c r="F1075" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN查否定投放状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076" ht="64" customHeight="1">
       <c r="A1076" s="41" t="n"/>
       <c r="B1076" s="27" t="inlineStr">
         <is>
@@ -34894,8 +36078,16 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1077" ht="15.95" customHeight="1">
+      <c r="F1076" s="44" t="inlineStr">
+        <is>
+          <t>否定关键词归档(含前置创建,可重复) — 64.7%
+否定商品投放归档(含前置创建,可重复) — 24.1%
+否定关键词暂停后恢复(含前置创建,可重复) — 6.4%
+否定关键词恢复enabled(含前置创建,可重复) — 3.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077" ht="16" customHeight="1">
       <c r="A1077" s="41" t="n"/>
       <c r="B1077" s="24" t="inlineStr">
         <is>
@@ -34917,13 +36109,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1077" s="36" t="inlineStr">
+      <c r="F1077" s="44" t="inlineStr">
         <is>
           <t>邮件通知规则生命周期(创建+查+改+暂停+删除)</t>
         </is>
       </c>
     </row>
-    <row r="1078">
+    <row r="1078" ht="16" customHeight="1">
       <c r="A1078" s="41" t="n"/>
       <c r="B1078" s="27" t="inlineStr">
         <is>
@@ -34943,6 +36135,11 @@
       <c r="E1078" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1078" s="44" t="inlineStr">
+        <is>
+          <t>保存预算通知设置(含读取+还原) — 50%</t>
         </is>
       </c>
     </row>
@@ -35173,7 +36370,7 @@
         </is>
       </c>
     </row>
-    <row r="1088" ht="15.95" customHeight="1">
+    <row r="1088" ht="16" customHeight="1">
       <c r="A1088" s="41" t="n"/>
       <c r="B1088" s="27" t="inlineStr">
         <is>
@@ -35195,13 +36392,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1088" s="36" t="inlineStr">
+      <c r="F1088" s="44" t="inlineStr">
         <is>
           <t>查询当前用户可用Profile列表</t>
         </is>
       </c>
     </row>
-    <row r="1089">
+    <row r="1089" ht="16" customHeight="1">
       <c r="A1089" s="41" t="n"/>
       <c r="B1089" s="23" t="inlineStr">
         <is>
@@ -35221,6 +36418,11 @@
       <c r="E1089" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1089" s="44" t="inlineStr">
+        <is>
+          <t>保存标签匹配规则提醒设置(含读取+还原)</t>
         </is>
       </c>
     </row>
@@ -35247,7 +36449,7 @@
         </is>
       </c>
     </row>
-    <row r="1091">
+    <row r="1091" ht="16" customHeight="1">
       <c r="A1091" s="41" t="n"/>
       <c r="B1091" s="23" t="inlineStr">
         <is>
@@ -35269,8 +36471,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1092">
+      <c r="F1091" s="44" t="inlineStr">
+        <is>
+          <t>保存超预算邮件提醒设置(含读取+还原) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092" ht="16" customHeight="1">
       <c r="A1092" s="41" t="n"/>
       <c r="B1092" s="27" t="inlineStr">
         <is>
@@ -35292,8 +36499,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1093">
+      <c r="F1092" s="44" t="inlineStr">
+        <is>
+          <t>保存商品资质邮件提醒设置(含读取+还原)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093" ht="16" customHeight="1">
       <c r="A1093" s="41" t="n"/>
       <c r="B1093" s="23" t="inlineStr">
         <is>
@@ -35315,8 +36527,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1094" ht="15.95" customHeight="1">
+      <c r="F1093" s="44" t="inlineStr">
+        <is>
+          <t>保存类型级邮件/站内信告警设置(含读取+还原)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094" ht="16" customHeight="1">
       <c r="A1094" s="41" t="n"/>
       <c r="B1094" s="27" t="inlineStr">
         <is>
@@ -35338,7 +36555,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1094" s="36" t="inlineStr">
+      <c r="F1094" s="44" t="inlineStr">
         <is>
           <t>通用邮件/站内信通知设置生命周期(创建+查+改状态+删除) — 100%</t>
         </is>
@@ -35574,7 +36791,7 @@
         </is>
       </c>
     </row>
-    <row r="1105" ht="15.95" customHeight="1">
+    <row r="1105" ht="16" customHeight="1">
       <c r="A1105" s="41" t="n"/>
       <c r="B1105" s="24" t="inlineStr">
         <is>
@@ -35596,7 +36813,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1105" s="34" t="inlineStr">
+      <c r="F1105" s="44" t="inlineStr">
         <is>
           <t>保存Campaign成本控制规则</t>
         </is>
@@ -35694,7 +36911,7 @@
         </is>
       </c>
     </row>
-    <row r="1110">
+    <row r="1110" ht="32" customHeight="1">
       <c r="A1110" s="41" t="n"/>
       <c r="B1110" s="26" t="inlineStr">
         <is>
@@ -35716,8 +36933,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1111">
+      <c r="F1110" s="44" t="inlineStr">
+        <is>
+          <t>场景1：添加单个 SB Campaign 到 Portfolio（含后置清理） — 33%
+场景2：批量添加多个 SP Campaign 到 Portfolio（含后置清理） — 67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111" ht="16" customHeight="1">
       <c r="A1111" s="41" t="n"/>
       <c r="B1111" s="23" t="inlineStr">
         <is>
@@ -35739,8 +36962,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1112">
+      <c r="F1111" s="44" t="inlineStr">
+        <is>
+          <t>场景1：按名称+状态过滤批量添加 Campaign 到 Portfolio — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112" ht="48" customHeight="1">
       <c r="A1112" s="41" t="n"/>
       <c r="B1112" s="27" t="inlineStr">
         <is>
@@ -35762,8 +36990,15 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1113">
+      <c r="F1112" s="44" t="inlineStr">
+        <is>
+          <t>场景1：全量 Portfolio 列表（Spend 排序，无过滤） — 40%
+场景2：指定 PortfolioIds 过滤 — 34.6%
+场景3：日期对比模式（startCompar/endCompar） — 12.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113" ht="48" customHeight="1">
       <c r="A1113" s="41" t="n"/>
       <c r="B1113" s="23" t="inlineStr">
         <is>
@@ -35785,8 +37020,15 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1114">
+      <c r="F1113" s="44" t="inlineStr">
+        <is>
+          <t>场景1：全量 Portfolio 汇总行（无对比） — 25%
+场景2：对比模式汇总行（isExchange=1） — 54.6%
+场景3：指定 Portfolio 过滤汇总行 — 32.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114" ht="32" customHeight="1">
       <c r="A1114" s="41" t="n"/>
       <c r="B1114" s="27" t="inlineStr">
         <is>
@@ -35808,8 +37050,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1115">
+      <c r="F1114" s="44" t="inlineStr">
+        <is>
+          <t>场景1：全量 Portfolio 趋势图（isExchange=1） — 64.2%
+场景2：含 ServingStatus 过滤的趋势图 — 3.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115" ht="16" customHeight="1">
       <c r="A1115" s="41" t="n"/>
       <c r="B1115" s="24" t="inlineStr">
         <is>
@@ -35831,8 +37079,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="1116">
+      <c r="F1115" s="44" t="inlineStr">
+        <is>
+          <t>批量更新ProductAd状态(旧版,含一次性campaign创建+清理)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116" ht="16" customHeight="1">
       <c r="A1116" s="41" t="n"/>
       <c r="B1116" s="27" t="inlineStr">
         <is>
@@ -35852,6 +37105,11 @@
       <c r="E1116" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F1116" s="44" t="inlineStr">
+        <is>
+          <t>批量更新ProductAd状态(含一次性campaign创建+清理) — 100%</t>
         </is>
       </c>
     </row>
@@ -35970,7 +37228,7 @@
         </is>
       </c>
     </row>
-    <row r="1122" ht="15.95" customHeight="1">
+    <row r="1122" ht="16" customHeight="1">
       <c r="A1122" s="41" t="n"/>
       <c r="B1122" s="26" t="inlineStr">
         <is>
@@ -35992,13 +37250,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1122" s="34" t="inlineStr">
+      <c r="F1122" s="44" t="inlineStr">
         <is>
           <t>导出Top商品数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1123" ht="15.95" customHeight="1">
+    <row r="1123" ht="16" customHeight="1">
       <c r="A1123" s="41" t="n"/>
       <c r="B1123" s="23" t="inlineStr">
         <is>
@@ -36020,13 +37278,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1123" s="34" t="inlineStr">
+      <c r="F1123" s="44" t="inlineStr">
         <is>
           <t>按ServingState查询商品资质分页数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1124" ht="15.95" customHeight="1">
+    <row r="1124" ht="16" customHeight="1">
       <c r="A1124" s="41" t="n"/>
       <c r="B1124" s="27" t="inlineStr">
         <is>
@@ -36048,13 +37306,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1124" s="34" t="inlineStr">
+      <c r="F1124" s="44" t="inlineStr">
         <is>
           <t>按标签+广告主查询Top商品 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1125" ht="15.95" customHeight="1">
+    <row r="1125" ht="16" customHeight="1">
       <c r="A1125" s="41" t="n"/>
       <c r="B1125" s="23" t="inlineStr">
         <is>
@@ -36076,7 +37334,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1125" s="34" t="inlineStr">
+      <c r="F1125" s="44" t="inlineStr">
         <is>
           <t>查询商品资质统计计数 — 100%</t>
         </is>
@@ -36220,7 +37478,7 @@
         </is>
       </c>
     </row>
-    <row r="1132">
+    <row r="1132" ht="16" customHeight="1">
       <c r="A1132" s="41" t="n"/>
       <c r="B1132" s="26" t="inlineStr">
         <is>
@@ -36242,8 +37500,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1133">
+      <c r="F1132" s="44" t="inlineStr">
+        <is>
+          <t>查询用户Profile国家码(结构构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133" ht="16" customHeight="1">
       <c r="A1133" s="41" t="n"/>
       <c r="B1133" s="23" t="inlineStr">
         <is>
@@ -36265,8 +37528,18 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1134">
+      <c r="F1133" s="44" t="inlineStr">
+        <is>
+          <t>查询3P Profile列表(结构构造)</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>[废弃/线上无调用][us] ES全时段无任何真实用户请求(仅测试触发)，疑似前端未接线的废弃接口。直连线上稳定返回 code=513: The multi-part identifier "ProfileListInput" could not be bound(后端将DTO类名误拼入SQL)，任何入参必失败。低优先级，建议后端确认下线或修复。(2026-08-18 自动化用例发现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134" ht="16" customHeight="1">
       <c r="A1134" s="41" t="n"/>
       <c r="B1134" s="27" t="inlineStr">
         <is>
@@ -36288,8 +37561,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1135">
+      <c r="F1134" s="44" t="inlineStr">
+        <is>
+          <t>按广告主ID查Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135" ht="16" customHeight="1">
       <c r="A1135" s="41" t="n"/>
       <c r="B1135" s="23" t="inlineStr">
         <is>
@@ -36311,8 +37589,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1136">
+      <c r="F1135" s="44" t="inlineStr">
+        <is>
+          <t>校验AMC授权 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136" ht="16" customHeight="1">
       <c r="A1136" s="41" t="n"/>
       <c r="B1136" s="27" t="inlineStr">
         <is>
@@ -36334,8 +37617,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1137">
+      <c r="F1136" s="44" t="inlineStr">
+        <is>
+          <t>查询Profile数据状态(结构构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137" ht="16" customHeight="1">
       <c r="A1137" s="41" t="n"/>
       <c r="B1137" s="23" t="inlineStr">
         <is>
@@ -36357,8 +37645,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1138">
+      <c r="F1137" s="44" t="inlineStr">
+        <is>
+          <t>查询Profile预算模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138" ht="16" customHeight="1">
       <c r="A1138" s="41" t="n"/>
       <c r="B1138" s="27" t="inlineStr">
         <is>
@@ -36380,8 +37673,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1139">
+      <c r="F1138" s="44" t="inlineStr">
+        <is>
+          <t>YTD趋势图数据 — 99.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139" ht="80" customHeight="1">
       <c r="A1139" s="41" t="n"/>
       <c r="B1139" s="23" t="inlineStr">
         <is>
@@ -36403,8 +37701,17 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1140">
+      <c r="F1139" s="44" t="inlineStr">
+        <is>
+          <t>YTD汇总(默认时间维度) — 85.7%
+自定义日期(dim=date)按天明细 — 10.2%
+高级过滤请求(大写字段+多指标Operand) — 7.4%
+按月维度(dim=month) — 2.4%
+按周维度(dim=week) — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140" ht="16" customHeight="1">
       <c r="A1140" s="41" t="n"/>
       <c r="B1140" s="27" t="inlineStr">
         <is>
@@ -36426,8 +37733,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1141">
+      <c r="F1140" s="44" t="inlineStr">
+        <is>
+          <t>自定义指标列表(结构构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141" ht="32" customHeight="1">
       <c r="A1141" s="41" t="n"/>
       <c r="B1141" s="23" t="inlineStr">
         <is>
@@ -36449,8 +37761,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1142">
+      <c r="F1141" s="44" t="inlineStr">
+        <is>
+          <t>YTD汇总合计行 — 87.8%
+自定义日期合计(大写字段+isDetail) — 8.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142" ht="16" customHeight="1">
       <c r="A1142" s="41" t="n"/>
       <c r="B1142" s="27" t="inlineStr">
         <is>
@@ -36472,8 +37790,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1143" ht="15.95" customHeight="1">
+      <c r="F1142" s="44" t="inlineStr">
+        <is>
+          <t>修改Profile别名(含后置还原,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143" ht="16" customHeight="1">
       <c r="A1143" s="41" t="n"/>
       <c r="B1143" s="24" t="inlineStr">
         <is>
@@ -36495,7 +37818,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1143" s="34" t="inlineStr">
+      <c r="F1143" s="44" t="inlineStr">
         <is>
           <t>基于Prompt整体表现数据生成AI洞察摘要</t>
         </is>
@@ -36915,7 +38238,7 @@
         </is>
       </c>
     </row>
-    <row r="1162">
+    <row r="1162" ht="32" customHeight="1">
       <c r="A1162" s="41" t="n"/>
       <c r="B1162" s="26" t="inlineStr">
         <is>
@@ -36937,8 +38260,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1163">
+      <c r="F1162" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 ASIN详情头信息 — 2.4%
+TimeType=1 ASIN详情头信息YoY — 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163" ht="32" customHeight="1">
       <c r="A1163" s="41" t="n"/>
       <c r="B1163" s="23" t="inlineStr">
         <is>
@@ -36960,8 +38289,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1164">
+      <c r="F1163" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 单周期ASIN表现趋势 — 1.4%
+TimeType=1 YoY含搜索词过滤趋势 — 4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164" ht="32" customHeight="1">
       <c r="A1164" s="41" t="n"/>
       <c r="B1164" s="27" t="inlineStr">
         <is>
@@ -36983,8 +38318,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1165">
+      <c r="F1164" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 单周期搜索词表现 — 2.0%
+TimeType=1 YoY含搜索词过滤 — 7.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165" ht="32" customHeight="1">
       <c r="A1165" s="41" t="n"/>
       <c r="B1165" s="23" t="inlineStr">
         <is>
@@ -37006,8 +38347,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1166">
+      <c r="F1165" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 搜索词明细表格 — 0.8%
+TimeType=1 YoY含搜索词过滤表格 — 3.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166" ht="16" customHeight="1">
       <c r="A1166" s="41" t="n"/>
       <c r="B1166" s="27" t="inlineStr">
         <is>
@@ -37029,8 +38376,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1167">
+      <c r="F1166" s="44" t="inlineStr">
+        <is>
+          <t>搜索词趋势列表 — 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167" ht="16" customHeight="1">
       <c r="A1167" s="41" t="n"/>
       <c r="B1167" s="23" t="inlineStr">
         <is>
@@ -37052,8 +38404,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1168">
+      <c r="F1167" s="44" t="inlineStr">
+        <is>
+          <t>基础搜索词趋势表现 — 0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168" ht="32" customHeight="1">
       <c r="A1168" s="41" t="n"/>
       <c r="B1168" s="27" t="inlineStr">
         <is>
@@ -37075,8 +38432,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1169">
+      <c r="F1168" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 ASIN详情指标汇总 — 1.4%
+TimeType=1 YoY对比含搜索词过滤 — 8.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169" ht="32" customHeight="1">
       <c r="A1169" s="41" t="n"/>
       <c r="B1169" s="23" t="inlineStr">
         <is>
@@ -37098,8 +38461,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1170">
+      <c r="F1169" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 基础ASIN分页表格 — 11.2%
+TimeType=1 YoY含ASIN过滤 — 8.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170" ht="32" customHeight="1">
       <c r="A1170" s="41" t="n"/>
       <c r="B1170" s="27" t="inlineStr">
         <is>
@@ -37121,8 +38490,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1171">
+      <c r="F1170" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 基础总计行 — 5.2%
+TimeType=1 YoY对比总计行 — 6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171" ht="32" customHeight="1">
       <c r="A1171" s="41" t="n"/>
       <c r="B1171" s="23" t="inlineStr">
         <is>
@@ -37144,8 +38519,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1172">
+      <c r="F1171" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 基础单周期查询 — 1.8%
+TimeType=1 YoY对比模式 — 2.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172" ht="32" customHeight="1">
       <c r="A1172" s="41" t="n"/>
       <c r="B1172" s="27" t="inlineStr">
         <is>
@@ -37167,8 +38548,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1173">
+      <c r="F1172" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 单周期ASIN表现 — 0.8%
+TimeType=1 YoY对比ASIN表现 — 0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173" ht="32" customHeight="1">
       <c r="A1173" s="41" t="n"/>
       <c r="B1173" s="23" t="inlineStr">
         <is>
@@ -37190,8 +38577,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1174">
+      <c r="F1173" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 基础单周期汇总 — 0.6%
+TimeType=1 YoY对比汇总 — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174" ht="32" customHeight="1">
       <c r="A1174" s="41" t="n"/>
       <c r="B1174" s="27" t="inlineStr">
         <is>
@@ -37211,6 +38604,12 @@
       <c r="E1174" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1174" s="44" t="inlineStr">
+        <is>
+          <t>TimeType=0 单周期趋势图 — 2.2%
+TimeType=1 YoY对比趋势 — 2.6%</t>
         </is>
       </c>
     </row>
@@ -37559,7 +38958,7 @@
         </is>
       </c>
     </row>
-    <row r="1190">
+    <row r="1190" ht="112" customHeight="1">
       <c r="A1190" s="41" t="n"/>
       <c r="B1190" s="26" t="inlineStr">
         <is>
@@ -37579,6 +38978,17 @@
       <c r="E1190" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1190" s="44" t="inlineStr">
+        <is>
+          <t>Campaign 维度报表导出定义 — 46.2%
+ASIN 维度报表导出定义 — 30.8%
+数值型 ReportType=2（简版 campaign 报表，与前端 autotest 探针一致） — 5.8%
+Profile 维度报表导出定义 — 3.8%
+Search Term/Query 维度报表导出定义 — 1.9%
+Portfolio/CampaignTag 维度报表导出定义 — 1.9%
+Keyword/Targeting 维度报表导出定义 — 1.9%</t>
         </is>
       </c>
     </row>
@@ -38065,7 +39475,7 @@
         </is>
       </c>
     </row>
-    <row r="1212">
+    <row r="1212" ht="16" customHeight="1">
       <c r="A1212" s="41" t="n"/>
       <c r="B1212" s="27" t="inlineStr">
         <is>
@@ -38087,8 +39497,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1213">
+      <c r="F1212" s="44" t="inlineStr">
+        <is>
+          <t>按 shareId 查询分享的 Amazon Portfolio — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213" ht="16" customHeight="1">
       <c r="A1213" s="41" t="n"/>
       <c r="B1213" s="23" t="inlineStr">
         <is>
@@ -38108,6 +39523,11 @@
       <c r="E1213" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1213" s="44" t="inlineStr">
+        <is>
+          <t>按 shareId 查询分享的 Campaign 标签 — 100%</t>
         </is>
       </c>
     </row>
@@ -38295,7 +39715,7 @@
         </is>
       </c>
     </row>
-    <row r="1222" ht="15.95" customHeight="1">
+    <row r="1222" ht="16" customHeight="1">
       <c r="A1222" s="41" t="n"/>
       <c r="B1222" s="26" t="inlineStr">
         <is>
@@ -38317,13 +39737,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1222" s="36" t="inlineStr">
+      <c r="F1222" s="44" t="inlineStr">
         <is>
           <t>按搜索词+国家查询SOV月度数据 — 100%</t>
         </is>
       </c>
     </row>
-    <row r="1223" ht="15.95" customHeight="1">
+    <row r="1223" ht="16" customHeight="1">
       <c r="A1223" s="41" t="n"/>
       <c r="B1223" s="23" t="inlineStr">
         <is>
@@ -38345,7 +39765,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1223" s="36" t="inlineStr">
+      <c r="F1223" s="44" t="inlineStr">
         <is>
           <t>按国家查询用户品牌列表 — 100%</t>
         </is>
@@ -38535,7 +39955,7 @@
         </is>
       </c>
     </row>
-    <row r="1232">
+    <row r="1232" ht="32" customHeight="1">
       <c r="A1232" s="41" t="n"/>
       <c r="B1232" s="26" t="inlineStr">
         <is>
@@ -38557,8 +39977,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1233">
+      <c r="F1232" s="44" t="inlineStr">
+        <is>
+          <t>SB Video广告-简单结构(仅Products+Videos)(含后置归档,可重复) — 60%
+SB Video广告-完整结构(Brand+LandingPage+BrandLogos)(含后置归档,可重复) — 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233" ht="32" customHeight="1">
       <c r="A1233" s="41" t="n"/>
       <c r="B1233" s="23" t="inlineStr">
         <is>
@@ -38580,8 +40006,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1234">
+      <c r="F1233" s="44" t="inlineStr">
+        <is>
+          <t>SB广告组+ProductCollection+phrase关键词(含后置归档,可重复) — 70%
+SB广告组+exact关键词+NegativeKeywords(含后置归档,可重复) — 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234" ht="48" customHeight="1">
       <c r="A1234" s="41" t="n"/>
       <c r="B1234" s="27" t="inlineStr">
         <is>
@@ -38603,8 +40035,15 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1235">
+      <c r="F1234" s="44" t="inlineStr">
+        <is>
+          <t>基本SB活动复制同profile(含后置归档,可重复) — 70%
+B2B站点限制SB活动复制(含后置归档,可重复) — 15%
+SB活动复制含portfolio和终止日(含后置归档,可重复) — 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235" ht="32" customHeight="1">
       <c r="A1235" s="41" t="n"/>
       <c r="B1235" s="23" t="inlineStr">
         <is>
@@ -38624,6 +40063,12 @@
       <c r="E1235" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1235" s="44" t="inlineStr">
+        <is>
+          <t>SB ProductCollection活动+KW关键词定向(含后置归档,可重复) — 60%
+SB Video活动+KW关键词定向(含后置归档,可重复) — 40%</t>
         </is>
       </c>
     </row>
@@ -41502,7 +42947,7 @@
         </is>
       </c>
     </row>
-    <row r="1361" ht="15.95" customHeight="1">
+    <row r="1361" ht="16" customHeight="1">
       <c r="A1361" s="41" t="n"/>
       <c r="B1361" s="23" t="inlineStr">
         <is>
@@ -41524,7 +42969,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1361" s="34" t="inlineStr">
+      <c r="F1361" s="44" t="inlineStr">
         <is>
           <t>场景1: SD广告组新增ASIN商品定向PAT(含后置清理,可重复) — 100.0%</t>
         </is>
@@ -41806,7 +43251,7 @@
         </is>
       </c>
     </row>
-    <row r="1374" ht="15.95" customHeight="1">
+    <row r="1374" ht="16" customHeight="1">
       <c r="A1374" s="41" t="n"/>
       <c r="B1374" s="27" t="inlineStr">
         <is>
@@ -41828,7 +43273,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1374" s="34" t="inlineStr">
+      <c r="F1374" s="44" t="inlineStr">
         <is>
           <t>场景1: 单PAT目标调整出价</t>
         </is>
@@ -41856,7 +43301,7 @@
           <t>guguangjie</t>
         </is>
       </c>
-      <c r="F1375" s="34" t="inlineStr">
+      <c r="F1375" s="44" t="inlineStr">
         <is>
           <t>场景1: 批量启用PAT Target — 57%
 场景2: 批量暂停PAT Target — 42%</t>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -314,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -437,6 +437,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2591,6 +2594,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F55" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H55" s="29" t="inlineStr">
+        <is>
+          <t>78% (7/9)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="41" t="n"/>
@@ -3201,6 +3217,19 @@
           <t>limin</t>
         </is>
       </c>
+      <c r="F76" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>100% (3/3)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="41" t="n"/>
@@ -4251,6 +4280,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F113" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G113" s="29" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="H113" s="29" t="inlineStr">
+        <is>
+          <t>100% (3/3)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="41" t="n"/>
@@ -4327,6 +4369,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F116" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H116" s="29" t="inlineStr">
+        <is>
+          <t>3% (2/58)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="41" t="n"/>
@@ -4403,6 +4458,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F119" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H119" s="29" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="41" t="n"/>
@@ -4477,6 +4545,19 @@
       <c r="E122" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F122" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="G122" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H122" s="29" t="inlineStr">
+        <is>
+          <t>70% (21/30)</t>
         </is>
       </c>
     </row>
@@ -27240,7 +27321,7 @@
         </is>
       </c>
     </row>
-    <row r="722">
+    <row r="722" ht="16" customHeight="1">
       <c r="A722" s="41" t="n"/>
       <c r="B722" s="27" t="inlineStr">
         <is>
@@ -27262,8 +27343,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="723">
+      <c r="F722" s="44" t="inlineStr">
+        <is>
+          <t>Campaign子标签报表数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="723" ht="16" customHeight="1">
       <c r="A723" s="41" t="n"/>
       <c r="B723" s="23" t="inlineStr">
         <is>
@@ -27285,8 +27371,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="724">
+      <c r="F723" s="44" t="inlineStr">
+        <is>
+          <t>Campaign子标签分组聚合数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="724" ht="16" customHeight="1">
       <c r="A724" s="41" t="n"/>
       <c r="B724" s="27" t="inlineStr">
         <is>
@@ -27308,8 +27399,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="725">
+      <c r="F724" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign查其所属标签 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="725" ht="16" customHeight="1">
       <c r="A725" s="41" t="n"/>
       <c r="B725" s="23" t="inlineStr">
         <is>
@@ -27331,8 +27427,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="726">
+      <c r="F725" s="44" t="inlineStr">
+        <is>
+          <t>Campaign标签报表列表页 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="726" ht="16" customHeight="1">
       <c r="A726" s="41" t="n"/>
       <c r="B726" s="27" t="inlineStr">
         <is>
@@ -27354,8 +27455,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="727">
+      <c r="F726" s="44" t="inlineStr">
+        <is>
+          <t>Campaign标签报表汇总行 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="727" ht="16" customHeight="1">
       <c r="A727" s="41" t="n"/>
       <c r="B727" s="23" t="inlineStr">
         <is>
@@ -27377,8 +27483,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="728">
+      <c r="F727" s="44" t="inlineStr">
+        <is>
+          <t>获取Campaign标签用户列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="728" ht="16" customHeight="1">
       <c r="A728" s="41" t="n"/>
       <c r="B728" s="27" t="inlineStr">
         <is>
@@ -27398,6 +27509,11 @@
       <c r="E728" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F728" s="44" t="inlineStr">
+        <is>
+          <t>Campaign标签趋势图 — 100%</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34351,7 @@
         </is>
       </c>
     </row>
-    <row r="989">
+    <row r="989" ht="16" customHeight="1">
       <c r="A989" s="41" t="n"/>
       <c r="B989" s="24" t="inlineStr">
         <is>
@@ -34257,8 +34373,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="990">
+      <c r="F989" s="44" t="inlineStr">
+        <is>
+          <t>关键词标签趋势图</t>
+        </is>
+      </c>
+    </row>
+    <row r="990" ht="16" customHeight="1">
       <c r="A990" s="41" t="n"/>
       <c r="B990" s="27" t="inlineStr">
         <is>
@@ -34280,8 +34401,13 @@
           <t>limin</t>
         </is>
       </c>
-    </row>
-    <row r="991">
+      <c r="F990" s="44" t="inlineStr">
+        <is>
+          <t>关键词标签报表列表页</t>
+        </is>
+      </c>
+    </row>
+    <row r="991" ht="16" customHeight="1">
       <c r="A991" s="41" t="n"/>
       <c r="B991" s="23" t="inlineStr">
         <is>
@@ -34301,6 +34427,11 @@
       <c r="E991" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F991" s="44" t="inlineStr">
+        <is>
+          <t>关键词标签报表汇总行</t>
         </is>
       </c>
     </row>
@@ -41667,7 +41798,7 @@
         </is>
       </c>
     </row>
-    <row r="1278">
+    <row r="1278" ht="32" customHeight="1">
       <c r="A1278" s="41" t="n"/>
       <c r="B1278" s="26" t="inlineStr">
         <is>
@@ -41689,8 +41820,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1279">
+      <c r="F1278" s="44" t="inlineStr">
+        <is>
+          <t>标准STV素材无LandingPage(含前置建层级+后置清理,可重复) — 96%
+STV素材含LandingPage=OFF AMAZON LINK(含前置建层级+后置清理,可重复) — 4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279" ht="16" customHeight="1">
       <c r="A1279" s="41" t="n"/>
       <c r="B1279" s="23" t="inlineStr">
         <is>
@@ -41712,8 +41849,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1280">
+      <c r="F1279" s="44" t="inlineStr">
+        <is>
+          <t>标准STV广告组(含前置建Campaign+后置清理,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280" ht="64" customHeight="1">
       <c r="A1280" s="41" t="n"/>
       <c r="B1280" s="27" t="inlineStr">
         <is>
@@ -41733,6 +41875,14 @@
       <c r="E1280" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1280" s="44" t="inlineStr">
+        <is>
+          <t>enabled持续投放(含后置归档,可重复) — 25%
+enabled限时投放(含后置归档,可重复) — 21%
+paused暂停建单(含后置归档,可重复) — 45%
+paused限时暂停(含后置归档,可重复) — 7%</t>
         </is>
       </c>
     </row>
@@ -42131,7 +42281,7 @@
         </is>
       </c>
     </row>
-    <row r="1296">
+    <row r="1296" ht="16" customHeight="1">
       <c r="A1296" s="41" t="n"/>
       <c r="B1296" s="26" t="inlineStr">
         <is>
@@ -42153,8 +42303,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1297">
+      <c r="F1296" s="44" t="inlineStr">
+        <is>
+          <t>添加广告组到标签（含后置清理,可重复） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297" ht="16" customHeight="1">
       <c r="A1297" s="41" t="n"/>
       <c r="B1297" s="23" t="inlineStr">
         <is>
@@ -42174,6 +42329,11 @@
       <c r="E1297" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1297" s="44" t="inlineStr">
+        <is>
+          <t>添加ASIN到标签（含后置清理,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -42407,7 +42567,7 @@
         </is>
       </c>
     </row>
-    <row r="1308">
+    <row r="1308" ht="16" customHeight="1">
       <c r="A1308" s="41" t="n"/>
       <c r="B1308" s="27" t="inlineStr">
         <is>
@@ -42427,6 +42587,11 @@
       <c r="E1308" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1308" s="44" t="inlineStr">
+        <is>
+          <t>检查标签是否有匹配规则 — 100%</t>
         </is>
       </c>
     </row>
@@ -42453,7 +42618,7 @@
         </is>
       </c>
     </row>
-    <row r="1310">
+    <row r="1310" ht="32" customHeight="1">
       <c r="A1310" s="41" t="n"/>
       <c r="B1310" s="27" t="inlineStr">
         <is>
@@ -42473,6 +42638,12 @@
       <c r="E1310" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1310" s="44" t="inlineStr">
+        <is>
+          <t>type=0 指定标签批量检查 — 60%
+type=1 大批量Campaign检查 — 40%</t>
         </is>
       </c>
     </row>
@@ -42545,7 +42716,7 @@
         </is>
       </c>
     </row>
-    <row r="1314">
+    <row r="1314" ht="32" customHeight="1">
       <c r="A1314" s="41" t="n"/>
       <c r="B1314" s="27" t="inlineStr">
         <is>
@@ -42565,6 +42736,12 @@
       <c r="E1314" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1314" s="44" t="inlineStr">
+        <is>
+          <t>创建父级ASIN标签 — 100%
+创建子级ASIN标签 — 100%</t>
         </is>
       </c>
     </row>
@@ -42614,7 +42791,7 @@
         </is>
       </c>
     </row>
-    <row r="1317">
+    <row r="1317" ht="16" customHeight="1">
       <c r="A1317" s="41" t="n"/>
       <c r="B1317" s="23" t="inlineStr">
         <is>
@@ -42634,6 +42811,11 @@
       <c r="E1317" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1317" s="44" t="inlineStr">
+        <is>
+          <t>创建顶级Campaign标签（含后置清理,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -42729,7 +42911,7 @@
         </is>
       </c>
     </row>
-    <row r="1322">
+    <row r="1322" ht="16" customHeight="1">
       <c r="A1322" s="41" t="n"/>
       <c r="B1322" s="27" t="inlineStr">
         <is>
@@ -42749,6 +42931,11 @@
       <c r="E1322" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1322" s="44" t="inlineStr">
+        <is>
+          <t>从标签删除Campaign（含前置添加,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -42798,7 +42985,7 @@
         </is>
       </c>
     </row>
-    <row r="1325">
+    <row r="1325" ht="16" customHeight="1">
       <c r="A1325" s="41" t="n"/>
       <c r="B1325" s="23" t="inlineStr">
         <is>
@@ -42818,6 +43005,11 @@
       <c r="E1325" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1325" s="44" t="inlineStr">
+        <is>
+          <t>重命名ASIN标签（含后置还原,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -42844,7 +43036,7 @@
         </is>
       </c>
     </row>
-    <row r="1327">
+    <row r="1327" ht="32" customHeight="1">
       <c r="A1327" s="41" t="n"/>
       <c r="B1327" s="23" t="inlineStr">
         <is>
@@ -42864,6 +43056,12 @@
       <c r="E1327" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1327" s="44" t="inlineStr">
+        <is>
+          <t>无参数（默认） — 95.7%
+isCheckEdit=true — 4.3%</t>
         </is>
       </c>
     </row>
@@ -42890,7 +43088,7 @@
         </is>
       </c>
     </row>
-    <row r="1329">
+    <row r="1329" ht="16" customHeight="1">
       <c r="A1329" s="41" t="n"/>
       <c r="B1329" s="23" t="inlineStr">
         <is>
@@ -42912,8 +43110,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1330">
+      <c r="F1329" s="44" t="inlineStr">
+        <is>
+          <t>按广告组查其标签（权限模式） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330" ht="16" customHeight="1">
       <c r="A1330" s="41" t="n"/>
       <c r="B1330" s="27" t="inlineStr">
         <is>
@@ -42935,8 +43138,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1331">
+      <c r="F1330" s="44" t="inlineStr">
+        <is>
+          <t>获取广告组标签映射 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331" ht="32" customHeight="1">
       <c r="A1331" s="41" t="n"/>
       <c r="B1331" s="23" t="inlineStr">
         <is>
@@ -42958,8 +43166,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1332">
+      <c r="F1331" s="44" t="inlineStr">
+        <is>
+          <t>无参数（默认） — 96.6%
+isCheckEdit=true — 3.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332" ht="16" customHeight="1">
       <c r="A1332" s="41" t="n"/>
       <c r="B1332" s="27" t="inlineStr">
         <is>
@@ -42981,8 +43195,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1333">
+      <c r="F1332" s="44" t="inlineStr">
+        <is>
+          <t>isCheckEdit=true — 99.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333" ht="16" customHeight="1">
       <c r="A1333" s="41" t="n"/>
       <c r="B1333" s="23" t="inlineStr">
         <is>
@@ -43004,8 +43223,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1334">
+      <c r="F1333" s="44" t="inlineStr">
+        <is>
+          <t>查询Campaign标签备注 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334" ht="16" customHeight="1">
       <c r="A1334" s="41" t="n"/>
       <c r="B1334" s="27" t="inlineStr">
         <is>
@@ -43025,6 +43249,11 @@
       <c r="E1334" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1334" s="44" t="inlineStr">
+        <is>
+          <t>按标签查ASIN列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -43074,7 +43303,7 @@
         </is>
       </c>
     </row>
-    <row r="1337">
+    <row r="1337" ht="16" customHeight="1">
       <c r="A1337" s="41" t="n"/>
       <c r="B1337" s="23" t="inlineStr">
         <is>
@@ -43094,6 +43323,11 @@
       <c r="E1337" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1337" s="44" t="inlineStr">
+        <is>
+          <t>按profileIds查Campaign标签 — 100%</t>
         </is>
       </c>
     </row>
@@ -43143,7 +43377,7 @@
         </is>
       </c>
     </row>
-    <row r="1340">
+    <row r="1340" ht="16" customHeight="1">
       <c r="A1340" s="41" t="n"/>
       <c r="B1340" s="27" t="inlineStr">
         <is>
@@ -43165,8 +43399,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1341">
+      <c r="F1340" s="44" t="inlineStr">
+        <is>
+          <t>按标签查关键词 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341" ht="16" customHeight="1">
       <c r="A1341" s="41" t="n"/>
       <c r="B1341" s="23" t="inlineStr">
         <is>
@@ -43188,8 +43427,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1342">
+      <c r="F1341" s="44" t="inlineStr">
+        <is>
+          <t>id=0（新建/初始化） — 18.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342" ht="16" customHeight="1">
       <c r="A1342" s="41" t="n"/>
       <c r="B1342" s="27" t="inlineStr">
         <is>
@@ -43211,8 +43455,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1343">
+      <c r="F1342" s="44" t="inlineStr">
+        <is>
+          <t>按标签查多profile Campaign — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343" ht="16" customHeight="1">
       <c r="A1343" s="41" t="n"/>
       <c r="B1343" s="23" t="inlineStr">
         <is>
@@ -43232,6 +43481,11 @@
       <c r="E1343" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1343" s="44" t="inlineStr">
+        <is>
+          <t>查询多标签匹配规则差异 — 100%</t>
         </is>
       </c>
     </row>
@@ -43258,7 +43512,7 @@
         </is>
       </c>
     </row>
-    <row r="1345">
+    <row r="1345" ht="16" customHeight="1">
       <c r="A1345" s="41" t="n"/>
       <c r="B1345" s="23" t="inlineStr">
         <is>
@@ -43278,6 +43532,11 @@
       <c r="E1345" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1345" s="44" t="inlineStr">
+        <is>
+          <t>保存ASIN到标签（含后置清理,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -43373,7 +43632,7 @@
         </is>
       </c>
     </row>
-    <row r="1350">
+    <row r="1350" ht="16" customHeight="1">
       <c r="A1350" s="41" t="n"/>
       <c r="B1350" s="27" t="inlineStr">
         <is>
@@ -43393,6 +43652,11 @@
       <c r="E1350" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1350" s="44" t="inlineStr">
+        <is>
+          <t>重命名Campaign标签（含后置还原,可重复） — 100%</t>
         </is>
       </c>
     </row>
@@ -44010,7 +44274,7 @@
         </is>
       </c>
     </row>
-    <row r="1377">
+    <row r="1377" ht="16" customHeight="1">
       <c r="A1377" s="41" t="n"/>
       <c r="B1377" s="24" t="inlineStr">
         <is>
@@ -44030,6 +44294,11 @@
       <c r="E1377" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1377" s="44" t="inlineStr">
+        <is>
+          <t>获取服务线程池状态</t>
         </is>
       </c>
     </row>
@@ -44704,6 +44973,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1402" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天零流量，接口用途不明，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1403">
       <c r="A1403" s="41" t="n"/>
@@ -44750,6 +45024,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1404" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天零流量，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1405">
       <c r="A1405" s="41" t="n"/>
@@ -44773,6 +45052,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1405" s="45" t="inlineStr">
+        <is>
+          <t>已在InsertWarRoomStrategy case中作为cleanup步骤验证，未独立立case</t>
+        </is>
+      </c>
     </row>
     <row r="1406">
       <c r="A1406" s="41" t="n"/>
@@ -44796,6 +45080,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1406" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天零流量，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1407">
       <c r="A1407" s="41" t="n"/>
@@ -44819,8 +45108,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1408">
+      <c r="F1407" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天零流量，路径参数id未知，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408" ht="16" customHeight="1">
       <c r="A1408" s="41" t="n"/>
       <c r="B1408" s="27" t="inlineStr">
         <is>
@@ -44842,8 +45136,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1409">
+      <c r="F1408" s="44" t="inlineStr">
+        <is>
+          <t>获取WarRoom购物事件 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409" ht="32" customHeight="1">
       <c r="A1409" s="41" t="n"/>
       <c r="B1409" s="23" t="inlineStr">
         <is>
@@ -44865,8 +45164,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1410">
+      <c r="F1409" s="44" t="inlineStr">
+        <is>
+          <t>level=Campaign — 80%
+level=Placement — 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410" ht="16" customHeight="1">
       <c r="A1410" s="41" t="n"/>
       <c r="B1410" s="27" t="inlineStr">
         <is>
@@ -44888,8 +45193,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1411">
+      <c r="F1410" s="44" t="inlineStr">
+        <is>
+          <t>Dayparting自动化统计 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411" ht="16" customHeight="1">
       <c r="A1411" s="41" t="n"/>
       <c r="B1411" s="23" t="inlineStr">
         <is>
@@ -44911,8 +45221,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1412">
+      <c r="F1411" s="44" t="inlineStr">
+        <is>
+          <t>获取Campaign标签 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412" ht="16" customHeight="1">
       <c r="A1412" s="41" t="n"/>
       <c r="B1412" s="27" t="inlineStr">
         <is>
@@ -44934,8 +45249,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1413">
+      <c r="F1412" s="44" t="inlineStr">
+        <is>
+          <t>按Campaign获取标签 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413" ht="16" customHeight="1">
       <c r="A1413" s="41" t="n"/>
       <c r="B1413" s="23" t="inlineStr">
         <is>
@@ -44957,8 +45277,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1414">
+      <c r="F1413" s="44" t="inlineStr">
+        <is>
+          <t>Campaign层级小时维度洞察 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414" ht="80" customHeight="1">
       <c r="A1414" s="41" t="n"/>
       <c r="B1414" s="27" t="inlineStr">
         <is>
@@ -44980,8 +45305,17 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1415">
+      <c r="F1414" s="44" t="inlineStr">
+        <is>
+          <t>level=Keyword — 20%
+level=Targeting PAT — 20%
+level=Targeting Automatic — 20%
+level=ProductAd — 20%
+level=Targeting Audienec — 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415" ht="16" customHeight="1">
       <c r="A1415" s="41" t="n"/>
       <c r="B1415" s="23" t="inlineStr">
         <is>
@@ -45001,6 +45335,11 @@
       <c r="E1415" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1415" s="44" t="inlineStr">
+        <is>
+          <t>Campaign维度Top5分析 — 100%</t>
         </is>
       </c>
     </row>
@@ -45026,8 +45365,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1417">
+      <c r="F1416" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天零流量，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417" ht="16" customHeight="1">
       <c r="A1417" s="41" t="n"/>
       <c r="B1417" s="23" t="inlineStr">
         <is>
@@ -45049,8 +45393,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1418">
+      <c r="F1417" s="44" t="inlineStr">
+        <is>
+          <t>获取WarRoom对比数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418" ht="16" customHeight="1">
       <c r="A1418" s="41" t="n"/>
       <c r="B1418" s="27" t="inlineStr">
         <is>
@@ -45072,8 +45421,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1419">
+      <c r="F1418" s="44" t="inlineStr">
+        <is>
+          <t>获取WarRoom数量 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419" ht="16" customHeight="1">
       <c r="A1419" s="41" t="n"/>
       <c r="B1419" s="23" t="inlineStr">
         <is>
@@ -45095,8 +45449,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1420">
+      <c r="F1419" s="44" t="inlineStr">
+        <is>
+          <t>isYesterday=1对比数据 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420" ht="16" customHeight="1">
       <c r="A1420" s="41" t="n"/>
       <c r="B1420" s="27" t="inlineStr">
         <is>
@@ -45116,6 +45475,11 @@
       <c r="E1420" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1420" s="44" t="inlineStr">
+        <is>
+          <t>指定日期范围趋势 — 100%</t>
         </is>
       </c>
     </row>
@@ -45141,6 +45505,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1421" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天零流量，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1422">
       <c r="A1422" s="41" t="n"/>
@@ -45164,8 +45533,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1423">
+      <c r="F1422" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天零流量，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423" ht="32" customHeight="1">
       <c r="A1423" s="41" t="n"/>
       <c r="B1423" s="23" t="inlineStr">
         <is>
@@ -45187,8 +45561,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1424">
+      <c r="F1423" s="44" t="inlineStr">
+        <is>
+          <t>含trendType+targetSales+targetOrders — 20%
+仅targetOrders无trendType — 80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424" ht="16" customHeight="1">
       <c r="A1424" s="41" t="n"/>
       <c r="B1424" s="27" t="inlineStr">
         <is>
@@ -45210,8 +45590,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1425">
+      <c r="F1424" s="44" t="inlineStr">
+        <is>
+          <t>策略效果查询 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425" ht="16" customHeight="1">
       <c r="A1425" s="41" t="n"/>
       <c r="B1425" s="23" t="inlineStr">
         <is>
@@ -45233,8 +45618,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1426">
+      <c r="F1425" s="44" t="inlineStr">
+        <is>
+          <t>策略趋势汇总 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426" ht="16" customHeight="1">
       <c r="A1426" s="41" t="n"/>
       <c r="B1426" s="27" t="inlineStr">
         <is>
@@ -45256,8 +45646,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1427">
+      <c r="F1426" s="44" t="inlineStr">
+        <is>
+          <t>获取WarRoom策略列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427" ht="16" customHeight="1">
       <c r="A1427" s="41" t="n"/>
       <c r="B1427" s="23" t="inlineStr">
         <is>
@@ -45279,8 +45674,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1428">
+      <c r="F1427" s="44" t="inlineStr">
+        <is>
+          <t>获取当前用户WarRoom列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428" ht="16" customHeight="1">
       <c r="A1428" s="41" t="n"/>
       <c r="B1428" s="27" t="inlineStr">
         <is>
@@ -45300,6 +45700,11 @@
       <c r="E1428" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1428" s="44" t="inlineStr">
+        <is>
+          <t>创建WarRoom(含后置删除,可重复) — 100%</t>
         </is>
       </c>
     </row>
@@ -45325,8 +45730,13 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1430">
+      <c r="F1429" s="45" t="inlineStr">
+        <is>
+          <t>ES近30天仅1次流量，写操作参数结构待确认，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430" ht="32" customHeight="1">
       <c r="A1430" s="41" t="n"/>
       <c r="B1430" s="27" t="inlineStr">
         <is>
@@ -45348,8 +45758,14 @@
           <t>zhanghaobo</t>
         </is>
       </c>
-    </row>
-    <row r="1431">
+      <c r="F1430" s="44" t="inlineStr">
+        <is>
+          <t>手动策略isAuto=0(含后置清理,可重复) — 60%
+自动策略isAuto=1(含后置清理,可重复) — 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431" ht="16" customHeight="1">
       <c r="A1431" s="41" t="n"/>
       <c r="B1431" s="23" t="inlineStr">
         <is>
@@ -45369,6 +45785,11 @@
       <c r="E1431" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1431" s="44" t="inlineStr">
+        <is>
+          <t>更新策略信息(含还原,可重复) — 100%</t>
         </is>
       </c>
     </row>

--- a/single-api/swagger_modules.xlsx
+++ b/single-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Amazon.Advertising.Api" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PacvueMainApi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'模块汇总'!$A$1:$H$126</definedName>
@@ -2150,6 +2150,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F45" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="G45" s="29" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="inlineStr">
+        <is>
+          <t>92% (91/99)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="41" t="n"/>
@@ -2239,6 +2252,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F48" s="29" t="n">
+        <v>98</v>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="inlineStr">
+        <is>
+          <t>93% (99/106)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="41" t="n"/>
@@ -2415,6 +2441,19 @@
       <c r="E54" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F54" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="G54" s="29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H54" s="29" t="inlineStr">
+        <is>
+          <t>64% (18/28)</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14813,7 @@
         </is>
       </c>
     </row>
-    <row r="242">
+    <row r="242" ht="16" customHeight="1">
       <c r="A242" s="41" t="n"/>
       <c r="B242" s="26" t="inlineStr">
         <is>
@@ -14796,8 +14835,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="243">
+      <c r="F242" s="44" t="inlineStr">
+        <is>
+          <t>按profile列表获取组合预测支出与销售额</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="16" customHeight="1">
       <c r="A243" s="41" t="n"/>
       <c r="B243" s="23" t="inlineStr">
         <is>
@@ -14819,8 +14863,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="244">
+      <c r="F243" s="44" t="inlineStr">
+        <is>
+          <t>基于历史预测数据推算新增花费下的ACOS与销售额</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="16" customHeight="1">
       <c r="A244" s="41" t="n"/>
       <c r="B244" s="27" t="inlineStr">
         <is>
@@ -14842,8 +14891,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="245">
+      <c r="F244" s="44" t="inlineStr">
+        <is>
+          <t>获取profile当前预算管理模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="16" customHeight="1">
       <c r="A245" s="41" t="n"/>
       <c r="B245" s="23" t="inlineStr">
         <is>
@@ -14865,8 +14919,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="246">
+      <c r="F245" s="44" t="inlineStr">
+        <is>
+          <t>获取指定tag指定月份的预算分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="16" customHeight="1">
       <c r="A246" s="41" t="n"/>
       <c r="B246" s="27" t="inlineStr">
         <is>
@@ -14888,8 +14947,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="247">
+      <c r="F246" s="44" t="inlineStr">
+        <is>
+          <t>批量为BudgetLine绑定Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="16" customHeight="1">
       <c r="A247" s="41" t="n"/>
       <c r="B247" s="23" t="inlineStr">
         <is>
@@ -14911,8 +14975,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="248">
+      <c r="F247" s="44" t="inlineStr">
+        <is>
+          <t>设置profile预算管理级别(SubTagging)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="16" customHeight="1">
       <c r="A248" s="41" t="n"/>
       <c r="B248" s="27" t="inlineStr">
         <is>
@@ -14934,8 +15003,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="249">
+      <c r="F248" s="44" t="inlineStr">
+        <is>
+          <t>校验预算级别设置前的冲突情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="16" customHeight="1">
       <c r="A249" s="41" t="n"/>
       <c r="B249" s="23" t="inlineStr">
         <is>
@@ -14957,8 +15031,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="250">
+      <c r="F249" s="44" t="inlineStr">
+        <is>
+          <t>设置预算级别V3(含pacing/控制/预算集)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="16" customHeight="1">
       <c r="A250" s="41" t="n"/>
       <c r="B250" s="27" t="inlineStr">
         <is>
@@ -14980,8 +15059,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="251">
+      <c r="F250" s="44" t="inlineStr">
+        <is>
+          <t>设置预算通知邮件规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="16" customHeight="1">
       <c r="A251" s="41" t="n"/>
       <c r="B251" s="23" t="inlineStr">
         <is>
@@ -15003,8 +15087,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="252">
+      <c r="F251" s="44" t="inlineStr">
+        <is>
+          <t>检查tag是否已被预算管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="16" customHeight="1">
       <c r="A252" s="41" t="n"/>
       <c r="B252" s="27" t="inlineStr">
         <is>
@@ -15026,8 +15115,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="253">
+      <c r="F252" s="44" t="inlineStr">
+        <is>
+          <t>新建Calendar(含后置删除,可重复执行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="16" customHeight="1">
       <c r="A253" s="41" t="n"/>
       <c r="B253" s="23" t="inlineStr">
         <is>
@@ -15047,6 +15141,11 @@
       <c r="E253" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F253" s="44" t="inlineStr">
+        <is>
+          <t>获取每日预算目标数据</t>
         </is>
       </c>
     </row>
@@ -15096,7 +15195,7 @@
         </is>
       </c>
     </row>
-    <row r="256">
+    <row r="256" ht="16" customHeight="1">
       <c r="A256" s="41" t="n"/>
       <c r="B256" s="27" t="inlineStr">
         <is>
@@ -15118,8 +15217,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="257">
+      <c r="F256" s="44" t="inlineStr">
+        <is>
+          <t>下载预算操作日志Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="16" customHeight="1">
       <c r="A257" s="41" t="n"/>
       <c r="B257" s="23" t="inlineStr">
         <is>
@@ -15141,8 +15245,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="258">
+      <c r="F257" s="44" t="inlineStr">
+        <is>
+          <t>下载预算导入模板Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="16" customHeight="1">
       <c r="A258" s="41" t="n"/>
       <c r="B258" s="27" t="inlineStr">
         <is>
@@ -15164,8 +15273,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="259">
+      <c r="F258" s="44" t="inlineStr">
+        <is>
+          <t>下载批量预算设置模板Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="16" customHeight="1">
       <c r="A259" s="41" t="n"/>
       <c r="B259" s="23" t="inlineStr">
         <is>
@@ -15187,8 +15301,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="260">
+      <c r="F259" s="44" t="inlineStr">
+        <is>
+          <t>下载campaign预算建议Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="16" customHeight="1">
       <c r="A260" s="41" t="n"/>
       <c r="B260" s="27" t="inlineStr">
         <is>
@@ -15210,8 +15329,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="261">
+      <c r="F260" s="44" t="inlineStr">
+        <is>
+          <t>获取profile下预算相关campaign标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="16" customHeight="1">
       <c r="A261" s="41" t="n"/>
       <c r="B261" s="23" t="inlineStr">
         <is>
@@ -15233,8 +15357,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="262">
+      <c r="F261" s="44" t="inlineStr">
+        <is>
+          <t>获取预算仪表盘数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="16" customHeight="1">
       <c r="A262" s="41" t="n"/>
       <c r="B262" s="27" t="inlineStr">
         <is>
@@ -15256,8 +15385,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="263">
+      <c r="F262" s="44" t="inlineStr">
+        <is>
+          <t>获取预算洞察</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="16" customHeight="1">
       <c r="A263" s="41" t="n"/>
       <c r="B263" s="23" t="inlineStr">
         <is>
@@ -15279,8 +15413,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="264">
+      <c r="F263" s="44" t="inlineStr">
+        <is>
+          <t>获取预算变更日志(分页)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="16" customHeight="1">
       <c r="A264" s="41" t="n"/>
       <c r="B264" s="27" t="inlineStr">
         <is>
@@ -15302,8 +15441,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="265">
+      <c r="F264" s="44" t="inlineStr">
+        <is>
+          <t>获取预算变更日志详情(分页)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="16" customHeight="1">
       <c r="A265" s="41" t="n"/>
       <c r="B265" s="23" t="inlineStr">
         <is>
@@ -15325,8 +15469,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="266">
+      <c r="F265" s="44" t="inlineStr">
+        <is>
+          <t>获取当前用户预算通知邮件设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="16" customHeight="1">
       <c r="A266" s="41" t="n"/>
       <c r="B266" s="27" t="inlineStr">
         <is>
@@ -15348,8 +15497,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="267">
+      <c r="F266" s="44" t="inlineStr">
+        <is>
+          <t>获取预算操作日志(分页)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="16" customHeight="1">
       <c r="A267" s="41" t="n"/>
       <c r="B267" s="23" t="inlineStr">
         <is>
@@ -15371,8 +15525,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="268">
+      <c r="F267" s="44" t="inlineStr">
+        <is>
+          <t>获取预算小组件汇总数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="16" customHeight="1">
       <c r="A268" s="41" t="n"/>
       <c r="B268" s="27" t="inlineStr">
         <is>
@@ -15394,8 +15553,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="269">
+      <c r="F268" s="44" t="inlineStr">
+        <is>
+          <t>获取Calendar变更日志(分页)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="16" customHeight="1">
       <c r="A269" s="41" t="n"/>
       <c r="B269" s="23" t="inlineStr">
         <is>
@@ -15417,8 +15581,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="270">
+      <c r="F269" s="44" t="inlineStr">
+        <is>
+          <t>获取Calendar管理列表(分页)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="16" customHeight="1">
       <c r="A270" s="41" t="n"/>
       <c r="B270" s="27" t="inlineStr">
         <is>
@@ -15440,8 +15609,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="271">
+      <c r="F270" s="44" t="inlineStr">
+        <is>
+          <t>获取Calendar名称列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="16" customHeight="1">
       <c r="A271" s="41" t="n"/>
       <c r="B271" s="23" t="inlineStr">
         <is>
@@ -15463,8 +15637,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="272">
+      <c r="F271" s="44" t="inlineStr">
+        <is>
+          <t>获取campaign预算批量操作日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="16" customHeight="1">
       <c r="A272" s="41" t="n"/>
       <c r="B272" s="27" t="inlineStr">
         <is>
@@ -15486,8 +15665,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="273">
+      <c r="F272" s="44" t="inlineStr">
+        <is>
+          <t>获取campaign预算建议(分页)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="16" customHeight="1">
       <c r="A273" s="41" t="n"/>
       <c r="B273" s="23" t="inlineStr">
         <is>
@@ -15509,8 +15693,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="274">
+      <c r="F273" s="44" t="inlineStr">
+        <is>
+          <t>获取每日预算数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="16" customHeight="1">
       <c r="A274" s="41" t="n"/>
       <c r="B274" s="27" t="inlineStr">
         <is>
@@ -15532,8 +15721,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="275">
+      <c r="F274" s="44" t="inlineStr">
+        <is>
+          <t>获取Calendar编辑详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="16" customHeight="1">
       <c r="A275" s="41" t="n"/>
       <c r="B275" s="23" t="inlineStr">
         <is>
@@ -15555,8 +15749,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="276">
+      <c r="F275" s="44" t="inlineStr">
+        <is>
+          <t>获取当前财年设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="16" customHeight="1">
       <c r="A276" s="41" t="n"/>
       <c r="B276" s="27" t="inlineStr">
         <is>
@@ -15578,8 +15777,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="277">
+      <c r="F276" s="44" t="inlineStr">
+        <is>
+          <t>获取预测支出与销售</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="16" customHeight="1">
       <c r="A277" s="41" t="n"/>
       <c r="B277" s="23" t="inlineStr">
         <is>
@@ -15601,8 +15805,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="278">
+      <c r="F277" s="44" t="inlineStr">
+        <is>
+          <t>获取上月花费(tag/subtag级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="16" customHeight="1">
       <c r="A278" s="41" t="n"/>
       <c r="B278" s="27" t="inlineStr">
         <is>
@@ -15624,8 +15833,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="279">
+      <c r="F278" s="44" t="inlineStr">
+        <is>
+          <t>获取按月每日预算启用情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="16" customHeight="1">
       <c r="A279" s="41" t="n"/>
       <c r="B279" s="23" t="inlineStr">
         <is>
@@ -15647,8 +15861,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="280">
+      <c r="F279" s="44" t="inlineStr">
+        <is>
+          <t>获取未选中tag之外的其他campaign信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="16" customHeight="1">
       <c r="A280" s="41" t="n"/>
       <c r="B280" s="27" t="inlineStr">
         <is>
@@ -15670,8 +15889,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="281">
+      <c r="F280" s="44" t="inlineStr">
+        <is>
+          <t>获取预算配速趋势(分页)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="16" customHeight="1">
       <c r="A281" s="41" t="n"/>
       <c r="B281" s="23" t="inlineStr">
         <is>
@@ -15693,8 +15917,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="282">
+      <c r="F281" s="44" t="inlineStr">
+        <is>
+          <t>获取父级标签列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="16" customHeight="1">
       <c r="A282" s="41" t="n"/>
       <c r="B282" s="27" t="inlineStr">
         <is>
@@ -15716,8 +15945,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="283">
+      <c r="F282" s="44" t="inlineStr">
+        <is>
+          <t>获取profile预算与实际花费对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="16" customHeight="1">
       <c r="A283" s="41" t="n"/>
       <c r="B283" s="23" t="inlineStr">
         <is>
@@ -15739,8 +15973,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="284">
+      <c r="F283" s="44" t="inlineStr">
+        <is>
+          <t>获取预算设置行详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="16" customHeight="1">
       <c r="A284" s="41" t="n"/>
       <c r="B284" s="27" t="inlineStr">
         <is>
@@ -15762,8 +16001,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="285">
+      <c r="F284" s="44" t="inlineStr">
+        <is>
+          <t>获取预算设置行列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="16" customHeight="1">
       <c r="A285" s="41" t="n"/>
       <c r="B285" s="23" t="inlineStr">
         <is>
@@ -15785,8 +16029,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="286">
+      <c r="F285" s="44" t="inlineStr">
+        <is>
+          <t>获取子标签默认预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="16" customHeight="1">
       <c r="A286" s="41" t="n"/>
       <c r="B286" s="27" t="inlineStr">
         <is>
@@ -15808,8 +16057,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="287">
+      <c r="F286" s="44" t="inlineStr">
+        <is>
+          <t>获取子标签月度预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="16" customHeight="1">
       <c r="A287" s="41" t="n"/>
       <c r="B287" s="23" t="inlineStr">
         <is>
@@ -15831,8 +16085,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="288">
+      <c r="F287" s="44" t="inlineStr">
+        <is>
+          <t>获取子标签建议分配额度</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="16" customHeight="1">
       <c r="A288" s="41" t="n"/>
       <c r="B288" s="27" t="inlineStr">
         <is>
@@ -15854,8 +16113,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="289">
+      <c r="F288" s="44" t="inlineStr">
+        <is>
+          <t>获取标签下的子标签列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="16" customHeight="1">
       <c r="A289" s="41" t="n"/>
       <c r="B289" s="23" t="inlineStr">
         <is>
@@ -15877,8 +16141,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="290">
+      <c r="F289" s="44" t="inlineStr">
+        <is>
+          <t>获取标签预算集合</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="16" customHeight="1">
       <c r="A290" s="41" t="n"/>
       <c r="B290" s="27" t="inlineStr">
         <is>
@@ -15900,8 +16169,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="291">
+      <c r="F290" s="44" t="inlineStr">
+        <is>
+          <t>获取标签预算与实际花费对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="16" customHeight="1">
       <c r="A291" s="41" t="n"/>
       <c r="B291" s="23" t="inlineStr">
         <is>
@@ -15923,8 +16197,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="292">
+      <c r="F291" s="44" t="inlineStr">
+        <is>
+          <t>获取花费Top5的campaign每日花费</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="16" customHeight="1">
       <c r="A292" s="41" t="n"/>
       <c r="B292" s="27" t="inlineStr">
         <is>
@@ -15946,8 +16225,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="293">
+      <c r="F292" s="44" t="inlineStr">
+        <is>
+          <t>获取配速不足标签Top列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="16" customHeight="1">
       <c r="A293" s="41" t="n"/>
       <c r="B293" s="23" t="inlineStr">
         <is>
@@ -15969,8 +16253,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="294">
+      <c r="F293" s="44" t="inlineStr">
+        <is>
+          <t>获取配速不足标签洞察</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="16" customHeight="1">
       <c r="A294" s="41" t="n"/>
       <c r="B294" s="27" t="inlineStr">
         <is>
@@ -15992,8 +16281,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="295">
+      <c r="F294" s="44" t="inlineStr">
+        <is>
+          <t>获取年度预算设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="16" customHeight="1">
       <c r="A295" s="41" t="n"/>
       <c r="B295" s="23" t="inlineStr">
         <is>
@@ -16015,8 +16309,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="296">
+      <c r="F295" s="44" t="inlineStr">
+        <is>
+          <t>移除profile预算设置(含后置恢复,保证可重复执行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="16" customHeight="1">
       <c r="A296" s="41" t="n"/>
       <c r="B296" s="27" t="inlineStr">
         <is>
@@ -16038,8 +16337,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="297">
+      <c r="F296" s="44" t="inlineStr">
+        <is>
+          <t>重置子标签默认目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="16" customHeight="1">
       <c r="A297" s="41" t="n"/>
       <c r="B297" s="23" t="inlineStr">
         <is>
@@ -16061,8 +16365,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="298">
+      <c r="F297" s="44" t="inlineStr">
+        <is>
+          <t>设置预算分配类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="16" customHeight="1">
       <c r="A298" s="41" t="n"/>
       <c r="B298" s="27" t="inlineStr">
         <is>
@@ -16084,8 +16393,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="299">
+      <c r="F298" s="44" t="inlineStr">
+        <is>
+          <t>设置自动重新启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="16" customHeight="1">
       <c r="A299" s="41" t="n"/>
       <c r="B299" s="23" t="inlineStr">
         <is>
@@ -16107,8 +16421,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="300">
+      <c r="F299" s="44" t="inlineStr">
+        <is>
+          <t>设置自动预算控制</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="16" customHeight="1">
       <c r="A300" s="41" t="n"/>
       <c r="B300" s="27" t="inlineStr">
         <is>
@@ -16130,8 +16449,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="301">
+      <c r="F300" s="44" t="inlineStr">
+        <is>
+          <t>设置自动预算配速</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="16" customHeight="1">
       <c r="A301" s="41" t="n"/>
       <c r="B301" s="23" t="inlineStr">
         <is>
@@ -16153,8 +16477,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="302">
+      <c r="F301" s="44" t="inlineStr">
+        <is>
+          <t>设置完整自动预算配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="16" customHeight="1">
       <c r="A302" s="41" t="n"/>
       <c r="B302" s="27" t="inlineStr">
         <is>
@@ -16176,8 +16505,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="303">
+      <c r="F302" s="44" t="inlineStr">
+        <is>
+          <t>设置预算结转</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="16" customHeight="1">
       <c r="A303" s="41" t="n"/>
       <c r="B303" s="23" t="inlineStr">
         <is>
@@ -16199,8 +16533,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="304">
+      <c r="F303" s="44" t="inlineStr">
+        <is>
+          <t>设置子标签默认目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="16" customHeight="1">
       <c r="A304" s="41" t="n"/>
       <c r="B304" s="27" t="inlineStr">
         <is>
@@ -16222,8 +16561,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="305">
+      <c r="F304" s="44" t="inlineStr">
+        <is>
+          <t>设置财年起止月份</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="16" customHeight="1">
       <c r="A305" s="41" t="n"/>
       <c r="B305" s="23" t="inlineStr">
         <is>
@@ -16245,8 +16589,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="306">
+      <c r="F305" s="44" t="inlineStr">
+        <is>
+          <t>设置财年预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="16" customHeight="1">
       <c r="A306" s="41" t="n"/>
       <c r="B306" s="27" t="inlineStr">
         <is>
@@ -16268,8 +16617,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="307">
+      <c r="F306" s="44" t="inlineStr">
+        <is>
+          <t>设置月度预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="16" customHeight="1">
       <c r="A307" s="41" t="n"/>
       <c r="B307" s="23" t="inlineStr">
         <is>
@@ -16291,8 +16645,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="308">
+      <c r="F307" s="44" t="inlineStr">
+        <is>
+          <t>设置子标签预算</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="16" customHeight="1">
       <c r="A308" s="41" t="n"/>
       <c r="B308" s="27" t="inlineStr">
         <is>
@@ -16314,8 +16673,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="309">
+      <c r="F308" s="44" t="inlineStr">
+        <is>
+          <t>设置子标签月度目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="16" customHeight="1">
       <c r="A309" s="41" t="n"/>
       <c r="B309" s="23" t="inlineStr">
         <is>
@@ -16337,8 +16701,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="310">
+      <c r="F309" s="44" t="inlineStr">
+        <is>
+          <t>设置目标ACOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="16" customHeight="1">
       <c r="A310" s="41" t="n"/>
       <c r="B310" s="27" t="inlineStr">
         <is>
@@ -16360,8 +16729,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="311">
+      <c r="F310" s="44" t="inlineStr">
+        <is>
+          <t>设置目标ROAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="16" customHeight="1">
       <c r="A311" s="41" t="n"/>
       <c r="B311" s="23" t="inlineStr">
         <is>
@@ -16383,8 +16757,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="312">
+      <c r="F311" s="44" t="inlineStr">
+        <is>
+          <t>提交每日预算设置(含前置创建Calendar+后置清理)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="16" customHeight="1">
       <c r="A312" s="41" t="n"/>
       <c r="B312" s="27" t="inlineStr">
         <is>
@@ -16406,8 +16785,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="313">
+      <c r="F312" s="44" t="inlineStr">
+        <is>
+          <t>批量更新campaign最大花费</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="16" customHeight="1">
       <c r="A313" s="41" t="n"/>
       <c r="B313" s="23" t="inlineStr">
         <is>
@@ -16429,8 +16813,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="314">
+      <c r="F313" s="44" t="inlineStr">
+        <is>
+          <t>批量更新campaign最小花费</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="16" customHeight="1">
       <c r="A314" s="41" t="n"/>
       <c r="B314" s="27" t="inlineStr">
         <is>
@@ -16452,8 +16841,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="315">
+      <c r="F314" s="44" t="inlineStr">
+        <is>
+          <t>更新profile预算模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="16" customHeight="1">
       <c r="A315" s="41" t="n"/>
       <c r="B315" s="23" t="inlineStr">
         <is>
@@ -16475,8 +16869,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="316">
+      <c r="F315" s="44" t="inlineStr">
+        <is>
+          <t>更新campaign每日预算(批量,含checking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="16" customHeight="1">
       <c r="A316" s="41" t="n"/>
       <c r="B316" s="27" t="inlineStr">
         <is>
@@ -16498,8 +16897,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="317">
+      <c r="F316" s="44" t="inlineStr">
+        <is>
+          <t>更新单个campaign最大花费</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="16" customHeight="1">
       <c r="A317" s="41" t="n"/>
       <c r="B317" s="23" t="inlineStr">
         <is>
@@ -16521,8 +16925,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="318">
+      <c r="F317" s="44" t="inlineStr">
+        <is>
+          <t>更新单个campaign最小花费</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="16" customHeight="1">
       <c r="A318" s="41" t="n"/>
       <c r="B318" s="27" t="inlineStr">
         <is>
@@ -16542,6 +16951,11 @@
       <c r="E318" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F318" s="44" t="inlineStr">
+        <is>
+          <t>更新最小预算百分比</t>
         </is>
       </c>
     </row>
@@ -16591,7 +17005,7 @@
         </is>
       </c>
     </row>
-    <row r="321">
+    <row r="321" ht="16" customHeight="1">
       <c r="A321" s="41" t="n"/>
       <c r="B321" s="23" t="inlineStr">
         <is>
@@ -16613,8 +17027,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="322">
+      <c r="F321" s="44" t="inlineStr">
+        <is>
+          <t>获取含启用广告组的campaign列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="16" customHeight="1">
       <c r="A322" s="41" t="n"/>
       <c r="B322" s="27" t="inlineStr">
         <is>
@@ -16636,8 +17055,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="323">
+      <c r="F322" s="44" t="inlineStr">
+        <is>
+          <t>获取预算通知设置(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="16" customHeight="1">
       <c r="A323" s="41" t="n"/>
       <c r="B323" s="23" t="inlineStr">
         <is>
@@ -16659,8 +17083,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="324">
+      <c r="F323" s="44" t="inlineStr">
+        <is>
+          <t>获取标签AI信息(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="16" customHeight="1">
       <c r="A324" s="41" t="n"/>
       <c r="B324" s="27" t="inlineStr">
         <is>
@@ -16682,8 +17111,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="325">
+      <c r="F324" s="44" t="inlineStr">
+        <is>
+          <t>获取campaign预算报表(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="16" customHeight="1">
       <c r="A325" s="41" t="n"/>
       <c r="B325" s="23" t="inlineStr">
         <is>
@@ -16705,8 +17139,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="326">
+      <c r="F325" s="44" t="inlineStr">
+        <is>
+          <t>获取campaign预算报表V1(含avgSpend,中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="16" customHeight="1">
       <c r="A326" s="41" t="n"/>
       <c r="B326" s="27" t="inlineStr">
         <is>
@@ -16728,8 +17167,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="327">
+      <c r="F326" s="44" t="inlineStr">
+        <is>
+          <t>获取campaign预算报表V2(含avgSpend与hasEnableAdgroup,中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="16" customHeight="1">
       <c r="A327" s="41" t="n"/>
       <c r="B327" s="23" t="inlineStr">
         <is>
@@ -16751,8 +17195,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="328">
+      <c r="F327" s="44" t="inlineStr">
+        <is>
+          <t>获取campaign标签预算报表(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="16" customHeight="1">
       <c r="A328" s="41" t="n"/>
       <c r="B328" s="27" t="inlineStr">
         <is>
@@ -16774,8 +17223,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="329">
+      <c r="F328" s="44" t="inlineStr">
+        <is>
+          <t>获取profile预算报表(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="16" customHeight="1">
       <c r="A329" s="41" t="n"/>
       <c r="B329" s="23" t="inlineStr">
         <is>
@@ -16797,8 +17251,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="330">
+      <c r="F329" s="44" t="inlineStr">
+        <is>
+          <t>获取预算洞察(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="16" customHeight="1">
       <c r="A330" s="41" t="n"/>
       <c r="B330" s="27" t="inlineStr">
         <is>
@@ -16820,8 +17279,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="331">
+      <c r="F330" s="44" t="inlineStr">
+        <is>
+          <t>获取无每日预算设置的campaign列表(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="16" customHeight="1">
       <c r="A331" s="41" t="n"/>
       <c r="B331" s="23" t="inlineStr">
         <is>
@@ -16843,8 +17307,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="332">
+      <c r="F331" s="44" t="inlineStr">
+        <is>
+          <t>按clientId/userId获取profile列表(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="16" customHeight="1">
       <c r="A332" s="41" t="n"/>
       <c r="B332" s="27" t="inlineStr">
         <is>
@@ -16866,8 +17335,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="333">
+      <c r="F332" s="44" t="inlineStr">
+        <is>
+          <t>按userId数组获取profile列表(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="16" customHeight="1">
       <c r="A333" s="41" t="n"/>
       <c r="B333" s="23" t="inlineStr">
         <is>
@@ -16889,8 +17363,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="334">
+      <c r="F333" s="44" t="inlineStr">
+        <is>
+          <t>获取用户列表(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="16" customHeight="1">
       <c r="A334" s="41" t="n"/>
       <c r="B334" s="27" t="inlineStr">
         <is>
@@ -16912,8 +17391,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="335">
+      <c r="F334" s="44" t="inlineStr">
+        <is>
+          <t>按用户id数组批量获取用户信息(中台集成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="16" customHeight="1">
       <c r="A335" s="41" t="n"/>
       <c r="B335" s="23" t="inlineStr">
         <is>
@@ -16933,6 +17417,11 @@
       <c r="E335" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F335" s="44" t="inlineStr">
+        <is>
+          <t>更新campaign状态或每日预算(页面操作调用)</t>
         </is>
       </c>
     </row>
@@ -20615,7 +21104,7 @@
         </is>
       </c>
     </row>
-    <row r="469">
+    <row r="469" ht="16" customHeight="1">
       <c r="A469" s="41" t="n"/>
       <c r="B469" s="24" t="inlineStr">
         <is>
@@ -20637,8 +21126,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="470">
+      <c r="F469" s="44" t="inlineStr">
+        <is>
+          <t>新增/更新用户级SuperWizard设置(捕获/还原)</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="16" customHeight="1">
       <c r="A470" s="41" t="n"/>
       <c r="B470" s="27" t="inlineStr">
         <is>
@@ -20660,8 +21154,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="471">
+      <c r="F470" s="44" t="inlineStr">
+        <is>
+          <t>按campaignIds为一次性Campaign设置预算调度器(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="16" customHeight="1">
       <c r="A471" s="41" t="n"/>
       <c r="B471" s="23" t="inlineStr">
         <is>
@@ -20683,8 +21182,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="472">
+      <c r="F471" s="44" t="inlineStr">
+        <is>
+          <t>向导批量创建SP自动投放Campaign(含后置清理,可重复) — 34.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="16" customHeight="1">
       <c r="A472" s="41" t="n"/>
       <c r="B472" s="27" t="inlineStr">
         <is>
@@ -20704,6 +21208,11 @@
       <c r="E472" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F472" s="44" t="inlineStr">
+        <is>
+          <t>向导批量创建SB关键词投放Campaign(含后置清理,可重复)</t>
         </is>
       </c>
     </row>
@@ -20753,7 +21262,7 @@
         </is>
       </c>
     </row>
-    <row r="475">
+    <row r="475" ht="16" customHeight="1">
       <c r="A475" s="41" t="n"/>
       <c r="B475" s="23" t="inlineStr">
         <is>
@@ -20775,8 +21284,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="476">
+      <c r="F475" s="44" t="inlineStr">
+        <is>
+          <t>按campaigns数组+公式化目标区间设置(BulkUpdateCampaignTargetSupportFormula)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="16" customHeight="1">
       <c r="A476" s="41" t="n"/>
       <c r="B476" s="27" t="inlineStr">
         <is>
@@ -20798,8 +21312,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="477">
+      <c r="F476" s="44" t="inlineStr">
+        <is>
+          <t>按campaignIds批量暂停一次性Campaign(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="16" customHeight="1">
       <c r="A477" s="41" t="n"/>
       <c r="B477" s="23" t="inlineStr">
         <is>
@@ -20819,6 +21338,11 @@
       <c r="E477" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F477" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 4.4%</t>
         </is>
       </c>
     </row>
@@ -20845,7 +21369,7 @@
         </is>
       </c>
     </row>
-    <row r="479">
+    <row r="479" ht="16" customHeight="1">
       <c r="A479" s="41" t="n"/>
       <c r="B479" s="23" t="inlineStr">
         <is>
@@ -20867,8 +21391,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="480">
+      <c r="F479" s="44" t="inlineStr">
+        <is>
+          <t>SP手动广告组新增商品定向PAT(含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="16" customHeight="1">
       <c r="A480" s="41" t="n"/>
       <c r="B480" s="27" t="inlineStr">
         <is>
@@ -20890,8 +21419,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="481">
+      <c r="F480" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 14.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="16" customHeight="1">
       <c r="A481" s="41" t="n"/>
       <c r="B481" s="23" t="inlineStr">
         <is>
@@ -20913,8 +21447,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="482">
+      <c r="F481" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="16" customHeight="1">
       <c r="A482" s="41" t="n"/>
       <c r="B482" s="27" t="inlineStr">
         <is>
@@ -20936,8 +21475,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="483">
+      <c r="F482" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="16" customHeight="1">
       <c r="A483" s="41" t="n"/>
       <c r="B483" s="23" t="inlineStr">
         <is>
@@ -20959,8 +21503,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="484">
+      <c r="F483" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="16" customHeight="1">
       <c r="A484" s="41" t="n"/>
       <c r="B484" s="27" t="inlineStr">
         <is>
@@ -20982,8 +21531,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="485">
+      <c r="F484" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="16" customHeight="1">
       <c r="A485" s="41" t="n"/>
       <c r="B485" s="23" t="inlineStr">
         <is>
@@ -21005,8 +21559,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="486">
+      <c r="F485" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="16" customHeight="1">
       <c r="A486" s="41" t="n"/>
       <c r="B486" s="27" t="inlineStr">
         <is>
@@ -21026,6 +21585,11 @@
       <c r="E486" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F486" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
         </is>
       </c>
     </row>
@@ -21052,7 +21616,7 @@
         </is>
       </c>
     </row>
-    <row r="488">
+    <row r="488" ht="16" customHeight="1">
       <c r="A488" s="41" t="n"/>
       <c r="B488" s="27" t="inlineStr">
         <is>
@@ -21072,6 +21636,11 @@
       <c r="E488" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F488" s="44" t="inlineStr">
+        <is>
+          <t>提交一次性Campaign的AutoTarget任务(含单例配置捕获/还原)</t>
         </is>
       </c>
     </row>
@@ -21098,7 +21667,7 @@
         </is>
       </c>
     </row>
-    <row r="490">
+    <row r="490" ht="16" customHeight="1">
       <c r="A490" s="41" t="n"/>
       <c r="B490" s="27" t="inlineStr">
         <is>
@@ -21120,8 +21689,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="491">
+      <c r="F490" s="44" t="inlineStr">
+        <is>
+          <t>批量新增CampaignExtend记录(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="16" customHeight="1">
       <c r="A491" s="41" t="n"/>
       <c r="B491" s="23" t="inlineStr">
         <is>
@@ -21141,6 +21715,11 @@
       <c r="E491" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F491" s="44" t="inlineStr">
+        <is>
+          <t>批量新增一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled)</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21746,7 @@
         </is>
       </c>
     </row>
-    <row r="493">
+    <row r="493" ht="16" customHeight="1">
       <c r="A493" s="41" t="n"/>
       <c r="B493" s="23" t="inlineStr">
         <is>
@@ -21189,8 +21768,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="494">
+      <c r="F493" s="44" t="inlineStr">
+        <is>
+          <t>批量更新CampaignExtend(IsAuto+CalibrationScale)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="16" customHeight="1">
       <c r="A494" s="41" t="n"/>
       <c r="B494" s="27" t="inlineStr">
         <is>
@@ -21212,8 +21796,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="495">
+      <c r="F494" s="44" t="inlineStr">
+        <is>
+          <t>批量更新CampaignExtend自动目标ROAS(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="16" customHeight="1">
       <c r="A495" s="41" t="n"/>
       <c r="B495" s="23" t="inlineStr">
         <is>
@@ -21235,8 +21824,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="496">
+      <c r="F495" s="44" t="inlineStr">
+        <is>
+          <t>批量更新CampaignExtend校准系数(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="16" customHeight="1">
       <c r="A496" s="41" t="n"/>
       <c r="B496" s="27" t="inlineStr">
         <is>
@@ -21258,8 +21852,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="497">
+      <c r="F496" s="44" t="inlineStr">
+        <is>
+          <t>批量更新CampaignExtend的IsAuto开关(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="16" customHeight="1">
       <c r="A497" s="41" t="n"/>
       <c r="B497" s="23" t="inlineStr">
         <is>
@@ -21281,8 +21880,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="498">
+      <c r="F497" s="44" t="inlineStr">
+        <is>
+          <t>按campaignIds设置ACOS/ROAS/CPC/CPA(BulkUpdateCampaignTargetACOS TargetROAS TargetCPC TargetCPA)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="16" customHeight="1">
       <c r="A498" s="41" t="n"/>
       <c r="B498" s="27" t="inlineStr">
         <is>
@@ -21304,8 +21908,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="499">
+      <c r="F498" s="44" t="inlineStr">
+        <is>
+          <t>批量更新一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="16" customHeight="1">
       <c r="A499" s="41" t="n"/>
       <c r="B499" s="23" t="inlineStr">
         <is>
@@ -21327,8 +21936,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="500">
+      <c r="F499" s="44" t="inlineStr">
+        <is>
+          <t>批量更新一次性ASIN自动目标GPM(isCreate=1,Status=0落地)(一次性ASIN,不可物理删除故落地为disabled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="16" customHeight="1">
       <c r="A500" s="41" t="n"/>
       <c r="B500" s="27" t="inlineStr">
         <is>
@@ -21350,8 +21964,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="501">
+      <c r="F500" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="16" customHeight="1">
       <c r="A501" s="41" t="n"/>
       <c r="B501" s="23" t="inlineStr">
         <is>
@@ -21373,8 +21992,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="502">
+      <c r="F501" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="16" customHeight="1">
       <c r="A502" s="41" t="n"/>
       <c r="B502" s="27" t="inlineStr">
         <is>
@@ -21396,8 +22020,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="503">
+      <c r="F502" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="16" customHeight="1">
       <c r="A503" s="41" t="n"/>
       <c r="B503" s="23" t="inlineStr">
         <is>
@@ -21419,8 +22048,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="504">
+      <c r="F503" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="16" customHeight="1">
       <c r="A504" s="41" t="n"/>
       <c r="B504" s="27" t="inlineStr">
         <is>
@@ -21442,8 +22076,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="505">
+      <c r="F504" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="16" customHeight="1">
       <c r="A505" s="41" t="n"/>
       <c r="B505" s="23" t="inlineStr">
         <is>
@@ -21465,8 +22104,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="506">
+      <c r="F505" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="16" customHeight="1">
       <c r="A506" s="41" t="n"/>
       <c r="B506" s="27" t="inlineStr">
         <is>
@@ -21488,8 +22132,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="507">
+      <c r="F506" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 12.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="16" customHeight="1">
       <c r="A507" s="41" t="n"/>
       <c r="B507" s="23" t="inlineStr">
         <is>
@@ -21511,8 +22160,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="508">
+      <c r="F507" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 11.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="16" customHeight="1">
       <c r="A508" s="41" t="n"/>
       <c r="B508" s="27" t="inlineStr">
         <is>
@@ -21534,8 +22188,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="509">
+      <c r="F508" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="16" customHeight="1">
       <c r="A509" s="41" t="n"/>
       <c r="B509" s="23" t="inlineStr">
         <is>
@@ -21557,8 +22216,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="510">
+      <c r="F509" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="16" customHeight="1">
       <c r="A510" s="41" t="n"/>
       <c r="B510" s="27" t="inlineStr">
         <is>
@@ -21580,8 +22244,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="511">
+      <c r="F510" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 37.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="16" customHeight="1">
       <c r="A511" s="41" t="n"/>
       <c r="B511" s="23" t="inlineStr">
         <is>
@@ -21603,8 +22272,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="512">
+      <c r="F511" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="16" customHeight="1">
       <c r="A512" s="41" t="n"/>
       <c r="B512" s="27" t="inlineStr">
         <is>
@@ -21626,8 +22300,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="513">
+      <c r="F512" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="16" customHeight="1">
       <c r="A513" s="41" t="n"/>
       <c r="B513" s="23" t="inlineStr">
         <is>
@@ -21649,8 +22328,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="514">
+      <c r="F513" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="16" customHeight="1">
       <c r="A514" s="41" t="n"/>
       <c r="B514" s="27" t="inlineStr">
         <is>
@@ -21672,8 +22356,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="515">
+      <c r="F514" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 1.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="16" customHeight="1">
       <c r="A515" s="41" t="n"/>
       <c r="B515" s="23" t="inlineStr">
         <is>
@@ -21695,8 +22384,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="516">
+      <c r="F515" s="44" t="inlineStr">
+        <is>
+          <t>真实调用场景(空body,由鉴权上下文决定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="16" customHeight="1">
       <c r="A516" s="41" t="n"/>
       <c r="B516" s="27" t="inlineStr">
         <is>
@@ -21718,8 +22412,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="517">
+      <c r="F516" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 11.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="16" customHeight="1">
       <c r="A517" s="41" t="n"/>
       <c r="B517" s="23" t="inlineStr">
         <is>
@@ -21741,8 +22440,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="518">
+      <c r="F517" s="44" t="inlineStr">
+        <is>
+          <t>从Commerce同步数据并更新自动目标(GetCampaignAutoTargetDataFromCommerceAndUpdateAutoTarget)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="16" customHeight="1">
       <c r="A518" s="41" t="n"/>
       <c r="B518" s="27" t="inlineStr">
         <is>
@@ -21764,8 +22468,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="519">
+      <c r="F518" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="16" customHeight="1">
       <c r="A519" s="41" t="n"/>
       <c r="B519" s="23" t="inlineStr">
         <is>
@@ -21787,8 +22496,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="520">
+      <c r="F519" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 9.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="520" ht="16" customHeight="1">
       <c r="A520" s="41" t="n"/>
       <c r="B520" s="27" t="inlineStr">
         <is>
@@ -21810,8 +22524,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="521">
+      <c r="F520" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="16" customHeight="1">
       <c r="A521" s="41" t="n"/>
       <c r="B521" s="23" t="inlineStr">
         <is>
@@ -21833,8 +22552,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="522">
+      <c r="F521" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="16" customHeight="1">
       <c r="A522" s="41" t="n"/>
       <c r="B522" s="27" t="inlineStr">
         <is>
@@ -21856,8 +22580,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="523">
+      <c r="F522" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 83.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="16" customHeight="1">
       <c r="A523" s="41" t="n"/>
       <c r="B523" s="23" t="inlineStr">
         <is>
@@ -21879,8 +22608,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="524">
+      <c r="F523" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 47.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="16" customHeight="1">
       <c r="A524" s="41" t="n"/>
       <c r="B524" s="27" t="inlineStr">
         <is>
@@ -21902,8 +22636,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="525">
+      <c r="F524" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="16" customHeight="1">
       <c r="A525" s="41" t="n"/>
       <c r="B525" s="23" t="inlineStr">
         <is>
@@ -21925,8 +22664,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="526">
+      <c r="F525" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 23.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="16" customHeight="1">
       <c r="A526" s="41" t="n"/>
       <c r="B526" s="27" t="inlineStr">
         <is>
@@ -21948,8 +22692,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="527">
+      <c r="F526" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="16" customHeight="1">
       <c r="A527" s="41" t="n"/>
       <c r="B527" s="23" t="inlineStr">
         <is>
@@ -21971,8 +22720,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="528">
+      <c r="F527" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="16" customHeight="1">
       <c r="A528" s="41" t="n"/>
       <c r="B528" s="27" t="inlineStr">
         <is>
@@ -21994,8 +22748,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="529">
+      <c r="F528" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="16" customHeight="1">
       <c r="A529" s="41" t="n"/>
       <c r="B529" s="23" t="inlineStr">
         <is>
@@ -22017,8 +22776,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="530">
+      <c r="F529" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="16" customHeight="1">
       <c r="A530" s="41" t="n"/>
       <c r="B530" s="27" t="inlineStr">
         <is>
@@ -22040,8 +22804,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="531">
+      <c r="F530" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="16" customHeight="1">
       <c r="A531" s="41" t="n"/>
       <c r="B531" s="23" t="inlineStr">
         <is>
@@ -22063,8 +22832,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="532">
+      <c r="F531" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="16" customHeight="1">
       <c r="A532" s="41" t="n"/>
       <c r="B532" s="27" t="inlineStr">
         <is>
@@ -22086,8 +22860,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="533">
+      <c r="F532" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 17.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="16" customHeight="1">
       <c r="A533" s="41" t="n"/>
       <c r="B533" s="23" t="inlineStr">
         <is>
@@ -22109,8 +22888,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="534">
+      <c r="F533" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 2.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="16" customHeight="1">
       <c r="A534" s="41" t="n"/>
       <c r="B534" s="27" t="inlineStr">
         <is>
@@ -22132,8 +22916,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="535">
+      <c r="F534" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 11.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="535" ht="16" customHeight="1">
       <c r="A535" s="41" t="n"/>
       <c r="B535" s="23" t="inlineStr">
         <is>
@@ -22155,8 +22944,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="536">
+      <c r="F535" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="16" customHeight="1">
       <c r="A536" s="41" t="n"/>
       <c r="B536" s="27" t="inlineStr">
         <is>
@@ -22178,8 +22972,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="537">
+      <c r="F536" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="537" ht="16" customHeight="1">
       <c r="A537" s="41" t="n"/>
       <c r="B537" s="23" t="inlineStr">
         <is>
@@ -22201,8 +23000,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="538">
+      <c r="F537" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="16" customHeight="1">
       <c r="A538" s="41" t="n"/>
       <c r="B538" s="27" t="inlineStr">
         <is>
@@ -22224,8 +23028,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="539">
+      <c r="F538" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="16" customHeight="1">
       <c r="A539" s="41" t="n"/>
       <c r="B539" s="23" t="inlineStr">
         <is>
@@ -22247,8 +23056,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="540">
+      <c r="F539" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 11.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="16" customHeight="1">
       <c r="A540" s="41" t="n"/>
       <c r="B540" s="27" t="inlineStr">
         <is>
@@ -22270,8 +23084,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="541">
+      <c r="F540" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="16" customHeight="1">
       <c r="A541" s="41" t="n"/>
       <c r="B541" s="23" t="inlineStr">
         <is>
@@ -22293,8 +23112,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="542">
+      <c r="F541" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="16" customHeight="1">
       <c r="A542" s="41" t="n"/>
       <c r="B542" s="27" t="inlineStr">
         <is>
@@ -22316,8 +23140,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="543">
+      <c r="F542" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="16" customHeight="1">
       <c r="A543" s="41" t="n"/>
       <c r="B543" s="23" t="inlineStr">
         <is>
@@ -22339,8 +23168,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="544">
+      <c r="F543" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="16" customHeight="1">
       <c r="A544" s="41" t="n"/>
       <c r="B544" s="27" t="inlineStr">
         <is>
@@ -22362,8 +23196,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="545">
+      <c r="F544" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 27.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="16" customHeight="1">
       <c r="A545" s="41" t="n"/>
       <c r="B545" s="23" t="inlineStr">
         <is>
@@ -22385,8 +23224,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="546">
+      <c r="F545" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="16" customHeight="1">
       <c r="A546" s="41" t="n"/>
       <c r="B546" s="27" t="inlineStr">
         <is>
@@ -22408,8 +23252,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="547">
+      <c r="F546" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="16" customHeight="1">
       <c r="A547" s="41" t="n"/>
       <c r="B547" s="23" t="inlineStr">
         <is>
@@ -22431,8 +23280,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="548">
+      <c r="F547" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="16" customHeight="1">
       <c r="A548" s="41" t="n"/>
       <c r="B548" s="27" t="inlineStr">
         <is>
@@ -22454,8 +23308,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="549">
+      <c r="F548" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 86.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="16" customHeight="1">
       <c r="A549" s="41" t="n"/>
       <c r="B549" s="23" t="inlineStr">
         <is>
@@ -22477,8 +23336,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="550">
+      <c r="F549" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="16" customHeight="1">
       <c r="A550" s="41" t="n"/>
       <c r="B550" s="27" t="inlineStr">
         <is>
@@ -22500,8 +23364,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="551">
+      <c r="F550" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 83.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="16" customHeight="1">
       <c r="A551" s="41" t="n"/>
       <c r="B551" s="23" t="inlineStr">
         <is>
@@ -22523,8 +23392,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="552">
+      <c r="F551" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 85.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="16" customHeight="1">
       <c r="A552" s="41" t="n"/>
       <c r="B552" s="27" t="inlineStr">
         <is>
@@ -22546,8 +23420,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="553">
+      <c r="F552" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="16" customHeight="1">
       <c r="A553" s="41" t="n"/>
       <c r="B553" s="23" t="inlineStr">
         <is>
@@ -22569,8 +23448,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="554">
+      <c r="F553" s="44" t="inlineStr">
+        <is>
+          <t>Insert写入AutoTargetConfig(实为按ClientId+UserId的Upsert)(捕获原值/验证/还原/复核,ClientId+UserId级单例配置)</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="16" customHeight="1">
       <c r="A554" s="41" t="n"/>
       <c r="B554" s="27" t="inlineStr">
         <is>
@@ -22592,8 +23476,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="555">
+      <c r="F554" s="44" t="inlineStr">
+        <is>
+          <t>插入CampaignExtend基线记录(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="16" customHeight="1">
       <c r="A555" s="41" t="n"/>
       <c r="B555" s="23" t="inlineStr">
         <is>
@@ -22613,6 +23502,11 @@
       <c r="E555" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F555" s="44" t="inlineStr">
+        <is>
+          <t>新增一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled)</t>
         </is>
       </c>
     </row>
@@ -22662,7 +23556,7 @@
         </is>
       </c>
     </row>
-    <row r="558">
+    <row r="558" ht="16" customHeight="1">
       <c r="A558" s="41" t="n"/>
       <c r="B558" s="27" t="inlineStr">
         <is>
@@ -22684,8 +23578,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="559">
+      <c r="F558" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="16" customHeight="1">
       <c r="A559" s="41" t="n"/>
       <c r="B559" s="23" t="inlineStr">
         <is>
@@ -22707,8 +23606,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="560">
+      <c r="F559" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="16" customHeight="1">
       <c r="A560" s="41" t="n"/>
       <c r="B560" s="27" t="inlineStr">
         <is>
@@ -22730,8 +23634,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="561">
+      <c r="F560" s="44" t="inlineStr">
+        <is>
+          <t>真实高频入参场景 — 0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="16" customHeight="1">
       <c r="A561" s="41" t="n"/>
       <c r="B561" s="23" t="inlineStr">
         <is>
@@ -22753,8 +23662,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="562">
+      <c r="F561" s="44" t="inlineStr">
+        <is>
+          <t>同步一次性Campaign的Commerce自动目标数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="16" customHeight="1">
       <c r="A562" s="41" t="n"/>
       <c r="B562" s="27" t="inlineStr">
         <is>
@@ -22776,8 +23690,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="563">
+      <c r="F562" s="44" t="inlineStr">
+        <is>
+          <t>Update更新AutoTargetConfig的Frequency/DateRange(捕获原值/验证/还原/复核,ClientId+UserId级单例配置)</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="16" customHeight="1">
       <c r="A563" s="41" t="n"/>
       <c r="B563" s="23" t="inlineStr">
         <is>
@@ -22799,8 +23718,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="564">
+      <c r="F563" s="44" t="inlineStr">
+        <is>
+          <t>UpdateStatus切换AutoTargetConfig启停状态(捕获原值/验证/还原/复核,ClientId+UserId级单例配置)</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="16" customHeight="1">
       <c r="A564" s="41" t="n"/>
       <c r="B564" s="27" t="inlineStr">
         <is>
@@ -22822,8 +23746,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="565">
+      <c r="F564" s="44" t="inlineStr">
+        <is>
+          <t>整体更新CampaignExtend记录(ProfileId/CampaignId/IsAuto/CalibrationScale/AutoTargetROAS)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="16" customHeight="1">
       <c r="A565" s="41" t="n"/>
       <c r="B565" s="23" t="inlineStr">
         <is>
@@ -22845,8 +23774,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="566">
+      <c r="F565" s="44" t="inlineStr">
+        <is>
+          <t>更新CampaignExtend自动目标ROAS(AutoTargetROAS)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="16" customHeight="1">
       <c r="A566" s="41" t="n"/>
       <c r="B566" s="27" t="inlineStr">
         <is>
@@ -22868,8 +23802,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="567">
+      <c r="F566" s="44" t="inlineStr">
+        <is>
+          <t>更新CampaignExtend校准系数(CalibrationScale)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="16" customHeight="1">
       <c r="A567" s="41" t="n"/>
       <c r="B567" s="23" t="inlineStr">
         <is>
@@ -22891,8 +23830,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="568">
+      <c r="F567" s="44" t="inlineStr">
+        <is>
+          <t>按data数组更新校准系数并开启IsAuto(UpdateCampaignExtendCalibrationScaleAndOpenIsAuto)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="16" customHeight="1">
       <c r="A568" s="41" t="n"/>
       <c r="B568" s="27" t="inlineStr">
         <is>
@@ -22914,8 +23858,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="569">
+      <c r="F568" s="44" t="inlineStr">
+        <is>
+          <t>开启CampaignExtend自动出价校准(IsAuto)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="16" customHeight="1">
       <c r="A569" s="41" t="n"/>
       <c r="B569" s="23" t="inlineStr">
         <is>
@@ -22937,8 +23886,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="570">
+      <c r="F569" s="44" t="inlineStr">
+        <is>
+          <t>设置目标ACOS/ROAS(UpdateCampaignTarget)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="16" customHeight="1">
       <c r="A570" s="41" t="n"/>
       <c r="B570" s="27" t="inlineStr">
         <is>
@@ -22960,8 +23914,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="571">
+      <c r="F570" s="44" t="inlineStr">
+        <is>
+          <t>批量设置目标ACOS/ROAS(UpdateCampaignTargetAll)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="16" customHeight="1">
       <c r="A571" s="41" t="n"/>
       <c r="B571" s="23" t="inlineStr">
         <is>
@@ -22983,8 +23942,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="572">
+      <c r="F571" s="44" t="inlineStr">
+        <is>
+          <t>按campaignTagIds批量设置目标(UpdateCampaignTargetWithTagAll)(一次性Campaign,含后置清理,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="16" customHeight="1">
       <c r="A572" s="41" t="n"/>
       <c r="B572" s="27" t="inlineStr">
         <is>
@@ -23006,8 +23970,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="573">
+      <c r="F572" s="44" t="inlineStr">
+        <is>
+          <t>更新一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="16" customHeight="1">
       <c r="A573" s="41" t="n"/>
       <c r="B573" s="23" t="inlineStr">
         <is>
@@ -23029,8 +23998,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="574">
+      <c r="F573" s="44" t="inlineStr">
+        <is>
+          <t>更新一次性ASIN自动目标GPM(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="16" customHeight="1">
       <c r="A574" s="41" t="n"/>
       <c r="B574" s="27" t="inlineStr">
         <is>
@@ -23050,6 +24024,11 @@
       <c r="E574" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F574" s="44" t="inlineStr">
+        <is>
+          <t>零流量接口最小可用请求(按swagger schema构造)</t>
         </is>
       </c>
     </row>
@@ -23311,7 +24290,7 @@
         </is>
       </c>
     </row>
-    <row r="586">
+    <row r="586" ht="16" customHeight="1">
       <c r="A586" s="41" t="n"/>
       <c r="B586" s="27" t="inlineStr">
         <is>
@@ -23331,6 +24310,11 @@
       <c r="E586" s="8" t="inlineStr">
         <is>
           <t>limin</t>
+        </is>
+      </c>
+      <c r="F586" s="44" t="inlineStr">
+        <is>
+          <t>brandEntityId缺省(undefined)查询素材列表 — 79.6%</t>
         </is>
       </c>
     </row>
@@ -26201,7 +27185,7 @@
         </is>
       </c>
     </row>
-    <row r="692">
+    <row r="692" ht="16" customHeight="1">
       <c r="A692" s="41" t="n"/>
       <c r="B692" s="26" t="inlineStr">
         <is>
@@ -26223,8 +27207,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="693">
+      <c r="F692" s="44" t="inlineStr">
+        <is>
+          <t>按ENTITY ID查询品牌StorePage列表 — 99.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="693" ht="16" customHeight="1">
       <c r="A693" s="41" t="n"/>
       <c r="B693" s="23" t="inlineStr">
         <is>
@@ -26244,6 +27233,11 @@
       <c r="E693" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F693" s="44" t="inlineStr">
+        <is>
+          <t>按profileId查询Store列表 — 100%</t>
         </is>
       </c>
     </row>
@@ -26270,7 +27264,7 @@
         </is>
       </c>
     </row>
-    <row r="695">
+    <row r="695" ht="16" customHeight="1">
       <c r="A695" s="41" t="n"/>
       <c r="B695" s="23" t="inlineStr">
         <is>
@@ -26290,6 +27284,11 @@
       <c r="E695" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F695" s="44" t="inlineStr">
+        <is>
+          <t>手动ProductCollection广告创建(含前置建活动+后置归档,可重复) — 63.4%</t>
         </is>
       </c>
     </row>
@@ -26431,7 +27430,7 @@
         </is>
       </c>
     </row>
-    <row r="702">
+    <row r="702" ht="16" customHeight="1">
       <c r="A702" s="41" t="n"/>
       <c r="B702" s="27" t="inlineStr">
         <is>
@@ -26453,8 +27452,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="703">
+      <c r="F702" s="44" t="inlineStr">
+        <is>
+          <t>按关键词搜索类目</t>
+        </is>
+      </c>
+    </row>
+    <row r="703" ht="16" customHeight="1">
       <c r="A703" s="41" t="n"/>
       <c r="B703" s="23" t="inlineStr">
         <is>
@@ -26476,8 +27480,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="704">
+      <c r="F703" s="44" t="inlineStr">
+        <is>
+          <t>按商品URL解析ASIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="704" ht="32" customHeight="1">
       <c r="A704" s="41" t="n"/>
       <c r="B704" s="27" t="inlineStr">
         <is>
@@ -26499,8 +27508,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="705">
+      <c r="F704" s="44" t="inlineStr">
+        <is>
+          <t>空ASIN列表查询 — 35.0%
+按真实ASIN获取推荐关键词 — 65.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="705" ht="16" customHeight="1">
       <c r="A705" s="41" t="n"/>
       <c r="B705" s="23" t="inlineStr">
         <is>
@@ -26522,8 +27537,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="706">
+      <c r="F705" s="44" t="inlineStr">
+        <is>
+          <t>brandEntityId缺省(undefined)查询素材列表 — 79.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="706" ht="16" customHeight="1">
       <c r="A706" s="41" t="n"/>
       <c r="B706" s="27" t="inlineStr">
         <is>
@@ -26545,8 +27565,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="707">
+      <c r="F706" s="44" t="inlineStr">
+        <is>
+          <t>按assetId查询单个素材详情 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="707" ht="16" customHeight="1">
       <c r="A707" s="41" t="n"/>
       <c r="B707" s="23" t="inlineStr">
         <is>
@@ -26568,8 +27593,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="708">
+      <c r="F707" s="44" t="inlineStr">
+        <is>
+          <t>批量按assetIds查询素材详情 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="708" ht="16" customHeight="1">
       <c r="A708" s="41" t="n"/>
       <c r="B708" s="27" t="inlineStr">
         <is>
@@ -26591,8 +27621,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="709">
+      <c r="F708" s="44" t="inlineStr">
+        <is>
+          <t>查询profile关联品牌列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="709" ht="16" customHeight="1">
       <c r="A709" s="41" t="n"/>
       <c r="B709" s="23" t="inlineStr">
         <is>
@@ -26614,8 +27649,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="710">
+      <c r="F709" s="44" t="inlineStr">
+        <is>
+          <t>查询全量商品类目树 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="710" ht="16" customHeight="1">
       <c r="A710" s="41" t="n"/>
       <c r="B710" s="27" t="inlineStr">
         <is>
@@ -26637,8 +27677,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="711">
+      <c r="F710" s="44" t="inlineStr">
+        <is>
+          <t>按Store页面URL获取页面内ASIN列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="711" ht="48" customHeight="1">
       <c r="A711" s="41" t="n"/>
       <c r="B711" s="23" t="inlineStr">
         <is>
@@ -26660,8 +27705,15 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="712">
+      <c r="F711" s="44" t="inlineStr">
+        <is>
+          <t>SP广告类型按SKU查询商品广告 — 82.4%
+SB广告类型按ASIN查询商品广告 — 12.0%
+SD广告类型查询商品广告 — 5.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="712" ht="16" customHeight="1">
       <c r="A712" s="41" t="n"/>
       <c r="B712" s="27" t="inlineStr">
         <is>
@@ -26683,8 +27735,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="713">
+      <c r="F712" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN获取推荐类目 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="713" ht="32" customHeight="1">
       <c r="A713" s="41" t="n"/>
       <c r="B713" s="23" t="inlineStr">
         <is>
@@ -26706,8 +27763,14 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="714">
+      <c r="F713" s="44" t="inlineStr">
+        <is>
+          <t>productCollection广告格式关键词出价推荐 — 49.0%
+video广告格式关键词出价推荐 — 33.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="714" ht="16" customHeight="1">
       <c r="A714" s="41" t="n"/>
       <c r="B714" s="27" t="inlineStr">
         <is>
@@ -26729,8 +27792,13 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="715">
+      <c r="F714" s="44" t="inlineStr">
+        <is>
+          <t>SB活动可选ASIN分页查询 — 96.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="715" ht="16" customHeight="1">
       <c r="A715" s="41" t="n"/>
       <c r="B715" s="23" t="inlineStr">
         <is>
@@ -26750,6 +27818,11 @@
       <c r="E715" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F715" s="44" t="inlineStr">
+        <is>
+          <t>查询profile关联Store列表</t>
         </is>
       </c>
     </row>
@@ -26776,7 +27849,7 @@
         </is>
       </c>
     </row>
-    <row r="717">
+    <row r="717" ht="16" customHeight="1">
       <c r="A717" s="41" t="n"/>
       <c r="B717" s="23" t="inlineStr">
         <is>
@@ -26796,6 +27869,11 @@
       <c r="E717" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F717" s="44" t="inlineStr">
+        <is>
+          <t>按ASIN列表获取推荐商品 — 100%</t>
         </is>
       </c>
     </row>
